--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/13/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/17/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>333.55</v>
+        <v>334.39</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.022</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.025</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.86</v>
+        <v>0.892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.965</v>
+        <v>0.968</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.654</v>
+        <v>3.526</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.025</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.41</v>
+        <v>56.79</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.011</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.021</v>
+        <v>0.003</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.154</v>
+        <v>0.123</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.204</v>
+        <v>0.193</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.279</v>
+        <v>0.266</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.245</v>
+        <v>0.227</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.318</v>
+        <v>0.388</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.807</v>
+        <v>1.668</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.61</v>
+        <v>1.484</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,13 +1744,13 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.06</v>
+        <v>83.03</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AH5" s="1" t="n">
         <v>0.006</v>
@@ -1759,13 +1759,13 @@
         <v>0.012</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AM5" s="1" t="n">
         <v>0.09</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>684.76</v>
+        <v>685.84</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>-0.013</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.013</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.017</v>
+        <v>0.029</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.063</v>
+        <v>0.068</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.722</v>
+        <v>0.749</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.866</v>
+        <v>0.87</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.313</v>
+        <v>3.18</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>105.62</v>
+        <v>103.9</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.016</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.152</v>
+        <v>0.129</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.145</v>
+        <v>0.128</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.213</v>
+        <v>0.193</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.157</v>
+        <v>0.13</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.22</v>
+        <v>0.296</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.793</v>
+        <v>1.636</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.125</v>
+        <v>1.946</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.183</v>
+        <v>0.164</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.14</v>
+        <v>120.08</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AH6" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>0.072</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AO6" s="1" t="n">
         <v>0.009</v>
-      </c>
-      <c r="AI6" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="AJ6" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AK6" s="1" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="AL6" s="1" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="AM6" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AN6" s="1" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AO6" s="1" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.24</v>
+        <v>71.37</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.113</v>
+        <v>0.138</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.397</v>
+        <v>0.401</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.509</v>
+        <v>0.522</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.289</v>
+        <v>2.178</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.84</v>
+        <v>27.48</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.013</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.034</v>
+        <v>0.016</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.194</v>
+        <v>0.151</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.375</v>
+        <v>0.361</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.353</v>
+        <v>0.342</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.266</v>
+        <v>0.328</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.274</v>
+        <v>1.184</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.334</v>
+        <v>0.317</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,34 +1982,34 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.21</v>
+        <v>97.2</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.087</v>
+        <v>0.082</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.052</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.097</v>
+        <v>0.103</v>
       </c>
       <c r="AO7" s="1" t="n">
         <v>0.014</v>
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>262.96</v>
+        <v>263.04</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.114</v>
+        <v>0.134</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.144</v>
+        <v>0.165</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.418</v>
+        <v>0.414</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>2.099</v>
+        <v>1.982</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.068</v>
+        <v>0.069</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.42</v>
+        <v>18.73</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.1</v>
+        <v>0.124</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.345</v>
+        <v>0.339</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.672</v>
+        <v>0.684</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.003</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.349</v>
+        <v>-0.319</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.841</v>
+        <v>1.704</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.121</v>
+        <v>0.14</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.9</v>
+        <v>104.03</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.047</v>
+        <v>0.061</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.07</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.187</v>
+        <v>-0.179</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.029</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.32</v>
+        <v>26.29</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.001</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.104</v>
+        <v>0.086</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.19</v>
+        <v>0.184</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.237</v>
+        <v>0.29</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.301</v>
+        <v>1.215</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.643</v>
+        <v>1.514</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.119</v>
+        <v>0.117</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.72</v>
+        <v>89.87</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.011</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.285</v>
+        <v>-0.277</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.104</v>
+        <v>-0.088</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.08</v>
+        <v>181.21</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.01</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.035</v>
+        <v>-0.001</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.09</v>
+        <v>0.069</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.258</v>
+        <v>0.278</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.259</v>
+        <v>0.254</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.326</v>
+        <v>0.315</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.708</v>
+        <v>0.692</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.37</v>
+        <v>2.212</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.189</v>
+        <v>0.177</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.39</v>
+        <v>111.23</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="AH10" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AI10" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="AI10" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="AK10" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AM10" s="1" t="n">
         <v>0.063</v>
       </c>
-      <c r="AL10" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AM10" s="1" t="n">
-        <v>0.059</v>
-      </c>
       <c r="AN10" s="1" t="n">
-        <v>0.327</v>
+        <v>0.333</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>223.71</v>
+        <v>223.2</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.094</v>
+        <v>0.107</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.133</v>
+        <v>0.136</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.482</v>
+        <v>0.496</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.704</v>
+        <v>0.695</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.112</v>
+        <v>2.011</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.63</v>
+        <v>59.63</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.022</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.089</v>
+        <v>0.061</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.508</v>
+        <v>0.506</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.672</v>
+        <v>0.651</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.526</v>
+        <v>0.498</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.907</v>
+        <v>0.79</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>5.023</v>
+        <v>4.484</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.181</v>
+        <v>0.161</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,16 +2410,16 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.01</v>
+        <v>102.9</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>0.008</v>
@@ -2428,10 +2428,10 @@
         <v>0.016</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.163</v>
+        <v>0.162</v>
       </c>
       <c r="AM11" s="1" t="n">
         <v>0.189</v>
@@ -2440,7 +2440,7 @@
         <v>0.372</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>447.17</v>
+        <v>449.35</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.045</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.036</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.084</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.908</v>
+        <v>0.941</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.81</v>
+        <v>0.833</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.44</v>
+        <v>4.265</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.051</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>89.33</v>
+        <v>86.47</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.056</v>
+        <v>-0.032</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.075</v>
+        <v>-0.021</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.076</v>
+        <v>0.04</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.359</v>
+        <v>0.346</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.821</v>
+        <v>0.751</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.548</v>
+        <v>1.544</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.037</v>
+        <v>3.101</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.362</v>
+        <v>2.414</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.482</v>
+        <v>5.61</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.213</v>
+        <v>0.174</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.26</v>
+        <v>108.33</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AH12" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.103</v>
+        <v>0.119</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>201.75</v>
+        <v>202.24</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.005</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.038</v>
+        <v>0.055</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.097</v>
+        <v>0.103</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.681</v>
+        <v>0.717</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.793</v>
+        <v>0.799</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.907</v>
+        <v>2.798</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.64</v>
+        <v>39.6</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.054</v>
+        <v>-0.049</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.057</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.051</v>
+        <v>-0.039</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.519</v>
+        <v>0.498</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.093</v>
+        <v>1.011</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>1.997</v>
+        <v>1.952</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.195</v>
+        <v>3.068</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.682</v>
+        <v>1.613</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.958</v>
+        <v>5.792</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.215</v>
+        <v>0.156</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.19</v>
+        <v>23.18</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="AH13" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.099</v>
+        <v>0.105</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.084</v>
+        <v>0.088</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.267</v>
+        <v>0.284</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.19</v>
+        <v>95.84</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.004</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.381</v>
+        <v>0.385</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.534</v>
+        <v>0.535</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.86</v>
+        <v>1.789</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.5</v>
+        <v>51.81</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.032</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.034</v>
+        <v>-0.027</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.095</v>
+        <v>0.05</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.402</v>
+        <v>0.391</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.712</v>
+        <v>0.668</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>0.979</v>
+        <v>0.925</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.207</v>
+        <v>0.169</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.95</v>
+        <v>76.79</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="AH14" s="1" t="n">
         <v>0.028</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.14</v>
+        <v>0.133</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.149</v>
+        <v>0.155</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.035</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,34 +2802,34 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>251.48</v>
+        <v>251.65</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.013</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.026</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.037</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.033</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.786</v>
+        <v>0.825</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.494</v>
+        <v>0.512</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.275</v>
+        <v>3.139</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>0.005</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.71</v>
+        <v>16.79</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.092</v>
+        <v>-0.066</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.148</v>
+        <v>0.111</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.657</v>
+        <v>0.659</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.865</v>
+        <v>0.901</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.069</v>
+        <v>0.074</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.42</v>
+        <v>97.62</v>
       </c>
       <c r="AF15" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.322</v>
+        <v>0.336</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.094</v>
+        <v>0.104</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.499</v>
+        <v>0.487</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.76</v>
+        <v>137.62</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.109</v>
+        <v>0.082</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.15</v>
+        <v>0.143</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.162</v>
+        <v>0.155</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.223</v>
+        <v>0.218</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.463</v>
+        <v>0.483</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.848</v>
+        <v>0.809</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.725</v>
+        <v>1.654</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.141</v>
+        <v>0.132</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>82.32</v>
+        <v>80.78</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.019</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>0.057</v>
+        <v>0.007</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.088</v>
+        <v>0.053</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.185</v>
+        <v>0.194</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.057</v>
+        <v>0.036</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.149</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.501</v>
+        <v>1.349</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.122</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.83</v>
+        <v>42.84</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AH16" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.079</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="AM16" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AO16" s="1" t="n">
         <v>0.031</v>
-      </c>
-      <c r="AN16" s="1" t="n">
-        <v>0.299</v>
-      </c>
-      <c r="AO16" s="1" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>148.21</v>
+        <v>148.42</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.016</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.122</v>
+        <v>0.124</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.685</v>
+        <v>0.709</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.74</v>
+        <v>0.746</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.19</v>
+        <v>108.05</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.002</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.089</v>
+        <v>0.064</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.181</v>
+        <v>0.2</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.436</v>
+        <v>0.419</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.389</v>
+        <v>1.387</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.379</v>
+        <v>1.397</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.501</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,34 +3110,34 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.94</v>
+        <v>42.97</v>
       </c>
       <c r="AF17" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.099</v>
+        <v>0.116</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.191</v>
+        <v>-0.182</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.044</v>
       </c>
       <c r="AO17" s="1" t="n">
         <v>0.031</v>
@@ -3166,7 +3166,7 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>159.55</v>
+        <v>160.23</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>0.004</v>
@@ -3175,28 +3175,28 @@
         <v>-0.004</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.111</v>
+        <v>0.138</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.155</v>
+        <v>0.161</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.594</v>
+        <v>0.613</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.653</v>
+        <v>0.667</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.782</v>
+        <v>2.657</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.077</v>
+        <v>0.081</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.23</v>
+        <v>36.43</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.08</v>
+        <v>0.066</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.197</v>
+        <v>0.234</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.272</v>
+        <v>0.306</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.464</v>
+        <v>0.472</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.161</v>
+        <v>0.168</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>56.17</v>
+        <v>55.86</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.015</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.19</v>
+        <v>0.192</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.672</v>
+        <v>0.698</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.892</v>
+        <v>0.887</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.396</v>
+        <v>2.198</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>79.91</v>
+        <v>80.8</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.016</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.031</v>
+        <v>0.039</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.116</v>
+        <v>0.15</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.137</v>
+        <v>0.151</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.119</v>
+        <v>0.126</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.401</v>
+        <v>0.426</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.459</v>
+        <v>0.484</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.84</v>
+        <v>1.763</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.072</v>
+        <v>0.084</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.99</v>
+        <v>101</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AH20" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AJ20" s="1" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AM20" s="1" t="n">
         <v>0.009</v>
       </c>
-      <c r="AH20" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AI20" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AJ20" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AK20" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AL20" s="1" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AM20" s="1" t="n">
-        <v>0.007</v>
-      </c>
       <c r="AN20" s="1" t="n">
-        <v>0.211</v>
+        <v>0.215</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.26</v>
+        <v>36.03</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.012</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.137</v>
+        <v>0.109</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.219</v>
+        <v>0.223</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.421</v>
+        <v>0.413</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.612</v>
+        <v>0.566</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.746</v>
+        <v>0.719</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.781</v>
+        <v>0.755</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.965</v>
+        <v>1.811</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.191</v>
+        <v>0.183</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>234.87</v>
+        <v>238.17</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.021</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.023</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.145</v>
+        <v>0.169</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.198</v>
+        <v>0.225</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.524</v>
+        <v>0.561</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.07</v>
+        <v>1.091</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.506</v>
+        <v>1.536</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>4.005</v>
+        <v>3.89</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.094</v>
+        <v>0.109</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.52</v>
+        <v>50.58</v>
       </c>
       <c r="AF21" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.036</v>
+        <v>0.04</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.163</v>
+        <v>0.167</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.282</v>
+        <v>0.278</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>81.03</v>
+        <v>80.76</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.126</v>
+        <v>0.091</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.226</v>
+        <v>0.25</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.332</v>
+        <v>0.342</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.605</v>
+        <v>0.591</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.567</v>
+        <v>0.523</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.227</v>
+        <v>1.205</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.326</v>
+        <v>1.193</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.169</v>
+        <v>0.165</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>101.47</v>
+        <v>101.41</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.017</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.043</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.018</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.01</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.582</v>
+        <v>0.574</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.416</v>
+        <v>0.409</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.366</v>
+        <v>2.227</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.017</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.47</v>
+        <v>49.65</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="AK22" s="1" t="n">
         <v>0.082</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.17</v>
+        <v>0.179</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.253</v>
+        <v>0.269</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.06</v>
+        <v>37.74</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.015</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.166</v>
+        <v>0.138</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.398</v>
+        <v>0.385</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.576</v>
+        <v>0.509</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.612</v>
+        <v>0.59</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.569</v>
+        <v>0.552</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.286</v>
+        <v>2.118</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.198</v>
+        <v>0.188</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>113.57</v>
+        <v>112.4</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0.04</v>
+        <v>-0.001</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.163</v>
+        <v>0.197</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.122</v>
+        <v>0.106</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.642</v>
+        <v>0.683</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.836</v>
+        <v>0.875</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4.371</v>
+        <v>4.143</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.55</v>
+        <v>96.34</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AI23" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.094</v>
+        <v>0.087</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="AM23" s="1" t="n">
         <v>0.02</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>67.37</v>
+        <v>67.88</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.074</v>
+        <v>0.108</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.315</v>
+        <v>0.317</v>
       </c>
       <c r="J24" s="1" t="n">
         <v>0.651</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.686</v>
+        <v>0.706</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.835</v>
+        <v>1.739</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.051</v>
+        <v>0.059</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.8</v>
+        <v>39.55</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.006</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.021</v>
+        <v>0.001</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.018</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.035</v>
+        <v>0.056</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.15</v>
+        <v>0.148</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.323</v>
+        <v>0.294</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.05</v>
+        <v>0.041</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.076</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.59</v>
+        <v>111.7</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.085</v>
+        <v>0.082</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.176</v>
+        <v>0.189</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>45.64</v>
+        <v>46.13</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.011</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.001</v>
+        <v>0.009</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.057</v>
+        <v>0.091</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.18</v>
+        <v>0.189</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.585</v>
+        <v>0.584</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.904</v>
+        <v>0.922</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.317</v>
+        <v>2.175</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>87.84</v>
+        <v>87.4</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.005</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.033</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.093</v>
+        <v>0.113</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.297</v>
+        <v>0.277</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.185</v>
+        <v>0.193</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.599</v>
+        <v>1.435</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,19 +3958,19 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.12</v>
+        <v>93.18</v>
       </c>
       <c r="AF25" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG25" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="AG25" s="1" t="n">
-        <v>-0.003</v>
       </c>
       <c r="AH25" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="AJ25" s="1" t="n">
         <v>0.03</v>
@@ -3979,16 +3979,16 @@
         <v>0.055</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.272</v>
+        <v>0.267</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.641</v>
+        <v>0.64</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.25</v>
+        <v>47.42</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>0.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.119</v>
+        <v>0.139</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.164</v>
+        <v>0.171</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.341</v>
+        <v>0.35</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.624</v>
+        <v>0.631</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.885</v>
+        <v>0.853</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.385</v>
+        <v>1.307</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>60.77</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.012</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.015</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.039</v>
+        <v>0.072</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.024</v>
+        <v>0.042</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.056</v>
+        <v>0.062</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.464</v>
+        <v>0.476</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.349</v>
+        <v>0.363</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.986</v>
+        <v>0.912</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.009</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.69</v>
+        <v>26.57</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.073</v>
+        <v>0.065</v>
       </c>
       <c r="AL26" s="1" t="n">
         <v>0.188</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>46.7</v>
+        <v>47.05</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.016</v>
+        <v>0.039</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.042</v>
+        <v>0.07</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.084</v>
+        <v>0.077</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.204</v>
+        <v>0.2</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.377</v>
+        <v>0.366</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.597</v>
+        <v>0.602</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.791</v>
+        <v>1.685</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.038</v>
+        <v>0.046</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.82</v>
+        <v>26.78</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.022</v>
+        <v>0.002</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.017</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.021</v>
+        <v>0.043</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.083</v>
+        <v>0.105</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,34 +4188,34 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.13</v>
+        <v>53.12</v>
       </c>
       <c r="AF27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG27" s="1" t="n">
-        <v>0.003</v>
-      </c>
       <c r="AH27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.071</v>
+        <v>0.069</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>0.13</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>0.008</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>43.97</v>
+        <v>44.04</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.066</v>
+        <v>0.101</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.038</v>
+        <v>0.034</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.228</v>
+        <v>0.229</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.679</v>
+        <v>0.674</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.509</v>
+        <v>0.532</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.424</v>
+        <v>1.345</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.81</v>
+        <v>75.07</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.109</v>
+        <v>0.083</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.126</v>
+        <v>0.123</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.095</v>
+        <v>0.087</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.242</v>
+        <v>0.235</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.775</v>
+        <v>1.673</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.133</v>
+        <v>0.122</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,34 +4307,34 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.35</v>
+        <v>54.38</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.222</v>
+        <v>0.233</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.069</v>
+        <v>0.074</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.406</v>
+        <v>0.409</v>
       </c>
       <c r="AO28" s="1" t="n">
         <v>0.013</v>
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>63.79</v>
+        <v>64.44</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.103</v>
+        <v>0.134</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.177</v>
+        <v>0.182</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.264</v>
+        <v>0.277</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.51</v>
+        <v>0.525</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.553</v>
+        <v>0.587</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.791</v>
+        <v>1.766</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.064</v>
+        <v>0.075</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.85</v>
+        <v>45.64</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.137</v>
+        <v>0.103</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.187</v>
+        <v>0.195</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.143</v>
+        <v>0.158</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.267</v>
+        <v>0.247</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.139</v>
+        <v>0.132</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.331</v>
+        <v>0.327</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.729</v>
+        <v>1.621</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.37</v>
+        <v>51.49</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.149</v>
+        <v>0.171</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.082</v>
+        <v>-0.078</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.392</v>
+        <v>0.399</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>103.85</v>
+        <v>103.65</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.055</v>
+        <v>0.047</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.116</v>
+        <v>0.126</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.214</v>
+        <v>0.226</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.413</v>
+        <v>0.401</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.598</v>
+        <v>0.638</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.148</v>
+        <v>0.143</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.752</v>
+        <v>1.645</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.73</v>
+        <v>49.9</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.016</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.113</v>
+        <v>0.077</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.076</v>
+        <v>0.065</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.157</v>
+        <v>0.131</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.409</v>
+        <v>0.393</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.904</v>
+        <v>0.823</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.132</v>
+        <v>0.114</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.53</v>
+        <v>24.57</v>
       </c>
       <c r="AF30" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AG30" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="AG30" s="1" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.28</v>
+        <v>0.264</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.13</v>
+        <v>20.15</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.075</v>
+        <v>0.061</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.143</v>
+        <v>0.145</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.163</v>
+        <v>0.185</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.307</v>
+        <v>0.305</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.479</v>
+        <v>0.493</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.638</v>
+        <v>0.661</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.273</v>
+        <v>1.211</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.75</v>
+        <v>65.71</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.178</v>
+        <v>0.152</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.081</v>
+        <v>0.092</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.218</v>
+        <v>0.23</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.351</v>
+        <v>0.362</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.82</v>
+        <v>1.722</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.85</v>
+        <v>80.81</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.288</v>
+        <v>0.294</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.206</v>
+        <v>0.208</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.787</v>
+        <v>0.77</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>39.16</v>
+        <v>38.94</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.006</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="F32" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="G32" s="1" t="n">
-        <v>0.023</v>
-      </c>
       <c r="H32" s="1" t="n">
-        <v>0.059</v>
+        <v>0.05</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.057</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.383</v>
+        <v>0.356</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.451</v>
+        <v>1.437</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.076</v>
+        <v>0.069</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.29</v>
+        <v>46.16</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.003</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.027</v>
+        <v>0.036</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.056</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.026</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>0.057</v>
+        <v>0.013</v>
       </c>
       <c r="W32" s="1" t="n">
+        <v>-0.106</v>
+      </c>
+      <c r="X32" s="1" t="n">
         <v>-0.112</v>
       </c>
-      <c r="X32" s="1" t="n">
-        <v>-0.103</v>
-      </c>
       <c r="Y32" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.372</v>
+        <v>1.27</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.037</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.7</v>
+        <v>29.67</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.162</v>
+        <v>1.15</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.89</v>
+        <v>53.27</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.009</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.025</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.321</v>
+        <v>0.328</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.469</v>
+        <v>1.444</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.014</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,34 +4863,34 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>90.42</v>
+        <v>90.44</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.134</v>
+        <v>0.123</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.336</v>
+        <v>0.313</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.301</v>
+        <v>0.322</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.538</v>
+        <v>0.552</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.594</v>
+        <v>0.601</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.364</v>
+        <v>1.242</v>
       </c>
       <c r="AA33" s="1" t="n">
         <v>0.066</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.26</v>
+        <v>48.3</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.163</v>
+        <v>0.171</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>93.85</v>
+        <v>91.87</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.021</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.013</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.111</v>
+        <v>0.075</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.173</v>
+        <v>0.156</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.228</v>
+        <v>0.189</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.765</v>
+        <v>0.76</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.757</v>
+        <v>1.582</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.162</v>
+        <v>0.138</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>172.5</v>
+        <v>174.02</v>
       </c>
       <c r="R34" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="S34" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="S34" s="1" t="n">
-        <v>-0.014</v>
-      </c>
       <c r="T34" s="1" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.26</v>
+        <v>0.256</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.262</v>
+        <v>0.278</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.296</v>
+        <v>0.315</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.024</v>
+        <v>0.053</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.115</v>
+        <v>1.012</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.022</v>
+        <v>0.031</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.73</v>
+        <v>104.81</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.009</v>
+        <v>0.001</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.066</v>
+        <v>0.078</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.133</v>
+        <v>0.137</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.496</v>
+        <v>0.512</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.108</v>
+        <v>0.12</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.596</v>
+        <v>2.501</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.35</v>
+        <v>60.61</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.022</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.031</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.023</v>
       </c>
       <c r="H35" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>-0.305</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>0.009</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>-0.302</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>0.005</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>57.99</v>
+        <v>58.58</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.053</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.078</v>
+        <v>-0.05</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.052</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.097</v>
+        <v>-0.086</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.084</v>
+        <v>0.108</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.013</v>
+        <v>0.04</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.276</v>
+        <v>2.196</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.057</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.15</v>
+        <v>23.43</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.044</v>
+        <v>0.081</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.108</v>
+        <v>0.141</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.45</v>
+        <v>0.455</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.231</v>
+        <v>0.282</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.889</v>
+        <v>0.863</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.089</v>
+        <v>0.103</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.06</v>
+        <v>29.51</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.301</v>
+        <v>0.297</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.295</v>
+        <v>0.305</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.159</v>
+        <v>0.187</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.427</v>
+        <v>-0.407</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.11</v>
+        <v>0.127</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>73.05</v>
+        <v>72.89</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.105</v>
+        <v>0.082</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.194</v>
+        <v>0.207</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.252</v>
+        <v>0.262</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>0.445</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.965</v>
+        <v>0.996</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.812</v>
+        <v>0.794</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>4.027</v>
+        <v>3.765</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.15</v>
+        <v>0.147</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>123.83</v>
+        <v>124.84</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.022</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.039</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.034</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.061</v>
+        <v>0.068</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.588</v>
+        <v>0.622</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.902</v>
+        <v>0.898</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.829</v>
+        <v>2.746</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.032</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>94.75</v>
+        <v>91.82</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.031</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.031</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.097</v>
+        <v>0.064</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.208</v>
+        <v>0.206</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.497</v>
+        <v>0.459</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.714</v>
+        <v>0.686</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.693</v>
+        <v>1.629</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.729</v>
+        <v>1.713</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.968</v>
+        <v>2.944</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.167</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>133.97</v>
+        <v>130.68</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.025</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.074</v>
+        <v>0.05</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.246</v>
+        <v>0.164</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.456</v>
+        <v>0.436</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.833</v>
+        <v>0.821</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.431</v>
+        <v>1.357</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.299</v>
+        <v>1.305</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.581</v>
+        <v>0.56</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.482</v>
+        <v>2.331</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.378</v>
+        <v>0.344</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>65.09</v>
+        <v>65.37</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.019</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.052</v>
+        <v>0.033</v>
       </c>
       <c r="U38" s="1" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="W38" s="1" t="n">
         <v>0.146</v>
       </c>
-      <c r="V38" s="1" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W38" s="1" t="n">
-        <v>0.144</v>
-      </c>
       <c r="X38" s="1" t="n">
-        <v>0.425</v>
+        <v>0.439</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.573</v>
+        <v>0.545</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.987</v>
+        <v>1.905</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.072</v>
+        <v>0.077</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>69.72</v>
+        <v>66.37</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.029</v>
+        <v>-0.048</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.096</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.113</v>
+        <v>-0.181</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>0.992</v>
+        <v>0.924</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.367</v>
+        <v>1.264</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.451</v>
+        <v>2.317</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>1.755</v>
+        <v>1.613</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>3.651</v>
+        <v>3.565</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.082</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.27</v>
+        <v>29.18</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.049</v>
+        <v>0.065</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.202</v>
+        <v>0.216</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>0.349</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.72</v>
+        <v>0.726</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.795</v>
+        <v>0.816</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.503</v>
+        <v>0.484</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.307</v>
+        <v>1.28</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.28</v>
+        <v>71.53</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.015</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.076</v>
+        <v>0.054</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.18</v>
+        <v>0.228</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.152</v>
+        <v>0.176</v>
       </c>
       <c r="W39" s="1" t="n">
         <v>0.149</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.228</v>
+        <v>0.239</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.336</v>
+        <v>0.309</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.648</v>
+        <v>1.581</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.1</v>
+        <v>0.104</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>186.98</v>
+        <v>182.93</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.022</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.038</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.117</v>
+        <v>-0.126</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.302</v>
+        <v>0.311</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.531</v>
+        <v>0.495</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.043</v>
+        <v>1.041</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.118</v>
+        <v>1.149</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.591</v>
+        <v>0.555</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.029</v>
+        <v>1.013</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>75.32</v>
+        <v>74.71</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.009</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.171</v>
+        <v>0.192</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.361</v>
+        <v>0.368</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.744</v>
+        <v>0.725</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.022</v>
+        <v>1.054</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.895</v>
+        <v>0.903</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.773</v>
+        <v>1.598</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.095</v>
+        <v>0.086</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>134.52</v>
+        <v>136.56</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.015</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.014</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.029</v>
+        <v>0.049</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.011</v>
+        <v>0.039</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.028</v>
+        <v>0.052</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.057</v>
+        <v>0.083</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.485</v>
+        <v>0.517</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.108</v>
+        <v>1.124</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.003</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.56</v>
+        <v>34.94</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.017</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.038</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.028</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.138</v>
+        <v>0.13</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.272</v>
+        <v>0.251</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.179</v>
+        <v>0.194</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.439</v>
+        <v>0.394</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.521</v>
+        <v>0.479</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.636</v>
+        <v>1.526</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.16</v>
+        <v>29.32</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.104</v>
+        <v>0.096</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.143</v>
+        <v>0.163</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.102</v>
+        <v>0.111</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.174</v>
+        <v>0.189</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.326</v>
+        <v>0.377</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.6</v>
+        <v>1.517</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.113</v>
+        <v>0.12</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,34 +5763,34 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>169.3</v>
+        <v>169.25</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.036</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.092</v>
+        <v>-0.11</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.004</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.024</v>
       </c>
       <c r="W41" s="1" t="n">
         <v>0.076</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.693</v>
+        <v>0.695</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.1</v>
+        <v>1.062</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.908</v>
+        <v>4.661</v>
       </c>
       <c r="AA41" s="1" t="n">
         <v>-0.056</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.25</v>
+        <v>73.1</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.055</v>
+        <v>0.046</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.116</v>
+        <v>0.13</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.353</v>
+        <v>0.347</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.627</v>
+        <v>0.641</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.488</v>
+        <v>0.481</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.716</v>
+        <v>1.607</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.32</v>
+        <v>23.46</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.066</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.218</v>
+        <v>-0.195</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.232</v>
+        <v>-0.196</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.303</v>
+        <v>-0.291</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.293</v>
+        <v>-0.288</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.092</v>
+        <v>0.104</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.52</v>
+        <v>-0.512</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.203</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,34 +5956,34 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.24</v>
+        <v>104.22</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.055</v>
+        <v>0.047</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.111</v>
+        <v>0.129</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.158</v>
+        <v>0.151</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.596</v>
+        <v>0.593</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.69</v>
+        <v>1.591</v>
       </c>
       <c r="M43" s="1" t="n">
         <v>0.085</v>
@@ -5995,34 +5995,34 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>190.54</v>
+        <v>190.48</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.047</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.03</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.029</v>
+        <v>0.036</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.157</v>
+        <v>0.15</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.215</v>
+        <v>1.257</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.084</v>
+        <v>1.108</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.563</v>
+        <v>7.186</v>
       </c>
       <c r="AA43" s="1" t="n">
         <v>-0.046</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>51.91</v>
+        <v>51.32</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.041</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.057</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>0.878</v>
+        <v>0.918</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.645</v>
+        <v>1.653</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.55</v>
+        <v>2.267</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.006</v>
+        <v>4.647</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.215</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.11</v>
+        <v>44.25</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.1</v>
+        <v>0.116</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.171</v>
+        <v>0.166</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.241</v>
+        <v>0.248</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.669</v>
+        <v>0.671</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.965</v>
+        <v>0.958</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.404</v>
+        <v>2.258</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.066</v>
+        <v>0.07</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.77</v>
+        <v>80.96</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.022</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.052</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.199</v>
+        <v>-0.176</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.225</v>
+        <v>-0.233</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.244</v>
+        <v>-0.258</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.224</v>
+        <v>-0.242</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.432</v>
+        <v>0.422</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.073</v>
+        <v>0.062</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.904</v>
+        <v>3.566</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.217</v>
+        <v>-0.234</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>76.22</v>
+        <v>75.73</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.029</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.037</v>
+        <v>0.057</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.091</v>
+        <v>0.062</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.097</v>
+        <v>0.13</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.908</v>
+        <v>0.852</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.144</v>
+        <v>0.078</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.102</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>61.12</v>
+        <v>60.87</v>
       </c>
       <c r="D45" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="F45" s="1" t="n">
-        <v>0.063</v>
+        <v>0.052</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.129</v>
+        <v>0.137</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.228</v>
+        <v>0.236</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.624</v>
+        <v>0.652</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.188</v>
+        <v>0.18</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.602</v>
+        <v>1.486</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.117</v>
+        <v>0.113</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.89</v>
+        <v>76.52</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.028</v>
+        <v>-0.018</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0.035</v>
+        <v>-0.013</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.036</v>
       </c>
       <c r="U45" s="1" t="n">
         <v>-0.077</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.076</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.073</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.651</v>
+        <v>0.63</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.265</v>
+        <v>0.273</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>3.125</v>
+        <v>2.843</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.048</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>31.89</v>
+        <v>31.78</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.025</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.048</v>
+        <v>0.065</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.108</v>
+        <v>0.084</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.089</v>
+        <v>0.079</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.125</v>
+        <v>0.162</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.044</v>
+        <v>0.981</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.075</v>
+        <v>1.929</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.126</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.28</v>
+        <v>33.22</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.044</v>
+        <v>0.027</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.134</v>
+        <v>0.151</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>354.66</v>
+        <v>354.1</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.002</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.064</v>
+        <v>0.034</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.227</v>
+        <v>0.251</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.402</v>
+        <v>0.431</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.603</v>
+        <v>0.599</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.569</v>
+        <v>1.613</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.538</v>
+        <v>1.565</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>14.222</v>
+        <v>13.341</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>12.44</v>
+        <v>11.9</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.043</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.019</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>0.099</v>
+        <v>0.152</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.16</v>
+        <v>-0.157</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.072</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.35</v>
+        <v>-0.394</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.627</v>
+        <v>-0.617</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.709</v>
+        <v>-0.737</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.892</v>
+        <v>-0.896</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.73</v>
+        <v>48.82</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.096</v>
+        <v>0.113</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>0.143</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.499</v>
+        <v>0.513</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.499</v>
+        <v>0.503</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.706</v>
+        <v>1.632</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.072</v>
+        <v>0.074</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>123.81</v>
+        <v>123.6</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.028</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.053</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.022</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.151</v>
+        <v>0.146</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.325</v>
+        <v>1.362</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>0.991</v>
+        <v>1.003</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>7.083</v>
+        <v>6.698</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.043</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>43.42</v>
+        <v>43.53</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.148</v>
+        <v>0.165</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.21</v>
+        <v>0.214</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.571</v>
+        <v>0.575</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.814</v>
+        <v>0.831</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.926</v>
+        <v>0.913</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.965</v>
+        <v>1.853</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.06</v>
+        <v>50.59</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.009</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.02</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.259</v>
+        <v>0.24</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.687</v>
+        <v>0.699</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.79</v>
+        <v>25.71</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.054</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.433</v>
+        <v>0.416</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.751</v>
+        <v>0.725</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.523</v>
+        <v>0.502</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>51.69</v>
+        <v>51.8</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.105</v>
+        <v>0.125</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.335</v>
+        <v>0.342</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.758</v>
+        <v>0.778</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.551</v>
+        <v>0.563</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.99</v>
+        <v>1.878</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,22 +6699,22 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.56</v>
+        <v>34.52</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.012</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.011</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.075</v>
+        <v>0.101</v>
       </c>
       <c r="W49" s="1" t="n">
         <v>0.223</v>
@@ -6723,7 +6723,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.65</v>
+        <v>17.45</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.001</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.032</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.051</v>
+        <v>0.021</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.141</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.341</v>
+        <v>-0.345</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.057</v>
+        <v>0.02</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.186</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>38.39</v>
+        <v>38.53</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.009</v>
       </c>
       <c r="T50" s="1" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="Y50" s="1" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>0.137</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="W50" s="1" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="X50" s="1" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="Y50" s="1" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="Z50" s="1" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>0.132</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>20.98</v>
+        <v>20.77</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.041</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.016</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.177</v>
+        <v>-0.216</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.475</v>
+        <v>-0.466</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.319</v>
+        <v>-0.33</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.526</v>
+        <v>-0.539</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.051</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>51.73</v>
+        <v>51.77</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.044</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.097</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.145</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.187</v>
+        <v>-0.185</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.093</v>
+        <v>-0.099</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.017</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.548</v>
+        <v>1.438</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.132</v>
+        <v>-0.131</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.44</v>
+        <v>23.45</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.08</v>
+        <v>0.067</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.015</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.062</v>
+        <v>0.057</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.175</v>
+        <v>-0.171</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.343</v>
+        <v>0.333</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.072</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.97</v>
+        <v>38.39</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.052</v>
+        <v>-0.015</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.273</v>
+        <v>-0.292</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.299</v>
+        <v>-0.263</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.442</v>
+        <v>-0.422</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.288</v>
+        <v>-0.306</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.215</v>
+        <v>-0.227</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.5</v>
+        <v>49.36</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.055</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.151</v>
+        <v>-0.125</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.082</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.152</v>
+        <v>-0.159</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.363</v>
+        <v>0.409</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.349</v>
+        <v>-0.348</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>2.223</v>
+        <v>2.03</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.106</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>15.44</v>
+        <v>15.05</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.068</v>
+        <v>-0.025</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.363</v>
+        <v>-0.395</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.355</v>
+        <v>-0.337</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.57</v>
+        <v>-0.546</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.231</v>
+        <v>-0.272</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.312</v>
+        <v>-0.329</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,31 +7107,31 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.98</v>
+        <v>92.93</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.001</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.051</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.116</v>
+        <v>-0.121</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.151</v>
+        <v>-0.136</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.187</v>
+        <v>-0.179</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.012</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.961</v>
+        <v>0.958</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.23</v>
+        <v>0.253</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
@@ -7144,7 +7144,7 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.03</v>
+        <v>9.02</v>
       </c>
       <c r="AF53" s="1" t="n">
         <v>-0.001</v>
@@ -7156,25 +7156,25 @@
         <v>-0.068</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.052</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.196</v>
+        <v>-0.183</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.249</v>
+        <v>-0.263</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.113</v>
+        <v>-0.12</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.266</v>
+        <v>0.229</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.075</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>63.45</v>
+        <v>63.73</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.024</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.094</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.026</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.081</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.047</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.412</v>
+        <v>0.424</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.16</v>
+        <v>0.166</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.623</v>
+        <v>1.509</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.05</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>117.77</v>
+        <v>117.41</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.003</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.068</v>
+        <v>0.045</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.083</v>
+        <v>0.066</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.082</v>
+        <v>0.09</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.513</v>
+        <v>0.498</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.718</v>
+        <v>0.727</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.716</v>
+        <v>1.698</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.087</v>
+        <v>0.084</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.39</v>
+        <v>38.18</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.024</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.314</v>
+        <v>0.305</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.339</v>
+        <v>0.32</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.28</v>
+        <v>0.284</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>46.5</v>
+        <v>46.38</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.028</v>
+        <v>-0.003</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.073</v>
+        <v>0.049</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.085</v>
+        <v>0.069</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.057</v>
+        <v>0.043</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.091</v>
+        <v>0.099</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.204</v>
+        <v>0.206</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.497</v>
+        <v>0.485</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.729</v>
+        <v>0.743</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.808</v>
+        <v>1.788</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.089</v>
+        <v>0.086</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>29.25</v>
+        <v>28.27</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.034</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.059</v>
+        <v>0.04</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.103</v>
+        <v>0.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.222</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.276</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.305</v>
+        <v>-0.327</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.844</v>
+        <v>-0.849</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.971</v>
+        <v>-0.972</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.105</v>
+        <v>0.068</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.58</v>
+        <v>72.4</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.02</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.026</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.009</v>
+        <v>0.029</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.002</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.358</v>
+        <v>0.345</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.511</v>
+        <v>0.524</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.936</v>
+        <v>2.759</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.22</v>
+        <v>101.21</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.05</v>
+        <v>0.029</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.068</v>
+        <v>0.084</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.067</v>
+        <v>0.079</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.066</v>
+        <v>0.081</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.176</v>
+        <v>0.209</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.274</v>
+        <v>0.302</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>1.026</v>
+        <v>0.989</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.067</v>
+        <v>0.078</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.04</v>
+        <v>90.15</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.036</v>
+        <v>0.028</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.062</v>
+        <v>0.043</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.076</v>
+        <v>0.081</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.104</v>
+        <v>0.118</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.083</v>
+        <v>0.102</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.264</v>
+        <v>0.287</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.419</v>
+        <v>0.448</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.183</v>
+        <v>1.143</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.077</v>
+        <v>0.091</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.59</v>
+        <v>95.49</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.05</v>
+        <v>0.031</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.068</v>
+        <v>0.085</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.073</v>
+        <v>0.085</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.068</v>
+        <v>0.083</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.176</v>
+        <v>0.208</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.271</v>
+        <v>0.295</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.946</v>
+        <v>0.913</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.069</v>
+        <v>0.079</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.79</v>
+        <v>22.67</v>
       </c>
       <c r="R60" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="S60" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="S60" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="T60" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.057</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.071</v>
+        <v>0.081</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.079</v>
+        <v>0.062</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.667</v>
+        <v>0.592</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.028</v>
+        <v>0.022</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>97.16</v>
+        <v>96.93</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="S61" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="T61" s="1" t="n">
         <v>0.098</v>
       </c>
-      <c r="T61" s="1" t="n">
-        <v>0.121</v>
-      </c>
       <c r="U61" s="1" t="n">
-        <v>0.123</v>
+        <v>0.141</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.163</v>
+        <v>0.178</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.206</v>
+        <v>0.199</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.436</v>
+        <v>0.428</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.431</v>
+        <v>0.466</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.364</v>
+        <v>2.156</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/17/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/18/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>334.39</v>
+        <v>336.07</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.014</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.013</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.892</v>
+        <v>0.902</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.968</v>
+        <v>0.987</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.526</v>
+        <v>3.57</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.02</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>56.79</v>
+        <v>57.9</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.02</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.123</v>
+        <v>0.145</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.193</v>
+        <v>0.207</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.266</v>
+        <v>0.297</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.227</v>
+        <v>0.234</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.388</v>
+        <v>0.415</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.668</v>
+        <v>1.786</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.484</v>
+        <v>1.556</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.195</v>
+        <v>0.218</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,37 +1744,37 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.03</v>
+        <v>82.98</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>685.84</v>
+        <v>689.35</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.008</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.008</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.029</v>
+        <v>0.043</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.068</v>
+        <v>0.073</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.749</v>
+        <v>0.758</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.87</v>
+        <v>0.887</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.18</v>
+        <v>3.219</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>103.9</v>
+        <v>105.49</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.015</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.001</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.129</v>
+        <v>0.146</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.128</v>
+        <v>0.131</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.193</v>
+        <v>0.224</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.296</v>
+        <v>0.316</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.636</v>
+        <v>1.773</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>1.946</v>
+        <v>2.083</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.164</v>
+        <v>0.182</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.08</v>
+        <v>119.92</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>0.029</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.072</v>
+        <v>0.073</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.159</v>
+        <v>0.155</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.37</v>
+        <v>71.67</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.138</v>
+        <v>0.139</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.133</v>
+        <v>0.127</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.401</v>
+        <v>0.407</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.522</v>
+        <v>0.545</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.178</v>
+        <v>2.196</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.081</v>
+        <v>0.086</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.48</v>
+        <v>28.18</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.025</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.151</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.361</v>
+        <v>0.385</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.578</v>
+        <v>0.603</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.342</v>
+        <v>0.354</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.328</v>
+        <v>0.362</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.184</v>
+        <v>1.339</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.03</v>
+        <v>0.064</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.317</v>
+        <v>0.35</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.2</v>
+        <v>97</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.082</v>
+        <v>0.085</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.054</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.103</v>
+        <v>0.096</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>263.04</v>
+        <v>263.99</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0.165</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.177</v>
+        <v>0.175</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.414</v>
+        <v>0.419</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.248</v>
+        <v>0.273</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.982</v>
+        <v>2.007</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.069</v>
+        <v>0.072</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.73</v>
+        <v>19.03</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.339</v>
+        <v>0.324</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.684</v>
+        <v>0.708</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.319</v>
+        <v>-0.27</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.704</v>
+        <v>1.748</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.14</v>
+        <v>0.158</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>104.03</v>
+        <v>103.7</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.07</v>
+        <v>0.076</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.179</v>
+        <v>-0.181</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.037</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.29</v>
+        <v>26.14</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.038</v>
+        <v>0.011</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.086</v>
+        <v>0.08</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.096</v>
+        <v>0.09</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.184</v>
+        <v>0.167</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.29</v>
+        <v>0.283</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.215</v>
+        <v>1.238</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.514</v>
+        <v>1.481</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.117</v>
+        <v>0.111</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.87</v>
+        <v>89.53</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="AJ9" s="1" t="n">
         <v>0.063</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.053</v>
+        <v>0.062</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.015</v>
       </c>
       <c r="AM9" s="1" t="n">
         <v>-0.277</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.102</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>181.21</v>
+        <v>182.88</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.009</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.069</v>
+        <v>0.079</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.278</v>
+        <v>0.288</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.254</v>
+        <v>0.271</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.315</v>
+        <v>0.308</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.426</v>
+        <v>0.439</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.692</v>
+        <v>0.724</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.212</v>
+        <v>2.254</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.177</v>
+        <v>0.188</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.23</v>
+        <v>111.16</v>
       </c>
       <c r="AF10" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ10" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
       <c r="AL10" s="1" t="n">
         <v>0.129</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.063</v>
+        <v>0.066</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>223.2</v>
+        <v>224.31</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>-0.002</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="F11" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.107</v>
+        <v>0.114</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.136</v>
+        <v>0.142</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.496</v>
+        <v>0.503</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.695</v>
+        <v>0.713</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.011</v>
+        <v>2.032</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>59.63</v>
+        <v>60.63</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.017</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.028</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.079</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.331</v>
+        <v>0.362</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.506</v>
+        <v>0.542</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.651</v>
+        <v>0.664</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.498</v>
+        <v>0.523</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.79</v>
+        <v>0.821</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.484</v>
+        <v>4.611</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.161</v>
+        <v>0.181</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2413,16 +2413,16 @@
         <v>102.9</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ11" s="1" t="n">
         <v>0.016</v>
@@ -2434,10 +2434,10 @@
         <v>0.162</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>0.005</v>
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>449.35</v>
+        <v>452.17</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.013</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>-0.045</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>-0.036</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.084</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.941</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>4.265</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>-0.051</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>86.47</v>
+        <v>88.7</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.026</v>
       </c>
       <c r="S12" s="1" t="n">
         <v>-0.021</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.04</v>
+        <v>0.067</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.346</v>
+        <v>0.366</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.751</v>
+        <v>0.798</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.544</v>
+        <v>1.584</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.101</v>
+        <v>3.207</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.414</v>
+        <v>2.546</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.61</v>
+        <v>5.444</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.174</v>
+        <v>0.205</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,31 +2529,31 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.33</v>
+        <v>108.31</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AH12" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AJ12" s="1" t="n">
         <v>0.058</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="AN12" s="1" t="n">
         <v>0.236</v>
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>202.24</v>
+        <v>203.49</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.055</v>
+        <v>0.068</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.081</v>
+        <v>0.088</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.717</v>
+        <v>0.728</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.799</v>
+        <v>0.814</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.798</v>
+        <v>2.83</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.6</v>
+        <v>40.85</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>-0.049</v>
+        <v>0.032</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.054</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.008</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.498</v>
+        <v>0.545</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.011</v>
+        <v>1.083</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>1.952</v>
+        <v>2.047</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.068</v>
+        <v>3.197</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.613</v>
+        <v>1.746</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.792</v>
+        <v>5.654</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.156</v>
+        <v>0.192</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,13 +2648,13 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.18</v>
+        <v>23.19</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1" t="n">
         <v>0.014</v>
@@ -2663,22 +2663,22 @@
         <v>0.037</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.063</v>
+        <v>0.07</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.088</v>
+        <v>0.095</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.284</v>
+        <v>0.282</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>95.84</v>
+        <v>96.03</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.385</v>
+        <v>0.388</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="L14" s="1" t="n">
         <v>1.789</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>51.81</v>
+        <v>53.01</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.023</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.038</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.05</v>
+        <v>0.074</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.391</v>
+        <v>0.442</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.668</v>
+        <v>0.729</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>0.925</v>
+        <v>0.967</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.169</v>
+        <v>0.196</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.79</v>
+        <v>76.26</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.155</v>
+        <v>0.147</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.041</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>251.65</v>
+        <v>253.49</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.007</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.019</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.825</v>
+        <v>0.839</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.512</v>
+        <v>0.534</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.139</v>
+        <v>3.205</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.79</v>
+        <v>17.16</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.046</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.111</v>
+        <v>0.156</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.659</v>
+        <v>0.681</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.901</v>
+        <v>0.955</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.074</v>
+        <v>0.098</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,10 +2874,10 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.62</v>
+        <v>97.66</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="1" t="n">
         <v>0.007</v>
@@ -2886,25 +2886,25 @@
         <v>0.019</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AJ15" s="1" t="n">
         <v>0.066</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.129</v>
+        <v>0.134</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.487</v>
+        <v>0.483</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>137.62</v>
+        <v>138.25</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.082</v>
+        <v>0.087</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.144</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.155</v>
+        <v>0.164</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>0.218</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.483</v>
+        <v>0.49</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.809</v>
+        <v>0.822</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.654</v>
+        <v>1.658</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.132</v>
+        <v>0.137</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>80.78</v>
+        <v>80.7</v>
       </c>
       <c r="R16" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S16" s="1" t="n">
         <v>-0.019</v>
       </c>
-      <c r="S16" s="1" t="n">
-        <v>0.007</v>
-      </c>
       <c r="T16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.194</v>
+        <v>0.204</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.1</v>
+        <v>0.107</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.041</v>
+        <v>0.049</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.349</v>
+        <v>1.358</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.84</v>
+        <v>42.71</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.18</v>
+        <v>0.174</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.258</v>
+        <v>0.254</v>
       </c>
       <c r="AM16" s="1" t="n">
         <v>0.039</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.3</v>
+        <v>0.302</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>148.42</v>
+        <v>149.24</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.008</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.022</v>
+        <v>0.037</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.709</v>
+        <v>0.718</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.746</v>
+        <v>0.763</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.05</v>
+        <v>107.78</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.183</v>
+        <v>0.187</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.419</v>
+        <v>0.413</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.387</v>
+        <v>1.381</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.397</v>
+        <v>1.427</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.2</v>
+        <v>4.218</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.167</v>
+        <v>0.164</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.97</v>
+        <v>42.67</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="AK17" s="1" t="n">
         <v>0.111</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.116</v>
+        <v>0.108</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.188</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.055</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.23</v>
+        <v>160.64</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.138</v>
+        <v>0.149</v>
       </c>
       <c r="V18" s="1" t="n">
         <v>0.12</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.161</v>
+        <v>0.154</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.613</v>
+        <v>0.617</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.667</v>
+        <v>0.682</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.657</v>
+        <v>2.674</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.081</v>
+        <v>0.084</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.43</v>
+        <v>36.38</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.306</v>
+        <v>0.295</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.472</v>
+        <v>0.455</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.168</v>
+        <v>0.166</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>55.86</v>
+        <v>56.46</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.011</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.013</v>
+        <v>0.024</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.192</v>
+        <v>0.203</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.698</v>
+        <v>0.716</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.887</v>
+        <v>0.912</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.198</v>
+        <v>2.234</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.8</v>
+        <v>81.81</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.004</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.039</v>
+        <v>0.052</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.15</v>
+        <v>0.167</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.151</v>
+        <v>0.162</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.426</v>
+        <v>0.444</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.484</v>
+        <v>0.507</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.763</v>
+        <v>1.811</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.084</v>
+        <v>0.098</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101</v>
+        <v>100.86</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AJ20" s="1" t="n">
         <v>0.041</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.03</v>
+        <v>36.16</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.025</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.109</v>
+        <v>0.113</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.223</v>
+        <v>0.228</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.413</v>
+        <v>0.412</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.566</v>
+        <v>0.563</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.719</v>
+        <v>0.725</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.755</v>
+        <v>0.791</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.811</v>
+        <v>1.866</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.183</v>
+        <v>0.188</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>238.17</v>
+        <v>240.32</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.021</v>
+        <v>0.041</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.014</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.169</v>
+        <v>0.185</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.225</v>
+        <v>0.231</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.561</v>
+        <v>0.563</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.091</v>
+        <v>1.11</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.536</v>
+        <v>1.593</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.89</v>
+        <v>3.909</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.109</v>
+        <v>0.119</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.58</v>
+        <v>50.56</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AH21" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AJ21" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="AL21" s="1" t="n">
         <v>0.167</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.76</v>
+        <v>80.15</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.091</v>
+        <v>0.083</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.25</v>
+        <v>0.225</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.342</v>
+        <v>0.335</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.591</v>
+        <v>0.563</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.523</v>
+        <v>0.511</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.205</v>
+        <v>1.235</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.193</v>
+        <v>1.172</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.165</v>
+        <v>0.156</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>101.41</v>
+        <v>102.19</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.003</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.036</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.574</v>
+        <v>0.586</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.409</v>
+        <v>0.426</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.227</v>
+        <v>2.28</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.009</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.65</v>
+        <v>49.5</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="AJ22" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.179</v>
+        <v>0.176</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.269</v>
+        <v>0.254</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>37.74</v>
+        <v>38.03</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.029</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.138</v>
+        <v>0.147</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.192</v>
+        <v>0.203</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.385</v>
+        <v>0.391</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.509</v>
+        <v>0.519</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.59</v>
+        <v>0.603</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.552</v>
+        <v>0.587</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.118</v>
+        <v>2.225</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.188</v>
+        <v>0.197</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>112.4</v>
+        <v>112.1</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.042</v>
+        <v>0.039</v>
       </c>
       <c r="U23" s="1" t="n">
         <v>0.197</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.106</v>
+        <v>0.117</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.683</v>
+        <v>0.678</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.875</v>
+        <v>0.883</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4.143</v>
+        <v>4.16</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.167</v>
+        <v>0.164</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.34</v>
+        <v>96.26</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.087</v>
+        <v>0.092</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>67.88</v>
+        <v>68.12</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.108</v>
+        <v>0.126</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.123</v>
+        <v>0.133</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.651</v>
+        <v>0.657</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.706</v>
+        <v>0.716</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.739</v>
+        <v>1.772</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.55</v>
+        <v>39.75</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.056</v>
+        <v>0.067</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.294</v>
+        <v>0.295</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.076</v>
+        <v>-0.059</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.7</v>
+        <v>111.59</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="AJ24" s="1" t="n">
         <v>0.041</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.082</v>
+        <v>0.086</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.4</v>
+        <v>0.387</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.13</v>
+        <v>46.49</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.091</v>
+        <v>0.108</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.121</v>
+        <v>0.133</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.584</v>
+        <v>0.596</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.922</v>
+        <v>0.948</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.175</v>
+        <v>2.216</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.054</v>
+        <v>0.062</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>87.4</v>
+        <v>88.06</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.008</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.009</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.026</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.113</v>
+        <v>0.121</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.111</v>
+        <v>0.12</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.277</v>
+        <v>0.286</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.193</v>
+        <v>0.219</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.435</v>
+        <v>1.458</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.032</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.18</v>
+        <v>93.38</v>
       </c>
       <c r="AF25" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AG25" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG25" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.253</v>
+        <v>0.256</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.64</v>
+        <v>0.636</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.42</v>
+        <v>47.88</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.015</v>
+        <v>0.009</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.139</v>
+        <v>0.157</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.171</v>
+        <v>0.182</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.631</v>
+        <v>0.647</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.853</v>
+        <v>0.882</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.307</v>
+        <v>1.342</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.078</v>
+        <v>0.089</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.77</v>
+        <v>61.53</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.016</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.003</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.072</v>
+        <v>0.073</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.042</v>
+        <v>0.052</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.062</v>
+        <v>0.069</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.476</v>
+        <v>0.495</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.363</v>
+        <v>0.377</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.912</v>
+        <v>0.936</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.003</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.57</v>
+        <v>26.62</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AG26" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.065</v>
+        <v>0.073</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.188</v>
+        <v>0.191</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.107</v>
+        <v>0.115</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.05</v>
+        <v>47.03</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.07</v>
+        <v>0.083</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.077</v>
+        <v>0.085</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.602</v>
+        <v>0.607</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.685</v>
+        <v>1.7</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.78</v>
+        <v>26.73</v>
       </c>
       <c r="R27" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.043</v>
+        <v>0.05</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,7 +4188,7 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.12</v>
+        <v>53.11</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>0</v>
@@ -4197,16 +4197,16 @@
         <v>0.002</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="AJ27" s="1" t="n">
         <v>0.029</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.069</v>
+        <v>0.07</v>
       </c>
       <c r="AL27" s="1" t="n">
         <v>0.195</v>
@@ -4215,7 +4215,7 @@
         <v>0.13</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.329</v>
+        <v>0.327</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>0.008</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.04</v>
+        <v>44.12</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.101</v>
+        <v>0.116</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.034</v>
+        <v>0.039</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.229</v>
+        <v>0.216</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.674</v>
+        <v>0.677</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.532</v>
+        <v>0.531</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.345</v>
+        <v>1.346</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,34 +4268,34 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.07</v>
+        <v>75.11</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.001</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>0.083</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.123</v>
+        <v>0.113</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.087</v>
+        <v>0.088</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
       <c r="X28" s="1" t="n">
         <v>0.235</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.424</v>
+        <v>0.425</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.673</v>
+        <v>1.679</v>
       </c>
       <c r="AA28" s="1" t="n">
         <v>0.122</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.38</v>
+        <v>54.33</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.233</v>
+        <v>0.231</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.409</v>
+        <v>0.404</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.44</v>
+        <v>64.26</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.065</v>
+        <v>0.062</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>0.182</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.277</v>
+        <v>0.276</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.525</v>
+        <v>0.521</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.587</v>
+        <v>0.586</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.766</v>
+        <v>1.77</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.075</v>
+        <v>0.072</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.64</v>
+        <v>45.49</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.195</v>
+        <v>0.187</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.158</v>
+        <v>0.152</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.247</v>
+        <v>0.226</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.132</v>
+        <v>0.128</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.327</v>
+        <v>0.347</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.621</v>
+        <v>1.595</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.49</v>
+        <v>51.41</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.081</v>
+        <v>0.087</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.171</v>
+        <v>0.169</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.078</v>
+        <v>-0.076</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.399</v>
+        <v>0.387</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>103.65</v>
+        <v>103.89</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.047</v>
+        <v>0.049</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.126</v>
+        <v>0.136</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.226</v>
+        <v>0.22</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.401</v>
+        <v>0.39</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.638</v>
+        <v>0.642</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.143</v>
+        <v>0.165</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.645</v>
+        <v>1.664</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.102</v>
+        <v>0.105</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>49.9</v>
+        <v>50.01</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.002</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.065</v>
+        <v>0.069</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.131</v>
+        <v>0.133</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.393</v>
+        <v>0.402</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.823</v>
+        <v>0.834</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.57</v>
+        <v>24.64</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.273</v>
+        <v>0.277</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.264</v>
+        <v>0.274</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.724</v>
+        <v>0.729</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.15</v>
+        <v>20.19</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.185</v>
+        <v>0.193</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.305</v>
+        <v>0.304</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.493</v>
+        <v>0.496</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.661</v>
+        <v>0.671</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.211</v>
+        <v>1.224</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.71</v>
+        <v>65.84</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.034</v>
+        <v>0.029</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.152</v>
+        <v>0.158</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.092</v>
+        <v>0.097</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.23</v>
+        <v>0.232</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.362</v>
+        <v>0.374</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.722</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.81</v>
+        <v>80.91</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG31" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.294</v>
+        <v>0.296</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.208</v>
+        <v>0.211</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>38.94</v>
+        <v>39.12</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.05</v>
+        <v>0.047</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.044</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.356</v>
+        <v>0.365</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.437</v>
+        <v>1.449</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.069</v>
+        <v>0.074</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.16</v>
+        <v>46.3</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.036</v>
+        <v>0.017</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.053</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.017</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.094</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.112</v>
+        <v>-0.11</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.27</v>
+        <v>1.285</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.034</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.67</v>
+        <v>29.71</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG32" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.09</v>
+        <v>0.093</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.291</v>
+        <v>0.293</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.19</v>
+        <v>0.196</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.15</v>
+        <v>1.157</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,34 +4824,34 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>53.27</v>
+        <v>53.32</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.004</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.024</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.003</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.328</v>
+        <v>0.334</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.444</v>
+        <v>1.463</v>
       </c>
       <c r="M33" s="1" t="n">
         <v>-0.014</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>90.44</v>
+        <v>90.38</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.123</v>
+        <v>0.112</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.322</v>
+        <v>0.316</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.552</v>
+        <v>0.551</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.601</v>
+        <v>0.612</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.242</v>
+        <v>1.287</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.3</v>
+        <v>48.25</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.171</v>
+        <v>0.169</v>
       </c>
       <c r="AM33" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.87</v>
+        <v>91.38</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.005</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.028</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.075</v>
+        <v>0.069</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.156</v>
+        <v>0.174</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.189</v>
+        <v>0.181</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.385</v>
+        <v>0.363</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.76</v>
+        <v>0.751</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.445</v>
+        <v>0.454</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.582</v>
+        <v>1.568</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>174.02</v>
+        <v>174.76</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.256</v>
+        <v>0.265</v>
       </c>
       <c r="W34" s="1" t="n">
         <v>0.278</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.315</v>
+        <v>0.321</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.053</v>
+        <v>0.075</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.012</v>
+        <v>1.074</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.81</v>
+        <v>105.1</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="AJ34" s="1" t="n">
         <v>0.137</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.512</v>
+        <v>0.516</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.12</v>
+        <v>0.131</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.501</v>
+        <v>2.523</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.61</v>
+        <v>60.95</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.016</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.025</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.012</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>0.028</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.159</v>
+        <v>0.154</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.306</v>
+        <v>0.313</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.305</v>
+        <v>-0.284</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.883</v>
+        <v>0.912</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.009</v>
+        <v>0.015</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>58.58</v>
+        <v>59.45</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.038</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.037</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.033</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.086</v>
+        <v>-0.071</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.108</v>
+        <v>0.125</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.04</v>
+        <v>0.066</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.196</v>
+        <v>2.26</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.043</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.43</v>
+        <v>23.56</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="E36" s="1" t="n">
         <v>-0.01</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.081</v>
+        <v>0.101</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.141</v>
+        <v>0.153</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.455</v>
+        <v>0.471</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.282</v>
+        <v>0.289</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.04</v>
+        <v>0.058</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.863</v>
+        <v>0.883</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.51</v>
+        <v>29.75</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.017</v>
+        <v>0.028</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.04</v>
+        <v>0.048</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.297</v>
+        <v>0.313</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.187</v>
+        <v>0.197</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.407</v>
+        <v>-0.385</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.127</v>
+        <v>0.136</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>72.89</v>
+        <v>72.98</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.082</v>
+        <v>0.084</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.207</v>
+        <v>0.218</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.262</v>
+        <v>0.251</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.445</v>
+        <v>0.436</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.996</v>
+        <v>0.998</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.794</v>
+        <v>0.803</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.765</v>
+        <v>3.767</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>124.84</v>
+        <v>125.8</v>
       </c>
       <c r="R37" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.001</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.031</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.026</v>
+        <v>0.033</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.068</v>
+        <v>0.069</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.622</v>
+        <v>0.635</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.898</v>
+        <v>0.918</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.746</v>
+        <v>2.796</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.024</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>91.82</v>
+        <v>93.85</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.022</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.02</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.064</v>
+        <v>0.088</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.206</v>
+        <v>0.224</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.459</v>
+        <v>0.493</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.686</v>
+        <v>0.695</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.629</v>
+        <v>1.687</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.713</v>
+        <v>1.775</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.944</v>
+        <v>2.927</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.131</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>130.68</v>
+        <v>132.93</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>-0.025</v>
+        <v>0.017</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.05</v>
+        <v>0.018</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.164</v>
+        <v>0.185</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.436</v>
+        <v>0.484</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.821</v>
+        <v>0.867</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.357</v>
+        <v>1.366</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.305</v>
+        <v>1.345</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.56</v>
+        <v>0.611</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.331</v>
+        <v>2.425</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.344</v>
+        <v>0.367</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>65.37</v>
+        <v>65.33</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.006</v>
       </c>
       <c r="T38" s="1" t="n">
         <v>0.033</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.192</v>
+        <v>0.182</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.145</v>
+        <v>0.139</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.146</v>
+        <v>0.136</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.545</v>
+        <v>0.561</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.905</v>
+        <v>1.953</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>66.37</v>
+        <v>70.09</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>-0.048</v>
+        <v>0.056</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.085</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.181</v>
+        <v>-0.135</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>0.924</v>
+        <v>1.029</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.264</v>
+        <v>1.343</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.317</v>
+        <v>2.503</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>1.613</v>
+        <v>1.797</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>3.565</v>
+        <v>3.749</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.03</v>
+        <v>0.088</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.18</v>
+        <v>29.49</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.011</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.065</v>
+        <v>0.076</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.216</v>
+        <v>0.255</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.349</v>
+        <v>0.369</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.726</v>
+        <v>0.736</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.816</v>
+        <v>0.835</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.484</v>
+        <v>0.508</v>
       </c>
       <c r="L39" s="1" t="n">
         <v>1.28</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.091</v>
+        <v>0.102</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.53</v>
+        <v>71.38</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.006</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.228</v>
+        <v>0.214</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.176</v>
+        <v>0.167</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.149</v>
+        <v>0.136</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.239</v>
+        <v>0.236</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.309</v>
+        <v>0.322</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.581</v>
+        <v>1.619</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.104</v>
+        <v>0.101</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>182.93</v>
+        <v>189.27</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.035</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.026</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.126</v>
+        <v>-0.096</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.311</v>
+        <v>0.353</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.495</v>
+        <v>0.558</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.041</v>
+        <v>1.103</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.149</v>
+        <v>1.224</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.555</v>
+        <v>0.588</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.013</v>
+        <v>1.077</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>74.71</v>
+        <v>75.57</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.012</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.013</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.192</v>
+        <v>0.205</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.368</v>
+        <v>0.396</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.054</v>
+        <v>1.078</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.903</v>
+        <v>0.922</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.598</v>
+        <v>1.615</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.086</v>
+        <v>0.098</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>136.56</v>
+        <v>135.37</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.009</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.004</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.039</v>
+        <v>0.026</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.052</v>
+        <v>0.045</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.083</v>
+        <v>0.067</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.517</v>
+        <v>0.503</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.124</v>
+        <v>1.116</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.52</v>
+        <v>2.495</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>34.94</v>
+        <v>35.58</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.018</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.033</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.01</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.13</v>
+        <v>0.155</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.251</v>
+        <v>0.278</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.194</v>
+        <v>0.234</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.394</v>
+        <v>0.42</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.479</v>
+        <v>0.47</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.526</v>
+        <v>1.575</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.32</v>
+        <v>29.31</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1" t="n">
         <v>0.096</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.163</v>
+        <v>0.174</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>0.111</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.517</v>
+        <v>1.507</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>169.25</v>
+        <v>172.91</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V41" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="Y41" s="1" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>4.849</v>
+      </c>
+      <c r="AA41" s="1" t="n">
         <v>-0.036</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="V41" s="1" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="W41" s="1" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="X41" s="1" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="Y41" s="1" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="Z41" s="1" t="n">
-        <v>4.661</v>
-      </c>
-      <c r="AA41" s="1" t="n">
-        <v>-0.056</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.1</v>
+        <v>73.35</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.046</v>
+        <v>0.05</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.13</v>
+        <v>0.144</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.18</v>
+        <v>0.183</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.347</v>
+        <v>0.342</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.641</v>
+        <v>0.647</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.481</v>
+        <v>0.498</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.607</v>
+        <v>1.625</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.089</v>
+        <v>0.093</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.46</v>
+        <v>23.89</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.012</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.195</v>
+        <v>-0.18</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.196</v>
+        <v>-0.174</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.291</v>
+        <v>-0.284</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.288</v>
+        <v>-0.283</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.104</v>
+        <v>0.124</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.512</v>
+        <v>-0.502</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.203</v>
+        <v>-0.188</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.22</v>
+        <v>104.34</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.129</v>
+        <v>0.145</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.151</v>
+        <v>0.154</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.318</v>
+        <v>0.31</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.616</v>
+        <v>0.618</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.593</v>
+        <v>0.603</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.591</v>
+        <v>1.607</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.085</v>
+        <v>0.087</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>190.48</v>
+        <v>192.48</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.015</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.037</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.004</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.15</v>
+        <v>0.156</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.257</v>
+        <v>1.281</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.108</v>
+        <v>1.141</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.186</v>
+        <v>7.323</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.036</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>51.32</v>
+        <v>52.99</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.033</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.013</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.026</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.378</v>
+        <v>0.416</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>0.918</v>
+        <v>0.969</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.653</v>
+        <v>1.739</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.267</v>
+        <v>2.601</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.647</v>
+        <v>4.849</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.201</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.25</v>
+        <v>44.59</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.116</v>
+        <v>0.138</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.248</v>
+        <v>0.246</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.671</v>
+        <v>0.684</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.958</v>
+        <v>0.99</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.258</v>
+        <v>2.301</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.07</v>
+        <v>0.078</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>80.96</v>
+        <v>82</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.013</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.015</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.176</v>
+        <v>-0.166</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.233</v>
+        <v>-0.215</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.258</v>
+        <v>-0.251</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.242</v>
+        <v>-0.24</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.422</v>
+        <v>0.44</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.062</v>
+        <v>0.079</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.566</v>
+        <v>3.682</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.234</v>
+        <v>-0.224</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>75.73</v>
+        <v>79.4</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.048</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.006</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.057</v>
+        <v>0.108</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.062</v>
+        <v>0.095</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.04</v>
+        <v>0.085</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.032</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.13</v>
+        <v>0.185</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.852</v>
+        <v>0.972</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.078</v>
+        <v>0.146</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.095</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>60.87</v>
+        <v>61.19</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.137</v>
+        <v>0.149</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>0.236</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.404</v>
+        <v>0.402</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.652</v>
+        <v>0.661</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.18</v>
+        <v>0.203</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.486</v>
+        <v>1.514</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.113</v>
+        <v>0.118</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.52</v>
+        <v>76.93</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.005</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.031</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.066</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.076</v>
+        <v>-0.074</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.069</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.63</v>
+        <v>0.639</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.273</v>
+        <v>0.284</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.843</v>
+        <v>2.918</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.043</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>31.78</v>
+        <v>33.27</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.047</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>-0.025</v>
+        <v>0.011</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.065</v>
+        <v>0.115</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.084</v>
+        <v>0.119</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.079</v>
+        <v>0.122</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.037</v>
+        <v>0.071</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.162</v>
+        <v>0.216</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>0.981</v>
+        <v>1.108</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>1.929</v>
+        <v>2.109</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.122</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.22</v>
+        <v>33.36</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.004</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.17</v>
+        <v>0.172</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.092</v>
+        <v>0.096</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>354.1</v>
+        <v>357.92</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.011</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.251</v>
+        <v>0.294</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.431</v>
+        <v>0.442</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.599</v>
+        <v>0.59</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.613</v>
+        <v>1.641</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.565</v>
+        <v>1.619</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.341</v>
+        <v>13.565</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.176</v>
+        <v>0.189</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.9</v>
+        <v>11.87</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.003</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.037</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.157</v>
+        <v>-0.165</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.067</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.394</v>
+        <v>-0.433</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.617</v>
+        <v>-0.618</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.737</v>
+        <v>-0.73</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.896</v>
+        <v>-0.891</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.82</v>
+        <v>48.94</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.113</v>
+        <v>0.125</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.243</v>
+        <v>0.238</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.513</v>
+        <v>0.517</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.503</v>
+        <v>0.512</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.632</v>
+        <v>1.627</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.074</v>
+        <v>0.077</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>123.6</v>
+        <v>124.77</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.009</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.015</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.044</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.022</v>
+        <v>0</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.048</v>
+        <v>0.058</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.146</v>
+        <v>0.153</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.362</v>
+        <v>1.385</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.003</v>
+        <v>1.031</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.698</v>
+        <v>6.811</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.034</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>43.53</v>
+        <v>43.6</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.165</v>
+        <v>0.177</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.214</v>
+        <v>0.223</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.831</v>
+        <v>0.834</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.913</v>
+        <v>0.927</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.853</v>
+        <v>1.855</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>50.59</v>
+        <v>51.2</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.012</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.013</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.008</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.098</v>
+        <v>0.128</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.18</v>
+        <v>0.191</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.24</v>
+        <v>0.242</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.699</v>
+        <v>0.719</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.039</v>
+        <v>0.073</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.05</v>
+        <v>0.063</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.71</v>
+        <v>25.84</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.009</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.057</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.416</v>
+        <v>0.423</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.725</v>
+        <v>0.728</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.502</v>
+        <v>0.514</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>51.8</v>
+        <v>52.18</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.125</v>
+        <v>0.145</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.141</v>
+        <v>0.15</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.778</v>
+        <v>0.791</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.563</v>
+        <v>0.58</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.878</v>
+        <v>1.897</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.08</v>
+        <v>0.088</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.52</v>
+        <v>34.86</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.01</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>-0.012</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.001</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.047</v>
+        <v>0.078</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.037</v>
+        <v>0.047</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,34 +6732,34 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.45</v>
+        <v>17.44</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.001</v>
       </c>
       <c r="AG49" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AI49" s="1" t="n">
         <v>-0.032</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.141</v>
+        <v>-0.153</v>
       </c>
       <c r="AL49" s="1" t="n">
         <v>-0.345</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.186</v>
+        <v>-0.182</v>
       </c>
       <c r="AO49" s="1" t="n">
         <v>-0.016</v>
@@ -6791,31 +6791,31 @@
         <v>38.53</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.01</v>
       </c>
       <c r="T50" s="1" t="n">
         <v>0.141</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.281</v>
+        <v>0.272</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="X50" s="1" t="n">
         <v>0.705</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.343</v>
+        <v>0.357</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="AA50" s="1" t="n">
         <v>0.137</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>20.77</v>
+        <v>21.14</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.018</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.004</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.207</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.466</v>
+        <v>-0.457</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.335</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.539</v>
+        <v>-0.528</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.04</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>51.77</v>
+        <v>52.22</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.001</v>
+        <v>0.009</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.026</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.097</v>
+        <v>-0.089</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.145</v>
+        <v>-0.135</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.185</v>
+        <v>-0.181</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.091</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.41</v>
+        <v>0.422</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.438</v>
+        <v>1.487</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.131</v>
+        <v>-0.123</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.45</v>
+        <v>23.42</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.013</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.171</v>
+        <v>-0.172</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.136</v>
+        <v>0.141</v>
       </c>
       <c r="AN51" s="1" t="n">
         <v>0.333</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.073</v>
+        <v>0.071</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.39</v>
+        <v>37.54</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.022</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.02</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.292</v>
+        <v>-0.308</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.263</v>
+        <v>-0.287</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.422</v>
+        <v>-0.432</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.306</v>
+        <v>-0.298</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.227</v>
+        <v>-0.244</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.36</v>
+        <v>49.88</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.011</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.034</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.125</v>
+        <v>-0.115</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.082</v>
+        <v>-0.068</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.159</v>
+        <v>-0.146</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.409</v>
+        <v>0.424</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.348</v>
+        <v>-0.334</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>2.03</v>
+        <v>2.061</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.097</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>15.05</v>
+        <v>14.63</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.395</v>
+        <v>-0.412</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.337</v>
+        <v>-0.38</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.546</v>
+        <v>-0.556</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.272</v>
+        <v>-0.265</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.329</v>
+        <v>-0.348</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.93</v>
+        <v>93.39</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.033</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.121</v>
+        <v>-0.116</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.136</v>
+        <v>-0.129</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.179</v>
+        <v>-0.18</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.958</v>
+        <v>0.967</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.253</v>
+        <v>0.267</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.099</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.02</v>
+        <v>9.17</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.017</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.016</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.053</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.033</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.183</v>
+        <v>-0.162</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.263</v>
+        <v>-0.251</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.12</v>
+        <v>-0.105</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.229</v>
+        <v>0.223</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.076</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>63.73</v>
+        <v>64.11</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.094</v>
+        <v>-0.088</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.074</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.045</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.424</v>
+        <v>0.432</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.166</v>
+        <v>0.177</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.509</v>
+        <v>1.521</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.044</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>117.41</v>
+        <v>115.57</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.045</v>
+        <v>0.019</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.186</v>
+        <v>0.158</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.498</v>
+        <v>0.474</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.727</v>
+        <v>0.69</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.698</v>
+        <v>1.616</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.084</v>
+        <v>0.067</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.18</v>
+        <v>38.69</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.011</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.08</v>
+        <v>0.091</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.121</v>
+        <v>0.132</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.305</v>
+        <v>0.322</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.32</v>
+        <v>0.334</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.284</v>
+        <v>0.292</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>46.38</v>
+        <v>45.61</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.017</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.049</v>
+        <v>0.023</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.069</v>
+        <v>0.051</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.099</v>
+        <v>0.085</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.206</v>
+        <v>0.175</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.485</v>
+        <v>0.461</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.743</v>
+        <v>0.704</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.788</v>
+        <v>1.698</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.086</v>
+        <v>0.068</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,25 +7421,25 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.27</v>
+        <v>28.26</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>-0.034</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="F56" s="1" t="n">
         <v>0.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.222</v>
+        <v>-0.247</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.276</v>
+        <v>-0.258</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.327</v>
+        <v>-0.324</v>
       </c>
       <c r="J56" s="1" t="n">
         <v>-0.849</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.4</v>
+        <v>72.75</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.021</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.029</v>
+        <v>0.038</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.083</v>
+        <v>0.078</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.524</v>
+        <v>0.537</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.759</v>
+        <v>2.758</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>101.21</v>
+        <v>100.01</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.084</v>
+        <v>0.066</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.081</v>
+        <v>0.064</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.209</v>
+        <v>0.195</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.302</v>
+        <v>0.29</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.989</v>
+        <v>0.947</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.078</v>
+        <v>0.065</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>90.15</v>
+        <v>88.9</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.028</v>
+        <v>0.001</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.043</v>
+        <v>0.029</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.081</v>
+        <v>0.061</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.118</v>
+        <v>0.11</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.102</v>
+        <v>0.083</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.287</v>
+        <v>0.269</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.448</v>
+        <v>0.429</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.143</v>
+        <v>1.094</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.091</v>
+        <v>0.076</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.49</v>
+        <v>94.37</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.085</v>
+        <v>0.067</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.085</v>
+        <v>0.081</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.083</v>
+        <v>0.066</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.208</v>
+        <v>0.194</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.913</v>
+        <v>0.872</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.079</v>
+        <v>0.066</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,34 +7744,34 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.67</v>
+        <v>22.66</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="T60" s="1" t="n">
         <v>-0.057</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.078</v>
+        <v>0.084</v>
       </c>
       <c r="W60" s="1" t="n">
         <v>0.062</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.056</v>
+        <v>0.076</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.592</v>
+        <v>0.584</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>0.022</v>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.93</v>
+        <v>96.38</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.098</v>
+        <v>0.092</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.178</v>
+        <v>0.174</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.199</v>
+        <v>0.183</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.428</v>
+        <v>0.419</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.466</v>
+        <v>0.478</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.156</v>
+        <v>2.147</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.14</v>
+        <v>0.134</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/18/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/19/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>336.07</v>
+        <v>335.1</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="H5" s="1" t="n">
-        <v>0.054</v>
+        <v>0.06</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.133</v>
+        <v>0.126</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.902</v>
+        <v>0.896</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.987</v>
+        <v>0.994</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.57</v>
+        <v>3.558</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.023</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.9</v>
+        <v>58.29</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.023</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.145</v>
+        <v>0.153</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.207</v>
+        <v>0.229</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.297</v>
+        <v>0.306</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.234</v>
+        <v>0.233</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.415</v>
+        <v>0.424</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.786</v>
+        <v>1.758</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.556</v>
+        <v>1.584</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.218</v>
+        <v>0.226</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1747,22 +1747,22 @@
         <v>82.98</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AH5" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AJ5" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AL5" s="1" t="n">
         <v>0.139</v>
@@ -1771,7 +1771,7 @@
         <v>0.089</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.18</v>
+        <v>0.181</v>
       </c>
       <c r="AO5" s="1" t="n">
         <v>0.005</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>689.35</v>
+        <v>687.68</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>-0.008</v>
-      </c>
       <c r="F6" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.073</v>
+        <v>0.077</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.136</v>
+        <v>0.131</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.758</v>
+        <v>0.753</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.887</v>
+        <v>0.886</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.219</v>
+        <v>3.211</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>105.49</v>
+        <v>107.03</v>
       </c>
       <c r="R6" s="1" t="n">
         <v>0.015</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.034</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.146</v>
+        <v>0.163</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.131</v>
+        <v>0.164</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.224</v>
+        <v>0.243</v>
       </c>
       <c r="W6" s="1" t="n">
         <v>0.133</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.316</v>
+        <v>0.335</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.773</v>
+        <v>1.739</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.083</v>
+        <v>2.154</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.182</v>
+        <v>0.199</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,34 +1863,34 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.92</v>
+        <v>119.96</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AH6" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.073</v>
+        <v>0.072</v>
       </c>
       <c r="AL6" s="1" t="n">
         <v>0.142</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="AO6" s="1" t="n">
         <v>0.008</v>
@@ -1904,31 +1904,31 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.67</v>
+        <v>71.66</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.023</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.139</v>
+        <v>0.138</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.127</v>
+        <v>0.133</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0.407</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.545</v>
+        <v>0.522</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>2.196</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.18</v>
+        <v>28.52</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.038</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.18</v>
+        <v>0.194</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.385</v>
+        <v>0.404</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.603</v>
+        <v>0.63</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.354</v>
+        <v>0.388</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.362</v>
+        <v>0.379</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.339</v>
+        <v>1.317</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.064</v>
+        <v>0.084</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.35</v>
+        <v>0.367</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97</v>
+        <v>97.09</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="AH7" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AI7" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="AI7" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AK7" s="1" t="n">
         <v>0.085</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.049</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>263.99</v>
+        <v>264.6</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>-0.004</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>-0.007</v>
-      </c>
       <c r="G8" s="1" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.165</v>
+        <v>0.177</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.175</v>
+        <v>0.182</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.419</v>
+        <v>0.423</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.273</v>
+        <v>0.249</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>2.007</v>
+        <v>1.999</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.072</v>
+        <v>0.075</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.03</v>
+        <v>18.81</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.023</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.155</v>
+        <v>0.145</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.708</v>
+        <v>0.682</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.27</v>
+        <v>-0.293</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.748</v>
+        <v>1.742</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.158</v>
+        <v>0.145</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.7</v>
+        <v>103.82</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="AK8" s="1" t="n">
         <v>0.076</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.181</v>
+        <v>-0.172</v>
       </c>
       <c r="AN8" s="1" t="n">
         <v>-0.037</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.14</v>
+        <v>26.37</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.009</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.09</v>
+        <v>0.098</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.146</v>
+        <v>0.156</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.283</v>
+        <v>0.294</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.238</v>
+        <v>1.249</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.481</v>
+        <v>1.576</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.111</v>
+        <v>0.121</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.53</v>
+        <v>89.62</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.014</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.277</v>
+        <v>-0.267</v>
       </c>
       <c r="AN9" s="1" t="n">
         <v>-0.102</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>182.88</v>
+        <v>182.59</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.002</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.01</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.079</v>
+        <v>0.077</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.288</v>
+        <v>0.279</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.271</v>
+        <v>0.269</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.308</v>
+        <v>0.319</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.724</v>
+        <v>0.684</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.254</v>
+        <v>2.281</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.188</v>
+        <v>0.186</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.16</v>
+        <v>111.25</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AJ10" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.066</v>
+        <v>0.072</v>
       </c>
       <c r="AN10" s="1" t="n">
         <v>0.328</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>224.31</v>
+        <v>223.97</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>0.114</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.142</v>
+        <v>0.136</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.167</v>
+        <v>0.162</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.503</v>
+        <v>0.501</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.713</v>
+        <v>0.702</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.032</v>
+        <v>2.033</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.63</v>
+        <v>60.2</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.007</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.008</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.079</v>
+        <v>0.071</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.362</v>
+        <v>0.346</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.542</v>
+        <v>0.531</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.664</v>
+        <v>0.684</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.523</v>
+        <v>0.512</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.821</v>
+        <v>0.765</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.611</v>
+        <v>4.543</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.181</v>
+        <v>0.173</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,10 +2410,10 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>102.9</v>
+        <v>102.97</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ11" s="1" t="n">
         <v>0.016</v>
@@ -2431,16 +2431,16 @@
         <v>0.053</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="AN11" s="1" t="n">
         <v>0.371</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>452.17</v>
+        <v>450.74</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.004</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.042</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.028</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.009</v>
+        <v>0.02</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.09</v>
+        <v>0.087</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.954</v>
+        <v>0.948</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.85</v>
+        <v>0.856</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.327</v>
+        <v>4.302</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.048</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>88.7</v>
+        <v>90.3</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.026</v>
+        <v>0.018</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.068</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.067</v>
+        <v>0.086</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.366</v>
+        <v>0.379</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.798</v>
+        <v>0.884</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.584</v>
+        <v>1.627</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.207</v>
+        <v>3.283</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.546</v>
+        <v>2.64</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.444</v>
+        <v>5.688</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.205</v>
+        <v>0.226</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.31</v>
+        <v>108.46</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.12</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.236</v>
+        <v>0.238</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>203.49</v>
+        <v>203.03</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="G13" s="1" t="n">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.088</v>
+        <v>0.089</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.728</v>
+        <v>0.724</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.814</v>
+        <v>0.816</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.83</v>
+        <v>2.825</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.85</v>
+        <v>41.88</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.054</v>
+        <v>0.061</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.545</v>
+        <v>0.558</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.083</v>
+        <v>1.209</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.047</v>
+        <v>2.147</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.197</v>
+        <v>3.303</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.746</v>
+        <v>1.782</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.654</v>
+        <v>5.746</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.192</v>
+        <v>0.222</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.19</v>
+        <v>23.14</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.07</v>
+        <v>0.067</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.106</v>
+        <v>0.103</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.095</v>
+        <v>0.091</v>
       </c>
       <c r="AN13" s="1" t="n">
         <v>0.282</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,34 +2689,34 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.03</v>
+        <v>96.05</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0.388</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.789</v>
+        <v>1.787</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>0.02</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.01</v>
+        <v>52.77</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.005</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-0.038</v>
+        <v>0.001</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.074</v>
+        <v>0.07</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.442</v>
+        <v>0.419</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.729</v>
+        <v>0.738</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>0.967</v>
+        <v>1.004</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.196</v>
+        <v>0.191</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.26</v>
+        <v>76.2</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.128</v>
+        <v>0.131</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.047</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>253.49</v>
+        <v>253.3</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.012</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.041</v>
+        <v>0.052</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.839</v>
+        <v>0.837</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>0.534</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.205</v>
+        <v>3.178</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.16</v>
+        <v>17.04</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.007</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.053</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.156</v>
+        <v>0.112</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.681</v>
+        <v>0.711</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.098</v>
+        <v>0.09</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.66</v>
+        <v>97.55</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="AN15" s="1" t="n">
         <v>0.483</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.25</v>
+        <v>138.12</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.087</v>
+        <v>0.086</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.144</v>
+        <v>0.148</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.164</v>
+        <v>0.155</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.218</v>
+        <v>0.205</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.822</v>
+        <v>0.829</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.658</v>
+        <v>1.66</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>80.7</v>
+        <v>79.85</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.011</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.032</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.051</v>
+        <v>0.04</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.204</v>
+        <v>0.197</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.107</v>
+        <v>0.088</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.049</v>
+        <v>0.021</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.358</v>
+        <v>1.337</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.121</v>
+        <v>0.109</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.71</v>
+        <v>42.63</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AJ16" s="1" t="n">
         <v>0.078</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.174</v>
+        <v>0.179</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.254</v>
+        <v>0.251</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.302</v>
+        <v>0.298</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.24</v>
+        <v>148.87</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.067</v>
+        <v>0.071</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.126</v>
+        <v>0.122</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.718</v>
+        <v>0.714</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>107.78</v>
+        <v>108.94</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.011</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.015</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.061</v>
+        <v>0.073</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.187</v>
+        <v>0.199</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.194</v>
+        <v>0.206</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.413</v>
+        <v>0.455</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.381</v>
+        <v>1.406</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.427</v>
+        <v>1.398</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.218</v>
+        <v>4.255</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.164</v>
+        <v>0.177</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3113,22 +3113,22 @@
         <v>42.67</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="AH17" s="1" t="n">
         <v>0.028</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.032</v>
+        <v>0.039</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="AL17" s="1" t="n">
         <v>0.108</v>
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.64</v>
+        <v>161.1</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.014</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.149</v>
+        <v>0.146</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.154</v>
+        <v>0.161</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.617</v>
+        <v>0.621</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.682</v>
+        <v>0.67</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.674</v>
+        <v>2.691</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.084</v>
+        <v>0.087</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.38</v>
+        <v>36.66</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.064</v>
+        <v>0.073</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.236</v>
+        <v>0.239</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.295</v>
+        <v>0.307</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.455</v>
+        <v>0.461</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.166</v>
+        <v>0.175</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>56.46</v>
+        <v>56.75</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.203</v>
+        <v>0.218</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.351</v>
+        <v>0.365</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.716</v>
+        <v>0.725</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.912</v>
+        <v>0.902</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.234</v>
+        <v>2.287</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.81</v>
+        <v>81.04</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.009</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.167</v>
+        <v>0.164</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.162</v>
+        <v>0.137</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.444</v>
+        <v>0.43</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.507</v>
+        <v>0.466</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.811</v>
+        <v>1.782</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.098</v>
+        <v>0.088</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,31 +3365,31 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.86</v>
+        <v>100.88</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AI20" s="1" t="n">
         <v>0.018</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="AL20" s="1" t="n">
         <v>0.148</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AN20" s="1" t="n">
         <v>0.21</v>
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.16</v>
+        <v>36.45</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.025</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.113</v>
+        <v>0.122</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.228</v>
+        <v>0.238</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.412</v>
+        <v>0.451</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.563</v>
+        <v>0.594</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.725</v>
+        <v>0.739</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.791</v>
+        <v>0.8</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.866</v>
+        <v>1.877</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.188</v>
+        <v>0.197</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>240.32</v>
+        <v>243.49</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.001</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.185</v>
+        <v>0.199</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.231</v>
+        <v>0.265</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.563</v>
+        <v>0.587</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.11</v>
+        <v>1.138</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.593</v>
+        <v>1.569</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.909</v>
+        <v>3.988</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.119</v>
+        <v>0.134</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.56</v>
+        <v>50.6</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AJ21" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.167</v>
+        <v>0.168</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="AN21" s="1" t="n">
         <v>0.275</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.15</v>
+        <v>79.94</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.563</v>
+        <v>0.587</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.511</v>
+        <v>0.507</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.235</v>
+        <v>1.239</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.172</v>
+        <v>1.169</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.19</v>
+        <v>101.39</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.043</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.586</v>
+        <v>0.574</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.426</v>
+        <v>0.414</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.017</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.5</v>
+        <v>49.36</v>
       </c>
       <c r="AF22" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AH22" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AI22" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AO22" s="1" t="n">
         <v>0.009</v>
-      </c>
-      <c r="AI22" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AJ22" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AK22" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="AL22" s="1" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="AM22" s="1" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="AN22" s="1" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="AO22" s="1" t="n">
-        <v>0.011</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.03</v>
+        <v>38.61</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.003</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.147</v>
+        <v>0.164</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.203</v>
+        <v>0.23</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.391</v>
+        <v>0.461</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.519</v>
+        <v>0.56</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.603</v>
+        <v>0.627</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.587</v>
+        <v>0.607</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.225</v>
+        <v>2.254</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.197</v>
+        <v>0.215</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>112.1</v>
+        <v>110.3</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.019</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.197</v>
+        <v>0.178</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.031</v>
+        <v>-0.004</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.678</v>
+        <v>0.651</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.883</v>
+        <v>0.827</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4.16</v>
+        <v>4.069</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.164</v>
+        <v>0.145</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.26</v>
+        <v>96.3</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AH23" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.153</v>
+        <v>0.155</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>68.12</v>
+        <v>67.81</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.126</v>
+        <v>0.123</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.133</v>
+        <v>0.125</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.657</v>
+        <v>0.649</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.716</v>
+        <v>0.7</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.772</v>
+        <v>1.764</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.063</v>
+        <v>0.058</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.75</v>
+        <v>39.67</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.011</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.067</v>
+        <v>0.072</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.15</v>
+        <v>0.148</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.295</v>
+        <v>0.298</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.073</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,16 +3839,16 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.59</v>
+        <v>111.68</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AI24" s="1" t="n">
         <v>0.023</v>
@@ -3860,16 +3860,16 @@
         <v>0.086</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.387</v>
+        <v>0.389</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.49</v>
+        <v>46.35</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.187</v>
+        <v>0.2</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.596</v>
+        <v>0.591</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.948</v>
+        <v>0.937</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.216</v>
+        <v>2.219</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,34 +3919,34 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>88.06</v>
+        <v>88.02</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.027</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="V25" s="1" t="n">
         <v>0.048</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="X25" s="1" t="n">
         <v>0.286</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.458</v>
+        <v>1.476</v>
       </c>
       <c r="AA25" s="1" t="n">
         <v>0.032</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.38</v>
+        <v>93.29</v>
       </c>
       <c r="AF25" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG25" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG25" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AJ25" s="1" t="n">
         <v>0.032</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.256</v>
+        <v>0.255</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.269</v>
+        <v>0.272</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.636</v>
+        <v>0.631</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.88</v>
+        <v>47.68</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.009</v>
+        <v>0.014</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.157</v>
+        <v>0.165</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.182</v>
+        <v>0.177</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.647</v>
+        <v>0.64</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.882</v>
+        <v>0.876</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.342</v>
+        <v>1.335</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.089</v>
+        <v>0.084</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>61.53</v>
+        <v>61.22</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.005</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.073</v>
+        <v>0.075</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="W26" s="1" t="n">
         <v>0.069</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.495</v>
+        <v>0.487</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.377</v>
+        <v>0.343</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.936</v>
+        <v>0.911</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.62</v>
+        <v>26.7</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.191</v>
+        <v>0.194</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.03</v>
+        <v>46.91</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.083</v>
+        <v>0.085</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.085</v>
+        <v>0.076</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.2</v>
+        <v>0.214</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.365</v>
+        <v>0.362</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.607</v>
+        <v>0.595</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.7</v>
+        <v>1.691</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.73</v>
+        <v>26.6</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="S27" s="1" t="n">
         <v>-0.008</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.102</v>
+        <v>0.087</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,7 +4188,7 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.11</v>
+        <v>53.13</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>0.002</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>0.016</v>
@@ -4206,16 +4206,16 @@
         <v>0.029</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.07</v>
+        <v>0.069</v>
       </c>
       <c r="AL27" s="1" t="n">
         <v>0.195</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>0.008</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.12</v>
+        <v>43.88</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.116</v>
+        <v>0.111</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.216</v>
+        <v>0.237</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.677</v>
+        <v>0.668</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.531</v>
+        <v>0.518</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.346</v>
+        <v>1.341</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.11</v>
+        <v>75.04</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.113</v>
+        <v>0.118</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.088</v>
+        <v>0.074</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.136</v>
+        <v>0.125</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.425</v>
+        <v>0.435</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.679</v>
+        <v>1.678</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,13 +4307,13 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.33</v>
+        <v>54.36</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AH28" s="1" t="n">
         <v>0.012</v>
@@ -4322,22 +4322,22 @@
         <v>0.022</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="AK28" s="1" t="n">
         <v>0.098</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.231</v>
+        <v>0.232</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.073</v>
+        <v>0.078</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.26</v>
+        <v>64.16</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.182</v>
+        <v>0.169</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.276</v>
+        <v>0.285</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.521</v>
+        <v>0.519</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.586</v>
+        <v>0.59</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.77</v>
+        <v>1.765</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.072</v>
+        <v>0.07</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.034</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.032</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.1</v>
+        <v>0.137</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.187</v>
+        <v>0.236</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.152</v>
+        <v>0.19</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.226</v>
+        <v>0.263</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.128</v>
+        <v>0.166</v>
       </c>
       <c r="Y29" s="1" t="n">
         <v>0.347</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.595</v>
+        <v>1.744</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.179</v>
+        <v>0.22</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.41</v>
+        <v>51.48</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.087</v>
+        <v>0.088</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.076</v>
+        <v>-0.065</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.387</v>
+        <v>0.392</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>103.89</v>
+        <v>103.68</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.22</v>
+        <v>0.227</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.642</v>
+        <v>0.639</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.165</v>
+        <v>0.153</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.664</v>
+        <v>1.666</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.105</v>
+        <v>0.103</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.01</v>
+        <v>49.97</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.069</v>
+        <v>0.063</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.402</v>
+        <v>0.411</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.834</v>
+        <v>0.83</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.64</v>
+        <v>24.58</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.009</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.277</v>
+        <v>0.274</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.274</v>
+        <v>0.279</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.729</v>
+        <v>0.725</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.19</v>
+        <v>20.34</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.063</v>
+        <v>0.071</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.142</v>
+        <v>0.154</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.193</v>
+        <v>0.207</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.304</v>
+        <v>0.323</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.496</v>
+        <v>0.507</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.671</v>
+        <v>0.688</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.224</v>
+        <v>1.272</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.84</v>
+        <v>65.73</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.158</v>
+        <v>0.15</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.097</v>
+        <v>0.082</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.232</v>
+        <v>0.23</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.374</v>
+        <v>0.385</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.75</v>
+        <v>1.744</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.91</v>
+        <v>80.94</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH31" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AJ31" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.296</v>
+        <v>0.297</v>
       </c>
       <c r="AM31" s="1" t="n">
         <v>0.211</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>39.12</v>
+        <v>38.13</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.034</v>
+        <v>0.008</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="H32" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>0.047</v>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>1.449</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>0.074</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.3</v>
+        <v>46.24</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.055</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.094</v>
+        <v>-0.11</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.111</v>
       </c>
       <c r="Y32" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.285</v>
+        <v>1.289</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.035</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,7 +4783,7 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.71</v>
+        <v>29.75</v>
       </c>
       <c r="AF32" s="1" t="n">
         <v>0.001</v>
@@ -4792,28 +4792,28 @@
         <v>0.003</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AI32" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="AK32" s="1" t="n">
         <v>0.093</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.293</v>
+        <v>0.295</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.157</v>
+        <v>1.15</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>53.32</v>
+        <v>52.3</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.019</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.015</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.046</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.025</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.075</v>
+        <v>0.051</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.335</v>
+        <v>0.309</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.334</v>
+        <v>0.315</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.463</v>
+        <v>1.411</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.032</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>90.38</v>
+        <v>90.48</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.316</v>
+        <v>0.307</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.551</v>
+        <v>0.553</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.612</v>
+        <v>0.621</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.287</v>
+        <v>1.281</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.065</v>
+        <v>0.067</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.25</v>
+        <v>48.27</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AH33" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.38</v>
+        <v>91.2</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.023</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.069</v>
+        <v>0.067</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.363</v>
+        <v>0.37</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.751</v>
+        <v>0.747</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.454</v>
+        <v>0.442</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.568</v>
+        <v>1.575</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>174.76</v>
+        <v>175.03</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
       <c r="V34" s="1" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="W34" s="1" t="n">
         <v>0.265</v>
       </c>
-      <c r="W34" s="1" t="n">
-        <v>0.278</v>
-      </c>
       <c r="X34" s="1" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.075</v>
+        <v>0.067</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.074</v>
+        <v>1.058</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.1</v>
+        <v>105.26</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AI34" s="1" t="n">
         <v>0.082</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.137</v>
+        <v>0.148</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.199</v>
+        <v>0.208</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.516</v>
+        <v>0.519</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.131</v>
+        <v>0.118</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.523</v>
+        <v>2.594</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.068</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.95</v>
+        <v>60.72</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.002</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.007</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.154</v>
+        <v>0.155</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.313</v>
+        <v>0.308</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.284</v>
+        <v>-0.292</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.912</v>
+        <v>0.893</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.45</v>
+        <v>59.12</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.006</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.014</v>
+        <v>0.031</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.044</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.044</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.043</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.085</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.125</v>
+        <v>0.119</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.066</v>
+        <v>0.072</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.26</v>
+        <v>2.229</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.049</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.56</v>
+        <v>23.58</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.011</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.101</v>
+        <v>0.112</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.289</v>
+        <v>0.29</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.883</v>
+        <v>0.873</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.75</v>
+        <v>30</v>
       </c>
       <c r="R36" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.028</v>
+        <v>0.043</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.138</v>
+        <v>0.163</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.313</v>
+        <v>0.338</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.31</v>
+        <v>0.322</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.197</v>
+        <v>0.207</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.385</v>
+        <v>-0.393</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.136</v>
+        <v>0.145</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>72.98</v>
+        <v>72.67</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.084</v>
+        <v>0.079</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.218</v>
+        <v>0.216</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.251</v>
+        <v>0.265</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.436</v>
+        <v>0.431</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.998</v>
+        <v>0.99</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.803</v>
+        <v>0.782</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.767</v>
+        <v>3.795</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>125.8</v>
+        <v>124.76</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.039</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.041</v>
+        <v>0.028</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.069</v>
+        <v>0.062</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.635</v>
+        <v>0.621</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.918</v>
+        <v>0.888</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.796</v>
+        <v>2.759</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.032</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>93.85</v>
+        <v>94.12</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.088</v>
+        <v>0.091</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.224</v>
+        <v>0.226</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.493</v>
+        <v>0.506</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.695</v>
+        <v>0.698</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.687</v>
+        <v>1.695</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.775</v>
+        <v>1.771</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.927</v>
+        <v>2.968</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.156</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>132.93</v>
+        <v>135.21</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.018</v>
+        <v>0.034</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.185</v>
+        <v>0.205</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.484</v>
+        <v>0.527</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.867</v>
+        <v>0.935</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.366</v>
+        <v>1.372</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.345</v>
+        <v>1.385</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.611</v>
+        <v>0.613</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.425</v>
+        <v>2.502</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.367</v>
+        <v>0.391</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>65.33</v>
+        <v>64.92</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.182</v>
+        <v>0.163</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.139</v>
+        <v>0.131</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.438</v>
+        <v>0.429</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.561</v>
+        <v>0.508</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.953</v>
+        <v>1.919</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.076</v>
+        <v>0.07</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>70.09</v>
+        <v>71.01</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.056</v>
+        <v>0.013</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>-0.085</v>
+        <v>0.048</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.135</v>
+        <v>-0.124</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.52</v>
+        <v>0.529</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.029</v>
+        <v>1.097</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.343</v>
+        <v>1.382</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.503</v>
+        <v>2.549</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>1.797</v>
+        <v>1.811</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>3.749</v>
+        <v>3.85</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.088</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.49</v>
+        <v>29.4</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.255</v>
+        <v>0.241</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.369</v>
+        <v>0.381</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.736</v>
+        <v>0.73</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.835</v>
+        <v>0.829</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.508</v>
+        <v>0.489</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.28</v>
+        <v>1.294</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.38</v>
+        <v>70.99</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.052</v>
+        <v>0.046</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.214</v>
+        <v>0.195</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.167</v>
+        <v>0.163</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.236</v>
+        <v>0.229</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.322</v>
+        <v>0.274</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.619</v>
+        <v>1.587</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.101</v>
+        <v>0.095</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>189.27</v>
+        <v>188.45</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.035</v>
+        <v>-0.004</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.038</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.099</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.353</v>
+        <v>0.341</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.558</v>
+        <v>0.578</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.103</v>
+        <v>1.108</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.224</v>
+        <v>1.214</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.588</v>
+        <v>0.578</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.077</v>
+        <v>1.075</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>75.57</v>
+        <v>75.01</v>
       </c>
       <c r="D40" s="1" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="E40" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>-0.013</v>
-      </c>
       <c r="F40" s="1" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.205</v>
+        <v>0.188</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>0.396</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.726</v>
+        <v>0.732</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.078</v>
+        <v>1.063</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.922</v>
+        <v>0.908</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.615</v>
+        <v>1.661</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.098</v>
+        <v>0.09</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>135.37</v>
+        <v>134.48</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.045</v>
+        <v>0.025</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.067</v>
+        <v>0.055</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.503</v>
+        <v>0.494</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.116</v>
+        <v>1.092</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.495</v>
+        <v>2.479</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.012</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.58</v>
+        <v>35.54</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.001</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>-0.033</v>
+        <v>0.001</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.155</v>
+        <v>0.142</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.278</v>
+        <v>0.289</v>
       </c>
       <c r="AK40" s="1" t="n">
         <v>0.234</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.47</v>
+        <v>0.415</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.575</v>
+        <v>1.577</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.31</v>
+        <v>29.37</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.174</v>
+        <v>0.181</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.111</v>
+        <v>0.123</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.191</v>
+        <v>0.211</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.425</v>
+        <v>0.426</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.507</v>
+        <v>1.518</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.91</v>
+        <v>171.21</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.01</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>0.009</v>
       </c>
-      <c r="T41" s="1" t="n">
-        <v>-0.091</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>0.025</v>
-      </c>
       <c r="V41" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.097</v>
+        <v>0.087</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.732</v>
+        <v>0.715</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.109</v>
+        <v>1.071</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.849</v>
+        <v>4.755</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.045</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.35</v>
+        <v>73.22</v>
       </c>
       <c r="D42" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E42" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>-0.006</v>
-      </c>
       <c r="F42" s="1" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.647</v>
+        <v>0.644</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.498</v>
+        <v>0.488</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.625</v>
+        <v>1.629</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.093</v>
+        <v>0.091</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.89</v>
+        <v>23.84</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.002</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.045</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.182</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.174</v>
+        <v>-0.171</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.284</v>
+        <v>-0.271</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.283</v>
+        <v>-0.272</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.502</v>
+        <v>-0.507</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.188</v>
+        <v>-0.19</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.34</v>
+        <v>104.05</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>0.145</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.154</v>
+        <v>0.15</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.618</v>
+        <v>0.614</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.603</v>
+        <v>0.594</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.607</v>
+        <v>1.603</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.087</v>
+        <v>0.084</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>192.48</v>
+        <v>191.64</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="S43" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="T43" s="1" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="U43" s="1" t="n">
         <v>-0.015</v>
       </c>
-      <c r="T43" s="1" t="n">
-        <v>-0.037</v>
-      </c>
-      <c r="U43" s="1" t="n">
-        <v>-0.004</v>
-      </c>
       <c r="V43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.062</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.281</v>
+        <v>1.271</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.141</v>
+        <v>1.132</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.323</v>
+        <v>7.262</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.04</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>52.99</v>
+        <v>53.92</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.042</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.009</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.27</v>
+        <v>0.252</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.416</v>
+        <v>0.529</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>0.969</v>
+        <v>1.063</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.739</v>
+        <v>1.787</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.601</v>
+        <v>2.548</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.849</v>
+        <v>4.956</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.24</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.59</v>
+        <v>44.51</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.138</v>
+        <v>0.133</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.172</v>
+        <v>0.168</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.246</v>
+        <v>0.258</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.684</v>
+        <v>0.681</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.301</v>
+        <v>2.31</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>82</v>
+        <v>81.78</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.01</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.168</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.215</v>
+        <v>-0.213</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.251</v>
+        <v>-0.233</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.24</v>
+        <v>-0.228</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.682</v>
+        <v>3.605</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.224</v>
+        <v>-0.226</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>79.4</v>
+        <v>81.19</v>
       </c>
       <c r="AF44" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AG44" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AH44" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AI44" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AJ44" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="AK44" s="1" t="n">
         <v>0.048</v>
       </c>
-      <c r="AG44" s="1" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="AH44" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="AI44" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AJ44" s="1" t="n">
-        <v>0.085</v>
-      </c>
-      <c r="AK44" s="1" t="n">
-        <v>0.032</v>
-      </c>
       <c r="AL44" s="1" t="n">
-        <v>0.185</v>
+        <v>0.211</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.972</v>
+        <v>1.046</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.146</v>
+        <v>0.187</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.148</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>61.19</v>
+        <v>61.04</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.236</v>
+        <v>0.243</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.661</v>
+        <v>0.656</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.203</v>
+        <v>0.192</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.514</v>
+        <v>1.52</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.93</v>
+        <v>76.5</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.01</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.037</v>
       </c>
       <c r="U45" s="1" t="n">
+        <v>-0.072</v>
+      </c>
+      <c r="V45" s="1" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="W45" s="1" t="n">
         <v>-0.066</v>
       </c>
-      <c r="V45" s="1" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="W45" s="1" t="n">
-        <v>-0.069</v>
-      </c>
       <c r="X45" s="1" t="n">
-        <v>0.639</v>
+        <v>0.63</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.284</v>
+        <v>0.269</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.918</v>
+        <v>2.831</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.048</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.27</v>
+        <v>34.01</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.047</v>
+        <v>0.022</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.115</v>
+        <v>0.14</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.119</v>
+        <v>0.17</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.122</v>
+        <v>0.158</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.071</v>
+        <v>0.089</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.216</v>
+        <v>0.244</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.108</v>
+        <v>1.182</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.109</v>
+        <v>2.23</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.175</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.36</v>
+        <v>33.38</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.009</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>0.158</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.172</v>
+        <v>0.176</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>357.92</v>
+        <v>355.84</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.012</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.294</v>
+        <v>0.265</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.442</v>
+        <v>0.457</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.59</v>
+        <v>0.554</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.641</v>
+        <v>1.626</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.619</v>
+        <v>1.543</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.565</v>
+        <v>13.417</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.189</v>
+        <v>0.182</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.87</v>
+        <v>11.8</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.051</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>0.149</v>
+        <v>0.142</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.165</v>
+        <v>-0.197</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.03</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.433</v>
+        <v>-0.478</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.618</v>
+        <v>-0.62</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.73</v>
+        <v>-0.736</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.891</v>
+        <v>-0.889</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.94</v>
+        <v>48.76</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.238</v>
+        <v>0.246</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.517</v>
+        <v>0.512</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.512</v>
+        <v>0.506</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.627</v>
+        <v>1.641</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.77</v>
+        <v>124.33</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.004</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.006</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.047</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.058</v>
+        <v>0.074</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.385</v>
+        <v>1.376</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.031</v>
+        <v>1.028</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.811</v>
+        <v>6.746</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.037</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>43.6</v>
+        <v>43.66</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.177</v>
+        <v>0.187</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.223</v>
+        <v>0.226</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.834</v>
+        <v>0.837</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.927</v>
+        <v>0.922</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.855</v>
+        <v>1.87</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.2</v>
+        <v>51.09</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.006</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.128</v>
+        <v>0.116</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.191</v>
+        <v>0.218</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.073</v>
+        <v>0.06</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.84</v>
+        <v>25.9</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.011</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.049</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.423</v>
+        <v>0.426</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.728</v>
+        <v>0.721</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.514</v>
+        <v>0.523</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.18</v>
+        <v>52.07</v>
       </c>
       <c r="D49" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E49" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>-0.007</v>
-      </c>
       <c r="F49" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.145</v>
+        <v>0.15</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.339</v>
+        <v>0.348</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.791</v>
+        <v>0.787</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.897</v>
+        <v>1.937</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.088</v>
+        <v>0.085</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.86</v>
+        <v>34.81</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.012</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.078</v>
+        <v>0.061</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.114</v>
+        <v>0.156</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.224</v>
+        <v>0.238</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.44</v>
+        <v>17.49</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.015</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.146</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.345</v>
+        <v>-0.343</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.18</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>38.53</v>
+        <v>38.67</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.017</v>
       </c>
       <c r="T50" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="U50" s="1" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="V50" s="1" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="W50" s="1" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="X50" s="1" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="Y50" s="1" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="Z50" s="1" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="AA50" s="1" t="n">
         <v>0.141</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="W50" s="1" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="X50" s="1" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="Y50" s="1" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="Z50" s="1" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="AA50" s="1" t="n">
-        <v>0.137</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.14</v>
+        <v>21.82</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.018</v>
+        <v>0.032</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.038</v>
+        <v>0.072</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>-0.024</v>
+        <v>0.024</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.004</v>
+        <v>0.042</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.207</v>
+        <v>-0.167</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.457</v>
+        <v>-0.439</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.335</v>
+        <v>-0.307</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.528</v>
+        <v>-0.512</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.059</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.22</v>
+        <v>52.15</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.001</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.003</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.091</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.135</v>
+        <v>-0.127</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.181</v>
+        <v>-0.165</v>
       </c>
       <c r="W51" s="1" t="n">
         <v>-0.091</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.487</v>
+        <v>1.476</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.123</v>
+        <v>-0.124</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.42</v>
+        <v>23.55</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.066</v>
+        <v>0.071</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.003</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.058</v>
+        <v>0.072</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.055</v>
+        <v>0.069</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.168</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.333</v>
+        <v>0.343</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.071</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>37.54</v>
+        <v>38.07</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.014</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.028</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.308</v>
+        <v>-0.298</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.287</v>
+        <v>-0.25</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.432</v>
+        <v>-0.407</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.303</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.244</v>
+        <v>-0.233</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.88</v>
+        <v>49.76</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.001</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.115</v>
+        <v>-0.117</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.064</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.146</v>
+        <v>-0.132</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.424</v>
+        <v>0.42</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.334</v>
+        <v>-0.341</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>2.061</v>
+        <v>2.026</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.097</v>
+        <v>-0.099</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.63</v>
+        <v>14.72</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.018</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.412</v>
+        <v>-0.408</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.38</v>
+        <v>-0.338</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.556</v>
+        <v>-0.53</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.265</v>
+        <v>-0.286</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.348</v>
+        <v>-0.344</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,31 +7107,31 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>93.39</v>
+        <v>93.35</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.01</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.116</v>
+        <v>-0.117</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.129</v>
+        <v>-0.121</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.169</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.016</v>
       </c>
       <c r="X53" s="1" t="n">
         <v>0.967</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.267</v>
+        <v>0.261</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.17</v>
+        <v>9.12</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.016</v>
+        <v>0.009</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.058</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.034</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.167</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.251</v>
+        <v>-0.264</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.105</v>
+        <v>-0.11</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.223</v>
+        <v>0.194</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.029</v>
+        <v>0.049</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>64.11</v>
+        <v>62.54</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>-0.111</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="E54" s="1" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>-0.088</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>0.035</v>
-      </c>
       <c r="H54" s="1" t="n">
-        <v>-0.074</v>
+        <v>-0.089</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.058</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.432</v>
+        <v>0.397</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.177</v>
+        <v>0.143</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.521</v>
+        <v>1.47</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.068</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>115.57</v>
+        <v>116.75</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.01</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.035</v>
+        <v>0.051</v>
       </c>
       <c r="V54" s="1" t="n">
         <v>0.077</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.158</v>
+        <v>0.165</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.474</v>
+        <v>0.489</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.69</v>
+        <v>0.731</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.616</v>
+        <v>1.659</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.067</v>
+        <v>0.077</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.69</v>
+        <v>38.91</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E55" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="E55" s="1" t="n">
-        <v>-0.006</v>
-      </c>
       <c r="F55" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.091</v>
+        <v>0.097</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.132</v>
+        <v>0.141</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.322</v>
+        <v>0.33</v>
       </c>
       <c r="K55" s="1" t="n">
         <v>0.334</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.292</v>
+        <v>0.3</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>45.61</v>
+        <v>46.11</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.011</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.051</v>
+        <v>0.063</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.085</v>
+        <v>0.087</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.175</v>
+        <v>0.182</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.461</v>
+        <v>0.477</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.704</v>
+        <v>0.749</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.698</v>
+        <v>1.745</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.068</v>
+        <v>0.08</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.26</v>
+        <v>28.98</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.042</v>
+        <v>0.007</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.07</v>
+        <v>0.097</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.247</v>
+        <v>-0.213</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.258</v>
+        <v>-0.253</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.324</v>
+        <v>-0.298</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.849</v>
+        <v>-0.845</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.972</v>
+        <v>-0.97</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.068</v>
+        <v>0.095</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.75</v>
+        <v>72.87</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.02</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.038</v>
+        <v>0.046</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.078</v>
+        <v>0.084</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.537</v>
+        <v>0.529</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.758</v>
+        <v>2.789</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.01</v>
+        <v>99.83</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.066</v>
+        <v>0.072</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.076</v>
+        <v>0.055</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.29</v>
+        <v>0.281</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.947</v>
+        <v>0.939</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>88.9</v>
+        <v>88.56</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.004</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.061</v>
+        <v>0.064</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.11</v>
+        <v>0.089</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.083</v>
+        <v>0.085</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.429</v>
+        <v>0.418</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.094</v>
+        <v>1.061</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.076</v>
+        <v>0.072</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.37</v>
+        <v>94.17</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.081</v>
+        <v>0.061</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.194</v>
+        <v>0.191</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.285</v>
+        <v>0.275</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.872</v>
+        <v>0.857</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.66</v>
+        <v>22.61</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.059</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.084</v>
+        <v>0.075</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.062</v>
+        <v>0.058</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.179</v>
+        <v>0.177</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.076</v>
+        <v>0.043</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.584</v>
+        <v>0.586</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.38</v>
+        <v>96.53</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.002</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.052</v>
+        <v>0.017</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.174</v>
+        <v>0.186</v>
       </c>
       <c r="W61" s="1" t="n">
         <v>0.183</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.419</v>
+        <v>0.422</v>
       </c>
       <c r="Y61" s="1" t="n">
         <v>0.478</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.147</v>
+        <v>2.105</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/19/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/20/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>335.1</v>
+        <v>337.83</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.023</v>
+        <v>0.008</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.06</v>
+        <v>0.074</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.126</v>
+        <v>0.14</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.896</v>
+        <v>0.912</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.994</v>
+        <v>1.011</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.558</v>
+        <v>3.595</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.015</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.29</v>
+        <v>58.06</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.229</v>
+        <v>0.239</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.306</v>
+        <v>0.29</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.233</v>
+        <v>0.217</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.424</v>
+        <v>0.419</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.758</v>
+        <v>1.747</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.584</v>
+        <v>1.574</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.226</v>
+        <v>0.222</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,19 +1744,19 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.98</v>
+        <v>82.99</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH5" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AJ5" s="1" t="n">
         <v>0.022</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>687.68</v>
+        <v>692.5</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.017</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.036</v>
+        <v>0.06</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.077</v>
+        <v>0.087</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.131</v>
+        <v>0.143</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.753</v>
+        <v>0.766</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.886</v>
+        <v>0.9</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.211</v>
+        <v>3.24</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>107.03</v>
+        <v>107.24</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="S6" s="1" t="n">
-        <v>0.034</v>
-      </c>
       <c r="T6" s="1" t="n">
-        <v>0.163</v>
+        <v>0.17</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.164</v>
+        <v>0.192</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.243</v>
+        <v>0.233</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.335</v>
+        <v>0.338</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.739</v>
+        <v>1.744</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.154</v>
+        <v>2.16</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.199</v>
+        <v>0.201</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.96</v>
+        <v>120.02</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.072</v>
+        <v>0.071</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.66</v>
+        <v>72.11</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.023</v>
+        <v>0.044</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.138</v>
+        <v>0.164</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.132</v>
+        <v>0.144</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.133</v>
+        <v>0.151</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.407</v>
+        <v>0.416</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.522</v>
+        <v>0.532</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.196</v>
+        <v>2.216</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.086</v>
+        <v>0.093</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.52</v>
+        <v>28.42</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.038</v>
+        <v>0.021</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.194</v>
+        <v>0.198</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.404</v>
+        <v>0.434</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.63</v>
+        <v>0.626</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.388</v>
+        <v>0.381</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.379</v>
+        <v>0.374</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.317</v>
+        <v>1.309</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.084</v>
+        <v>0.08</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.367</v>
+        <v>0.362</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1985,22 +1985,22 @@
         <v>97.09</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.085</v>
+        <v>0.083</v>
       </c>
       <c r="AL7" s="1" t="n">
         <v>0.117</v>
@@ -2023,31 +2023,31 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>264.6</v>
+        <v>264.61</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.008</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.137</v>
+        <v>0.159</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.177</v>
+        <v>0.181</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.182</v>
+        <v>0.193</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>0.423</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>1.999</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.81</v>
+        <v>18.91</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.005</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.063</v>
+        <v>0.079</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.145</v>
+        <v>0.185</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.682</v>
+        <v>0.672</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.293</v>
+        <v>-0.289</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.742</v>
+        <v>1.757</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.145</v>
+        <v>0.151</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.82</v>
+        <v>103.67</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.056</v>
+        <v>0.052</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.076</v>
+        <v>0.071</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.173</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.038</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.37</v>
+        <v>26.5</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.09</v>
+        <v>0.102</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.098</v>
+        <v>0.127</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.156</v>
+        <v>0.155</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.174</v>
+        <v>0.166</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.294</v>
+        <v>0.3</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.249</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.576</v>
+        <v>1.588</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.121</v>
+        <v>0.126</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.62</v>
+        <v>89.41</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.025</v>
+        <v>0.036</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.016</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.267</v>
+        <v>-0.268</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.104</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>182.59</v>
+        <v>184.09</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.085</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.279</v>
+        <v>0.321</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.269</v>
+        <v>0.275</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.319</v>
+        <v>0.333</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.437</v>
+        <v>0.448</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.684</v>
+        <v>0.698</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.281</v>
+        <v>2.307</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.186</v>
+        <v>0.196</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,31 +2291,31 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.25</v>
+        <v>111.19</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.072</v>
+        <v>0.071</v>
       </c>
       <c r="AN10" s="1" t="n">
         <v>0.328</v>
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>223.97</v>
+        <v>225.27</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.043</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.114</v>
+        <v>0.132</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.136</v>
+        <v>0.142</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.162</v>
+        <v>0.174</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.501</v>
+        <v>0.51</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.702</v>
+        <v>0.712</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.033</v>
+        <v>2.051</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.065</v>
+        <v>0.071</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.2</v>
+        <v>61.44</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.021</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.013</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.071</v>
+        <v>0.086</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.346</v>
+        <v>0.4</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.531</v>
+        <v>0.571</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.684</v>
+        <v>0.687</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.512</v>
+        <v>0.544</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.765</v>
+        <v>0.801</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.543</v>
+        <v>4.657</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.173</v>
+        <v>0.197</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,16 +2410,16 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>102.97</v>
+        <v>102.96</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>0.008</v>
@@ -2428,7 +2428,7 @@
         <v>0.016</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AL11" s="1" t="n">
         <v>0.163</v>
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>450.74</v>
+        <v>453.86</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.01</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.001</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.087</v>
+        <v>0.1</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.948</v>
+        <v>0.961</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.856</v>
+        <v>0.869</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.302</v>
+        <v>4.339</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.041</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>90.3</v>
+        <v>91.11</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.068</v>
+        <v>0.02</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.086</v>
+        <v>0.04</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.379</v>
+        <v>0.465</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.884</v>
+        <v>0.847</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.627</v>
+        <v>1.608</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.283</v>
+        <v>3.321</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.64</v>
+        <v>2.673</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.688</v>
+        <v>5.748</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.226</v>
+        <v>0.237</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,7 +2529,7 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.46</v>
+        <v>108.54</v>
       </c>
       <c r="AF12" s="1" t="n">
         <v>0.001</v>
@@ -2538,28 +2538,28 @@
         <v>0.003</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="AK12" s="1" t="n">
         <v>0.049</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.238</v>
+        <v>0.239</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>203.03</v>
+        <v>204.39</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.024</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.062</v>
+        <v>0.083</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.101</v>
+        <v>0.112</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.724</v>
+        <v>0.735</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.816</v>
+        <v>0.828</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.825</v>
+        <v>2.851</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.88</v>
+        <v>43.32</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.061</v>
+        <v>0.04</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.558</v>
+        <v>0.699</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.209</v>
+        <v>1.232</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.147</v>
+        <v>2.138</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.303</v>
+        <v>3.45</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.782</v>
+        <v>1.878</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.746</v>
+        <v>5.978</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.222</v>
+        <v>0.264</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.14</v>
+        <v>23.11</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG13" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.067</v>
+        <v>0.061</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.282</v>
+        <v>0.28</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.05</v>
+        <v>96.19</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>0.009</v>
-      </c>
       <c r="F14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.028</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.043</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.552</v>
+        <v>0.554</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.787</v>
+        <v>1.792</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.77</v>
+        <v>54.2</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.027</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.07</v>
+        <v>0.081</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.419</v>
+        <v>0.51</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.738</v>
+        <v>0.792</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.004</v>
+        <v>1.012</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.191</v>
+        <v>0.223</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.2</v>
+        <v>76.35</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.008</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.131</v>
+        <v>0.122</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.146</v>
+        <v>0.148</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.045</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>253.3</v>
+        <v>254.78</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.008</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.073</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.116</v>
+        <v>0.143</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.837</v>
+        <v>0.848</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.534</v>
+        <v>0.543</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.178</v>
+        <v>3.202</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.04</v>
+        <v>16.81</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.041</v>
+        <v>0.006</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.067</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.141</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.711</v>
+        <v>0.733</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.957</v>
+        <v>0.886</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.09</v>
+        <v>0.076</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.55</v>
+        <v>97.65</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.12</v>
+        <v>137.9</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.086</v>
+        <v>0.091</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.148</v>
+        <v>0.152</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.155</v>
+        <v>0.147</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.205</v>
+        <v>0.191</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.489</v>
+        <v>0.486</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.829</v>
+        <v>0.826</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.66</v>
+        <v>1.656</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>79.85</v>
+        <v>80.47</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.008</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.022</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.04</v>
+        <v>0.071</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.197</v>
+        <v>0.22</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.088</v>
+        <v>0.096</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.136</v>
+        <v>0.145</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.021</v>
+        <v>0.029</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.337</v>
+        <v>1.355</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.109</v>
+        <v>0.117</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.63</v>
+        <v>42.74</v>
       </c>
       <c r="AF16" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AG16" s="1" t="n">
         <v>-0.002</v>
       </c>
-      <c r="AG16" s="1" t="n">
-        <v>-0.004</v>
-      </c>
       <c r="AH16" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.179</v>
+        <v>0.175</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.251</v>
+        <v>0.255</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.298</v>
+        <v>0.302</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>148.87</v>
+        <v>149.94</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.016</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.03</v>
+        <v>0.054</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.071</v>
+        <v>0.081</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.122</v>
+        <v>0.134</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.714</v>
+        <v>0.726</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.762</v>
+        <v>0.775</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.94</v>
+        <v>110.5</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.073</v>
+        <v>0.112</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.199</v>
+        <v>0.243</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.206</v>
+        <v>0.239</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.455</v>
+        <v>0.498</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.406</v>
+        <v>1.441</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.398</v>
+        <v>1.433</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.255</v>
+        <v>4.33</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.177</v>
+        <v>0.193</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.67</v>
+        <v>42.77</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.039</v>
+        <v>0.042</v>
       </c>
       <c r="AJ17" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>-0.186</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="AO17" s="1" t="n">
         <v>0.027</v>
-      </c>
-      <c r="AK17" s="1" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="AL17" s="1" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="AM17" s="1" t="n">
-        <v>-0.188</v>
-      </c>
-      <c r="AN17" s="1" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="AO17" s="1" t="n">
-        <v>0.024</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>161.1</v>
+        <v>161.91</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.03</v>
+        <v>0.058</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.146</v>
+        <v>0.168</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.122</v>
+        <v>0.129</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.161</v>
+        <v>0.178</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.621</v>
+        <v>0.63</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.67</v>
+        <v>0.678</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.691</v>
+        <v>2.71</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.087</v>
+        <v>0.093</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.66</v>
+        <v>36.81</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.073</v>
+        <v>0.098</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.239</v>
+        <v>0.274</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.461</v>
+        <v>0.476</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>56.75</v>
+        <v>57.16</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.131</v>
+        <v>0.155</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.218</v>
+        <v>0.224</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.365</v>
+        <v>0.375</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.725</v>
+        <v>0.737</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.902</v>
+        <v>0.916</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.287</v>
+        <v>2.311</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.04</v>
+        <v>82.4</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.017</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.022</v>
+        <v>0.031</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.042</v>
+        <v>0.084</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.164</v>
+        <v>0.212</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.137</v>
+        <v>0.174</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.131</v>
+        <v>0.154</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.43</v>
+        <v>0.454</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.466</v>
+        <v>0.491</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.782</v>
+        <v>1.829</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.088</v>
+        <v>0.106</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,25 +3365,25 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.88</v>
+        <v>100.9</v>
       </c>
       <c r="AF20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AJ20" s="1" t="n">
         <v>0.039</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="AL20" s="1" t="n">
         <v>0.148</v>
@@ -3395,7 +3395,7 @@
         <v>0.21</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.45</v>
+        <v>37.08</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.122</v>
+        <v>0.127</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.238</v>
+        <v>0.283</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.451</v>
+        <v>0.469</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.594</v>
+        <v>0.608</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.739</v>
+        <v>0.769</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.8</v>
+        <v>0.831</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.877</v>
+        <v>1.927</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.197</v>
+        <v>0.218</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>243.49</v>
+        <v>243.65</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.047</v>
+        <v>0.037</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.024</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.199</v>
+        <v>0.226</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.265</v>
+        <v>0.259</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.587</v>
+        <v>0.603</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.138</v>
+        <v>1.139</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.569</v>
+        <v>1.571</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.988</v>
+        <v>3.991</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,7 +3484,7 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.6</v>
+        <v>50.66</v>
       </c>
       <c r="AF21" s="1" t="n">
         <v>0.001</v>
@@ -3493,28 +3493,28 @@
         <v>0.003</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="AJ21" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.168</v>
+        <v>0.169</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>79.94</v>
+        <v>81.23</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.016</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.22</v>
+        <v>0.254</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.33</v>
+        <v>0.353</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.587</v>
+        <v>0.594</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.507</v>
+        <v>0.532</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.239</v>
+        <v>1.276</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.169</v>
+        <v>1.204</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.153</v>
+        <v>0.172</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>101.39</v>
+        <v>102.27</v>
       </c>
       <c r="R22" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T22" s="1" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="V22" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W22" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="X22" s="1" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="Y22" s="1" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="Z22" s="1" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AA22" s="1" t="n">
         <v>-0.008</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="U22" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="V22" s="1" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="W22" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="X22" s="1" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="Y22" s="1" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="Z22" s="1" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>-0.017</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3606,13 +3606,13 @@
         <v>49.36</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="AI22" s="1" t="n">
         <v>0.016</v>
@@ -3621,7 +3621,7 @@
         <v>0.029</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.077</v>
+        <v>0.07</v>
       </c>
       <c r="AL22" s="1" t="n">
         <v>0.172</v>
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.61</v>
+        <v>39.37</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.034</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.164</v>
+        <v>0.171</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.23</v>
+        <v>0.277</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.461</v>
+        <v>0.472</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.56</v>
+        <v>0.584</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.627</v>
+        <v>0.659</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.607</v>
+        <v>0.639</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.254</v>
+        <v>2.318</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.215</v>
+        <v>0.239</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>110.3</v>
+        <v>110.91</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.006</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.023</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.022</v>
+        <v>0.051</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.178</v>
+        <v>0.185</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.029</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.116</v>
+        <v>0.119</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.651</v>
+        <v>0.66</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.827</v>
+        <v>0.837</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4.069</v>
+        <v>4.097</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,25 +3722,25 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.3</v>
+        <v>96.35</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.091</v>
+        <v>0.088</v>
       </c>
       <c r="AL23" s="1" t="n">
         <v>0.154</v>
@@ -3749,7 +3749,7 @@
         <v>0.02</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="AO23" s="1" t="n">
         <v>0.015</v>
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>67.81</v>
+        <v>68.68</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.026</v>
+        <v>0.058</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.123</v>
+        <v>0.154</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.125</v>
+        <v>0.137</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.33</v>
+        <v>0.337</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.649</v>
+        <v>0.67</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.7</v>
+        <v>0.722</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.764</v>
+        <v>1.799</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.058</v>
+        <v>0.071</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.67</v>
+        <v>39.71</v>
       </c>
       <c r="R24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S24" s="1" t="n">
         <v>-0.002</v>
       </c>
-      <c r="S24" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="T24" s="1" t="n">
-        <v>0.021</v>
+        <v>0.029</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.072</v>
+        <v>0.112</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.148</v>
+        <v>0.162</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.298</v>
+        <v>0.296</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.072</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.68</v>
+        <v>111.59</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.086</v>
+        <v>0.082</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.35</v>
+        <v>46.88</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.011</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.011</v>
+        <v>0.027</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.013</v>
+        <v>0.054</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.105</v>
+        <v>0.135</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.124</v>
+        <v>0.134</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.2</v>
+        <v>0.213</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.591</v>
+        <v>0.609</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.937</v>
+        <v>0.96</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.219</v>
+        <v>2.256</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.059</v>
+        <v>0.071</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>88.02</v>
+        <v>88.66</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.126</v>
+        <v>0.15</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.048</v>
+        <v>0.062</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.127</v>
+        <v>0.15</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.286</v>
+        <v>0.295</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.476</v>
+        <v>1.494</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,16 +3958,16 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.29</v>
+        <v>93.25</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="1" t="n">
         <v>0.02</v>
@@ -3976,13 +3976,13 @@
         <v>0.032</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.255</v>
+        <v>0.254</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.272</v>
+        <v>0.271</v>
       </c>
       <c r="AN25" s="1" t="n">
         <v>0.631</v>
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.68</v>
+        <v>48.04</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.055</v>
+        <v>0.075</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.165</v>
+        <v>0.185</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.177</v>
+        <v>0.174</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.354</v>
+        <v>0.367</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.64</v>
+        <v>0.653</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.876</v>
+        <v>0.89</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.335</v>
+        <v>1.353</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.084</v>
+        <v>0.092</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>61.22</v>
+        <v>61.46</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.015</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.075</v>
+        <v>0.104</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.047</v>
+        <v>0.054</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.069</v>
+        <v>0.087</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.487</v>
+        <v>0.493</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.911</v>
+        <v>0.918</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.7</v>
+        <v>26.66</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.074</v>
+        <v>0.072</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>46.91</v>
+        <v>47.68</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.016</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.005</v>
+        <v>0.021</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.036</v>
+        <v>0.07</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.085</v>
+        <v>0.115</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.076</v>
+        <v>0.09</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.214</v>
+        <v>0.223</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.362</v>
+        <v>0.384</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.595</v>
+        <v>0.622</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.691</v>
+        <v>1.735</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.043</v>
+        <v>0.06</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.6</v>
+        <v>27.29</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.026</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.011</v>
+        <v>0.063</v>
       </c>
       <c r="U27" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>0.049</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>0.087</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>0.029</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.023</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="1" t="n">
         <v>0.008</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>43.88</v>
+        <v>44.32</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.111</v>
+        <v>0.14</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.035</v>
+        <v>0.046</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.237</v>
+        <v>0.245</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.668</v>
+        <v>0.685</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.518</v>
+        <v>0.533</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.341</v>
+        <v>1.365</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.04</v>
+        <v>75.45</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.082</v>
+        <v>0.084</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.118</v>
+        <v>0.124</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.074</v>
+        <v>0.07</v>
       </c>
       <c r="W28" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.234</v>
+        <v>0.241</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.435</v>
+        <v>0.442</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.678</v>
+        <v>1.692</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.121</v>
+        <v>0.127</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,25 +4307,25 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.36</v>
+        <v>54.37</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="AJ28" s="1" t="n">
         <v>0.041</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="AL28" s="1" t="n">
         <v>0.232</v>
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.16</v>
+        <v>64.38</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.138</v>
+        <v>0.156</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.169</v>
+        <v>0.16</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.285</v>
+        <v>0.279</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.519</v>
+        <v>0.524</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.765</v>
+        <v>1.774</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.07</v>
+        <v>0.074</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>47.04</v>
+        <v>47.16</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.034</v>
+        <v>0.003</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.137</v>
+        <v>0.146</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.236</v>
+        <v>0.249</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.19</v>
+        <v>0.186</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.263</v>
+        <v>0.275</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.166</v>
+        <v>0.169</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.744</v>
+        <v>1.751</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.22</v>
+        <v>0.223</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.48</v>
+        <v>51.41</v>
       </c>
       <c r="AF29" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG29" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG29" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="AH29" s="1" t="n">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.088</v>
+        <v>0.083</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.065</v>
+        <v>-0.066</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>103.68</v>
+        <v>106.14</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.024</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.047</v>
+        <v>0.084</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.139</v>
+        <v>0.18</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.227</v>
+        <v>0.26</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.388</v>
+        <v>0.41</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.639</v>
+        <v>0.678</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.153</v>
+        <v>0.18</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.666</v>
+        <v>1.729</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.103</v>
+        <v>0.129</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>49.97</v>
+        <v>50.23</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.142</v>
+        <v>0.159</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.063</v>
+        <v>0.072</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.411</v>
+        <v>0.419</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.115</v>
+        <v>0.121</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4548,22 +4548,22 @@
         <v>24.58</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG30" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.005</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AJ30" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AL30" s="1" t="n">
         <v>0.274</v>
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.34</v>
+        <v>20.56</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.071</v>
+        <v>0.086</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.154</v>
+        <v>0.172</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.207</v>
+        <v>0.21</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.507</v>
+        <v>0.523</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.688</v>
+        <v>0.706</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.272</v>
+        <v>1.297</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.11</v>
+        <v>0.122</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.73</v>
+        <v>65.58</v>
       </c>
       <c r="R31" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.15</v>
+        <v>0.141</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.082</v>
+        <v>0.073</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.23</v>
+        <v>0.227</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.385</v>
+        <v>0.382</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.744</v>
+        <v>1.738</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.94</v>
+        <v>81</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG31" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="AL31" s="1" t="n">
         <v>0.297</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>38.13</v>
+        <v>38.63</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.025</v>
+        <v>0.013</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.014</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.004</v>
+        <v>0.024</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.063</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.097</v>
+        <v>0.112</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.325</v>
+        <v>0.343</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.366</v>
+        <v>1.397</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.047</v>
+        <v>0.061</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.24</v>
+        <v>46.04</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.005</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.059</v>
       </c>
       <c r="U32" s="1" t="n">
         <v>-0.01</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.108</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.111</v>
+        <v>-0.115</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.289</v>
+        <v>1.279</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.04</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4786,13 +4786,13 @@
         <v>29.75</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="AI32" s="1" t="n">
         <v>0.036</v>
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.3</v>
+        <v>53.42</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.01</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.033</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.007</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.051</v>
+        <v>0.067</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.309</v>
+        <v>0.337</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.315</v>
+        <v>0.343</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.411</v>
+        <v>1.463</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.012</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>90.48</v>
+        <v>89.85</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.11</v>
+        <v>0.111</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.31</v>
+        <v>0.295</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.307</v>
+        <v>0.289</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.553</v>
+        <v>0.542</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.621</v>
+        <v>0.61</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.067</v>
+        <v>0.059</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,31 +4902,31 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.27</v>
+        <v>48.28</v>
       </c>
       <c r="AF33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="AJ33" s="1" t="n">
         <v>0.033</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="AL33" s="1" t="n">
         <v>0.17</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.2</v>
+        <v>91.47</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.025</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.067</v>
+        <v>0.093</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.173</v>
+        <v>0.194</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.182</v>
+        <v>0.192</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.575</v>
+        <v>1.583</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>175.03</v>
+        <v>174.39</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.026</v>
+        <v>0.011</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.271</v>
+        <v>0.262</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.265</v>
+        <v>0.254</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.323</v>
+        <v>0.318</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.058</v>
+        <v>1.051</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.26</v>
+        <v>105.05</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.082</v>
+        <v>0.101</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="AK34" s="1" t="n">
         <v>0.208</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.519</v>
+        <v>0.516</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.594</v>
+        <v>2.587</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.07</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.72</v>
+        <v>61.01</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.01</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.014</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>0.031</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.155</v>
+        <v>0.14</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.308</v>
+        <v>0.314</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.292</v>
+        <v>-0.289</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.893</v>
+        <v>0.902</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.12</v>
+        <v>59.36</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.033</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.028</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.05</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.081</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.072</v>
+        <v>0.077</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.229</v>
+        <v>2.242</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.045</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.58</v>
+        <v>23.76</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.046</v>
+        <v>0.065</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.112</v>
+        <v>0.133</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.154</v>
+        <v>0.159</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.873</v>
+        <v>0.887</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.11</v>
+        <v>0.118</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>29.63</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.043</v>
+        <v>0.02</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.057</v>
+        <v>0.038</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.163</v>
+        <v>0.154</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.338</v>
+        <v>0.323</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.322</v>
+        <v>0.299</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.207</v>
+        <v>0.192</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.393</v>
+        <v>-0.4</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.145</v>
+        <v>0.131</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>72.67</v>
+        <v>74.38</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.024</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.079</v>
+        <v>0.118</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.216</v>
+        <v>0.261</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.265</v>
+        <v>0.324</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.431</v>
+        <v>0.463</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.99</v>
+        <v>1.037</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.782</v>
+        <v>0.824</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.795</v>
+        <v>3.908</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.144</v>
+        <v>0.171</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>124.76</v>
+        <v>125.34</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="S37" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.013</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="V37" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.062</v>
+        <v>0.083</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.621</v>
+        <v>0.629</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.888</v>
+        <v>0.897</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.759</v>
+        <v>2.776</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>94.12</v>
+        <v>95.95</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.091</v>
+        <v>0.071</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.226</v>
+        <v>0.25</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.506</v>
+        <v>0.52</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.698</v>
+        <v>0.731</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.695</v>
+        <v>1.747</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.771</v>
+        <v>1.825</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.968</v>
+        <v>3.045</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.16</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>135.21</v>
+        <v>141.88</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.017</v>
+        <v>0.049</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.034</v>
+        <v>0.059</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.205</v>
+        <v>0.279</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.527</v>
+        <v>0.639</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.935</v>
+        <v>1.033</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.372</v>
+        <v>1.481</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.385</v>
+        <v>1.503</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.613</v>
+        <v>0.692</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.502</v>
+        <v>2.675</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.391</v>
+        <v>0.459</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>64.92</v>
+        <v>65.52</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.009</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.026</v>
+        <v>0.051</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.163</v>
+        <v>0.179</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.131</v>
+        <v>0.14</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.135</v>
+        <v>0.164</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.429</v>
+        <v>0.443</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.508</v>
+        <v>0.522</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.919</v>
+        <v>1.946</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>71.01</v>
+        <v>76.62</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.013</v>
+        <v>0.079</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.048</v>
+        <v>0.099</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.103</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.529</v>
+        <v>0.674</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.097</v>
+        <v>1.225</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.382</v>
+        <v>1.558</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.549</v>
+        <v>2.829</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>1.811</v>
+        <v>2.033</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>3.85</v>
+        <v>4.234</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.102</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.4</v>
+        <v>29.82</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.014</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.073</v>
+        <v>0.065</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.241</v>
+        <v>0.29</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.381</v>
+        <v>0.401</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.73</v>
+        <v>0.754</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.829</v>
+        <v>0.855</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.489</v>
+        <v>0.511</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.294</v>
+        <v>1.327</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.099</v>
+        <v>0.115</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.99</v>
+        <v>71.9</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.013</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.046</v>
+        <v>0.074</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.195</v>
+        <v>0.214</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.163</v>
+        <v>0.173</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.134</v>
+        <v>0.17</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.229</v>
+        <v>0.245</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.274</v>
+        <v>0.29</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.587</v>
+        <v>1.62</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.095</v>
+        <v>0.109</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>188.45</v>
+        <v>196.49</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.043</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.123</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.341</v>
+        <v>0.431</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.578</v>
+        <v>0.608</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.108</v>
+        <v>1.192</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.214</v>
+        <v>1.308</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.578</v>
+        <v>0.645</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.075</v>
+        <v>1.163</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.011</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>75.01</v>
+        <v>77.25</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.03</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.031</v>
+        <v>0.052</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.188</v>
+        <v>0.255</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.396</v>
+        <v>0.427</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.732</v>
+        <v>0.761</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.063</v>
+        <v>1.124</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.908</v>
+        <v>0.965</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.661</v>
+        <v>1.741</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.09</v>
+        <v>0.123</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>134.48</v>
+        <v>135.66</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.009</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.033</v>
+        <v>0.045</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.055</v>
+        <v>0.069</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.494</v>
+        <v>0.507</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.092</v>
+        <v>1.111</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.479</v>
+        <v>2.509</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.54</v>
+        <v>36.17</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.018</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.142</v>
+        <v>0.175</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.289</v>
+        <v>0.308</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.234</v>
+        <v>0.244</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.418</v>
+        <v>0.443</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.415</v>
+        <v>0.44</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.577</v>
+        <v>1.623</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.37</v>
+        <v>29.7</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.009</v>
+        <v>0.019</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.098</v>
+        <v>0.122</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.181</v>
+        <v>0.211</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.123</v>
+        <v>0.131</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.211</v>
+        <v>0.222</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.379</v>
+        <v>0.395</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.426</v>
+        <v>0.443</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.518</v>
+        <v>1.546</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.121</v>
+        <v>0.134</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>171.21</v>
+        <v>172.04</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.069</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>0.009</v>
+        <v>0.034</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.087</v>
+        <v>0.117</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.715</v>
+        <v>0.723</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.071</v>
+        <v>1.081</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.755</v>
+        <v>4.783</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.041</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.22</v>
+        <v>74.12</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.048</v>
+        <v>0.074</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.145</v>
+        <v>0.175</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.184</v>
+        <v>0.197</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.349</v>
+        <v>0.358</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.644</v>
+        <v>0.664</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.488</v>
+        <v>0.507</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.629</v>
+        <v>1.661</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.84</v>
+        <v>23.81</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.045</v>
+        <v>0.021</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.162</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.171</v>
+        <v>-0.15</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.271</v>
+        <v>-0.272</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.272</v>
+        <v>-0.267</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="Y42" s="1" t="n">
         <v>-0.507</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.191</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.05</v>
+        <v>104.9</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.045</v>
+        <v>0.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.145</v>
+        <v>0.171</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.32</v>
+        <v>0.324</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.614</v>
+        <v>0.627</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.594</v>
+        <v>0.607</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.603</v>
+        <v>1.624</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.084</v>
+        <v>0.092</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>191.64</v>
+        <v>192.93</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.009</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.02</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.062</v>
+        <v>0.077</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.152</v>
+        <v>0.165</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.271</v>
+        <v>1.286</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.132</v>
+        <v>1.146</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.262</v>
+        <v>7.318</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.034</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>53.92</v>
+        <v>54.36</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.004</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.252</v>
+        <v>0.353</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.529</v>
+        <v>0.563</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.063</v>
+        <v>1.09</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.787</v>
+        <v>1.81</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.548</v>
+        <v>2.577</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.956</v>
+        <v>5.005</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.262</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.51</v>
+        <v>44.82</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.133</v>
+        <v>0.154</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.168</v>
+        <v>0.174</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.258</v>
+        <v>0.27</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.681</v>
+        <v>0.692</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.985</v>
+        <v>0.999</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.31</v>
+        <v>2.334</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.076</v>
+        <v>0.084</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>81.78</v>
+        <v>80.78</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.024</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.158</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.213</v>
+        <v>-0.199</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.233</v>
+        <v>-0.24</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.228</v>
+        <v>-0.223</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.436</v>
+        <v>0.419</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.075</v>
+        <v>0.062</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.605</v>
+        <v>3.548</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.226</v>
+        <v>-0.236</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>81.19</v>
+        <v>80.85</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.004</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.133</v>
+        <v>0.125</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.145</v>
+        <v>0.153</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.123</v>
+        <v>0.1</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.048</v>
+        <v>0.04</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.211</v>
+        <v>0.206</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>1.046</v>
+        <v>1.038</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.187</v>
+        <v>0.182</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.174</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>61.04</v>
+        <v>62.34</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.055</v>
+        <v>0.088</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.15</v>
+        <v>0.191</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.243</v>
+        <v>0.271</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.401</v>
+        <v>0.418</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.656</v>
+        <v>0.692</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.192</v>
+        <v>0.218</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.52</v>
+        <v>1.573</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.116</v>
+        <v>0.139</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.5</v>
+        <v>74.17</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.03</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.048</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.042</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.081</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.1</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.079</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.269</v>
+        <v>0.231</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.831</v>
+        <v>2.714</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.077</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>34.01</v>
+        <v>33.88</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.004</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.17</v>
+        <v>0.175</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.158</v>
+        <v>0.135</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.089</v>
+        <v>0.081</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.244</v>
+        <v>0.239</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.182</v>
+        <v>1.173</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.23</v>
+        <v>2.217</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.201</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.38</v>
+        <v>33.52</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.032</v>
+        <v>0.048</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.158</v>
+        <v>0.184</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.176</v>
+        <v>0.183</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.097</v>
+        <v>0.102</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>355.84</v>
+        <v>359.43</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.01</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.039</v>
+        <v>0.065</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.265</v>
+        <v>0.343</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.457</v>
+        <v>0.48</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.554</v>
+        <v>0.566</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.626</v>
+        <v>1.652</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.543</v>
+        <v>1.569</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.417</v>
+        <v>13.562</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.182</v>
+        <v>0.194</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.8</v>
+        <v>12.01</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.035</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>0.142</v>
+        <v>-0.029</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.197</v>
+        <v>-0.167</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.478</v>
+        <v>-0.447</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.62</v>
+        <v>-0.613</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.736</v>
+        <v>-0.731</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.889</v>
+        <v>-0.887</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.76</v>
+        <v>49.26</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.01</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.032</v>
+        <v>0.057</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.125</v>
+        <v>0.152</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.142</v>
+        <v>0.148</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.246</v>
+        <v>0.248</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.512</v>
+        <v>0.527</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.506</v>
+        <v>0.521</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.641</v>
+        <v>1.668</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.073</v>
+        <v>0.084</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.33</v>
+        <v>125.29</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.008</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.014</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.025</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.074</v>
+        <v>0.09</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.152</v>
+        <v>0.169</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.376</v>
+        <v>1.395</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.028</v>
+        <v>1.044</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.746</v>
+        <v>6.806</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.03</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>43.66</v>
+        <v>44.23</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.08</v>
+        <v>0.102</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.187</v>
+        <v>0.215</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.226</v>
+        <v>0.232</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.58</v>
+        <v>0.587</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.837</v>
+        <v>0.861</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.922</v>
+        <v>0.947</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.87</v>
+        <v>1.908</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.107</v>
+        <v>0.121</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.09</v>
+        <v>51.25</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.016</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.218</v>
+        <v>0.24</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.246</v>
+        <v>0.269</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.716</v>
+        <v>0.721</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.9</v>
+        <v>26.03</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.029</v>
+        <v>0.04</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.034</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.426</v>
+        <v>0.433</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.721</v>
+        <v>0.73</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.523</v>
+        <v>0.531</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.07</v>
+        <v>52.56</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.009</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.036</v>
+        <v>0.057</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.15</v>
+        <v>0.175</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.155</v>
+        <v>0.161</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.348</v>
+        <v>0.359</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.787</v>
+        <v>0.804</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.57</v>
+        <v>0.585</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.937</v>
+        <v>1.965</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.085</v>
+        <v>0.096</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.81</v>
+        <v>35.17</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.01</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.035</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.061</v>
+        <v>0.116</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.156</v>
+        <v>0.185</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.238</v>
+        <v>0.269</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.49</v>
+        <v>17.62</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.001</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.146</v>
+        <v>-0.142</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.343</v>
+        <v>-0.339</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.174</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>38.67</v>
+        <v>39.03</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.145</v>
+        <v>0.164</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.213</v>
+        <v>0.262</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.288</v>
+        <v>0.298</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.385</v>
+        <v>0.398</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.712</v>
+        <v>0.728</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.366</v>
+        <v>0.379</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.792</v>
+        <v>0.809</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.141</v>
+        <v>0.151</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.82</v>
+        <v>22.17</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.032</v>
+        <v>0.016</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.022</v>
+        <v>0.057</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.072</v>
+        <v>0.102</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.024</v>
+        <v>0.058</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.167</v>
+        <v>-0.147</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.439</v>
+        <v>-0.43</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.307</v>
+        <v>-0.296</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.512</v>
+        <v>-0.504</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.093</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.15</v>
+        <v>52.14</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.091</v>
+        <v>-0.069</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.102</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.165</v>
+        <v>-0.161</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.091</v>
+        <v>-0.084</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.421</v>
+        <v>0.42</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.476</v>
+        <v>1.475</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.125</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.55</v>
+        <v>23.49</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AH51" s="1" t="n">
         <v>0.071</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.072</v>
+        <v>0.067</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.069</v>
+        <v>0.053</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.17</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.138</v>
+        <v>0.135</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.343</v>
+        <v>0.339</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.07</v>
+        <v>38.42</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.028</v>
+        <v>-0.014</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.243</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.215</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.407</v>
+        <v>-0.408</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.303</v>
+        <v>-0.314</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.233</v>
+        <v>-0.226</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.76</v>
+        <v>50.34</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.017</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.117</v>
+        <v>-0.088</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.036</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.132</v>
+        <v>-0.114</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.014</v>
+        <v>0.034</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.42</v>
+        <v>0.437</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.341</v>
+        <v>-0.334</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>2.026</v>
+        <v>2.062</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.088</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,22 +7074,22 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.72</v>
+        <v>14.89</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.036</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.408</v>
+        <v>-0.343</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.338</v>
+        <v>-0.305</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.53</v>
+        <v>-0.548</v>
       </c>
       <c r="I53" s="1" t="n">
         <v>-0.286</v>
@@ -7098,7 +7098,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.344</v>
+        <v>-0.336</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>93.35</v>
+        <v>92.92</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.117</v>
+        <v>-0.103</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.121</v>
+        <v>-0.108</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.169</v>
+        <v>-0.166</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.024</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.967</v>
+        <v>0.958</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.261</v>
+        <v>0.255</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.103</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.12</v>
+        <v>9.23</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.009</v>
+        <v>0.022</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.034</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.023</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.167</v>
+        <v>-0.168</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.264</v>
+        <v>-0.267</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.194</v>
+        <v>0.208</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.049</v>
+        <v>0.062</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>62.54</v>
+        <v>62.45</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.001</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.016</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.111</v>
+        <v>-0.078</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.084</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.056</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.397</v>
+        <v>0.395</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.143</v>
+        <v>0.141</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.47</v>
+        <v>1.466</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.069</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>116.75</v>
+        <v>117.14</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="T54" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="U54" s="1" t="n">
         <v>0.06</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>0.051</v>
-      </c>
       <c r="V54" s="1" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.165</v>
+        <v>0.169</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.489</v>
+        <v>0.494</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.731</v>
+        <v>0.737</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.659</v>
+        <v>1.667</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.077</v>
+        <v>0.081</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.91</v>
+        <v>38.84</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F55" s="1" t="n">
         <v>0.006</v>
-      </c>
-      <c r="E55" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="F55" s="1" t="n">
-        <v>-0.005</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>0.048</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
       <c r="I55" s="1" t="n">
         <v>0.141</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>46.11</v>
+        <v>46.33</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.004</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.063</v>
+        <v>0.078</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.05</v>
+        <v>0.061</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.087</v>
+        <v>0.091</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.182</v>
+        <v>0.188</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.477</v>
+        <v>0.484</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.749</v>
+        <v>0.757</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.745</v>
+        <v>1.758</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.08</v>
+        <v>0.085</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.98</v>
+        <v>28.37</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.021</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.03</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.097</v>
+        <v>-0.034</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.213</v>
+        <v>-0.281</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.253</v>
+        <v>-0.266</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.316</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.845</v>
+        <v>-0.848</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.97</v>
+        <v>-0.971</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.095</v>
+        <v>0.072</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,34 +7458,34 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.87</v>
+        <v>72.9</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.003</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.084</v>
+        <v>0.09</v>
       </c>
       <c r="X56" s="1" t="n">
         <v>0.354</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.789</v>
+        <v>2.791</v>
       </c>
       <c r="AA56" s="1" t="n">
         <v>0.035</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>99.83</v>
+        <v>100.54</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.015</v>
+        <v>0.043</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.072</v>
+        <v>0.084</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.055</v>
+        <v>0.059</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.193</v>
+        <v>0.201</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.281</v>
+        <v>0.291</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.939</v>
+        <v>0.953</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.063</v>
+        <v>0.071</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>88.56</v>
+        <v>88.89</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.089</v>
+        <v>0.087</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.085</v>
+        <v>0.078</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.265</v>
+        <v>0.269</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.418</v>
+        <v>0.423</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.061</v>
+        <v>1.068</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.072</v>
+        <v>0.076</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.17</v>
+        <v>94.88</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.017</v>
+        <v>0.044</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.074</v>
+        <v>0.086</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.063</v>
+        <v>0.066</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.191</v>
+        <v>0.2</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.275</v>
+        <v>0.285</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.857</v>
+        <v>0.871</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.064</v>
+        <v>0.072</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.61</v>
+        <v>22.64</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.035</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.078</v>
+        <v>0.083</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.075</v>
+        <v>0.069</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.177</v>
+        <v>0.178</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.586</v>
+        <v>0.588</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.53</v>
+        <v>97.08</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.001</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.094</v>
+        <v>0.132</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.144</v>
+        <v>0.176</v>
       </c>
       <c r="V61" s="1" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="W61" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="W61" s="1" t="n">
-        <v>0.183</v>
-      </c>
       <c r="X61" s="1" t="n">
-        <v>0.422</v>
+        <v>0.43</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.478</v>
+        <v>0.486</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.105</v>
+        <v>2.123</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.136</v>
+        <v>0.142</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/20/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/23/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>337.83</v>
+        <v>334.41</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.029</v>
+        <v>0.011</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.074</v>
+        <v>0.052</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.14</v>
+        <v>0.147</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.912</v>
+        <v>0.922</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.011</v>
+        <v>1.007</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.595</v>
+        <v>3.547</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.06</v>
+        <v>58.29</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.152</v>
+        <v>0.12</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.239</v>
+        <v>0.236</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.29</v>
+        <v>0.262</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.217</v>
+        <v>0.25</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.419</v>
+        <v>0.417</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.747</v>
+        <v>1.632</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.574</v>
+        <v>1.611</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,37 +1744,37 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.99</v>
+        <v>83.06</v>
       </c>
       <c r="AF5" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG5" s="1" t="n">
-        <v>-0.001</v>
-      </c>
       <c r="AH5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>692.5</v>
+        <v>685.49</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.06</v>
+        <v>0.039</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.087</v>
+        <v>0.064</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.143</v>
+        <v>0.152</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.766</v>
+        <v>0.777</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.9</v>
+        <v>0.893</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.24</v>
+        <v>3.189</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>107.24</v>
+        <v>105.81</v>
       </c>
       <c r="R6" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="S6" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="T6" s="1" t="n">
-        <v>0.17</v>
+        <v>0.116</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.192</v>
+        <v>0.167</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.233</v>
+        <v>0.181</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.128</v>
+        <v>0.149</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.338</v>
+        <v>0.296</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.744</v>
+        <v>1.551</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.16</v>
+        <v>2.139</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.201</v>
+        <v>0.185</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,16 +1863,16 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.02</v>
+        <v>120.33</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>0.011</v>
@@ -1881,19 +1881,19 @@
         <v>0.027</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.071</v>
+        <v>0.07</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.143</v>
+        <v>0.15</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>72.11</v>
+        <v>70.87</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.017</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.005</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.044</v>
+        <v>0.018</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.164</v>
+        <v>0.117</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.144</v>
+        <v>0.096</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.151</v>
+        <v>0.159</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.416</v>
+        <v>0.418</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.532</v>
+        <v>0.508</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.216</v>
+        <v>2.149</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.093</v>
+        <v>0.074</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.42</v>
+        <v>28.62</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.198</v>
+        <v>0.148</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.434</v>
+        <v>0.413</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.626</v>
+        <v>0.544</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.381</v>
+        <v>0.432</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.374</v>
+        <v>0.418</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.309</v>
+        <v>1.251</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.08</v>
+        <v>0.092</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.362</v>
+        <v>0.371</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,13 +1982,13 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.09</v>
+        <v>97.44</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH7" s="1" t="n">
         <v>0.019</v>
@@ -1997,22 +1997,22 @@
         <v>0.012</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.045</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.097</v>
+        <v>0.099</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>264.61</v>
+        <v>260.49</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.009</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.159</v>
+        <v>0.109</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.181</v>
+        <v>0.116</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.193</v>
+        <v>0.209</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.423</v>
+        <v>0.429</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.25</v>
+        <v>0.249</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.999</v>
+        <v>1.947</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.058</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.91</v>
+        <v>18.98</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.079</v>
+        <v>0.039</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.324</v>
+        <v>0.304</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.672</v>
+        <v>0.702</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.012</v>
+        <v>0.034</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.289</v>
+        <v>-0.225</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.757</v>
+        <v>1.76</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.151</v>
+        <v>0.155</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.67</v>
+        <v>104.08</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.071</v>
+        <v>0.065</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.059</v>
+        <v>0.068</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.173</v>
+        <v>-0.162</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.036</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.5</v>
+        <v>26.32</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.102</v>
+        <v>0.09</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.155</v>
+        <v>0.119</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.166</v>
+        <v>0.181</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.26</v>
+        <v>1.148</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.588</v>
+        <v>1.579</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.126</v>
+        <v>0.119</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.41</v>
+        <v>89.74</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.055</v>
+        <v>0.046</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.268</v>
+        <v>-0.258</v>
       </c>
       <c r="AN9" s="1" t="n">
         <v>-0.104</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>184.09</v>
+        <v>185.25</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.085</v>
+        <v>0.057</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.321</v>
+        <v>0.303</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.275</v>
+        <v>0.257</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.448</v>
+        <v>0.468</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.698</v>
+        <v>0.689</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.307</v>
+        <v>2.357</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.196</v>
+        <v>0.203</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.19</v>
+        <v>111.29</v>
       </c>
       <c r="AF10" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG10" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="AG10" s="1" t="n">
-        <v>-0.002</v>
-      </c>
       <c r="AH10" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.071</v>
+        <v>0.072</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.328</v>
+        <v>0.321</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>225.27</v>
+        <v>223.06</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.043</v>
+        <v>0.021</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.132</v>
+        <v>0.104</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.142</v>
+        <v>0.116</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.174</v>
+        <v>0.179</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.51</v>
+        <v>0.523</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.712</v>
+        <v>0.683</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.051</v>
+        <v>2.014</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.071</v>
+        <v>0.06</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>61.44</v>
+        <v>62.03</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.086</v>
+        <v>0.048</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.571</v>
+        <v>0.535</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.687</v>
+        <v>0.743</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.544</v>
+        <v>0.603</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.801</v>
+        <v>0.785</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.657</v>
+        <v>4.587</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.197</v>
+        <v>0.208</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,34 +2410,34 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>102.96</v>
+        <v>103.05</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ11" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="AK11" s="1" t="n">
         <v>0.052</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>0.006</v>
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>453.86</v>
+        <v>447.99</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.043</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.033</v>
+        <v>0.008</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.1</v>
+        <v>0.111</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.961</v>
+        <v>0.963</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.869</v>
+        <v>0.89</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.339</v>
+        <v>4.255</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.053</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>91.11</v>
+        <v>94.55</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.009</v>
+        <v>0.038</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.02</v>
+        <v>0.058</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.04</v>
+        <v>0.034</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.465</v>
+        <v>0.508</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.847</v>
+        <v>0.857</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.608</v>
+        <v>1.81</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.321</v>
+        <v>3.636</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.673</v>
+        <v>2.74</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.748</v>
+        <v>5.783</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.237</v>
+        <v>0.284</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,34 +2529,34 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.54</v>
+        <v>108.51</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="AO12" s="1" t="n">
         <v>0.016</v>
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>204.39</v>
+        <v>202.26</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.083</v>
+        <v>0.057</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.098</v>
+        <v>0.074</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.112</v>
+        <v>0.119</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.735</v>
+        <v>0.742</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.828</v>
+        <v>0.815</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.851</v>
+        <v>2.807</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>43.32</v>
+        <v>44.49</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.027</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.04</v>
+        <v>0.068</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.057</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.699</v>
+        <v>0.737</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.232</v>
+        <v>1.193</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.138</v>
+        <v>2.368</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.45</v>
+        <v>3.759</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.878</v>
+        <v>1.794</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.978</v>
+        <v>6.196</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.264</v>
+        <v>0.298</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.11</v>
+        <v>23.23</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.039</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.061</v>
+        <v>0.068</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.102</v>
+        <v>0.116</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.09</v>
+        <v>0.097</v>
       </c>
       <c r="AN13" s="1" t="n">
         <v>0.28</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.19</v>
+        <v>95.8</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.043</v>
+        <v>0.027</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.39</v>
+        <v>0.407</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.554</v>
+        <v>0.553</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.792</v>
+        <v>1.767</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.2</v>
+        <v>54.83</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.081</v>
+        <v>0.052</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.51</v>
+        <v>0.504</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.792</v>
+        <v>0.743</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.012</v>
+        <v>1.123</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.223</v>
+        <v>0.237</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,34 +2761,34 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.35</v>
+        <v>76.36</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="1" t="n">
         <v>-0.008</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="AI14" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.148</v>
+        <v>0.159</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.047</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
       <c r="AO14" s="1" t="n">
         <v>0.015</v>
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>254.78</v>
+        <v>249.75</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.007</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.022</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.073</v>
+        <v>0.053</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.054</v>
+        <v>0.03</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.143</v>
+        <v>0.147</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.848</v>
+        <v>0.824</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.543</v>
+        <v>0.583</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.202</v>
+        <v>3.078</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.002</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.81</v>
+        <v>17.2</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.024</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.124</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.141</v>
+        <v>0.216</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.733</v>
+        <v>0.715</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.886</v>
+        <v>0.949</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.076</v>
+        <v>0.101</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,34 +2874,34 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.65</v>
+        <v>97.71</v>
       </c>
       <c r="AF15" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="AK15" s="1" t="n">
         <v>0.132</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.337</v>
+        <v>0.331</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.484</v>
+        <v>0.478</v>
       </c>
       <c r="AO15" s="1" t="n">
         <v>0.019</v>
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>137.9</v>
+        <v>138.83</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.152</v>
+        <v>0.144</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.147</v>
+        <v>0.143</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.191</v>
+        <v>0.196</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.486</v>
+        <v>0.517</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.826</v>
+        <v>0.817</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.656</v>
+        <v>1.674</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.134</v>
+        <v>0.142</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>80.47</v>
+        <v>78.87</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.042</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.071</v>
+        <v>0.024</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.22</v>
+        <v>0.176</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.096</v>
+        <v>0.042</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.029</v>
+        <v>0.016</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.355</v>
+        <v>1.309</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.117</v>
+        <v>0.095</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.74</v>
+        <v>42.78</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.175</v>
+        <v>0.179</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.255</v>
+        <v>0.265</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.302</v>
+        <v>0.298</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.94</v>
+        <v>148.12</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.001</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.014</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.054</v>
+        <v>0.031</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.081</v>
+        <v>0.056</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.134</v>
+        <v>0.141</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.726</v>
+        <v>0.732</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.775</v>
+        <v>0.768</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.006</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>110.5</v>
+        <v>108.87</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.003</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.112</v>
+        <v>0.088</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.243</v>
+        <v>0.202</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.239</v>
+        <v>0.185</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.498</v>
+        <v>0.527</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.441</v>
+        <v>1.445</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.433</v>
+        <v>1.411</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.33</v>
+        <v>4.155</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.193</v>
+        <v>0.176</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.77</v>
+        <v>42.82</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.027</v>
+        <v>0.016</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AK17" s="1" t="n">
         <v>0.109</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.11</v>
+        <v>0.125</v>
       </c>
       <c r="AM17" s="1" t="n">
         <v>-0.186</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.049</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>161.91</v>
+        <v>158.46</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.021</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.058</v>
+        <v>0.029</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.168</v>
+        <v>0.123</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.129</v>
+        <v>0.085</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.178</v>
+        <v>0.179</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.63</v>
+        <v>0.626</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.678</v>
+        <v>0.65</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.71</v>
+        <v>2.614</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.069</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.81</v>
+        <v>36.38</v>
       </c>
       <c r="R19" s="1" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="S19" s="1" t="n">
-        <v>0.016</v>
-      </c>
       <c r="T19" s="1" t="n">
-        <v>0.098</v>
+        <v>0.074</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.274</v>
+        <v>0.233</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.32</v>
+        <v>0.277</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.476</v>
+        <v>0.494</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.18</v>
+        <v>0.166</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.16</v>
+        <v>56.95</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.044</v>
+        <v>0.021</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.155</v>
+        <v>0.139</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.224</v>
+        <v>0.196</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.375</v>
+        <v>0.392</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.737</v>
+        <v>0.769</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.916</v>
+        <v>0.908</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.311</v>
+        <v>2.318</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>82.4</v>
+        <v>80.01</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.029</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.084</v>
+        <v>0.041</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.212</v>
+        <v>0.145</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.174</v>
+        <v>0.106</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.454</v>
+        <v>0.446</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.491</v>
+        <v>0.435</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.829</v>
+        <v>1.727</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.106</v>
+        <v>0.074</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AI20" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>37.08</v>
+        <v>36.41</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.018</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.127</v>
+        <v>0.041</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.283</v>
+        <v>0.251</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.469</v>
+        <v>0.395</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.608</v>
+        <v>0.626</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.769</v>
+        <v>0.747</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.831</v>
+        <v>0.851</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.927</v>
+        <v>1.834</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.218</v>
+        <v>0.196</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>243.65</v>
+        <v>241.26</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.037</v>
+        <v>0.027</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.226</v>
+        <v>0.217</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.259</v>
+        <v>0.237</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.603</v>
+        <v>0.626</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.139</v>
+        <v>1.13</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.571</v>
+        <v>1.569</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.991</v>
+        <v>3.86</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.135</v>
+        <v>0.124</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,13 +3484,13 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.66</v>
+        <v>50.72</v>
       </c>
       <c r="AF21" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AH21" s="1" t="n">
         <v>0.013</v>
@@ -3499,22 +3499,22 @@
         <v>0.015</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.169</v>
+        <v>0.174</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.276</v>
+        <v>0.279</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>81.23</v>
+        <v>79.54</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.021</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.018</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.089</v>
+        <v>0.045</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.254</v>
+        <v>0.228</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.353</v>
+        <v>0.291</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.594</v>
+        <v>0.587</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.532</v>
+        <v>0.521</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.276</v>
+        <v>1.218</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.204</v>
+        <v>1.161</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.172</v>
+        <v>0.147</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.27</v>
+        <v>100.33</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.019</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.011</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.052</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.055</v>
+        <v>0.018</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.032</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.588</v>
+        <v>0.604</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.426</v>
+        <v>0.401</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.268</v>
+        <v>2.164</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.027</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.36</v>
+        <v>49.55</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.07</v>
+        <v>0.076</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.172</v>
+        <v>0.184</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.046</v>
+        <v>0.052</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.26</v>
+        <v>0.263</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>39.37</v>
+        <v>38.77</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.015</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.034</v>
+        <v>0.019</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.171</v>
+        <v>0.06</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.277</v>
+        <v>0.253</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.472</v>
+        <v>0.403</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.584</v>
+        <v>0.605</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.659</v>
+        <v>0.642</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.639</v>
+        <v>0.675</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.318</v>
+        <v>2.15</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.239</v>
+        <v>0.22</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>110.91</v>
+        <v>109.59</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.012</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.035</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.051</v>
+        <v>0.042</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.185</v>
+        <v>0.115</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>0.029</v>
+        <v>-0.027</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.119</v>
+        <v>0.134</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.66</v>
+        <v>0.671</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.837</v>
+        <v>0.852</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>4.097</v>
+        <v>3.899</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.152</v>
+        <v>0.138</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.35</v>
+        <v>96.56</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.088</v>
+        <v>0.085</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.154</v>
+        <v>0.163</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>68.68</v>
+        <v>68.43</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.058</v>
+        <v>0.029</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.154</v>
+        <v>0.137</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.137</v>
+        <v>0.123</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.67</v>
+        <v>0.688</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.799</v>
+        <v>1.803</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.071</v>
+        <v>0.068</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.71</v>
+        <v>39.61</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.029</v>
+        <v>-0.016</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.112</v>
+        <v>0.098</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.162</v>
+        <v>0.111</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.296</v>
+        <v>0.303</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.046</v>
+        <v>0.077</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.041</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.59</v>
+        <v>111.71</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH24" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AI24" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="AI24" s="1" t="n">
-        <v>0.021</v>
-      </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.082</v>
+        <v>0.08</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.188</v>
+        <v>0.194</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.388</v>
+        <v>0.384</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.88</v>
+        <v>46.78</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.054</v>
+        <v>0.034</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.135</v>
+        <v>0.117</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.134</v>
+        <v>0.129</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.213</v>
+        <v>0.214</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.609</v>
+        <v>0.616</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.96</v>
+        <v>0.966</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.256</v>
+        <v>2.235</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.071</v>
+        <v>0.069</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>88.66</v>
+        <v>86.81</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.021</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.012</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.023</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.15</v>
+        <v>0.088</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.062</v>
+        <v>0.021</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.295</v>
+        <v>0.333</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.209</v>
+        <v>0.201</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.494</v>
+        <v>1.396</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.25</v>
+        <v>92.99</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.032</v>
+        <v>0.027</v>
       </c>
       <c r="AK25" s="1" t="n">
         <v>0.055</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.254</v>
+        <v>0.249</v>
       </c>
       <c r="AM25" s="1" t="n">
         <v>0.271</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.631</v>
+        <v>0.622</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.04</v>
+        <v>47.89</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.075</v>
+        <v>0.051</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.185</v>
+        <v>0.161</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.174</v>
+        <v>0.16</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.653</v>
+        <v>0.661</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.89</v>
+        <v>0.861</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.353</v>
+        <v>1.401</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>61.46</v>
+        <v>59.89</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.026</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.02</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.104</v>
+        <v>0.051</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.054</v>
+        <v>0.008</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.087</v>
+        <v>0.092</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.493</v>
+        <v>0.475</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.348</v>
+        <v>0.277</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.918</v>
+        <v>0.844</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.023</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.66</v>
+        <v>26.62</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AH26" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AI26" s="1" t="n">
         <v>0.014</v>
       </c>
-      <c r="AI26" s="1" t="n">
-        <v>0.018</v>
-      </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.031</v>
+        <v>0.021</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.072</v>
+        <v>0.066</v>
       </c>
       <c r="AL26" s="1" t="n">
         <v>0.192</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.68</v>
+        <v>47.49</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.07</v>
+        <v>0.044</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.115</v>
+        <v>0.092</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.223</v>
+        <v>0.227</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.384</v>
+        <v>0.395</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.622</v>
+        <v>0.606</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.735</v>
+        <v>1.747</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.29</v>
+        <v>27.01</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.01</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.063</v>
+        <v>0.034</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.095</v>
+        <v>0.059</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.11</v>
+        <v>0.084</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,37 +4188,37 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.13</v>
+        <v>53.19</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH27" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="AK27" s="1" t="n">
         <v>0.069</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.195</v>
+        <v>0.199</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.131</v>
+        <v>0.133</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.32</v>
+        <v>43.9</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F28" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>0.042</v>
-      </c>
       <c r="G28" s="1" t="n">
-        <v>0.14</v>
+        <v>0.114</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.046</v>
+        <v>0.029</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.685</v>
+        <v>0.69</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.533</v>
+        <v>0.534</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.365</v>
+        <v>1.361</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.043</v>
+        <v>0.033</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.45</v>
+        <v>76.54</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.084</v>
+        <v>0.087</v>
       </c>
       <c r="U28" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="V28" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="W28" s="1" t="n">
         <v>0.124</v>
       </c>
-      <c r="V28" s="1" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>0.125</v>
-      </c>
       <c r="X28" s="1" t="n">
-        <v>0.241</v>
+        <v>0.264</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.442</v>
+        <v>0.5</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.692</v>
+        <v>1.712</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.127</v>
+        <v>0.144</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.37</v>
+        <v>54.5</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.232</v>
+        <v>0.241</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.405</v>
+        <v>0.406</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.38</v>
+        <v>64.31</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.07</v>
+        <v>0.057</v>
       </c>
       <c r="G29" s="1" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="H29" s="1" t="n">
         <v>0.156</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>0.16</v>
-      </c>
       <c r="I29" s="1" t="n">
-        <v>0.279</v>
+        <v>0.269</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.524</v>
+        <v>0.537</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.595</v>
+        <v>0.619</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.774</v>
+        <v>1.801</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>47.16</v>
+        <v>46.51</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.014</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.146</v>
+        <v>0.108</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.249</v>
+        <v>0.211</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.186</v>
+        <v>0.153</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.275</v>
+        <v>0.266</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.169</v>
+        <v>0.152</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.35</v>
+        <v>0.317</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.751</v>
+        <v>1.71</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.223</v>
+        <v>0.206</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.41</v>
+        <v>51.38</v>
       </c>
       <c r="AF29" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.057</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>106.14</v>
+        <v>104.87</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.084</v>
+        <v>0.046</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.18</v>
+        <v>0.166</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.26</v>
+        <v>0.223</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.678</v>
+        <v>0.686</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.18</v>
+        <v>0.198</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.729</v>
+        <v>1.705</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.129</v>
+        <v>0.115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.23</v>
+        <v>50.37</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.159</v>
+        <v>0.143</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.072</v>
+        <v>0.08</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.138</v>
+        <v>0.147</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.419</v>
+        <v>0.432</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.84</v>
+        <v>0.836</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.58</v>
+        <v>24.45</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.018</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.036</v>
+        <v>0.028</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.274</v>
+        <v>0.264</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.279</v>
+        <v>0.275</v>
       </c>
       <c r="AN30" s="1" t="n">
         <v>0.725</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.56</v>
+        <v>20.47</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.004</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.086</v>
+        <v>0.051</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.172</v>
+        <v>0.165</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.21</v>
+        <v>0.188</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.523</v>
+        <v>0.543</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.706</v>
+        <v>0.689</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.297</v>
+        <v>1.279</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.122</v>
+        <v>0.117</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.58</v>
+        <v>66.2</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.009</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.073</v>
+        <v>0.089</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.227</v>
+        <v>0.257</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.382</v>
+        <v>0.408</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.738</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>81</v>
+        <v>80.87</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="1" t="n">
         <v>0.002</v>
       </c>
-      <c r="AH31" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="AI31" s="1" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="AK31" s="1" t="n">
         <v>0.076</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.297</v>
+        <v>0.294</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.769</v>
+        <v>0.755</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>38.63</v>
+        <v>38.3</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>0.024</v>
-      </c>
       <c r="H32" s="1" t="n">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.062</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.112</v>
+        <v>0.144</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.343</v>
+        <v>0.314</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.397</v>
+        <v>1.314</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.04</v>
+        <v>45.63</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.009</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.014</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.088</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.042</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.023</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.084</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.115</v>
+        <v>-0.106</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.279</v>
+        <v>1.201</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.048</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.75</v>
+        <v>29.7</v>
       </c>
       <c r="AF32" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG32" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AH32" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.093</v>
+        <v>0.095</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.295</v>
+        <v>0.298</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.15</v>
+        <v>1.138</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>53.42</v>
+        <v>52.61</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.015</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.03</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0.067</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.337</v>
+        <v>0.347</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.343</v>
+        <v>0.335</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.463</v>
+        <v>1.45</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.027</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>89.85</v>
+        <v>91.07</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.014</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.007</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.111</v>
+        <v>0.106</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.295</v>
+        <v>0.297</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.289</v>
+        <v>0.299</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.542</v>
+        <v>0.585</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.61</v>
+        <v>0.666</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.265</v>
+        <v>1.301</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.059</v>
+        <v>0.074</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,31 +4902,31 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.28</v>
+        <v>48.31</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.17</v>
+        <v>0.174</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.47</v>
+        <v>91.39</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.026</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.093</v>
+        <v>0.081</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.194</v>
+        <v>0.168</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.372</v>
+        <v>0.383</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.753</v>
+        <v>0.768</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.447</v>
+        <v>0.452</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.583</v>
+        <v>1.58</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.133</v>
+        <v>0.132</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>174.39</v>
+        <v>175.1</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.063</v>
+        <v>0.046</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.262</v>
+        <v>0.254</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.254</v>
+        <v>0.264</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.318</v>
+        <v>0.368</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.063</v>
+        <v>0.11</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.051</v>
+        <v>1.095</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.033</v>
+        <v>0.038</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.05</v>
+        <v>104.37</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.023</v>
+        <v>0.007</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.101</v>
+        <v>0.093</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.146</v>
+        <v>0.121</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.208</v>
+        <v>0.216</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.516</v>
+        <v>0.51</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.116</v>
+        <v>0.151</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.587</v>
+        <v>2.49</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.068</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>61.01</v>
+        <v>60.76</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E35" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>-0.263</v>
+      </c>
+      <c r="L35" s="1" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>0.011</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="K35" s="1" t="n">
-        <v>-0.289</v>
-      </c>
-      <c r="L35" s="1" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="M35" s="1" t="n">
-        <v>0.016</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.36</v>
+        <v>59.54</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.012</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.049</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.051</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.072</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.123</v>
+        <v>0.146</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.077</v>
+        <v>0.094</v>
       </c>
       <c r="Z35" s="1" t="n">
         <v>2.242</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.042</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.76</v>
+        <v>23.78</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.065</v>
+        <v>0.051</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.159</v>
+        <v>0.143</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.475</v>
+        <v>0.459</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.06</v>
+        <v>0.033</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.887</v>
+        <v>0.865</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.63</v>
+        <v>30.43</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.027</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.02</v>
+        <v>0.047</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.299</v>
+        <v>0.334</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.192</v>
+        <v>0.272</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.4</v>
+        <v>-0.339</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.131</v>
+        <v>0.162</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>74.38</v>
+        <v>73.18</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.016</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.118</v>
+        <v>0.05</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.261</v>
+        <v>0.239</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.324</v>
+        <v>0.283</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.463</v>
+        <v>0.446</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.037</v>
+        <v>0.982</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.824</v>
+        <v>0.798</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.908</v>
+        <v>3.818</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.171</v>
+        <v>0.152</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>125.34</v>
+        <v>121.67</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.029</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.017</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.04</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.044</v>
+        <v>0.004</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.019</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.083</v>
+        <v>0.069</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.629</v>
+        <v>0.615</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.897</v>
+        <v>0.813</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.776</v>
+        <v>2.672</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.056</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>95.95</v>
+        <v>98.57</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.013</v>
+        <v>0.04</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.071</v>
+        <v>0.051</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.25</v>
+        <v>0.287</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.731</v>
+        <v>0.78</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.747</v>
+        <v>1.85</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.825</v>
+        <v>1.865</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.045</v>
+        <v>3.163</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.182</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>141.88</v>
+        <v>139.3</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.049</v>
+        <v>-0.018</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.059</v>
+        <v>0.04</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.279</v>
+        <v>0.181</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.639</v>
+        <v>0.596</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.033</v>
+        <v>0.938</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.481</v>
+        <v>1.473</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.503</v>
+        <v>1.473</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.692</v>
+        <v>0.7</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.675</v>
+        <v>2.594</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.459</v>
+        <v>0.433</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>65.52</v>
+        <v>62.67</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.043</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.037</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.051</v>
+        <v>-0.002</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.179</v>
+        <v>0.094</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.14</v>
+        <v>0.046</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.164</v>
+        <v>0.138</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.443</v>
+        <v>0.413</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.522</v>
+        <v>0.416</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.946</v>
+        <v>1.84</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.08</v>
+        <v>0.033</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>76.62</v>
+        <v>80.57</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.079</v>
+        <v>0.052</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.099</v>
+        <v>0.156</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.133</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.674</v>
+        <v>0.779</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.225</v>
+        <v>1.28</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.558</v>
+        <v>1.723</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.829</v>
+        <v>3.104</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.033</v>
+        <v>2.134</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.234</v>
+        <v>4.541</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.189</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.82</v>
+        <v>30.09</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.065</v>
+        <v>0.038</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.401</v>
+        <v>0.369</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.754</v>
+        <v>0.799</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.855</v>
+        <v>0.92</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.511</v>
+        <v>0.543</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.327</v>
+        <v>1.348</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.9</v>
+        <v>68.74</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.044</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.036</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.074</v>
+        <v>0.017</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.214</v>
+        <v>0.123</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.173</v>
+        <v>0.073</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.17</v>
+        <v>0.149</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.245</v>
+        <v>0.22</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.29</v>
+        <v>0.197</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.62</v>
+        <v>1.523</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.109</v>
+        <v>0.061</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>196.49</v>
+        <v>197.36</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.043</v>
+        <v>0.004</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.123</v>
+        <v>-0.218</v>
       </c>
       <c r="AI39" s="1" t="n">
         <v>0.431</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.608</v>
+        <v>0.592</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.192</v>
+        <v>1.225</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.308</v>
+        <v>1.247</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.645</v>
+        <v>0.698</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.163</v>
+        <v>1.172</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.054</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>77.25</v>
+        <v>77.89</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.052</v>
+        <v>0.02</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.255</v>
+        <v>0.267</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.427</v>
+        <v>0.397</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.761</v>
+        <v>0.785</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.124</v>
+        <v>1.185</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.965</v>
+        <v>0.986</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.741</v>
+        <v>1.781</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.123</v>
+        <v>0.132</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>135.66</v>
+        <v>134.15</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.011</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="T40" s="1" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>0.029</v>
-      </c>
       <c r="V40" s="1" t="n">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.069</v>
+        <v>0.066</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.507</v>
+        <v>0.511</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.111</v>
+        <v>1.037</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.509</v>
+        <v>2.484</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.015</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.17</v>
+        <v>35.68</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.014</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.175</v>
+        <v>0.148</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.308</v>
+        <v>0.285</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.244</v>
+        <v>0.248</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.443</v>
+        <v>0.447</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.44</v>
+        <v>0.368</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.623</v>
+        <v>1.538</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.035</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.7</v>
+        <v>29.45</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.122</v>
+        <v>0.076</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.211</v>
+        <v>0.183</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.131</v>
+        <v>0.099</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.222</v>
+        <v>0.239</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.395</v>
+        <v>0.403</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.443</v>
+        <v>0.412</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.546</v>
+        <v>1.504</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.134</v>
+        <v>0.124</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.04</v>
+        <v>167.2</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.028</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.096</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>0.034</v>
+        <v>0.001</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.042</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.117</v>
+        <v>0.107</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.723</v>
+        <v>0.712</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.081</v>
+        <v>1.005</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.783</v>
+        <v>4.68</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.068</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>74.12</v>
+        <v>73.65</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.074</v>
+        <v>0.044</v>
       </c>
       <c r="G42" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="H42" s="1" t="n">
         <v>0.175</v>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>0.197</v>
       </c>
       <c r="I42" s="1" t="n">
         <v>0.358</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.664</v>
+        <v>0.674</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.507</v>
+        <v>0.511</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.661</v>
+        <v>1.655</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.104</v>
+        <v>0.097</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.81</v>
+        <v>22.84</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.041</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.021</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.214</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.201</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.272</v>
+        <v>-0.324</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.267</v>
+        <v>-0.265</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.12</v>
+        <v>0.092</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.507</v>
+        <v>-0.506</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.191</v>
+        <v>-0.224</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.9</v>
+        <v>104.47</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.07</v>
+        <v>0.045</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.171</v>
+        <v>0.148</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.155</v>
+        <v>0.141</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.324</v>
+        <v>0.327</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.627</v>
+        <v>0.639</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.607</v>
+        <v>0.603</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.624</v>
+        <v>1.627</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.092</v>
+        <v>0.088</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>192.93</v>
+        <v>189.8</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.05</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.077</v>
+        <v>0.047</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.165</v>
+        <v>0.177</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.286</v>
+        <v>1.271</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.146</v>
+        <v>1.178</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.318</v>
+        <v>7.228</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.049</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>54.36</v>
+        <v>53.44</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.017</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.029</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.062</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.353</v>
+        <v>0.346</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.563</v>
+        <v>0.42</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.09</v>
+        <v>1.149</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.81</v>
+        <v>1.877</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.577</v>
+        <v>2.568</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.005</v>
+        <v>4.903</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.272</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.82</v>
+        <v>44.62</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.06</v>
+        <v>0.046</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.154</v>
+        <v>0.134</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.174</v>
+        <v>0.162</v>
       </c>
       <c r="I44" s="1" t="n">
         <v>0.27</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.692</v>
+        <v>0.694</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.999</v>
+        <v>0.998</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.334</v>
+        <v>2.319</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.084</v>
+        <v>0.079</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>80.78</v>
+        <v>76.94</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.048</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.07</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.158</v>
+        <v>-0.213</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.199</v>
+        <v>-0.238</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.24</v>
+        <v>-0.284</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.223</v>
+        <v>-0.234</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.419</v>
+        <v>0.353</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.062</v>
+        <v>0.054</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.548</v>
+        <v>3.325</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.236</v>
+        <v>-0.272</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>80.85</v>
+        <v>80.9</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG44" s="1" t="n">
         <v>0.061</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.153</v>
+        <v>0.167</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.1</v>
+        <v>0.084</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.04</v>
+        <v>0.074</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.206</v>
+        <v>0.219</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>1.038</v>
+        <v>0.944</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.182</v>
+        <v>0.193</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>62.34</v>
+        <v>61.65</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.011</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.02</v>
+        <v>0.009</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.088</v>
+        <v>0.044</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.191</v>
+        <v>0.178</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.271</v>
+        <v>0.235</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.418</v>
+        <v>0.406</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.692</v>
+        <v>0.694</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.218</v>
+        <v>0.235</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.573</v>
+        <v>1.537</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.139</v>
+        <v>0.127</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>74.17</v>
+        <v>70.69</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.047</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.092</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.1</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.124</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.079</v>
+        <v>-0.098</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.58</v>
+        <v>0.511</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.231</v>
+        <v>0.226</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.714</v>
+        <v>2.519</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.12</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.88</v>
+        <v>33.89</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.138</v>
+        <v>0.104</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.175</v>
+        <v>0.188</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.135</v>
+        <v>0.12</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.081</v>
+        <v>0.114</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.239</v>
+        <v>0.246</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.173</v>
+        <v>1.074</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.217</v>
+        <v>2.2</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.196</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.52</v>
+        <v>33.16</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.048</v>
+        <v>0.019</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.184</v>
+        <v>0.147</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.183</v>
+        <v>0.14</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.102</v>
+        <v>0.09</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>359.43</v>
+        <v>356.82</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.065</v>
+        <v>0.035</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.343</v>
+        <v>0.319</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.48</v>
+        <v>0.438</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.566</v>
+        <v>0.604</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.652</v>
+        <v>1.647</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.569</v>
+        <v>1.666</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.562</v>
+        <v>13.46</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.194</v>
+        <v>0.185</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>12.01</v>
+        <v>11.74</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.022</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.056</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.16</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.167</v>
+        <v>-0.199</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.014</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.447</v>
+        <v>-0.469</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.613</v>
+        <v>-0.636</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.731</v>
+        <v>-0.725</v>
       </c>
       <c r="AN46" s="1" t="n">
         <v>-0.887</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.042</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.26</v>
+        <v>49.06</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.057</v>
+        <v>0.034</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.152</v>
+        <v>0.131</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.148</v>
+        <v>0.132</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.527</v>
+        <v>0.541</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.521</v>
+        <v>0.52</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.668</v>
+        <v>1.646</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.084</v>
+        <v>0.079</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>125.29</v>
+        <v>122.84</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.052</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.09</v>
+        <v>0.053</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.169</v>
+        <v>0.179</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.395</v>
+        <v>1.375</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.044</v>
+        <v>1.055</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.806</v>
+        <v>6.661</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.049</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.23</v>
+        <v>44.19</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.215</v>
+        <v>0.199</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.232</v>
+        <v>0.216</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.587</v>
+        <v>0.595</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.861</v>
+        <v>0.886</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.947</v>
+        <v>0.92</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.908</v>
+        <v>1.909</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.25</v>
+        <v>49.92</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.026</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.022</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.043</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.159</v>
+        <v>0.123</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.24</v>
+        <v>0.188</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.269</v>
+        <v>0.283</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.721</v>
+        <v>0.684</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.064</v>
+        <v>0.097</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.064</v>
+        <v>0.036</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.03</v>
+        <v>25.97</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="AG48" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AH48" s="1" t="n">
         <v>0.009</v>
-      </c>
-      <c r="AH48" s="1" t="n">
-        <v>0.021</v>
       </c>
       <c r="AI48" s="1" t="n">
         <v>0.04</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.025</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.023</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.73</v>
+        <v>0.694</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.531</v>
+        <v>0.511</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.56</v>
+        <v>52.42</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.003</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.057</v>
+        <v>0.039</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.175</v>
+        <v>0.163</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.161</v>
+        <v>0.146</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.359</v>
+        <v>0.375</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.804</v>
+        <v>0.811</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.585</v>
+        <v>0.616</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.965</v>
+        <v>1.894</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.096</v>
+        <v>0.093</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.17</v>
+        <v>34.61</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.016</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.018</v>
+        <v>0.001</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.035</v>
+        <v>0.001</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.116</v>
+        <v>0.108</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.185</v>
+        <v>0.141</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.269</v>
+        <v>0.288</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.056</v>
+        <v>0.039</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6735,31 +6735,31 @@
         <v>17.62</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AG49" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.026</v>
+        <v>0.011</v>
       </c>
       <c r="AI49" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.142</v>
+        <v>-0.129</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.339</v>
+        <v>-0.325</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.174</v>
+        <v>-0.168</v>
       </c>
       <c r="AO49" s="1" t="n">
         <v>-0.006</v>
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.03</v>
+        <v>39.04</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.009</v>
+        <v>0</v>
       </c>
       <c r="S50" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.164</v>
+        <v>0.142</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.262</v>
+        <v>0.24</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.298</v>
+        <v>0.277</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.398</v>
+        <v>0.412</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.728</v>
+        <v>0.786</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.379</v>
+        <v>0.397</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.809</v>
+        <v>0.774</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>22.17</v>
+        <v>21.91</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.057</v>
+        <v>0.044</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.102</v>
+        <v>0.056</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.058</v>
+        <v>0.046</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.048</v>
+        <v>0.038</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.147</v>
+        <v>-0.162</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.43</v>
+        <v>-0.421</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.296</v>
+        <v>-0.317</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.504</v>
+        <v>-0.5</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.11</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.14</v>
+        <v>51.08</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.013</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.114</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.127</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.186</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.085</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.42</v>
+        <v>0.428</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.025</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.475</v>
+        <v>1.389</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.125</v>
+        <v>-0.143</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.49</v>
+        <v>23.47</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.071</v>
+        <v>0.054</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.067</v>
+        <v>0.048</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.172</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.135</v>
+        <v>0.113</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.339</v>
+        <v>0.351</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.42</v>
+        <v>36.55</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.049</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.062</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.243</v>
+        <v>-0.279</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.215</v>
+        <v>-0.238</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.408</v>
+        <v>-0.448</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.314</v>
+        <v>-0.322</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.226</v>
+        <v>-0.264</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>50.34</v>
+        <v>49.27</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.021</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.147</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.073</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.149</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.034</v>
+        <v>0.009</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.334</v>
+        <v>-0.33</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>2.062</v>
+        <v>1.965</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.108</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.89</v>
+        <v>14.05</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.056</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.09</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.343</v>
+        <v>-0.367</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.305</v>
+        <v>-0.321</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.548</v>
+        <v>-0.616</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.286</v>
+        <v>-0.293</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.336</v>
+        <v>-0.374</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.92</v>
+        <v>92.68</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.114</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.127</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.184</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.958</v>
+        <v>0.99</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.255</v>
+        <v>0.323</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.105</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.23</v>
+        <v>9.34</v>
       </c>
       <c r="AF53" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.022</v>
+        <v>0.034</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.022</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.15</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.267</v>
+        <v>-0.263</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.112</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.208</v>
+        <v>0.219</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.062</v>
+        <v>0.003</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.043</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>62.45</v>
+        <v>60.44</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.032</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.047</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>-0.124</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="H54" s="1" t="n">
+        <v>-0.131</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>-0.078</v>
       </c>
-      <c r="G54" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>-0.084</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>-0.056</v>
-      </c>
       <c r="J54" s="1" t="n">
-        <v>0.395</v>
+        <v>0.375</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.141</v>
+        <v>0.119</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.466</v>
+        <v>1.397</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.099</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>117.14</v>
+        <v>117.86</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.075</v>
+        <v>0.086</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.08</v>
+        <v>0.088</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.169</v>
+        <v>0.175</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.494</v>
+        <v>0.546</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.737</v>
+        <v>0.767</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.667</v>
+        <v>1.655</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.081</v>
+        <v>0.088</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,34 +7304,34 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.84</v>
+        <v>38.85</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.048</v>
+        <v>0.042</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.096</v>
+        <v>0.088</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.141</v>
+        <v>0.152</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.327</v>
+        <v>0.341</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.332</v>
+        <v>0.317</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.297</v>
+        <v>0.296</v>
       </c>
       <c r="M55" s="1" t="n">
         <v>0.022</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>46.33</v>
+        <v>46.68</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.078</v>
+        <v>0.097</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.061</v>
+        <v>0.067</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.091</v>
+        <v>0.101</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.188</v>
+        <v>0.196</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.484</v>
+        <v>0.537</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.757</v>
+        <v>0.791</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.758</v>
+        <v>1.745</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.085</v>
+        <v>0.093</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.37</v>
+        <v>29.44</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.006</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.281</v>
+        <v>-0.211</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.266</v>
+        <v>-0.182</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.316</v>
+        <v>-0.336</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.848</v>
+        <v>-0.844</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.971</v>
+        <v>-0.969</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.072</v>
+        <v>0.112</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.9</v>
+        <v>72.1</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.024</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.055</v>
+        <v>0.019</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.023</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.354</v>
+        <v>0.372</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.53</v>
+        <v>0.519</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.791</v>
+        <v>2.741</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,34 +7546,34 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.54</v>
+        <v>100.51</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="S57" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.084</v>
+        <v>0.067</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.059</v>
+        <v>0.045</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.062</v>
+        <v>0.07</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.201</v>
+        <v>0.23</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.291</v>
+        <v>0.275</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.953</v>
+        <v>0.935</v>
       </c>
       <c r="AA57" s="1" t="n">
         <v>0.071</v>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>88.89</v>
+        <v>89.28</v>
       </c>
       <c r="R58" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.066</v>
+        <v>0.055</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.087</v>
+        <v>0.082</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.078</v>
+        <v>0.089</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.269</v>
+        <v>0.304</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.423</v>
+        <v>0.394</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.068</v>
+        <v>1.065</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,34 +7678,34 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.88</v>
+        <v>94.89</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="S59" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.086</v>
+        <v>0.069</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.066</v>
+        <v>0.049</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.066</v>
+        <v>0.076</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.2</v>
+        <v>0.227</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.285</v>
+        <v>0.266</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.871</v>
+        <v>0.859</v>
       </c>
       <c r="AA59" s="1" t="n">
         <v>0.072</v>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.64</v>
+        <v>22.35</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.013</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.019</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.05</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.083</v>
+        <v>0.048</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.069</v>
+        <v>0.04</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.178</v>
+        <v>0.188</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.044</v>
+        <v>0.031</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.588</v>
+        <v>0.546</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.021</v>
+        <v>0.008</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>97.08</v>
+        <v>96.18</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.009</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="T61" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="U61" s="1" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="V61" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W61" s="1" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="X61" s="1" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="Y61" s="1" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="Z61" s="1" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="AA61" s="1" t="n">
         <v>0.132</v>
-      </c>
-      <c r="U61" s="1" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="V61" s="1" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="W61" s="1" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="X61" s="1" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Y61" s="1" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="Z61" s="1" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="AA61" s="1" t="n">
-        <v>0.142</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/23/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/24/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>334.41</v>
+        <v>336.88</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.007</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.013</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.147</v>
+        <v>0.162</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.922</v>
+        <v>0.959</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.007</v>
+        <v>1.005</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.547</v>
+        <v>3.565</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.018</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,34 +1705,34 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.29</v>
+        <v>58.28</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.236</v>
+        <v>0.238</v>
       </c>
       <c r="V5" s="1" t="n">
         <v>0.262</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.248</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.632</v>
+        <v>1.54</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.611</v>
+        <v>1.582</v>
       </c>
       <c r="AA5" s="1" t="n">
         <v>0.226</v>
@@ -1747,7 +1747,7 @@
         <v>83.06</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
         <v>0</v>
@@ -1756,19 +1756,19 @@
         <v>0.006</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ5" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.141</v>
+        <v>0.144</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="AN5" s="1" t="n">
         <v>0.182</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>685.49</v>
+        <v>690.51</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.007</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.064</v>
+        <v>0.072</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.152</v>
+        <v>0.166</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.777</v>
+        <v>0.809</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.893</v>
+        <v>0.886</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.189</v>
+        <v>3.2</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>105.81</v>
+        <v>106.22</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.004</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.181</v>
+        <v>0.185</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.149</v>
+        <v>0.155</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.296</v>
+        <v>0.3</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.551</v>
+        <v>1.467</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.139</v>
+        <v>2.076</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,10 +1863,10 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.33</v>
+        <v>120.27</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>0.002</v>
@@ -1875,22 +1875,22 @@
         <v>0.013</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.07</v>
+        <v>0.068</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.15</v>
+        <v>0.154</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="AO6" s="1" t="n">
         <v>0.011</v>
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>70.87</v>
+        <v>71.51</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.159</v>
+        <v>0.171</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.418</v>
+        <v>0.439</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.508</v>
+        <v>0.494</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.149</v>
+        <v>2.156</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.074</v>
+        <v>0.083</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.62</v>
+        <v>29.18</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.028</v>
+        <v>0.062</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.148</v>
+        <v>0.171</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.413</v>
+        <v>0.435</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.544</v>
+        <v>0.574</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.432</v>
+        <v>0.473</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.418</v>
+        <v>0.414</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.251</v>
+        <v>1.156</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.092</v>
+        <v>0.114</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.371</v>
+        <v>0.398</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,10 +1982,10 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.44</v>
+        <v>97.42</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="1" t="n">
         <v>0.002</v>
@@ -1994,25 +1994,25 @@
         <v>0.019</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AJ7" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.127</v>
+        <v>0.134</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.044</v>
       </c>
       <c r="AN7" s="1" t="n">
         <v>0.099</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>260.49</v>
+        <v>263.33</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.011</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.001</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.006</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.109</v>
+        <v>0.101</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.116</v>
+        <v>0.128</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.209</v>
+        <v>0.232</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.429</v>
+        <v>0.458</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.249</v>
+        <v>0.234</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.947</v>
+        <v>1.95</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.058</v>
+        <v>0.07</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.98</v>
+        <v>19.19</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.039</v>
+        <v>0.05</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.304</v>
+        <v>0.318</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.702</v>
+        <v>0.714</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.034</v>
+        <v>0.065</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.225</v>
+        <v>-0.232</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.76</v>
+        <v>1.744</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.155</v>
+        <v>0.168</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,34 +2101,34 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>104.08</v>
+        <v>104.15</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AH8" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.068</v>
+        <v>0.082</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.157</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.034</v>
       </c>
       <c r="AO8" s="1" t="n">
         <v>0.028</v>
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.32</v>
+        <v>26.85</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.02</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.09</v>
+        <v>0.112</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.119</v>
+        <v>0.141</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.181</v>
+        <v>0.206</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.297</v>
+        <v>0.324</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.148</v>
+        <v>1.143</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.579</v>
+        <v>1.665</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.119</v>
+        <v>0.141</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.74</v>
+        <v>89.9</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AG9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.003</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.258</v>
+        <v>-0.252</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.104</v>
+        <v>-0.101</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>185.25</v>
+        <v>187.09</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.057</v>
+        <v>0.067</v>
       </c>
       <c r="U10" s="1" t="n">
         <v>0.303</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.257</v>
+        <v>0.269</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.367</v>
+        <v>0.382</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.468</v>
+        <v>0.473</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.689</v>
+        <v>0.687</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.357</v>
+        <v>2.361</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,13 +2291,13 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.29</v>
+        <v>111.31</v>
       </c>
       <c r="AF10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="AG10" s="1" t="n">
-        <v>-0.001</v>
       </c>
       <c r="AH10" s="1" t="n">
         <v>0.01</v>
@@ -2309,16 +2309,16 @@
         <v>0.018</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.132</v>
+        <v>0.14</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.072</v>
+        <v>0.073</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.321</v>
+        <v>0.319</v>
       </c>
       <c r="AO10" s="1" t="n">
         <v>0.013</v>
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>223.06</v>
+        <v>224.39</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.006</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.005</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.116</v>
+        <v>0.122</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.523</v>
+        <v>0.541</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.683</v>
+        <v>0.669</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.014</v>
+        <v>2.021</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>62.03</v>
+        <v>62.86</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.023</v>
+        <v>0.054</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.048</v>
+        <v>0.062</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.403</v>
+        <v>0.399</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.535</v>
+        <v>0.556</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.743</v>
+        <v>0.777</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.603</v>
+        <v>0.672</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.587</v>
+        <v>4.81</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.208</v>
+        <v>0.224</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,16 +2410,16 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.05</v>
+        <v>103</v>
       </c>
       <c r="AF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>0.007</v>
@@ -2428,16 +2428,16 @@
         <v>0.012</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.165</v>
+        <v>0.168</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>0.006</v>
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>447.99</v>
+        <v>452.66</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.01</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.033</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.031</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.111</v>
+        <v>0.134</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.963</v>
+        <v>1.015</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.89</v>
+        <v>0.897</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.255</v>
+        <v>4.283</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.044</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>94.55</v>
+        <v>95.25</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.038</v>
+        <v>0.007</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.102</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.034</v>
+        <v>0.042</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.508</v>
+        <v>0.443</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.857</v>
+        <v>0.87</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.81</v>
+        <v>1.824</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.636</v>
+        <v>3.715</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.74</v>
+        <v>2.718</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.783</v>
+        <v>5.724</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.284</v>
+        <v>0.293</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.51</v>
+        <v>108.71</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.046</v>
+        <v>0.048</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.124</v>
+        <v>0.13</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.063</v>
+        <v>0.068</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.24</v>
+        <v>0.244</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>202.26</v>
+        <v>203.97</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.008</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.003</v>
+        <v>0.009</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.074</v>
+        <v>0.083</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.119</v>
+        <v>0.132</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.742</v>
+        <v>0.777</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.815</v>
+        <v>0.81</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.807</v>
+        <v>2.819</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.49</v>
+        <v>44.92</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.027</v>
+        <v>0.01</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.068</v>
+        <v>0.134</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.048</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.737</v>
+        <v>0.644</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.193</v>
+        <v>1.214</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.368</v>
+        <v>2.403</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.759</v>
+        <v>3.932</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.794</v>
+        <v>1.735</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.196</v>
+        <v>6.176</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.298</v>
+        <v>0.311</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.23</v>
+        <v>23.27</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.068</v>
+        <v>0.071</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.116</v>
+        <v>0.127</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.28</v>
+        <v>0.286</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>95.8</v>
+        <v>96.39</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.407</v>
+        <v>0.427</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.553</v>
+        <v>0.555</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.767</v>
+        <v>1.771</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>54.83</v>
+        <v>56.05</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.082</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.052</v>
+        <v>0.075</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.504</v>
+        <v>0.495</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.743</v>
+        <v>0.781</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.123</v>
+        <v>1.179</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.237</v>
+        <v>0.265</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,19 +2761,19 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.36</v>
+        <v>76.29</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="AJ14" s="1" t="n">
         <v>0.02</v>
@@ -2782,16 +2782,16 @@
         <v>0.126</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.159</v>
+        <v>0.167</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.048</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>249.75</v>
+        <v>252.14</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.002</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.013</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.147</v>
+        <v>0.17</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.824</v>
+        <v>0.852</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.583</v>
+        <v>0.587</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.078</v>
+        <v>3.093</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.2</v>
+        <v>17.91</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.041</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.029</v>
+        <v>0.067</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.088</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.216</v>
+        <v>0.287</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.715</v>
+        <v>0.786</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.949</v>
+        <v>1.034</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.101</v>
+        <v>0.146</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,34 +2874,34 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.71</v>
+        <v>97.65</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="AJ15" s="1" t="n">
         <v>0.063</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.331</v>
+        <v>0.34</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="AO15" s="1" t="n">
         <v>0.019</v>
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.83</v>
+        <v>139.06</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.144</v>
+        <v>0.154</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>0.143</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>0.817</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>1.674</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>0.142</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>78.87</v>
+        <v>79.12</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.003</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.021</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.176</v>
+        <v>0.184</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.144</v>
+        <v>0.161</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.309</v>
+        <v>1.315</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.095</v>
+        <v>0.099</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,19 +2993,19 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.78</v>
+        <v>42.79</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="AJ16" s="1" t="n">
         <v>0.074</v>
@@ -3014,13 +3014,13 @@
         <v>0.179</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.265</v>
+        <v>0.274</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.298</v>
+        <v>0.301</v>
       </c>
       <c r="AO16" s="1" t="n">
         <v>0.029</v>
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>148.12</v>
+        <v>149.31</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.008</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.006</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.031</v>
+        <v>0.024</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.056</v>
+        <v>0.064</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.141</v>
+        <v>0.156</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.732</v>
+        <v>0.767</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.002</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.87</v>
+        <v>110.24</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.02</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.088</v>
+        <v>0.102</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.202</v>
+        <v>0.191</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.185</v>
+        <v>0.2</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.527</v>
+        <v>0.565</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.445</v>
+        <v>1.487</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.411</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.155</v>
+        <v>4.161</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.176</v>
+        <v>0.191</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.82</v>
+        <v>42.74</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.109</v>
+        <v>0.112</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.125</v>
+        <v>0.135</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.186</v>
+        <v>-0.188</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.052</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>158.46</v>
+        <v>160.38</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.012</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.001</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.029</v>
+        <v>0.042</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.123</v>
+        <v>0.133</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.085</v>
+        <v>0.098</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.179</v>
+        <v>0.197</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.626</v>
+        <v>0.658</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.65</v>
+        <v>0.645</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.614</v>
+        <v>2.646</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.069</v>
+        <v>0.082</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.38</v>
+        <v>37</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.017</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.074</v>
+        <v>0.092</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.233</v>
+        <v>0.236</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.277</v>
+        <v>0.299</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.494</v>
+        <v>0.528</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.166</v>
+        <v>0.186</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>56.95</v>
+        <v>57.15</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.139</v>
+        <v>0.129</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.392</v>
+        <v>0.403</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.769</v>
+        <v>0.782</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.908</v>
+        <v>0.886</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.318</v>
+        <v>2.321</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.01</v>
+        <v>80.78</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.01</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.145</v>
+        <v>0.153</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.106</v>
+        <v>0.117</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.153</v>
+        <v>0.173</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.446</v>
+        <v>0.468</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.435</v>
+        <v>0.426</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.727</v>
+        <v>1.769</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.074</v>
+        <v>0.084</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,10 +3365,10 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101.1</v>
+        <v>101.09</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
         <v>0.001</v>
@@ -3377,25 +3377,25 @@
         <v>0.013</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AJ20" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.073</v>
+        <v>0.071</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.154</v>
+        <v>0.161</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.41</v>
+        <v>37.05</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.018</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.041</v>
+        <v>0.059</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.251</v>
+        <v>0.266</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.395</v>
+        <v>0.42</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.626</v>
+        <v>0.672</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.747</v>
+        <v>0.823</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.851</v>
+        <v>0.865</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.834</v>
+        <v>1.885</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.196</v>
+        <v>0.217</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>241.26</v>
+        <v>243.11</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.008</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.026</v>
+        <v>0.034</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.217</v>
+        <v>0.211</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.626</v>
+        <v>0.635</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.13</v>
+        <v>1.158</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.569</v>
+        <v>1.508</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.124</v>
+        <v>0.132</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3487,31 +3487,31 @@
         <v>50.72</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AH21" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AJ21" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.174</v>
+        <v>0.177</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.279</v>
+        <v>0.278</v>
       </c>
       <c r="AO21" s="1" t="n">
         <v>0.016</v>
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>79.54</v>
+        <v>80.37</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.01</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.005</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.228</v>
+        <v>0.231</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.291</v>
+        <v>0.304</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.587</v>
+        <v>0.614</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.521</v>
+        <v>0.551</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.218</v>
+        <v>1.223</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.161</v>
+        <v>1.18</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.147</v>
+        <v>0.159</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>100.33</v>
+        <v>101.81</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.015</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.004</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.038</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.018</v>
+        <v>0.028</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.018</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.042</v>
+        <v>0.059</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.604</v>
+        <v>0.651</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.401</v>
+        <v>0.416</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.164</v>
+        <v>2.19</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,34 +3603,34 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.55</v>
+        <v>49.59</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AH22" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="AL22" s="1" t="n">
         <v>0.184</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.263</v>
+        <v>0.265</v>
       </c>
       <c r="AO22" s="1" t="n">
         <v>0.013</v>
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.77</v>
+        <v>39.47</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.018</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.046</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.06</v>
+        <v>0.079</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.253</v>
+        <v>0.269</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.403</v>
+        <v>0.428</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.605</v>
+        <v>0.661</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.642</v>
+        <v>0.723</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.675</v>
+        <v>0.688</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.15</v>
+        <v>2.232</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.22</v>
+        <v>0.242</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>109.59</v>
+        <v>110.15</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.005</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.02</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.115</v>
+        <v>0.126</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.022</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.134</v>
+        <v>0.145</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.671</v>
+        <v>0.694</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.852</v>
+        <v>0.845</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.899</v>
+        <v>3.879</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,34 +3722,34 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.56</v>
+        <v>96.55</v>
       </c>
       <c r="AF23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="1" t="n">
         <v>0.002</v>
-      </c>
-      <c r="AG23" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="AH23" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.085</v>
+        <v>0.083</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.163</v>
+        <v>0.17</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="AO23" s="1" t="n">
         <v>0.018</v>
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>68.43</v>
+        <v>68.54</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.029</v>
+        <v>0.031</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.137</v>
+        <v>0.14</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.688</v>
+        <v>0.729</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.721</v>
+        <v>0.708</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.803</v>
+        <v>1.834</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.068</v>
+        <v>0.069</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.61</v>
+        <v>40.89</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.032</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.034</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.016</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.098</v>
+        <v>0.128</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.111</v>
+        <v>0.147</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.303</v>
+        <v>0.356</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.077</v>
+        <v>0.147</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.032</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.044</v>
+        <v>0.078</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.71</v>
+        <v>111.68</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
       <c r="AJ24" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.194</v>
+        <v>0.203</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.78</v>
+        <v>46.89</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.214</v>
+        <v>0.218</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.616</v>
+        <v>0.646</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.966</v>
+        <v>0.956</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.235</v>
+        <v>2.262</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.069</v>
+        <v>0.072</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.81</v>
+        <v>87.38</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.007</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.088</v>
+        <v>0.1</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.021</v>
+        <v>0.028</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.163</v>
+        <v>0.167</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.333</v>
+        <v>0.368</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.201</v>
+        <v>0.148</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.396</v>
+        <v>1.383</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.99</v>
+        <v>92.93</v>
       </c>
       <c r="AF25" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG25" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="AG25" s="1" t="n">
-        <v>-0.001</v>
-      </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AJ25" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.249</v>
+        <v>0.251</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.271</v>
+        <v>0.266</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.622</v>
+        <v>0.624</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.89</v>
+        <v>47.98</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.161</v>
+        <v>0.167</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.16</v>
+        <v>0.162</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.661</v>
+        <v>0.679</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.861</v>
+        <v>0.848</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.401</v>
+        <v>1.419</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.089</v>
+        <v>0.091</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>59.89</v>
+        <v>60.59</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.012</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.009</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.051</v>
+        <v>0.072</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.092</v>
+        <v>0.096</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.475</v>
+        <v>0.522</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.277</v>
+        <v>0.265</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.844</v>
+        <v>0.851</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.012</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.62</v>
+        <v>26.64</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ26" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.49</v>
+        <v>47.62</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.08</v>
+        <v>0.083</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.227</v>
+        <v>0.237</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.395</v>
+        <v>0.432</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.606</v>
+        <v>0.604</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.747</v>
+        <v>1.759</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.01</v>
+        <v>27.25</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.009</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.034</v>
+        <v>0.043</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.059</v>
+        <v>0.067</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.084</v>
+        <v>0.094</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,37 +4188,37 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.19</v>
+        <v>53.17</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>0.015</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.069</v>
+        <v>0.067</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.199</v>
+        <v>0.202</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>0.133</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>43.9</v>
+        <v>43.95</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.001</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>0.114</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.69</v>
+        <v>0.739</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.534</v>
+        <v>0.519</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.361</v>
+        <v>1.394</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.54</v>
+        <v>76.9</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.087</v>
+        <v>0.092</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.125</v>
+        <v>0.142</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.089</v>
+        <v>0.095</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.124</v>
+        <v>0.126</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.264</v>
+        <v>0.277</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.5</v>
+        <v>0.486</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.712</v>
+        <v>1.718</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.144</v>
+        <v>0.149</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.5</v>
+        <v>54.44</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AH28" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AI28" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AJ28" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AK28" s="1" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="AL28" s="1" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="AM28" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AN28" s="1" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AO28" s="1" t="n">
         <v>0.014</v>
-      </c>
-      <c r="AI28" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ28" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK28" s="1" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="AL28" s="1" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="AM28" s="1" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="AN28" s="1" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="AO28" s="1" t="n">
-        <v>0.015</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.31</v>
+        <v>64.82</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.057</v>
+        <v>0.065</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.134</v>
+        <v>0.149</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.156</v>
+        <v>0.165</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.269</v>
+        <v>0.281</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.537</v>
+        <v>0.576</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.801</v>
+        <v>1.822</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.51</v>
+        <v>46.84</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.007</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.108</v>
+        <v>0.116</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.211</v>
+        <v>0.22</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.266</v>
+        <v>0.281</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.152</v>
+        <v>0.172</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.317</v>
+        <v>0.311</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.206</v>
+        <v>0.214</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,34 +4426,34 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.38</v>
+        <v>51.39</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AH29" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="AJ29" s="1" t="n">
         <v>0.043</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.172</v>
+        <v>0.184</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.058</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="AO29" s="1" t="n">
         <v>0.023</v>
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>104.87</v>
+        <v>106.51</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.016</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.166</v>
+        <v>0.172</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.223</v>
+        <v>0.242</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.686</v>
+        <v>0.747</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.198</v>
+        <v>0.226</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.705</v>
+        <v>1.748</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.115</v>
+        <v>0.133</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.37</v>
+        <v>50.93</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.021</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.074</v>
+        <v>0.085</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.143</v>
+        <v>0.155</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.048</v>
+        <v>0.059</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.08</v>
+        <v>0.093</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.147</v>
+        <v>0.168</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.836</v>
+        <v>0.844</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.124</v>
+        <v>0.137</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.45</v>
+        <v>24.41</v>
       </c>
       <c r="AF30" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG30" s="1" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AI30" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ30" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AK30" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AL30" s="1" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AM30" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="AO30" s="1" t="n">
         <v>-0.005</v>
-      </c>
-      <c r="AG30" s="1" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="AH30" s="1" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="AI30" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AJ30" s="1" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="AK30" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AL30" s="1" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="AM30" s="1" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="AN30" s="1" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AO30" s="1" t="n">
-        <v>-0.003</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.47</v>
+        <v>20.53</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.165</v>
+        <v>0.158</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.188</v>
+        <v>0.191</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.338</v>
+        <v>0.347</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.543</v>
+        <v>0.567</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.689</v>
+        <v>0.677</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.279</v>
+        <v>1.305</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.2</v>
+        <v>66.02</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.003</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.089</v>
+        <v>0.078</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.257</v>
+        <v>0.27</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.408</v>
+        <v>0.395</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.75</v>
+        <v>1.732</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.87</v>
+        <v>80.81</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.211</v>
+        <v>0.209</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.755</v>
+        <v>0.751</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>38.3</v>
+        <v>38.18</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.003</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.02</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.021</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.063</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>0.144</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.314</v>
+        <v>1.307</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>45.63</v>
+        <v>44.79</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.018</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.03</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.105</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.067</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.041</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.103</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.111</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.028</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.201</v>
+        <v>1.158</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.066</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4786,31 +4786,31 @@
         <v>29.7</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH32" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.032</v>
+        <v>0.028</v>
       </c>
       <c r="AJ32" s="1" t="n">
         <v>0.044</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.095</v>
+        <v>0.094</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.298</v>
+        <v>0.303</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.196</v>
+        <v>0.197</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.138</v>
+        <v>1.13</v>
       </c>
       <c r="AO32" s="1" t="n">
         <v>0.017</v>
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.61</v>
+        <v>52.67</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.001</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.029</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.017</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.067</v>
+        <v>0.069</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.347</v>
+        <v>0.363</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.335</v>
+        <v>0.323</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.45</v>
+        <v>1.454</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.026</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>91.07</v>
+        <v>91.6</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.05</v>
+        <v>0.056</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.106</v>
+        <v>0.097</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.297</v>
+        <v>0.305</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.585</v>
+        <v>0.621</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.666</v>
+        <v>0.643</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.301</v>
+        <v>1.308</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.074</v>
+        <v>0.08</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,28 +4902,28 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.31</v>
+        <v>48.3</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.073</v>
+        <v>0.07</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.174</v>
+        <v>0.179</v>
       </c>
       <c r="AM33" s="1" t="n">
         <v>0.027</v>
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.39</v>
+        <v>91.23</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.007</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.168</v>
+        <v>0.158</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.383</v>
+        <v>0.387</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.768</v>
+        <v>0.792</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.452</v>
+        <v>0.462</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>175.1</v>
+        <v>176.36</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.254</v>
+        <v>0.263</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.264</v>
+        <v>0.274</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.368</v>
+        <v>0.406</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.095</v>
+        <v>1.098</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.37</v>
+        <v>104.9</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.093</v>
+        <v>0.076</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.121</v>
+        <v>0.127</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.216</v>
+        <v>0.232</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.51</v>
+        <v>0.533</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.151</v>
+        <v>0.147</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.49</v>
+        <v>2.508</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.76</v>
+        <v>60.43</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.037</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.114</v>
+        <v>0.153</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.339</v>
+        <v>0.369</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.263</v>
+        <v>-0.252</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.896</v>
+        <v>0.883</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.54</v>
+        <v>59.41</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.027</v>
+        <v>0.014</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.061</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.053</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.079</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.146</v>
+        <v>0.16</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.094</v>
+        <v>0.084</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.242</v>
+        <v>2.205</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.044</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.78</v>
+        <v>23.95</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.051</v>
+        <v>0.058</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.131</v>
+        <v>0.117</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.143</v>
+        <v>0.151</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.459</v>
+        <v>0.467</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.33</v>
+        <v>0.357</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.033</v>
+        <v>0.061</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.865</v>
+        <v>0.881</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.119</v>
+        <v>0.127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.43</v>
+        <v>31.09</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.047</v>
+        <v>0.054</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.031</v>
+        <v>0.053</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.158</v>
+        <v>0.168</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.333</v>
+        <v>0.361</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.334</v>
+        <v>0.38</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.272</v>
+        <v>0.347</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.339</v>
+        <v>-0.328</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.162</v>
+        <v>0.187</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>73.18</v>
+        <v>75.73</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.035</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.002</v>
+        <v>0.039</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.05</v>
+        <v>0.086</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.239</v>
+        <v>0.267</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.283</v>
+        <v>0.328</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.446</v>
+        <v>0.507</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.982</v>
+        <v>1.104</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.798</v>
+        <v>0.849</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.818</v>
+        <v>4.001</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.152</v>
+        <v>0.192</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>121.67</v>
+        <v>122.35</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.006</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.02</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.035</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.069</v>
+        <v>0.071</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.615</v>
+        <v>0.624</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.813</v>
+        <v>0.79</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.672</v>
+        <v>2.698</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.051</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>98.57</v>
+        <v>97.2</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.027</v>
+        <v>-0.014</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.04</v>
+        <v>0.059</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.051</v>
+        <v>0.036</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.287</v>
+        <v>0.249</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.55</v>
+        <v>0.529</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.78</v>
+        <v>0.746</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.85</v>
+        <v>1.831</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.865</v>
+        <v>1.829</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.163</v>
+        <v>3.098</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.214</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>139.3</v>
+        <v>144.55</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.038</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.04</v>
+        <v>0.106</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.181</v>
+        <v>0.225</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.596</v>
+        <v>0.637</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.938</v>
+        <v>1.011</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.473</v>
+        <v>1.572</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.473</v>
+        <v>1.649</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.7</v>
+        <v>0.784</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.594</v>
+        <v>2.726</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.433</v>
+        <v>0.487</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,34 +5406,34 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>62.67</v>
+        <v>62.7</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>-0.043</v>
+        <v>0</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.041</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="V38" s="1" t="n">
         <v>0.046</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.138</v>
+        <v>0.146</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.416</v>
+        <v>0.377</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.84</v>
+        <v>1.856</v>
       </c>
       <c r="AA38" s="1" t="n">
         <v>0.033</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>80.57</v>
+        <v>79.08</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.052</v>
+        <v>-0.018</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.156</v>
+        <v>0.192</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.133</v>
+        <v>-0.149</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.779</v>
+        <v>0.696</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.28</v>
+        <v>1.238</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.723</v>
+        <v>1.686</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.104</v>
+        <v>3.142</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.134</v>
+        <v>2.049</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.541</v>
+        <v>4.446</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.251</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>30.09</v>
+        <v>30.18</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.289</v>
+        <v>0.282</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.369</v>
+        <v>0.374</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.799</v>
+        <v>0.812</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.92</v>
+        <v>0.949</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.543</v>
+        <v>0.524</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.348</v>
+        <v>1.375</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.125</v>
+        <v>0.128</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>68.74</v>
+        <v>68.67</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.001</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.04</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.123</v>
+        <v>0.121</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.073</v>
+        <v>0.072</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.149</v>
+        <v>0.156</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.22</v>
+        <v>0.218</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.197</v>
+        <v>0.16</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.523</v>
+        <v>1.539</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>197.36</v>
+        <v>197.63</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.056</v>
+        <v>0.08</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.218</v>
+        <v>-0.217</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.431</v>
+        <v>0.405</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.592</v>
+        <v>0.594</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.225</v>
+        <v>1.241</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.247</v>
+        <v>1.343</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.698</v>
+        <v>0.662</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.172</v>
+        <v>1.182</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>77.89</v>
+        <v>79.25</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.034</v>
+        <v>0.061</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.397</v>
+        <v>0.422</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.785</v>
+        <v>0.836</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.185</v>
+        <v>1.286</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.986</v>
+        <v>1.013</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.781</v>
+        <v>1.866</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.132</v>
+        <v>0.152</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>134.15</v>
+        <v>135.02</v>
       </c>
       <c r="R40" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="S40" s="1" t="n">
         <v>-0.011</v>
       </c>
-      <c r="S40" s="1" t="n">
-        <v>-0.003</v>
-      </c>
       <c r="T40" s="1" t="n">
-        <v>0.032</v>
+        <v>0.039</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.511</v>
+        <v>0.517</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.037</v>
+        <v>1.017</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.484</v>
+        <v>2.503</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.68</v>
+        <v>36.3</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.017</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.006</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.148</v>
+        <v>0.167</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.285</v>
+        <v>0.307</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.248</v>
+        <v>0.278</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.447</v>
+        <v>0.509</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.368</v>
+        <v>0.357</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.538</v>
+        <v>1.571</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.021</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.45</v>
+        <v>29.58</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.004</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>0.183</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.099</v>
+        <v>0.104</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.403</v>
+        <v>0.436</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.412</v>
+        <v>0.408</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.504</v>
+        <v>1.542</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.124</v>
+        <v>0.129</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>167.2</v>
+        <v>169.59</v>
       </c>
       <c r="R41" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>-0.083</v>
+      </c>
+      <c r="U41" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="V41" s="1" t="n">
         <v>-0.028</v>
       </c>
-      <c r="S41" s="1" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="T41" s="1" t="n">
-        <v>-0.096</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V41" s="1" t="n">
-        <v>-0.042</v>
-      </c>
       <c r="W41" s="1" t="n">
-        <v>0.107</v>
+        <v>0.13</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.712</v>
+        <v>0.73</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.005</v>
+        <v>0.989</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.68</v>
+        <v>4.764</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.055</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.65</v>
+        <v>74.09</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.006</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.044</v>
+        <v>0.05</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.175</v>
+        <v>0.182</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.358</v>
+        <v>0.373</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.674</v>
+        <v>0.715</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.511</v>
+        <v>0.519</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.655</v>
+        <v>1.674</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.097</v>
+        <v>0.104</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>22.84</v>
+        <v>23.31</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>-0.041</v>
+        <v>0.021</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.006</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.214</v>
+        <v>-0.198</v>
       </c>
       <c r="U42" s="1" t="n">
         <v>-0.201</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.324</v>
+        <v>-0.31</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.265</v>
+        <v>-0.242</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.092</v>
+        <v>0.133</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.506</v>
+        <v>-0.493</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.224</v>
+        <v>-0.208</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.47</v>
+        <v>104.66</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.639</v>
+        <v>0.67</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.603</v>
+        <v>0.601</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.627</v>
+        <v>1.641</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.088</v>
+        <v>0.09</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>189.8</v>
+        <v>192.22</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.013</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.009</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.038</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.06</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.177</v>
+        <v>0.21</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.271</v>
+        <v>1.343</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.178</v>
+        <v>1.184</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.228</v>
+        <v>7.253</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.037</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>53.44</v>
+        <v>54.95</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.028</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.029</v>
+        <v>0.071</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.036</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.346</v>
+        <v>0.33</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.149</v>
+        <v>1.244</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.877</v>
+        <v>1.995</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.568</v>
+        <v>2.643</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.903</v>
+        <v>5.08</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.251</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.62</v>
+        <v>44.79</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="E44" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.046</v>
+        <v>0.05</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.162</v>
+        <v>0.167</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.27</v>
+        <v>0.274</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.694</v>
+        <v>0.715</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.319</v>
+        <v>2.333</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.079</v>
+        <v>0.083</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>76.94</v>
+        <v>78.41</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>-0.048</v>
+        <v>0.019</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.031</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.213</v>
+        <v>-0.198</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.238</v>
+        <v>-0.233</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.284</v>
+        <v>-0.27</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.234</v>
+        <v>-0.21</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.353</v>
+        <v>0.409</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.054</v>
+        <v>0.064</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.325</v>
+        <v>3.376</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.272</v>
+        <v>-0.258</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>80.9</v>
+        <v>80.76</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.061</v>
+        <v>0.066</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.167</v>
+        <v>0.147</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.084</v>
+        <v>0.082</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.219</v>
+        <v>0.204</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.944</v>
+        <v>0.9</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.193</v>
+        <v>0.175</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>61.65</v>
+        <v>62.62</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.016</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.009</v>
+        <v>0.029</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.044</v>
+        <v>0.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.178</v>
+        <v>0.184</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.235</v>
+        <v>0.255</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.406</v>
+        <v>0.451</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.694</v>
+        <v>0.761</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.235</v>
+        <v>0.263</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.537</v>
+        <v>1.583</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.127</v>
+        <v>0.145</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>70.69</v>
+        <v>71.24</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>-0.047</v>
+        <v>0.008</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.092</v>
+        <v>-0.069</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.093</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.132</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.144</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.098</v>
+        <v>-0.076</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.511</v>
+        <v>0.547</v>
       </c>
       <c r="Y45" s="1" t="n">
         <v>0.226</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.519</v>
+        <v>2.49</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.12</v>
+        <v>-0.114</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,34 +6272,34 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.89</v>
+        <v>33.91</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.063</v>
+        <v>0.067</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.188</v>
+        <v>0.17</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.114</v>
+        <v>0.107</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.246</v>
+        <v>0.234</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.074</v>
+        <v>1.034</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.2</v>
+        <v>2.108</v>
       </c>
       <c r="AO45" s="1" t="n">
         <v>0.197</v>
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.16</v>
+        <v>33.43</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.008</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.147</v>
+        <v>0.143</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.14</v>
+        <v>0.149</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.09</v>
+        <v>0.099</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>356.82</v>
+        <v>362.04</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.015</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.035</v>
+        <v>0.05</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.319</v>
+        <v>0.283</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.438</v>
+        <v>0.459</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.604</v>
+        <v>0.667</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.647</v>
+        <v>1.735</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.666</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.46</v>
+        <v>13.479</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.185</v>
+        <v>0.202</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.74</v>
+        <v>11.46</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.037</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.199</v>
+        <v>-0.205</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.038</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.469</v>
+        <v>-0.46</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.636</v>
+        <v>-0.663</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.725</v>
+        <v>-0.727</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.887</v>
+        <v>-0.89</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.06</v>
+        <v>49.35</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.131</v>
+        <v>0.138</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.249</v>
+        <v>0.259</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.541</v>
+        <v>0.577</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.52</v>
+        <v>0.531</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.646</v>
+        <v>1.653</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.079</v>
+        <v>0.086</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>122.84</v>
+        <v>124.21</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.011</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.042</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.053</v>
+        <v>0.065</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.179</v>
+        <v>0.211</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.375</v>
+        <v>1.442</v>
       </c>
       <c r="Y47" s="1" t="n">
         <v>1.055</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.661</v>
+        <v>6.679</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.038</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.19</v>
+        <v>44.23</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.199</v>
+        <v>0.2</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.216</v>
+        <v>0.217</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.595</v>
+        <v>0.586</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.886</v>
+        <v>0.908</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.92</v>
+        <v>0.909</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.909</v>
+        <v>1.932</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>49.92</v>
+        <v>51.1</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.024</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.01</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.02</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.123</v>
+        <v>0.114</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.188</v>
+        <v>0.216</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.283</v>
+        <v>0.351</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.684</v>
+        <v>0.763</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.097</v>
+        <v>0.112</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.036</v>
+        <v>0.061</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.97</v>
+        <v>26.01</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.023</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.003</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.424</v>
+        <v>0.448</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.694</v>
+        <v>0.674</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.511</v>
+        <v>0.51</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,34 +6660,34 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.42</v>
+        <v>52.44</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="F49" s="1" t="n">
         <v>0.039</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.811</v>
+        <v>0.833</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.616</v>
+        <v>0.627</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.894</v>
+        <v>1.895</v>
       </c>
       <c r="M49" s="1" t="n">
         <v>0.093</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.61</v>
+        <v>35.26</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.019</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.001</v>
+        <v>0.021</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.108</v>
+        <v>0.076</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.141</v>
+        <v>0.162</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.288</v>
+        <v>0.344</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.62</v>
+        <v>17.59</v>
       </c>
       <c r="AF49" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG49" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AH49" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG49" s="1" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="AH49" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AI49" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.129</v>
+        <v>-0.119</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.325</v>
+        <v>-0.314</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.165</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.008</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.04</v>
+        <v>39.4</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0</v>
+        <v>0.009</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.142</v>
+        <v>0.153</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.24</v>
+        <v>0.235</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.277</v>
+        <v>0.288</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.412</v>
+        <v>0.426</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.786</v>
+        <v>0.841</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.397</v>
+        <v>0.401</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.774</v>
+        <v>0.758</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.152</v>
+        <v>0.162</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.91</v>
+        <v>21.87</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.044</v>
+        <v>0.053</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.046</v>
+        <v>0.051</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.151</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.421</v>
+        <v>-0.398</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.317</v>
+        <v>-0.327</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.5</v>
+        <v>-0.497</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>51.08</v>
+        <v>52.1</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.006</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.096</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.126</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.186</v>
+        <v>-0.17</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.057</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.428</v>
+        <v>0.491</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.007</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.389</v>
+        <v>1.414</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.143</v>
+        <v>-0.125</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.47</v>
+        <v>23.57</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.056</v>
+        <v>0.068</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.162</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.113</v>
+        <v>0.105</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.351</v>
+        <v>0.359</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.074</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,25 +6963,25 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>36.55</v>
+        <v>36.53</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.001</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.048</v>
       </c>
       <c r="F52" s="1" t="n">
         <v>-0.279</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.238</v>
+        <v>-0.278</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.448</v>
+        <v>-0.449</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.322</v>
+        <v>-0.316</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.27</v>
+        <v>49.14</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.003</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.147</v>
+        <v>-0.15</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.103</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.149</v>
+        <v>-0.152</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.009</v>
+        <v>0.039</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.436</v>
+        <v>0.48</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.33</v>
+        <v>-0.323</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.965</v>
+        <v>1.932</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.11</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,25 +7074,25 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.05</v>
+        <v>14.03</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.001</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.09</v>
+        <v>-0.068</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.367</v>
+        <v>-0.368</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.321</v>
+        <v>-0.375</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.616</v>
+        <v>-0.617</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.293</v>
+        <v>-0.298</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.68</v>
+        <v>92.4</v>
       </c>
       <c r="R53" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.117</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.145</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.184</v>
+        <v>-0.186</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.004</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.99</v>
+        <v>1.046</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.105</v>
+        <v>-0.108</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.001</v>
       </c>
       <c r="AG53" s="1" t="n">
         <v>0.034</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.023</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.024</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.151</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.263</v>
+        <v>-0.254</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.112</v>
+        <v>-0.086</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.219</v>
+        <v>0.202</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.044</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>60.44</v>
+        <v>60.64</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.048</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.124</v>
+        <v>-0.121</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>-0.033</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.131</v>
+        <v>-0.128</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.078</v>
+        <v>-0.064</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.375</v>
+        <v>0.408</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.397</v>
+        <v>1.405</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.096</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>117.86</v>
+        <v>119.03</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.086</v>
+        <v>0.097</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.088</v>
+        <v>0.099</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.175</v>
+        <v>0.191</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.546</v>
+        <v>0.563</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.767</v>
+        <v>0.802</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.655</v>
+        <v>1.667</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.088</v>
+        <v>0.098</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>38.85</v>
+        <v>39.32</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.009</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.088</v>
+        <v>0.101</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.152</v>
+        <v>0.161</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.341</v>
+        <v>0.368</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.317</v>
+        <v>0.321</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.296</v>
+        <v>0.312</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.022</v>
+        <v>0.034</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>46.68</v>
+        <v>47.2</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.004</v>
+        <v>0.018</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.097</v>
+        <v>0.109</v>
       </c>
       <c r="U55" s="1" t="n">
         <v>0.067</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.101</v>
+        <v>0.113</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.196</v>
+        <v>0.216</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.537</v>
+        <v>0.554</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.791</v>
+        <v>0.832</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.745</v>
+        <v>1.762</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.093</v>
+        <v>0.106</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>29.44</v>
+        <v>28.49</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.038</v>
+        <v>-0.032</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.11</v>
+        <v>0.074</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.211</v>
+        <v>-0.181</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.208</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.336</v>
+        <v>-0.363</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.844</v>
+        <v>-0.855</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>-0.969</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.112</v>
+        <v>0.076</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.1</v>
+        <v>72.96</v>
       </c>
       <c r="R56" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="S56" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="U56" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>-0.011</v>
       </c>
-      <c r="S56" s="1" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="T56" s="1" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="U56" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>-0.023</v>
-      </c>
       <c r="W56" s="1" t="n">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.372</v>
+        <v>0.402</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.519</v>
+        <v>0.52</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.741</v>
+        <v>2.79</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.51</v>
+        <v>100.76</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>0.047</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>0.045</v>
-      </c>
       <c r="W57" s="1" t="n">
-        <v>0.07</v>
+        <v>0.069</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.23</v>
+        <v>0.255</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.275</v>
+        <v>0.272</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.935</v>
+        <v>0.939</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.071</v>
+        <v>0.073</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.28</v>
+        <v>89.36</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.009</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.082</v>
+        <v>0.083</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.089</v>
+        <v>0.078</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.304</v>
+        <v>0.32</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.394</v>
+        <v>0.384</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.065</v>
+        <v>1.074</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.89</v>
+        <v>95.13</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="U59" s="1" t="n">
         <v>0.069</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.227</v>
+        <v>0.252</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.266</v>
+        <v>0.26</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.859</v>
+        <v>0.865</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.072</v>
+        <v>0.075</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.35</v>
+        <v>22.43</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.004</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.011</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.046</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.051</v>
+        <v>0.056</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.188</v>
+        <v>0.21</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.031</v>
+        <v>0.001</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.546</v>
+        <v>0.549</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.18</v>
+        <v>97.05</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.009</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.001</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.113</v>
+        <v>0.124</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.155</v>
+        <v>0.142</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.201</v>
+        <v>0.237</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.428</v>
+        <v>0.479</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.512</v>
+        <v>0.509</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.047</v>
+        <v>2.022</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.132</v>
+        <v>0.142</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/24/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/25/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>336.88</v>
+        <v>340.04</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.06</v>
+        <v>0.071</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.162</v>
+        <v>0.181</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.959</v>
+        <v>0.977</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.005</v>
+        <v>1.073</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.565</v>
+        <v>3.556</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.009</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.28</v>
+        <v>57.93</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.026</v>
+        <v>0.001</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.119</v>
+        <v>0.113</v>
       </c>
       <c r="U5" s="1" t="n">
         <v>0.238</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.262</v>
+        <v>0.25</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.248</v>
+        <v>0.26</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.418</v>
+        <v>0.409</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.54</v>
+        <v>1.578</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.582</v>
+        <v>1.561</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.226</v>
+        <v>0.219</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,16 +1744,16 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.06</v>
+        <v>83.04</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>0.009</v>
@@ -1762,16 +1762,16 @@
         <v>0.021</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AL5" s="1" t="n">
         <v>0.144</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.182</v>
+        <v>0.181</v>
       </c>
       <c r="AO5" s="1" t="n">
         <v>0.006</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>690.51</v>
+        <v>696.25</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.072</v>
+        <v>0.085</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.166</v>
+        <v>0.181</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.809</v>
+        <v>0.824</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.886</v>
+        <v>0.948</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.2</v>
+        <v>3.186</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>106.22</v>
+        <v>105.47</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.12</v>
+        <v>0.112</v>
       </c>
       <c r="U6" s="1" t="n">
         <v>0.166</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.185</v>
+        <v>0.167</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.155</v>
+        <v>0.169</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.3</v>
+        <v>0.291</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.467</v>
+        <v>1.516</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.076</v>
+        <v>2.049</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.19</v>
+        <v>0.182</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.27</v>
+        <v>120.17</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>0.027</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.51</v>
+        <v>71.78</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.106</v>
+        <v>0.118</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.171</v>
+        <v>0.176</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.439</v>
+        <v>0.445</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.494</v>
+        <v>0.547</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.156</v>
+        <v>2.133</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.083</v>
+        <v>0.088</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.18</v>
+        <v>29.04</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.062</v>
+        <v>0.031</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.171</v>
+        <v>0.165</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.473</v>
+        <v>0.488</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.414</v>
+        <v>0.407</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.156</v>
+        <v>1.163</v>
       </c>
       <c r="Z7" s="1" t="n">
         <v>0.114</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.398</v>
+        <v>0.391</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,34 +1982,34 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.42</v>
+        <v>97.34</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.078</v>
+        <v>0.068</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.032</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.099</v>
+        <v>0.095</v>
       </c>
       <c r="AO7" s="1" t="n">
         <v>0.016</v>
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>263.33</v>
+        <v>264.58</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.101</v>
+        <v>0.083</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.128</v>
+        <v>0.146</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.232</v>
+        <v>0.242</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.458</v>
+        <v>0.465</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.234</v>
+        <v>0.287</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.95</v>
+        <v>1.937</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.07</v>
+        <v>0.075</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.19</v>
+        <v>19.09</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.187</v>
+        <v>0.171</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.318</v>
+        <v>0.337</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.714</v>
+        <v>0.689</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.232</v>
+        <v>-0.198</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.744</v>
+        <v>1.723</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.168</v>
+        <v>0.162</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,34 +2101,34 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>104.15</v>
+        <v>104.1</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AH8" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.054</v>
+        <v>0.056</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="AL8" s="1" t="n">
         <v>0.082</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.157</v>
+        <v>-0.138</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.038</v>
       </c>
       <c r="AO8" s="1" t="n">
         <v>0.028</v>
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.85</v>
+        <v>26.82</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.001</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.206</v>
+        <v>0.22</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.143</v>
+        <v>1.167</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.665</v>
+        <v>1.593</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,34 +2196,34 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.9</v>
+        <v>89.91</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AH9" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.045</v>
+        <v>0.028</v>
       </c>
       <c r="AL9" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.252</v>
+        <v>-0.239</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.101</v>
+        <v>-0.104</v>
       </c>
       <c r="AO9" s="1" t="n">
         <v>0.035</v>
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>187.09</v>
+        <v>187.39</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.067</v>
+        <v>0.069</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.303</v>
+        <v>0.287</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.269</v>
+        <v>0.276</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.382</v>
+        <v>0.378</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.687</v>
+        <v>0.738</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.361</v>
+        <v>2.32</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.31</v>
+        <v>111.41</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.073</v>
+        <v>0.087</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>224.39</v>
+        <v>225.04</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.103</v>
+        <v>0.091</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.122</v>
+        <v>0.133</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.185</v>
+        <v>0.186</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.541</v>
+        <v>0.546</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.669</v>
+        <v>0.707</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.021</v>
+        <v>1.994</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.067</v>
+        <v>0.07</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>62.86</v>
+        <v>64.42</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.054</v>
+        <v>0.063</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.062</v>
+        <v>0.088</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.399</v>
+        <v>0.42</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.556</v>
+        <v>0.596</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.777</v>
+        <v>0.83</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.672</v>
+        <v>0.713</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.783</v>
+        <v>0.891</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.81</v>
+        <v>4.924</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.224</v>
+        <v>0.255</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,37 +2410,37 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103</v>
+        <v>103.06</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="AJ11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AL11" s="1" t="n">
         <v>0.168</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.189</v>
+        <v>0.195</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>452.66</v>
+        <v>458.5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.021</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>4.291</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>-0.031</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>1.015</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>4.283</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>-0.044</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.25</v>
+        <v>95.4</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.102</v>
+        <v>0.076</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.824</v>
+        <v>1.878</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.715</v>
+        <v>3.722</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.718</v>
+        <v>2.889</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.724</v>
+        <v>5.62</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.293</v>
+        <v>0.295</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,10 +2529,10 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.71</v>
+        <v>108.75</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="1" t="n">
         <v>0.004</v>
@@ -2547,16 +2547,16 @@
         <v>0.06</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="AL12" s="1" t="n">
         <v>0.13</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.068</v>
+        <v>0.073</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.244</v>
+        <v>0.243</v>
       </c>
       <c r="AO12" s="1" t="n">
         <v>0.018</v>
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>203.97</v>
+        <v>205.45</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.083</v>
+        <v>0.096</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.132</v>
+        <v>0.141</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.777</v>
+        <v>0.79</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.81</v>
+        <v>0.869</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.819</v>
+        <v>2.806</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.92</v>
+        <v>45.25</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.134</v>
+        <v>0.108</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.041</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.644</v>
+        <v>0.634</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.214</v>
+        <v>1.26</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.403</v>
+        <v>2.464</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.932</v>
+        <v>3.968</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.735</v>
+        <v>1.893</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.176</v>
+        <v>6.169</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.311</v>
+        <v>0.32</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.27</v>
+        <v>23.35</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
       <c r="AJ13" s="1" t="n">
         <v>0.056</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.071</v>
+        <v>0.077</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.098</v>
+        <v>0.113</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.286</v>
+        <v>0.287</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,34 +2689,34 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.39</v>
+        <v>96.41</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.023</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.037</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>0.427</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.555</v>
+        <v>0.574</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.771</v>
+        <v>1.738</v>
       </c>
       <c r="M14" s="1" t="n">
         <v>0.024</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.05</v>
+        <v>57.3</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.075</v>
+        <v>0.099</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.495</v>
+        <v>0.508</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.781</v>
+        <v>0.82</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.179</v>
+        <v>1.256</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.265</v>
+        <v>0.293</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.29</v>
+        <v>76.47</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="AI14" s="1" t="n">
         <v>0.035</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.046</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>252.14</v>
+        <v>256.38</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.003</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.043</v>
+        <v>0.053</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.04</v>
+        <v>0.061</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.17</v>
+        <v>0.194</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.852</v>
+        <v>0.883</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.587</v>
+        <v>0.678</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.093</v>
+        <v>3.1</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.91</v>
+        <v>18.77</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.041</v>
+        <v>0.048</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.067</v>
+        <v>0.094</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.044</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.287</v>
+        <v>0.311</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.786</v>
+        <v>0.872</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1.034</v>
+        <v>1.166</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.146</v>
+        <v>0.202</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.65</v>
+        <v>97.74</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.063</v>
+        <v>0.068</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.116</v>
+        <v>0.137</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.477</v>
+        <v>0.473</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>139.06</v>
+        <v>138.76</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.145</v>
+        <v>0.152</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.193</v>
+        <v>0.189</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.529</v>
+        <v>0.526</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.8</v>
+        <v>0.818</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.672</v>
+        <v>1.642</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.143</v>
+        <v>0.141</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>79.12</v>
+        <v>78.53</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.027</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.184</v>
+        <v>0.155</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.046</v>
+        <v>0.043</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.161</v>
+        <v>0.153</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.315</v>
+        <v>1.288</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.099</v>
+        <v>0.091</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.79</v>
+        <v>43</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.074</v>
+        <v>0.084</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.179</v>
+        <v>0.181</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.274</v>
+        <v>0.28</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.043</v>
+        <v>0.065</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.301</v>
+        <v>0.307</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.31</v>
+        <v>150.59</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.002</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.064</v>
+        <v>0.078</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.156</v>
+        <v>0.172</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.767</v>
+        <v>0.782</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.765</v>
+        <v>0.826</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>110.24</v>
+        <v>109.19</v>
       </c>
       <c r="R17" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="S17" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="S17" s="1" t="n">
-        <v>0.02</v>
-      </c>
       <c r="T17" s="1" t="n">
-        <v>0.102</v>
+        <v>0.091</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.191</v>
+        <v>0.157</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.565</v>
+        <v>0.525</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.487</v>
+        <v>1.464</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.161</v>
+        <v>4.061</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.191</v>
+        <v>0.179</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.74</v>
+        <v>42.81</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.112</v>
+        <v>0.106</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.188</v>
+        <v>-0.177</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.053</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.38</v>
+        <v>159.77</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.133</v>
+        <v>0.11</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.098</v>
+        <v>0.104</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.197</v>
+        <v>0.186</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.658</v>
+        <v>0.651</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.645</v>
+        <v>0.674</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.646</v>
+        <v>2.59</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>36.81</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.005</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.092</v>
+        <v>0.086</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.236</v>
+        <v>0.213</v>
       </c>
       <c r="V19" s="1" t="n">
         <v>0.299</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.528</v>
+        <v>0.518</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.186</v>
+        <v>0.18</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.15</v>
+        <v>57.59</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.403</v>
+        <v>0.415</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.782</v>
+        <v>0.796</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.886</v>
+        <v>0.941</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.321</v>
+        <v>2.306</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.06</v>
+        <v>0.068</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.78</v>
+        <v>80.44</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.051</v>
+        <v>0.046</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.153</v>
+        <v>0.128</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.117</v>
+        <v>0.134</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.173</v>
+        <v>0.17</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.426</v>
+        <v>0.446</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.769</v>
+        <v>1.727</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.084</v>
+        <v>0.08</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,34 +3365,34 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101.09</v>
+        <v>101.04</v>
       </c>
       <c r="AF20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH20" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.071</v>
+        <v>0.063</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.211</v>
+        <v>0.208</v>
       </c>
       <c r="AO20" s="1" t="n">
         <v>0.015</v>
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>37.05</v>
+        <v>37.32</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.028</v>
+        <v>0.032</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.059</v>
+        <v>0.067</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.266</v>
+        <v>0.26</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.42</v>
+        <v>0.431</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.672</v>
+        <v>0.68</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.823</v>
+        <v>0.837</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.865</v>
+        <v>0.971</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.885</v>
+        <v>1.898</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.217</v>
+        <v>0.226</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>243.11</v>
+        <v>241.22</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.021</v>
+        <v>0.004</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.211</v>
+        <v>0.192</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.246</v>
+        <v>0.239</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.635</v>
+        <v>0.614</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.158</v>
+        <v>1.142</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.508</v>
+        <v>1.588</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.9</v>
+        <v>3.783</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.132</v>
+        <v>0.124</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,10 +3484,10 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.72</v>
+        <v>50.69</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
         <v>0.003</v>
@@ -3496,22 +3496,22 @@
         <v>0.013</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.065</v>
+        <v>0.07</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="AO21" s="1" t="n">
         <v>0.016</v>
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.37</v>
+        <v>80.45</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.231</v>
+        <v>0.21</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.304</v>
+        <v>0.329</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.614</v>
+        <v>0.635</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.551</v>
+        <v>0.552</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.223</v>
+        <v>1.326</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.18</v>
+        <v>1.158</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.159</v>
+        <v>0.16</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>101.81</v>
+        <v>102.11</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.035</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.028</v>
+        <v>0.013</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.012</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.651</v>
+        <v>0.656</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.416</v>
+        <v>0.459</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.01</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.59</v>
+        <v>49.64</v>
       </c>
       <c r="AF22" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="AK22" s="1" t="n">
         <v>0.077</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.184</v>
+        <v>0.185</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.265</v>
+        <v>0.262</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>39.47</v>
+        <v>39.59</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.269</v>
+        <v>0.259</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.661</v>
+        <v>0.651</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.723</v>
+        <v>0.729</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.688</v>
+        <v>0.781</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.232</v>
+        <v>2.247</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>110.15</v>
+        <v>106.43</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.034</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.051</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.047</v>
+        <v>0.012</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.126</v>
+        <v>0.039</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.043</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.145</v>
+        <v>0.072</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.694</v>
+        <v>0.636</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.845</v>
+        <v>0.88</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.879</v>
+        <v>3.632</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.144</v>
+        <v>0.105</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.55</v>
+        <v>96.52</v>
       </c>
       <c r="AF23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH23" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.024</v>
+        <v>0.03</v>
       </c>
       <c r="AN23" s="1" t="n">
         <v>0.158</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>68.54</v>
+        <v>69.23</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.031</v>
+        <v>0.042</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.729</v>
+        <v>0.746</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.708</v>
+        <v>0.754</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.834</v>
+        <v>1.826</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.069</v>
+        <v>0.08</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>40.89</v>
+        <v>41.29</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.032</v>
+        <v>0.01</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.034</v>
+        <v>0.039</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.128</v>
+        <v>0.122</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.147</v>
+        <v>0.172</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.356</v>
+        <v>0.363</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.147</v>
+        <v>0.158</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.014</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.078</v>
+        <v>0.089</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,34 +3839,34 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.68</v>
+        <v>111.65</v>
       </c>
       <c r="AF24" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH24" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.382</v>
+        <v>0.374</v>
       </c>
       <c r="AO24" s="1" t="n">
         <v>0.017</v>
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.89</v>
+        <v>47.29</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.037</v>
+        <v>0.046</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.132</v>
+        <v>0.15</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.218</v>
+        <v>0.219</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.646</v>
+        <v>0.66</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.956</v>
+        <v>1.001</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.262</v>
+        <v>2.259</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.072</v>
+        <v>0.081</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>87.38</v>
+        <v>86.69</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.024</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.1</v>
+        <v>0.044</v>
       </c>
       <c r="V25" s="1" t="n">
         <v>0.028</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.167</v>
+        <v>0.153</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.368</v>
+        <v>0.357</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.148</v>
+        <v>0.175</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.383</v>
+        <v>1.332</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.93</v>
+        <v>93.06</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG25" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.008</v>
       </c>
       <c r="AI25" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.251</v>
+        <v>0.253</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.266</v>
+        <v>0.276</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.624</v>
+        <v>0.621</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.98</v>
+        <v>48.66</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.053</v>
+        <v>0.068</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>0.167</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.162</v>
+        <v>0.187</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.371</v>
+        <v>0.378</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.679</v>
+        <v>0.703</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.848</v>
+        <v>0.913</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.419</v>
+        <v>1.411</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.091</v>
+        <v>0.106</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,34 +4038,34 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.59</v>
+        <v>60.62</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.008</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.072</v>
+        <v>0.045</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.096</v>
+        <v>0.118</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.522</v>
+        <v>0.523</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.265</v>
+        <v>0.312</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.851</v>
+        <v>0.831</v>
       </c>
       <c r="AA26" s="1" t="n">
         <v>-0.012</v>
@@ -4080,28 +4080,28 @@
         <v>26.64</v>
       </c>
       <c r="AF26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="1" t="n">
         <v>0.001</v>
-      </c>
-      <c r="AG26" s="1" t="n">
-        <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="AJ26" s="1" t="n">
         <v>0.021</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.067</v>
+        <v>0.06</v>
       </c>
       <c r="AL26" s="1" t="n">
         <v>0.202</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.133</v>
+        <v>0.158</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.62</v>
+        <v>48.02</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.083</v>
+        <v>0.123</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>0.237</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.432</v>
+        <v>0.444</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.604</v>
+        <v>0.637</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.759</v>
+        <v>1.746</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.058</v>
+        <v>0.067</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.25</v>
+        <v>27.06</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.067</v>
+        <v>0.042</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4200,22 +4200,22 @@
         <v>0.007</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.067</v>
+        <v>0.065</v>
       </c>
       <c r="AL27" s="1" t="n">
         <v>0.202</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>0.009</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>43.95</v>
+        <v>44.35</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.114</v>
+        <v>0.104</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.03</v>
+        <v>0.053</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.239</v>
+        <v>0.233</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.739</v>
+        <v>0.755</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.519</v>
+        <v>0.555</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.394</v>
+        <v>1.39</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.034</v>
+        <v>0.044</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.9</v>
+        <v>76.51</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.092</v>
+        <v>0.087</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.142</v>
+        <v>0.122</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.095</v>
+        <v>0.107</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.126</v>
+        <v>0.107</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.277</v>
+        <v>0.271</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.486</v>
+        <v>0.519</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.718</v>
+        <v>1.664</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.149</v>
+        <v>0.143</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,7 +4307,7 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.44</v>
+        <v>54.41</v>
       </c>
       <c r="AF28" s="1" t="n">
         <v>-0.001</v>
@@ -4316,25 +4316,25 @@
         <v>0.001</v>
       </c>
       <c r="AH28" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AI28" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="AI28" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.092</v>
+        <v>0.085</v>
       </c>
       <c r="AL28" s="1" t="n">
         <v>0.246</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.08</v>
+        <v>0.095</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.404</v>
+        <v>0.401</v>
       </c>
       <c r="AO28" s="1" t="n">
         <v>0.014</v>
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.82</v>
+        <v>64.85</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0.065</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.149</v>
+        <v>0.133</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.165</v>
+        <v>0.18</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.281</v>
+        <v>0.271</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.576</v>
+        <v>0.577</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.624</v>
+        <v>0.648</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.822</v>
+        <v>1.79</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.84</v>
+        <v>46.07</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.116</v>
+        <v>0.098</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.22</v>
+        <v>0.183</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.161</v>
+        <v>0.146</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.281</v>
+        <v>0.248</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.172</v>
+        <v>0.153</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.728</v>
+        <v>1.645</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.214</v>
+        <v>0.194</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,34 +4426,34 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.39</v>
+        <v>51.37</v>
       </c>
       <c r="AF29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.073</v>
+        <v>0.06</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.038</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.384</v>
+        <v>0.378</v>
       </c>
       <c r="AO29" s="1" t="n">
         <v>0.023</v>
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>106.51</v>
+        <v>107.87</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.062</v>
+        <v>0.076</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.172</v>
+        <v>0.185</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.242</v>
+        <v>0.263</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.44</v>
+        <v>0.461</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.747</v>
+        <v>0.769</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.226</v>
+        <v>0.264</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.748</v>
+        <v>1.777</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.133</v>
+        <v>0.147</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.93</v>
+        <v>50.3</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.021</v>
+        <v>0.006</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.085</v>
+        <v>0.072</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.155</v>
+        <v>0.119</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.093</v>
+        <v>0.077</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.168</v>
+        <v>0.153</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.438</v>
+        <v>0.447</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.844</v>
+        <v>0.795</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.137</v>
+        <v>0.123</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.41</v>
+        <v>24.46</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AG30" s="1" t="n">
         <v>-0.007</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.018</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.265</v>
+        <v>0.268</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.272</v>
+        <v>0.278</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.53</v>
+        <v>20.65</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.054</v>
+        <v>0.061</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>0.158</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.191</v>
+        <v>0.206</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.347</v>
+        <v>0.356</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.567</v>
+        <v>0.576</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.677</v>
+        <v>0.724</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.305</v>
+        <v>1.301</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.12</v>
+        <v>0.127</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.02</v>
+        <v>65.94</v>
       </c>
       <c r="R31" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S31" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="T31" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="S31" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="T31" s="1" t="n">
-        <v>-0.002</v>
-      </c>
       <c r="U31" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V31" s="1" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="W31" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="X31" s="1" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="Y31" s="1" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="Z31" s="1" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="AA31" s="1" t="n">
         <v>0.013</v>
-      </c>
-      <c r="V31" s="1" t="n">
-        <v>0.142</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="Z31" s="1" t="n">
-        <v>1.732</v>
-      </c>
-      <c r="AA31" s="1" t="n">
-        <v>0.014</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.81</v>
+        <v>80.92</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.301</v>
+        <v>0.303</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.209</v>
+        <v>0.222</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.751</v>
+        <v>0.744</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>38.18</v>
+        <v>37.92</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.031</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.028</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.013</v>
+        <v>0.021</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.069</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.144</v>
+        <v>0.136</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.316</v>
+        <v>0.309</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.307</v>
+        <v>1.291</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.049</v>
+        <v>0.041</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>44.79</v>
+        <v>45.49</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S32" s="1" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="T32" s="1" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>-0.071</v>
+      </c>
+      <c r="V32" s="1" t="n">
         <v>-0.018</v>
       </c>
-      <c r="S32" s="1" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="T32" s="1" t="n">
+      <c r="W32" s="1" t="n">
         <v>-0.105</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>-0.067</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>-0.103</v>
-      </c>
       <c r="X32" s="1" t="n">
-        <v>-0.111</v>
+        <v>-0.097</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.017</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.158</v>
+        <v>1.17</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.051</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,34 +4783,34 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.7</v>
+        <v>29.71</v>
       </c>
       <c r="AF32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.197</v>
+        <v>0.213</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.13</v>
+        <v>1.128</v>
       </c>
       <c r="AO32" s="1" t="n">
         <v>0.017</v>
@@ -4824,7 +4824,7 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.67</v>
+        <v>52.74</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>0.001</v>
@@ -4833,28 +4833,28 @@
         <v>-0.011</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.009</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.069</v>
+        <v>0.071</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.323</v>
+        <v>0.348</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.454</v>
+        <v>1.462</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.024</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>91.6</v>
+        <v>91.51</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="S33" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.097</v>
+        <v>0.073</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.305</v>
+        <v>0.321</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.298</v>
+        <v>0.282</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.621</v>
+        <v>0.619</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.643</v>
+        <v>0.662</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.308</v>
+        <v>1.289</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,31 +4902,31 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.3</v>
+        <v>48.28</v>
       </c>
       <c r="AF33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AJ33" s="1" t="n">
         <v>0.031</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.07</v>
+        <v>0.065</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>91.23</v>
+        <v>92.44</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.013</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.012</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.079</v>
+        <v>0.093</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.158</v>
+        <v>0.171</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.183</v>
+        <v>0.213</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.387</v>
+        <v>0.392</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.792</v>
+        <v>0.816</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.462</v>
+        <v>0.507</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.55</v>
+        <v>1.553</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.13</v>
+        <v>0.145</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>176.36</v>
+        <v>175.3</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.263</v>
+        <v>0.281</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.274</v>
+        <v>0.275</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.406</v>
+        <v>0.398</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.107</v>
+        <v>0.131</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.098</v>
+        <v>1.082</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.9</v>
+        <v>105.69</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.127</v>
+        <v>0.139</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.232</v>
+        <v>0.251</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.533</v>
+        <v>0.545</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.147</v>
+        <v>0.196</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.508</v>
+        <v>2.535</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.43</v>
+        <v>60.67</v>
       </c>
       <c r="D35" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E35" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>-0.003</v>
-      </c>
       <c r="F35" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.033</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>-0.013</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.153</v>
+        <v>0.147</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.252</v>
+        <v>-0.232</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.883</v>
+        <v>0.898</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.41</v>
+        <v>59.67</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.004</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.01</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.074</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.036</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.079</v>
+        <v>-0.064</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.16</v>
+        <v>0.165</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.084</v>
+        <v>0.103</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.205</v>
+        <v>2.174</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.04</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.95</v>
+        <v>23.86</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.022</v>
+        <v>0.013</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.151</v>
+        <v>0.145</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.467</v>
+        <v>0.448</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.357</v>
+        <v>0.352</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.061</v>
+        <v>0.071</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.881</v>
+        <v>0.876</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.127</v>
+        <v>0.123</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.09</v>
+        <v>30.8</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.009</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.054</v>
+        <v>0.035</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.168</v>
+        <v>0.137</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.361</v>
+        <v>0.4</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.347</v>
+        <v>0.334</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.328</v>
+        <v>-0.315</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.187</v>
+        <v>0.176</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>75.73</v>
+        <v>77.06</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.035</v>
+        <v>0.018</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.039</v>
+        <v>0.056</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.086</v>
+        <v>0.105</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.267</v>
+        <v>0.283</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.328</v>
+        <v>0.36</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.507</v>
+        <v>0.539</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.104</v>
+        <v>1.14</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.849</v>
+        <v>0.913</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>4.001</v>
+        <v>4.006</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.192</v>
+        <v>0.213</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>122.35</v>
+        <v>124.17</v>
       </c>
       <c r="R37" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="T37" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="U37" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="S37" s="1" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="T37" s="1" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="U37" s="1" t="n">
-        <v>0.004</v>
-      </c>
       <c r="V37" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.007</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.071</v>
+        <v>0.09</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.624</v>
+        <v>0.648</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.79</v>
+        <v>0.851</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.698</v>
+        <v>2.699</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.037</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>97.2</v>
+        <v>96.97</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.002</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.059</v>
+        <v>0.033</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.249</v>
+        <v>0.246</v>
       </c>
       <c r="AJ37" s="1" t="n">
         <v>0.529</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.746</v>
+        <v>0.764</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.831</v>
+        <v>1.825</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.829</v>
+        <v>1.876</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.098</v>
+        <v>3.068</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.197</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>144.55</v>
+        <v>148.89</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.106</v>
+        <v>0.12</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.225</v>
+        <v>0.262</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.637</v>
+        <v>0.695</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.011</v>
+        <v>1.093</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.572</v>
+        <v>1.645</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.649</v>
+        <v>1.729</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.784</v>
+        <v>0.857</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.726</v>
+        <v>2.824</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.487</v>
+        <v>0.531</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>62.7</v>
+        <v>63.79</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.016</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.093</v>
+        <v>0.082</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.046</v>
+        <v>0.071</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.146</v>
+        <v>0.164</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.414</v>
+        <v>0.439</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.377</v>
+        <v>0.441</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.856</v>
+        <v>1.866</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.033</v>
+        <v>0.051</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>79.08</v>
+        <v>80.04</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.012</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.192</v>
+        <v>0.142</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.149</v>
+        <v>-0.139</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.696</v>
+        <v>0.715</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.238</v>
+        <v>1.286</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.686</v>
+        <v>1.776</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.142</v>
+        <v>3.193</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.049</v>
+        <v>2.151</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.446</v>
+        <v>4.554</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.228</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>30.18</v>
+        <v>30.52</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.041</v>
+        <v>0.052</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.282</v>
+        <v>0.272</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.374</v>
+        <v>0.383</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.812</v>
+        <v>0.832</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.949</v>
+        <v>0.971</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.524</v>
+        <v>0.607</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.375</v>
+        <v>1.39</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>68.67</v>
+        <v>69.87</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.017</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.021</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.016</v>
+        <v>0.033</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.121</v>
+        <v>0.109</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.072</v>
+        <v>0.097</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.156</v>
+        <v>0.175</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.218</v>
+        <v>0.24</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.16</v>
+        <v>0.216</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.539</v>
+        <v>1.543</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.06</v>
+        <v>0.078</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>197.63</v>
+        <v>207.26</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.001</v>
+        <v>0.049</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.08</v>
+        <v>0.095</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.217</v>
+        <v>-0.178</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.405</v>
+        <v>0.466</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.594</v>
+        <v>0.695</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.241</v>
+        <v>1.344</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.343</v>
+        <v>1.457</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.662</v>
+        <v>0.809</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.182</v>
+        <v>1.32</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.06</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>79.25</v>
+        <v>80.27</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.269</v>
+        <v>0.277</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.422</v>
+        <v>0.451</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.836</v>
+        <v>0.857</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.286</v>
+        <v>1.316</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.013</v>
+        <v>1.149</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.866</v>
+        <v>1.881</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.152</v>
+        <v>0.167</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>135.02</v>
+        <v>135.15</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.517</v>
+        <v>0.518</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.017</v>
+        <v>1.064</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.503</v>
+        <v>2.458</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.3</v>
+        <v>36.78</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.039</v>
+        <v>0.034</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.167</v>
+        <v>0.18</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.278</v>
+        <v>0.297</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.509</v>
+        <v>0.529</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.357</v>
+        <v>0.408</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.571</v>
+        <v>1.658</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.038</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.58</v>
+        <v>30.16</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.004</v>
+        <v>0.02</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.009</v>
+        <v>0.029</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.08</v>
+        <v>0.102</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.183</v>
+        <v>0.197</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.104</v>
+        <v>0.143</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.24</v>
+        <v>0.269</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.436</v>
+        <v>0.464</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.408</v>
+        <v>0.468</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.542</v>
+        <v>1.589</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.129</v>
+        <v>0.152</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>169.59</v>
+        <v>173.34</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.014</v>
+        <v>0.022</v>
       </c>
       <c r="S41" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.062</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.001</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.13</v>
+        <v>0.168</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.73</v>
+        <v>0.768</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>0.989</v>
+        <v>1.057</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.764</v>
+        <v>4.797</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.034</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>74.09</v>
+        <v>74.84</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.05</v>
+        <v>0.061</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.182</v>
+        <v>0.206</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.373</v>
+        <v>0.378</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.715</v>
+        <v>0.732</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.519</v>
+        <v>0.563</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.674</v>
+        <v>1.673</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.104</v>
+        <v>0.115</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>23.31</v>
+        <v>24.23</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.014</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.166</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.201</v>
+        <v>-0.178</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.274</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.242</v>
+        <v>-0.202</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.133</v>
+        <v>0.178</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.493</v>
+        <v>-0.453</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.177</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>104.66</v>
+        <v>105.66</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.149</v>
+        <v>0.146</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.143</v>
+        <v>0.169</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.67</v>
+        <v>0.686</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.601</v>
+        <v>0.644</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.641</v>
+        <v>1.635</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>192.22</v>
+        <v>195.98</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.019</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.003</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.06</v>
+        <v>0.082</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.21</v>
+        <v>0.254</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.343</v>
+        <v>1.389</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.184</v>
+        <v>1.314</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.253</v>
+        <v>7.311</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.019</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>54.95</v>
+        <v>55.19</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.028</v>
+        <v>0.004</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.071</v>
+        <v>0.042</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.032</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.33</v>
+        <v>0.317</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.244</v>
+        <v>1.296</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.995</v>
+        <v>2.008</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.643</v>
+        <v>2.665</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.08</v>
+        <v>5.18</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.286</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.79</v>
+        <v>45.18</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.05</v>
+        <v>0.059</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>0.137</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.167</v>
+        <v>0.185</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.274</v>
+        <v>0.279</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.715</v>
+        <v>0.73</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1</v>
+        <v>1.046</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.333</v>
+        <v>2.318</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.083</v>
+        <v>0.092</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>78.41</v>
+        <v>80.85</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.019</v>
+        <v>0.031</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.014</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.173</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.233</v>
+        <v>-0.216</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.27</v>
+        <v>-0.242</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.21</v>
+        <v>-0.172</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.409</v>
+        <v>0.452</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.064</v>
+        <v>0.141</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.376</v>
+        <v>3.398</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.258</v>
+        <v>-0.235</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>80.76</v>
+        <v>79.73</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.013</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.066</v>
+        <v>0.004</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.092</v>
+        <v>0.078</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.147</v>
+        <v>0.151</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.082</v>
+        <v>0.053</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.063</v>
+        <v>0.076</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.204</v>
+        <v>0.188</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.9</v>
+        <v>0.878</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.175</v>
+        <v>0.133</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.168</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>62.62</v>
+        <v>63.31</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.06</v>
+        <v>0.072</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.184</v>
+        <v>0.192</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.255</v>
+        <v>0.276</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.451</v>
+        <v>0.466</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.761</v>
+        <v>0.78</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.263</v>
+        <v>0.306</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.583</v>
+        <v>1.603</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.145</v>
+        <v>0.157</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>71.24</v>
+        <v>72.63</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.056</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.093</v>
+        <v>-0.075</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.132</v>
+        <v>-0.131</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.144</v>
+        <v>-0.12</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.076</v>
+        <v>-0.05</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.547</v>
+        <v>0.577</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.226</v>
+        <v>0.297</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.49</v>
+        <v>2.466</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.096</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.91</v>
+        <v>33.65</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.067</v>
+        <v>0.011</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.105</v>
+        <v>0.096</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.121</v>
+        <v>0.098</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.107</v>
+        <v>0.124</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.234</v>
+        <v>0.225</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.034</v>
+        <v>1.027</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.108</v>
+        <v>2.054</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.197</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.43</v>
+        <v>33.56</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="E46" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.143</v>
+        <v>0.127</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.149</v>
+        <v>0.163</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.099</v>
+        <v>0.103</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>362.04</v>
+        <v>368</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.022</v>
+        <v>0.028</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.05</v>
+        <v>0.068</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.283</v>
+        <v>0.3</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.459</v>
+        <v>0.486</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.667</v>
+        <v>0.73</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.735</v>
+        <v>1.78</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.62</v>
+        <v>1.824</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.479</v>
+        <v>13.541</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.202</v>
+        <v>0.222</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.46</v>
+        <v>11.6</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.024</v>
+        <v>0.012</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.023</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.205</v>
+        <v>-0.161</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.029</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.46</v>
+        <v>-0.467</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.663</v>
+        <v>-0.658</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.727</v>
+        <v>-0.719</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.89</v>
+        <v>-0.885</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.065</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.35</v>
+        <v>49.72</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.04</v>
+        <v>0.048</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.138</v>
+        <v>0.134</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.138</v>
+        <v>0.161</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.259</v>
+        <v>0.262</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.577</v>
+        <v>0.588</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.531</v>
+        <v>0.572</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.653</v>
+        <v>1.675</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.086</v>
+        <v>0.094</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.21</v>
+        <v>126.74</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.022</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.01</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.065</v>
+        <v>0.087</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.211</v>
+        <v>0.256</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.442</v>
+        <v>1.492</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.055</v>
+        <v>1.176</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.679</v>
+        <v>6.74</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.019</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.23</v>
+        <v>44.8</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.016</v>
+        <v>0.028</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.074</v>
+        <v>0.087</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.217</v>
+        <v>0.25</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.586</v>
+        <v>0.585</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.908</v>
+        <v>0.933</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.909</v>
+        <v>0.95</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.932</v>
+        <v>1.948</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.121</v>
+        <v>0.136</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.1</v>
+        <v>52.42</v>
       </c>
       <c r="R48" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="S48" s="1" t="n">
         <v>0.024</v>
       </c>
-      <c r="S48" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T48" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.005</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.114</v>
+        <v>0.135</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.216</v>
+        <v>0.255</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.351</v>
+        <v>0.419</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.763</v>
+        <v>0.808</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.112</v>
+        <v>0.185</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.061</v>
+        <v>0.088</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.01</v>
+        <v>26.12</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.019</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.448</v>
+        <v>0.454</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.674</v>
+        <v>0.687</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.51</v>
+        <v>0.519</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.44</v>
+        <v>53.08</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.039</v>
+        <v>0.052</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.147</v>
+        <v>0.177</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.378</v>
+        <v>0.388</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.833</v>
+        <v>0.855</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.627</v>
+        <v>0.679</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.895</v>
+        <v>1.887</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.093</v>
+        <v>0.107</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.26</v>
+        <v>36.08</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.02</v>
+        <v>0.044</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.076</v>
+        <v>0.097</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.162</v>
+        <v>0.19</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.344</v>
+        <v>0.41</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.059</v>
+        <v>0.083</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.59</v>
+        <v>17.7</v>
       </c>
       <c r="AF49" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AG49" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AH49" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AI49" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AJ49" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK49" s="1" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="AL49" s="1" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AM49" s="1" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AN49" s="1" t="n">
+        <v>-0.152</v>
+      </c>
+      <c r="AO49" s="1" t="n">
         <v>-0.002</v>
-      </c>
-      <c r="AG49" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AH49" s="1" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AI49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AK49" s="1" t="n">
-        <v>-0.119</v>
-      </c>
-      <c r="AL49" s="1" t="n">
-        <v>-0.314</v>
-      </c>
-      <c r="AM49" s="1" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="AN49" s="1" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="AO49" s="1" t="n">
-        <v>-0.008</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.4</v>
+        <v>39.37</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.001</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.235</v>
+        <v>0.227</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.288</v>
+        <v>0.284</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.841</v>
+        <v>0.839</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.401</v>
+        <v>0.425</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.758</v>
+        <v>0.744</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.87</v>
+        <v>21.75</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.053</v>
+        <v>0.029</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.054</v>
+        <v>0.048</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.051</v>
+        <v>0.041</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.151</v>
+        <v>-0.147</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.398</v>
+        <v>-0.401</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.327</v>
+        <v>-0.326</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.497</v>
+        <v>-0.498</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.095</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.1</v>
+        <v>52.85</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.083</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.126</v>
+        <v>-0.114</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.159</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.035</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.491</v>
+        <v>0.512</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.047</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.414</v>
+        <v>1.457</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.125</v>
+        <v>-0.113</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.57</v>
+        <v>23.74</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.052</v>
+        <v>0.065</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.068</v>
+        <v>0.077</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.156</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.105</v>
+        <v>0.124</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.359</v>
+        <v>0.379</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.078</v>
+        <v>0.086</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>36.53</v>
+        <v>39.23</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.074</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.048</v>
+        <v>0.045</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.279</v>
+        <v>-0.226</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.278</v>
+        <v>-0.208</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.449</v>
+        <v>-0.376</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.316</v>
+        <v>-0.216</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.264</v>
+        <v>-0.21</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.14</v>
+        <v>49.49</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.143</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.109</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.152</v>
+        <v>-0.147</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.039</v>
+        <v>0.05</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.48</v>
+        <v>0.491</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.323</v>
+        <v>-0.297</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.932</v>
+        <v>1.97</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.104</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.03</v>
+        <v>15.68</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.118</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.068</v>
+        <v>0.072</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.368</v>
+        <v>-0.294</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.375</v>
+        <v>-0.291</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.617</v>
+        <v>-0.531</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.167</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.374</v>
+        <v>-0.301</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.4</v>
+        <v>93.75</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.015</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.117</v>
+        <v>-0.104</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.145</v>
+        <v>-0.133</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.186</v>
+        <v>-0.172</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.021</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>1.046</v>
+        <v>1.076</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.328</v>
+        <v>0.386</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.095</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7147,31 +7147,31 @@
         <v>9.33</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="AH53" s="1" t="n">
         <v>-0.023</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.028</v>
       </c>
       <c r="AJ53" s="1" t="n">
         <v>-0.151</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.254</v>
+        <v>-0.268</v>
       </c>
       <c r="AL53" s="1" t="n">
         <v>-0.086</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.202</v>
+        <v>0.221</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.024</v>
       </c>
       <c r="AO53" s="1" t="n">
         <v>-0.044</v>
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>60.64</v>
+        <v>61.52</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.04</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.121</v>
+        <v>-0.108</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>-0.033</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.128</v>
+        <v>-0.106</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.054</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.408</v>
+        <v>0.428</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.118</v>
+        <v>0.163</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.405</v>
+        <v>1.419</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.083</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.03</v>
+        <v>119.44</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.014</v>
+        <v>0.033</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.097</v>
+        <v>0.101</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.066</v>
+        <v>0.072</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.099</v>
+        <v>0.116</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.191</v>
+        <v>0.199</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.563</v>
+        <v>0.568</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.802</v>
+        <v>0.826</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.667</v>
+        <v>1.652</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.098</v>
+        <v>0.102</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.32</v>
+        <v>39.66</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.047</v>
+        <v>0.058</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.101</v>
+        <v>0.115</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.161</v>
+        <v>0.183</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>0.321</v>
       </c>
-      <c r="L55" s="1" t="n">
-        <v>0.312</v>
-      </c>
       <c r="M55" s="1" t="n">
-        <v>0.034</v>
+        <v>0.043</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.2</v>
+        <v>47.36</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.018</v>
+        <v>0.038</v>
       </c>
       <c r="T55" s="1" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="U55" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V55" s="1" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="W55" s="1" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="X55" s="1" t="n">
+        <v>0.559</v>
+      </c>
+      <c r="Y55" s="1" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="Z55" s="1" t="n">
+        <v>1.744</v>
+      </c>
+      <c r="AA55" s="1" t="n">
         <v>0.109</v>
-      </c>
-      <c r="U55" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="V55" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="W55" s="1" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="X55" s="1" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="Y55" s="1" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="Z55" s="1" t="n">
-        <v>1.762</v>
-      </c>
-      <c r="AA55" s="1" t="n">
-        <v>0.106</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.49</v>
+        <v>27.38</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.039</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.031</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.074</v>
+        <v>0.032</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.181</v>
+        <v>-0.187</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.242</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.363</v>
+        <v>-0.393</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.855</v>
+        <v>-0.86</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.969</v>
+        <v>-0.975</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.076</v>
+        <v>0.034</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.96</v>
+        <v>72.69</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.004</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.108</v>
+        <v>0.089</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.402</v>
+        <v>0.397</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.52</v>
+        <v>0.532</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.79</v>
+        <v>2.755</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.76</v>
+        <v>100.37</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.004</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="U57" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>0.049</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>0.047</v>
-      </c>
       <c r="W57" s="1" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="X57" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y57" s="1" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="Z57" s="1" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AA57" s="1" t="n">
         <v>0.069</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="Y57" s="1" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="Z57" s="1" t="n">
-        <v>0.939</v>
-      </c>
-      <c r="AA57" s="1" t="n">
-        <v>0.073</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.36</v>
+        <v>89.22</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.004</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.053</v>
+        <v>0.041</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.083</v>
+        <v>0.088</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.078</v>
+        <v>0.06</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.384</v>
+        <v>0.409</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.074</v>
+        <v>1.029</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.13</v>
+        <v>94.87</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.069</v>
+        <v>0.056</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.075</v>
+        <v>0.059</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.252</v>
+        <v>0.249</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.26</v>
+        <v>0.281</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.865</v>
+        <v>0.823</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.075</v>
+        <v>0.072</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7747,31 +7747,31 @@
         <v>22.43</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.01</v>
       </c>
       <c r="T60" s="1" t="n">
         <v>-0.046</v>
       </c>
       <c r="U60" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="V60" s="1" t="n">
         <v>0.052</v>
       </c>
-      <c r="V60" s="1" t="n">
-        <v>0.044</v>
-      </c>
       <c r="W60" s="1" t="n">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
       <c r="X60" s="1" t="n">
         <v>0.21</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.549</v>
+        <v>0.523</v>
       </c>
       <c r="AA60" s="1" t="n">
         <v>0.011</v>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>97.05</v>
+        <v>97.48</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.124</v>
+        <v>0.129</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.142</v>
+        <v>0.134</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.17</v>
+        <v>0.179</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.237</v>
+        <v>0.241</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.479</v>
+        <v>0.485</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.509</v>
+        <v>0.537</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>2.022</v>
+        <v>1.994</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/25/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/26/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>340.04</v>
+        <v>336.91</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.009</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.014</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.071</v>
+        <v>0.057</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.181</v>
+        <v>0.169</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.977</v>
+        <v>0.959</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.073</v>
+        <v>1.066</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.556</v>
+        <v>3.529</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.018</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>57.93</v>
+        <v>58.16</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.238</v>
+        <v>0.233</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.26</v>
+        <v>0.271</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.409</v>
+        <v>0.415</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.578</v>
+        <v>1.652</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.561</v>
+        <v>1.558</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.219</v>
+        <v>0.224</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,7 +1744,7 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.04</v>
+        <v>83.07</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>0</v>
@@ -1768,10 +1768,10 @@
         <v>0.144</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
       <c r="AO5" s="1" t="n">
         <v>0.006</v>
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>696.25</v>
+        <v>692.41</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.085</v>
+        <v>0.075</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.181</v>
+        <v>0.174</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.824</v>
+        <v>0.814</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>0.948</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.186</v>
+        <v>3.17</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>105.47</v>
+        <v>106.19</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.007</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.112</v>
+        <v>0.122</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.166</v>
+        <v>0.159</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.167</v>
+        <v>0.177</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.169</v>
+        <v>0.186</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.291</v>
+        <v>0.3</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.516</v>
+        <v>1.598</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.049</v>
+        <v>2.017</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.182</v>
+        <v>0.19</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,19 +1863,19 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.17</v>
+        <v>120.38</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="AJ6" s="1" t="n">
         <v>0.027</v>
@@ -1884,16 +1884,16 @@
         <v>0.062</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.153</v>
+        <v>0.155</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.155</v>
+        <v>0.16</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.78</v>
+        <v>72.07</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0.118</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.176</v>
+        <v>0.179</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.445</v>
+        <v>0.451</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.547</v>
+        <v>0.555</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.133</v>
+        <v>2.13</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.088</v>
+        <v>0.092</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.04</v>
+        <v>28.92</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.031</v>
+        <v>0.014</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.165</v>
+        <v>0.138</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.417</v>
+        <v>0.409</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.573</v>
+        <v>0.58</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.488</v>
+        <v>0.499</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.407</v>
+        <v>0.401</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.163</v>
+        <v>1.183</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.114</v>
+        <v>0.074</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.391</v>
+        <v>0.386</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,19 +1982,19 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.34</v>
+        <v>97.6</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="AJ7" s="1" t="n">
         <v>0.038</v>
@@ -2003,16 +2003,16 @@
         <v>0.068</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.133</v>
+        <v>0.136</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.038</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.095</v>
+        <v>0.103</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>264.58</v>
+        <v>265.99</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.083</v>
+        <v>0.079</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.242</v>
+        <v>0.247</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.465</v>
+        <v>0.473</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.287</v>
+        <v>0.296</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.937</v>
+        <v>1.934</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.09</v>
+        <v>18.67</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.022</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.045</v>
+        <v>0.026</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.171</v>
+        <v>0.12</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.337</v>
+        <v>0.308</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.689</v>
+        <v>0.646</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.059</v>
+        <v>0.036</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.226</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.723</v>
+        <v>1.66</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.162</v>
+        <v>0.136</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>104.1</v>
+        <v>104.48</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AH8" s="1" t="n">
         <v>0.024</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.082</v>
+        <v>0.085</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.138</v>
+        <v>-0.158</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.029</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.82</v>
+        <v>26.63</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.118</v>
+        <v>0.089</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.138</v>
+        <v>0.132</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.22</v>
+        <v>0.216</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.323</v>
+        <v>0.313</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.167</v>
+        <v>1.206</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.593</v>
+        <v>1.554</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.14</v>
+        <v>0.132</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.91</v>
+        <v>90.27</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AH9" s="1" t="n">
         <v>0.026</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.239</v>
+        <v>-0.26</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.104</v>
+        <v>-0.091</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>187.39</v>
+        <v>187.16</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>0.025</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.069</v>
+        <v>0.066</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.287</v>
+        <v>0.264</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.276</v>
+        <v>0.271</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.475</v>
+        <v>0.473</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.738</v>
+        <v>0.761</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.217</v>
+        <v>0.216</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.41</v>
+        <v>111.71</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.141</v>
+        <v>0.144</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.087</v>
+        <v>0.077</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.315</v>
+        <v>0.322</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>225.04</v>
+        <v>225.38</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.091</v>
+        <v>0.086</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>0.133</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.186</v>
+        <v>0.193</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.546</v>
+        <v>0.548</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.707</v>
+        <v>0.73</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.994</v>
+        <v>1.999</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.07</v>
+        <v>0.072</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>64.42</v>
+        <v>64.13</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.005</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.088</v>
+        <v>0.076</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.42</v>
+        <v>0.387</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.596</v>
+        <v>0.593</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.713</v>
+        <v>0.706</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.891</v>
+        <v>0.941</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.924</v>
+        <v>4.898</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.255</v>
+        <v>0.249</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,7 +2410,7 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.06</v>
+        <v>103.21</v>
       </c>
       <c r="AF11" s="1" t="n">
         <v>0.001</v>
@@ -2419,28 +2419,28 @@
         <v>0.002</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ11" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.168</v>
+        <v>0.17</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>458.5</v>
+        <v>454.15</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.036</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.042</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>1.041</v>
+        <v>1.021</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.982</v>
+        <v>0.958</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.291</v>
+        <v>4.245</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.04</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.4</v>
+        <v>97.54</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.044</v>
+        <v>0.059</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.442</v>
+        <v>0.41</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.865</v>
+        <v>0.864</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.878</v>
+        <v>1.9</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.722</v>
+        <v>3.828</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.889</v>
+        <v>3.132</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.62</v>
+        <v>6.024</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.295</v>
+        <v>0.325</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.75</v>
+        <v>108.92</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG12" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AK12" s="1" t="n">
         <v>0.045</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.073</v>
+        <v>0.072</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.243</v>
+        <v>0.247</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>205.45</v>
+        <v>204.8</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.051</v>
+        <v>0.041</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.096</v>
+        <v>0.089</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.79</v>
+        <v>0.785</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.869</v>
+        <v>0.871</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.806</v>
+        <v>2.81</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>45.25</v>
+        <v>46.47</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.007</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.634</v>
+        <v>0.581</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.464</v>
+        <v>2.474</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.968</v>
+        <v>4.102</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.893</v>
+        <v>2.118</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.169</v>
+        <v>6.464</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.32</v>
+        <v>0.356</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2651,28 +2651,28 @@
         <v>23.35</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.113</v>
+        <v>0.107</v>
       </c>
       <c r="AN13" s="1" t="n">
         <v>0.287</v>
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.41</v>
+        <v>96.8</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.042</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.427</v>
+        <v>0.433</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.574</v>
+        <v>0.596</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.738</v>
+        <v>1.771</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>57.3</v>
+        <v>56.96</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.006</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.099</v>
+        <v>0.071</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.508</v>
+        <v>0.464</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.82</v>
+        <v>0.798</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.256</v>
+        <v>1.231</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.293</v>
+        <v>0.285</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.47</v>
+        <v>76.4</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG14" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
       <c r="AK14" s="1" t="n">
         <v>0.125</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.04</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.044</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>256.38</v>
+        <v>254.89</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.053</v>
+        <v>0.032</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.061</v>
+        <v>0.045</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.194</v>
+        <v>0.18</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.883</v>
+        <v>0.872</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.678</v>
+        <v>0.655</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.77</v>
+        <v>18.43</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.048</v>
+        <v>-0.018</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.094</v>
+        <v>0.082</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.034</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.311</v>
+        <v>0.249</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.872</v>
+        <v>0.848</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1.166</v>
+        <v>1.089</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.202</v>
+        <v>0.18</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.74</v>
+        <v>97.68</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.137</v>
+        <v>0.131</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.473</v>
+        <v>0.47</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.76</v>
+        <v>138.42</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.079</v>
+        <v>0.071</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.14</v>
+        <v>0.134</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.152</v>
+        <v>0.15</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.189</v>
+        <v>0.2</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.526</v>
+        <v>0.522</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.818</v>
+        <v>0.851</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.642</v>
+        <v>1.66</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,34 +2954,34 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>78.53</v>
+        <v>78.58</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.001</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.016</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.155</v>
+        <v>0.141</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.021</v>
+        <v>0.039</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.288</v>
+        <v>1.275</v>
       </c>
       <c r="AA16" s="1" t="n">
         <v>0.091</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>43</v>
+        <v>42.93</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="AG16" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.084</v>
+        <v>0.081</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.181</v>
+        <v>0.177</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.28</v>
+        <v>0.278</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.065</v>
+        <v>0.069</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.307</v>
+        <v>0.314</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>150.59</v>
+        <v>149.85</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.005</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.078</v>
+        <v>0.069</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.172</v>
+        <v>0.165</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.782</v>
+        <v>0.773</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.19</v>
+        <v>109.84</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.006</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>0.091</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.157</v>
+        <v>0.15</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.195</v>
+        <v>0.19</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.525</v>
+        <v>0.52</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.464</v>
+        <v>1.478</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.47</v>
+        <v>1.468</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.061</v>
+        <v>4.055</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.179</v>
+        <v>0.186</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.81</v>
+        <v>42.86</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.177</v>
+        <v>-0.175</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.045</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>159.77</v>
+        <v>160.93</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.104</v>
+        <v>0.103</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.186</v>
+        <v>0.195</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.651</v>
+        <v>0.663</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.674</v>
+        <v>0.697</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.59</v>
+        <v>2.603</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.078</v>
+        <v>0.086</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.81</v>
+        <v>36.56</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.003</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.086</v>
+        <v>0.079</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.213</v>
+        <v>0.197</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.299</v>
+        <v>0.28</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.518</v>
+        <v>0.502</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.18</v>
+        <v>0.172</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.59</v>
+        <v>58.15</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.033</v>
+        <v>0.044</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.127</v>
+        <v>0.123</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>0.222</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.415</v>
+        <v>0.426</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.796</v>
+        <v>0.814</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.941</v>
+        <v>1.002</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.306</v>
+        <v>2.317</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.068</v>
+        <v>0.078</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>80.44</v>
+        <v>82.22</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.022</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.015</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.046</v>
+        <v>0.071</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.128</v>
+        <v>0.137</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.134</v>
+        <v>0.151</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.17</v>
+        <v>0.196</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.462</v>
+        <v>0.495</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.446</v>
+        <v>0.481</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.727</v>
+        <v>1.774</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.08</v>
+        <v>0.103</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,13 +3365,13 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101.04</v>
+        <v>101.2</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH20" s="1" t="n">
         <v>0.013</v>
@@ -3380,22 +3380,22 @@
         <v>0.012</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="AK20" s="1" t="n">
         <v>0.063</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.16</v>
+        <v>0.162</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.208</v>
+        <v>0.212</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>37.32</v>
+        <v>36.8</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.032</v>
+        <v>0.01</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.067</v>
+        <v>0.048</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.26</v>
+        <v>0.218</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.431</v>
+        <v>0.417</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.68</v>
+        <v>0.663</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.837</v>
+        <v>0.811</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.971</v>
+        <v>0.983</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.898</v>
+        <v>1.897</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.226</v>
+        <v>0.209</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>241.22</v>
+        <v>242.82</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.007</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.026</v>
+        <v>0.04</v>
       </c>
       <c r="U21" s="1" t="n">
         <v>0.192</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.239</v>
+        <v>0.219</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.614</v>
+        <v>0.617</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.142</v>
+        <v>1.156</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.588</v>
+        <v>1.653</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.783</v>
+        <v>3.794</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.124</v>
+        <v>0.131</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,16 +3484,16 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.69</v>
+        <v>50.74</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AI21" s="1" t="n">
         <v>0.012</v>
@@ -3505,16 +3505,16 @@
         <v>0.041</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.07</v>
+        <v>0.066</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.45</v>
+        <v>80.66</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.057</v>
+        <v>0.052</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.21</v>
+        <v>0.211</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.329</v>
+        <v>0.338</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.635</v>
+        <v>0.625</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.552</v>
+        <v>0.556</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.326</v>
+        <v>1.318</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.158</v>
+        <v>1.186</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.16</v>
+        <v>0.163</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.11</v>
+        <v>102.62</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.012</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.026</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.01</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.064</v>
+        <v>0.073</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.656</v>
+        <v>0.664</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.17</v>
+        <v>2.197</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,28 +3603,28 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.64</v>
+        <v>49.55</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AH22" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI22" s="1" t="n">
         <v>0.012</v>
       </c>
-      <c r="AI22" s="1" t="n">
-        <v>0.014</v>
-      </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.077</v>
+        <v>0.069</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="AM22" s="1" t="n">
         <v>0.058</v>
@@ -3633,7 +3633,7 @@
         <v>0.262</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>39.59</v>
+        <v>39.1</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.041</v>
+        <v>0.013</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.082</v>
+        <v>0.068</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.259</v>
+        <v>0.209</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.426</v>
+        <v>0.415</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.651</v>
+        <v>0.657</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.729</v>
+        <v>0.707</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.781</v>
+        <v>0.82</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.247</v>
+        <v>2.263</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.246</v>
+        <v>0.231</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>106.43</v>
+        <v>107.24</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.008</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.028</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.039</v>
+        <v>0.034</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.03</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.072</v>
+        <v>0.093</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.636</v>
+        <v>0.649</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.88</v>
+        <v>0.857</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.632</v>
+        <v>3.65</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.105</v>
+        <v>0.114</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.52</v>
+        <v>96.75</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AH23" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="AM23" s="1" t="n">
         <v>0.03</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.158</v>
+        <v>0.161</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>69.23</v>
+        <v>69.06</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.132</v>
+        <v>0.117</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.341</v>
+        <v>0.336</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.754</v>
+        <v>0.766</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.826</v>
+        <v>1.827</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>41.29</v>
+        <v>41.06</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.122</v>
+        <v>0.096</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.172</v>
+        <v>0.15</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.363</v>
+        <v>0.331</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.158</v>
+        <v>0.152</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.089</v>
+        <v>0.083</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.65</v>
+        <v>111.72</v>
       </c>
       <c r="AF24" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG24" s="1" t="n">
         <v>0</v>
-      </c>
-      <c r="AG24" s="1" t="n">
-        <v>0.001</v>
       </c>
       <c r="AH24" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>47.29</v>
+        <v>47.15</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.046</v>
+        <v>0.041</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.116</v>
+        <v>0.103</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.15</v>
+        <v>0.154</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.219</v>
+        <v>0.212</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.66</v>
+        <v>0.655</v>
       </c>
       <c r="K25" s="1" t="n">
         <v>1.001</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.259</v>
+        <v>2.23</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.69</v>
+        <v>87.67</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.011</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.013</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="V25" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="AA25" s="1" t="n">
         <v>0.028</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="Z25" s="1" t="n">
-        <v>1.332</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>0.016</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,19 +3958,19 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>93.06</v>
+        <v>92.94</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="AH25" s="1" t="n">
         <v>-0.008</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="AJ25" s="1" t="n">
         <v>0.029</v>
@@ -3979,16 +3979,16 @@
         <v>0.057</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AM25" s="1" t="n">
         <v>0.276</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.621</v>
+        <v>0.615</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.66</v>
+        <v>48.61</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.001</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.068</v>
+        <v>0.061</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.167</v>
+        <v>0.153</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>0.187</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.703</v>
+        <v>0.701</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.913</v>
+        <v>0.95</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.411</v>
+        <v>1.41</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.62</v>
+        <v>62.08</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.014</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.022</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.026</v>
+        <v>0.042</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.118</v>
+        <v>0.136</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.523</v>
+        <v>0.559</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.831</v>
+        <v>0.877</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.012</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.64</v>
+        <v>26.66</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.158</v>
+        <v>0.134</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>48.02</v>
+        <v>48.35</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.055</v>
+        <v>0.059</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.095</v>
+        <v>0.094</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.123</v>
+        <v>0.141</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.237</v>
+        <v>0.246</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.444</v>
+        <v>0.454</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.637</v>
+        <v>0.669</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.746</v>
+        <v>1.778</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.067</v>
+        <v>0.075</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.06</v>
+        <v>27.25</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.007</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.103</v>
+        <v>0.099</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,7 +4188,7 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.17</v>
+        <v>53.19</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>0</v>
@@ -4197,28 +4197,28 @@
         <v>0.001</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="AK27" s="1" t="n">
         <v>0.065</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.138</v>
+        <v>0.136</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.35</v>
+        <v>44.56</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.104</v>
+        <v>0.098</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.053</v>
+        <v>0.058</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.233</v>
+        <v>0.234</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.755</v>
+        <v>0.763</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.555</v>
+        <v>0.574</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.39</v>
+        <v>1.402</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.51</v>
+        <v>76.72</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.003</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="T28" s="1" t="n">
         <v>0.087</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.107</v>
+        <v>0.115</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.107</v>
+        <v>0.128</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.271</v>
+        <v>0.274</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.519</v>
+        <v>0.54</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.664</v>
+        <v>1.693</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.41</v>
+        <v>54.47</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH28" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="AK28" s="1" t="n">
         <v>0.085</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.095</v>
+        <v>0.089</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.401</v>
+        <v>0.403</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.85</v>
+        <v>64.63</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.133</v>
+        <v>0.123</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.18</v>
+        <v>0.173</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.271</v>
+        <v>0.266</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.577</v>
+        <v>0.571</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.648</v>
+        <v>0.651</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.79</v>
+        <v>1.791</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.07</v>
+        <v>45.96</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.098</v>
+        <v>0.089</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.183</v>
+        <v>0.195</v>
       </c>
       <c r="V29" s="1" t="n">
         <v>0.146</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.248</v>
+        <v>0.258</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.312</v>
+        <v>0.321</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.645</v>
+        <v>1.624</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,10 +4426,10 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.37</v>
+        <v>51.41</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG29" s="1" t="n">
         <v>-0.001</v>
@@ -4438,25 +4438,25 @@
         <v>0.011</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.061</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>107.87</v>
+        <v>106.71</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.038</v>
+        <v>0.029</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.076</v>
+        <v>0.062</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.185</v>
+        <v>0.164</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.263</v>
+        <v>0.251</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.461</v>
+        <v>0.427</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.264</v>
+        <v>0.267</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.777</v>
+        <v>1.759</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.147</v>
+        <v>0.135</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.3</v>
+        <v>50.47</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.003</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="T30" s="1" t="n">
         <v>0.072</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.119</v>
+        <v>0.11</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.058</v>
+        <v>0.07</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.077</v>
+        <v>0.091</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.153</v>
+        <v>0.157</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.447</v>
+        <v>0.459</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.795</v>
+        <v>0.822</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.123</v>
+        <v>0.127</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.46</v>
+        <v>24.4</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AG30" s="1" t="n">
         <v>-0.007</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.019</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="AJ30" s="1" t="n">
         <v>0.029</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.268</v>
+        <v>0.265</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.278</v>
+        <v>0.276</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.725</v>
+        <v>0.721</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.65</v>
+        <v>20.46</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>0.006</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>0.023</v>
-      </c>
       <c r="F31" s="1" t="n">
-        <v>0.061</v>
+        <v>0.05</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.158</v>
+        <v>0.144</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.206</v>
+        <v>0.21</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.356</v>
+        <v>0.34</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.576</v>
+        <v>0.561</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.724</v>
+        <v>0.699</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.301</v>
+        <v>1.287</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.94</v>
+        <v>65.77</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.009</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.157</v>
+        <v>0.147</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.069</v>
+        <v>0.073</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.411</v>
+        <v>0.415</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.695</v>
+        <v>1.691</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.92</v>
+        <v>80.85</v>
       </c>
       <c r="AF31" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG31" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AH31" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AI31" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.073</v>
+        <v>0.07</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.222</v>
+        <v>0.225</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.744</v>
+        <v>0.73</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>37.92</v>
+        <v>37.13</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.026</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.063</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.082</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.136</v>
+        <v>0.112</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.309</v>
+        <v>0.306</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.291</v>
+        <v>1.244</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.041</v>
+        <v>0.02</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>45.49</v>
+        <v>45.78</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="T32" s="1" t="n">
+        <v>-0.085</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="V32" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="W32" s="1" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="X32" s="1" t="n">
         <v>-0.091</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>-0.071</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>-0.105</v>
-      </c>
-      <c r="X32" s="1" t="n">
-        <v>-0.097</v>
-      </c>
       <c r="Y32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.17</v>
+        <v>1.165</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.045</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH32" s="1" t="n">
         <v>0.009</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="AL32" s="1" t="n">
         <v>0.304</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.213</v>
+        <v>0.209</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.128</v>
+        <v>1.105</v>
       </c>
       <c r="AO32" s="1" t="n">
         <v>0.017</v>
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.74</v>
+        <v>52.58</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="H33" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>-0.009</v>
-      </c>
       <c r="I33" s="1" t="n">
-        <v>0.071</v>
+        <v>0.073</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.365</v>
+        <v>0.361</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.348</v>
+        <v>0.377</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.462</v>
+        <v>1.482</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.027</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>91.51</v>
+        <v>90.73</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.009</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.055</v>
+        <v>0.046</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.321</v>
+        <v>0.294</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.282</v>
+        <v>0.276</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.619</v>
+        <v>0.605</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.662</v>
+        <v>0.659</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.289</v>
+        <v>1.258</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.079</v>
+        <v>0.07</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,16 +4902,16 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.28</v>
+        <v>48.33</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG33" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="AI33" s="1" t="n">
         <v>0.011</v>
@@ -4923,14 +4923,14 @@
         <v>0.065</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,34 +4941,34 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>92.44</v>
+        <v>92.48</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>0.093</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.171</v>
+        <v>0.152</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.213</v>
+        <v>0.216</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="J34" s="1" t="n">
         <v>0.816</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.507</v>
+        <v>0.53</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.553</v>
+        <v>1.557</v>
       </c>
       <c r="M34" s="1" t="n">
         <v>0.145</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>175.3</v>
+        <v>173.88</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.281</v>
+        <v>0.258</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.275</v>
+        <v>0.272</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.398</v>
+        <v>0.387</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.131</v>
+        <v>0.123</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.082</v>
+        <v>1.048</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.69</v>
+        <v>105.39</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.077</v>
+        <v>0.063</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.139</v>
+        <v>0.132</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.251</v>
+        <v>0.24</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.545</v>
+        <v>0.54</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.196</v>
+        <v>0.181</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.535</v>
+        <v>2.525</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.074</v>
+        <v>0.071</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>60.67</v>
+        <v>59.23</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.024</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.055</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.032</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.147</v>
+        <v>0.093</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.375</v>
+        <v>0.342</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.232</v>
+        <v>-0.242</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.898</v>
+        <v>0.851</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.014</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.67</v>
+        <v>60.32</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.004</v>
+        <v>0.02</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.074</v>
+        <v>-0.061</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.028</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.058</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.165</v>
+        <v>0.177</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.103</v>
+        <v>0.122</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.174</v>
+        <v>2.204</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.029</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,34 +5155,34 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.86</v>
+        <v>23.87</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.054</v>
+        <v>0.046</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>0.112</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.145</v>
+        <v>0.148</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.448</v>
+        <v>0.426</v>
       </c>
       <c r="J36" s="1" t="n">
         <v>0.352</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.071</v>
+        <v>0.096</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.876</v>
+        <v>0.864</v>
       </c>
       <c r="M36" s="1" t="n">
         <v>0.123</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.8</v>
+        <v>30.89</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.003</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.043</v>
+        <v>0.05</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.137</v>
+        <v>0.13</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.378</v>
+        <v>0.394</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.334</v>
+        <v>0.338</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.315</v>
+        <v>-0.313</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.176</v>
+        <v>0.179</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>77.06</v>
+        <v>76.14</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.012</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.056</v>
+        <v>0.048</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.105</v>
+        <v>0.089</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.283</v>
+        <v>0.251</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.36</v>
+        <v>0.338</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.539</v>
+        <v>0.5</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.14</v>
+        <v>1.115</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.913</v>
+        <v>0.918</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>4.006</v>
+        <v>3.973</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.213</v>
+        <v>0.198</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>124.17</v>
+        <v>125.66</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.007</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.014</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.09</v>
+        <v>0.103</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.648</v>
+        <v>0.668</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.851</v>
+        <v>0.905</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.699</v>
+        <v>2.725</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.025</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>96.97</v>
+        <v>97.79</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.034</v>
+        <v>0.027</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.529</v>
+        <v>0.531</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.764</v>
+        <v>0.777</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.825</v>
+        <v>1.849</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.876</v>
+        <v>1.974</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.068</v>
+        <v>3.14</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.195</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>148.89</v>
+        <v>150.41</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.12</v>
+        <v>0.112</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.262</v>
+        <v>0.282</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.695</v>
+        <v>0.68</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.093</v>
+        <v>1.124</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.645</v>
+        <v>1.66</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.729</v>
+        <v>1.757</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.857</v>
+        <v>0.898</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.824</v>
+        <v>2.924</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.531</v>
+        <v>0.547</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>63.79</v>
+        <v>64.23</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="S38" s="1" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>0.016</v>
-      </c>
       <c r="U38" s="1" t="n">
-        <v>0.082</v>
+        <v>0.093</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.071</v>
+        <v>0.068</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.164</v>
+        <v>0.171</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.439</v>
+        <v>0.449</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.441</v>
+        <v>0.482</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.866</v>
+        <v>1.829</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.051</v>
+        <v>0.058</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>80.04</v>
+        <v>80.45</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.142</v>
+        <v>0.133</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.139</v>
+        <v>-0.182</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.715</v>
+        <v>0.662</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.286</v>
+        <v>1.297</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.776</v>
+        <v>1.78</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.193</v>
+        <v>3.214</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.151</v>
+        <v>2.262</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.554</v>
+        <v>4.738</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.242</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>30.52</v>
+        <v>30.48</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.001</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.052</v>
+        <v>0.043</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.272</v>
+        <v>0.249</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.383</v>
+        <v>0.372</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.832</v>
+        <v>0.82</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.971</v>
+        <v>0.969</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.607</v>
+        <v>0.622</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.39</v>
+        <v>1.358</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>69.87</v>
+        <v>70.39</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.008</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.109</v>
+        <v>0.121</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.097</v>
+        <v>0.093</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.175</v>
+        <v>0.181</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.24</v>
+        <v>0.249</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.216</v>
+        <v>0.254</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.543</v>
+        <v>1.512</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.078</v>
+        <v>0.086</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>207.26</v>
+        <v>207.08</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.049</v>
+        <v>-0.001</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.095</v>
+        <v>0.099</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.178</v>
+        <v>-0.161</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.466</v>
+        <v>0.429</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.695</v>
+        <v>0.681</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.344</v>
+        <v>1.341</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.457</v>
+        <v>1.455</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.809</v>
+        <v>0.862</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.32</v>
+        <v>1.353</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>80.27</v>
+        <v>80.76</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.013</v>
+        <v>0.006</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.062</v>
+        <v>0.077</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.051</v>
+        <v>0.044</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.277</v>
+        <v>0.256</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.451</v>
+        <v>0.466</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.857</v>
+        <v>0.87</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.316</v>
+        <v>1.33</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.149</v>
+        <v>1.17</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.881</v>
+        <v>2.007</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>135.15</v>
+        <v>136.8</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.017</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.04</v>
+        <v>0.061</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.518</v>
+        <v>0.537</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.064</v>
+        <v>1.11</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.458</v>
+        <v>2.496</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.78</v>
+        <v>36.73</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.18</v>
+        <v>0.154</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.297</v>
+        <v>0.284</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.529</v>
+        <v>0.527</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.408</v>
+        <v>0.463</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.658</v>
+        <v>1.605</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>30.16</v>
+        <v>30.14</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.001</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.102</v>
+        <v>0.091</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.197</v>
+        <v>0.187</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.143</v>
+        <v>0.137</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.269</v>
+        <v>0.274</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.468</v>
+        <v>0.51</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.589</v>
+        <v>1.632</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>173.34</v>
+        <v>176.65</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.002</v>
+        <v>0.032</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.049</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.168</v>
+        <v>0.186</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.768</v>
+        <v>0.802</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.057</v>
+        <v>1.131</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.797</v>
+        <v>4.815</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.015</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>74.84</v>
+        <v>74.63</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.159</v>
+        <v>0.144</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.206</v>
+        <v>0.204</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.378</v>
+        <v>0.369</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.732</v>
+        <v>0.727</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.563</v>
+        <v>0.584</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.673</v>
+        <v>1.675</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.23</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.014</v>
+        <v>0.036</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.144</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.178</v>
+        <v>-0.172</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.274</v>
+        <v>-0.259</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.202</v>
+        <v>-0.189</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.178</v>
+        <v>0.201</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.453</v>
+        <v>-0.437</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.177</v>
+        <v>-0.161</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>105.66</v>
+        <v>105.57</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.146</v>
+        <v>0.133</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.331</v>
+        <v>0.328</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.686</v>
+        <v>0.684</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.644</v>
+        <v>0.666</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.635</v>
+        <v>1.64</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>195.98</v>
+        <v>193.2</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.014</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.04</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.02</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.082</v>
+        <v>0.063</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.254</v>
+        <v>0.225</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.389</v>
+        <v>1.355</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.314</v>
+        <v>1.263</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.311</v>
+        <v>7.207</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.032</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>55.19</v>
+        <v>54.87</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.042</v>
+        <v>0.018</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.001</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.317</v>
+        <v>0.284</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.464</v>
+        <v>0.421</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.296</v>
+        <v>1.236</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>2.008</v>
+        <v>1.99</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.665</v>
+        <v>2.821</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.18</v>
+        <v>5.11</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.292</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>45.18</v>
+        <v>45.12</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.001</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>0.059</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.137</v>
+        <v>0.125</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.185</v>
+        <v>0.188</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.279</v>
+        <v>0.274</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1.046</v>
+        <v>1.057</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.318</v>
+        <v>2.301</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>80.85</v>
+        <v>82.6</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.031</v>
+        <v>0.022</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.01</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.173</v>
+        <v>-0.164</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.198</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.242</v>
+        <v>-0.225</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.165</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.452</v>
+        <v>0.484</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.141</v>
+        <v>0.165</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.398</v>
+        <v>3.495</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.235</v>
+        <v>-0.218</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,34 +6153,34 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>79.73</v>
+        <v>79.77</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.001</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.017</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.078</v>
+        <v>0.086</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.151</v>
+        <v>0.139</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.053</v>
+        <v>0.077</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.878</v>
+        <v>0.931</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.133</v>
+        <v>0.136</v>
       </c>
       <c r="AO44" s="1" t="n">
         <v>0.153</v>
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>63.31</v>
+        <v>62.71</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.072</v>
+        <v>0.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.192</v>
+        <v>0.173</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.276</v>
+        <v>0.267</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.466</v>
+        <v>0.437</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.78</v>
+        <v>0.763</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.306</v>
+        <v>0.312</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.603</v>
+        <v>1.604</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.157</v>
+        <v>0.146</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>72.63</v>
+        <v>73.7</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.037</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.075</v>
+        <v>-0.081</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.131</v>
+        <v>-0.111</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.12</v>
+        <v>-0.107</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.045</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.577</v>
+        <v>0.6</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.297</v>
+        <v>0.324</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.466</v>
+        <v>2.468</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.083</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.65</v>
+        <v>33.81</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.096</v>
+        <v>0.106</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.18</v>
+        <v>0.173</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.098</v>
+        <v>0.127</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.124</v>
+        <v>0.135</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.027</v>
+        <v>1.087</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.054</v>
+        <v>2.06</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.188</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.56</v>
+        <v>33.73</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.127</v>
+        <v>0.121</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>368</v>
+        <v>356.8</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.03</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0.028</v>
+        <v>0.003</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.068</v>
+        <v>0.04</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.3</v>
+        <v>0.226</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.486</v>
+        <v>0.427</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.73</v>
+        <v>0.649</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.78</v>
+        <v>1.695</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.824</v>
+        <v>1.677</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.541</v>
+        <v>13.008</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.222</v>
+        <v>0.185</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.6</v>
+        <v>11.38</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.019</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.036</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.233</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.201</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.049</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.467</v>
+        <v>-0.462</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.658</v>
+        <v>-0.665</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.719</v>
+        <v>-0.724</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.885</v>
+        <v>-0.888</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.072</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.72</v>
+        <v>49.54</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E47" s="1" t="n">
         <v>0.016</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.048</v>
+        <v>0.039</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.134</v>
+        <v>0.118</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.161</v>
+        <v>0.158</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.262</v>
+        <v>0.258</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.588</v>
+        <v>0.583</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.572</v>
+        <v>0.586</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.675</v>
+        <v>1.648</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.094</v>
+        <v>0.09</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>126.74</v>
+        <v>125.37</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.011</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.041</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.029</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.087</v>
+        <v>0.072</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.256</v>
+        <v>0.229</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.492</v>
+        <v>1.465</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.176</v>
+        <v>1.134</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.74</v>
+        <v>6.667</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.029</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.8</v>
+        <v>44.75</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.087</v>
+        <v>0.079</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.199</v>
+        <v>0.184</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.585</v>
+        <v>0.586</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.933</v>
+        <v>0.93</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.95</v>
+        <v>0.986</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.948</v>
+        <v>1.984</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>52.42</v>
+        <v>51.79</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.012</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.135</v>
+        <v>0.106</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.255</v>
+        <v>0.231</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.419</v>
+        <v>0.374</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.808</v>
+        <v>0.787</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.185</v>
+        <v>0.172</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.088</v>
+        <v>0.075</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.12</v>
+        <v>26.05</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AG48" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AH48" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="AH48" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="AI48" s="1" t="n">
-        <v>0.047</v>
+        <v>0.033</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.016</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.454</v>
+        <v>0.45</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.687</v>
+        <v>0.706</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.519</v>
+        <v>0.518</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>53.08</v>
+        <v>53.05</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.001</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.16</v>
+        <v>0.142</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.388</v>
+        <v>0.383</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.855</v>
+        <v>0.854</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.679</v>
+        <v>0.695</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.887</v>
+        <v>1.908</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>36.08</v>
+        <v>35.25</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.023</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.035</v>
+        <v>0.013</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.044</v>
+        <v>0.02</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.097</v>
+        <v>0.048</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.19</v>
+        <v>0.151</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.41</v>
+        <v>0.355</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.083</v>
+        <v>0.059</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.7</v>
+        <v>17.74</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.112</v>
+        <v>-0.107</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.31</v>
+        <v>-0.308</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.152</v>
+        <v>-0.148</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.37</v>
+        <v>38.96</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.152</v>
+        <v>0.135</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.284</v>
+        <v>0.266</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.427</v>
+        <v>0.411</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.839</v>
+        <v>0.82</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.425</v>
+        <v>0.429</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.744</v>
+        <v>0.711</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.161</v>
+        <v>0.149</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.75</v>
+        <v>21.92</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.048</v>
+        <v>0.068</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.041</v>
+        <v>0.046</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.147</v>
+        <v>-0.128</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.401</v>
+        <v>-0.396</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.326</v>
+        <v>-0.303</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.498</v>
+        <v>-0.494</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,34 +6883,34 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.85</v>
+        <v>52.84</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.087</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.118</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.159</v>
+        <v>-0.161</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.044</v>
       </c>
       <c r="X51" s="1" t="n">
         <v>0.512</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>0.047</v>
+        <v>0.027</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.457</v>
+        <v>1.449</v>
       </c>
       <c r="AA51" s="1" t="n">
         <v>-0.113</v>
@@ -6925,31 +6925,31 @@
         <v>23.74</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="AH51" s="1" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AI51" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AJ51" s="1" t="n">
         <v>0.066</v>
       </c>
-      <c r="AI51" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AJ51" s="1" t="n">
-        <v>0.065</v>
-      </c>
       <c r="AK51" s="1" t="n">
-        <v>0.077</v>
+        <v>0.084</v>
       </c>
       <c r="AL51" s="1" t="n">
         <v>-0.156</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.379</v>
+        <v>0.385</v>
       </c>
       <c r="AO51" s="1" t="n">
         <v>0.086</v>
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>39.23</v>
+        <v>38.26</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.074</v>
+        <v>-0.025</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.045</v>
+        <v>0.005</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.226</v>
+        <v>-0.229</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.25</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.376</v>
+        <v>-0.394</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.202</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.21</v>
+        <v>-0.229</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,34 +6996,34 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.49</v>
+        <v>49.45</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.001</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.143</v>
+        <v>-0.142</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.109</v>
+        <v>-0.105</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.147</v>
+        <v>-0.149</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="Y52" s="1" t="n">
         <v>-0.297</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.97</v>
+        <v>1.964</v>
       </c>
       <c r="AA52" s="1" t="n">
         <v>-0.104</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>15.68</v>
+        <v>15.29</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.118</v>
+        <v>-0.025</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.072</v>
+        <v>0.039</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.294</v>
+        <v>-0.302</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.291</v>
+        <v>-0.332</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.531</v>
+        <v>-0.561</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.167</v>
+        <v>-0.134</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.301</v>
+        <v>-0.318</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>93.75</v>
+        <v>94.52</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.104</v>
+        <v>-0.107</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.133</v>
+        <v>-0.129</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.169</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>1.076</v>
+        <v>1.093</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.386</v>
+        <v>0.403</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.095</v>
+        <v>-0.088</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.017</v>
+        <v>0.022</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.022</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.043</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.151</v>
+        <v>-0.153</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.268</v>
+        <v>-0.257</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.086</v>
+        <v>-0.087</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.221</v>
+        <v>0.251</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.016</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>61.52</v>
+        <v>61.79</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.012</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.098</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.035</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>-0.106</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.053</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.428</v>
+        <v>0.434</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.163</v>
+        <v>0.172</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.419</v>
+        <v>1.415</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.079</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.44</v>
+        <v>119.25</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.101</v>
+        <v>0.091</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.072</v>
+        <v>0.057</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.116</v>
+        <v>0.111</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.199</v>
+        <v>0.194</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.568</v>
+        <v>0.566</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.826</v>
+        <v>0.862</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.652</v>
+        <v>1.72</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.66</v>
+        <v>39.54</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.003</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.025</v>
+        <v>0.016</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.058</v>
+        <v>0.05</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.183</v>
+        <v>0.181</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.38</v>
+        <v>0.376</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.342</v>
+        <v>0.355</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.36</v>
+        <v>47.18</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.113</v>
+        <v>0.101</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.075</v>
+        <v>0.056</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.226</v>
+        <v>0.216</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.559</v>
+        <v>0.553</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.855</v>
+        <v>0.883</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.744</v>
+        <v>1.811</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>27.38</v>
+        <v>27.72</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>-0.039</v>
+        <v>0.012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.043</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.187</v>
+        <v>-0.154</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.242</v>
+        <v>-0.227</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.393</v>
+        <v>-0.371</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.86</v>
+        <v>-0.859</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.975</v>
+        <v>-0.973</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.034</v>
+        <v>0.047</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.69</v>
+        <v>73.52</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.009</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.007</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.089</v>
+        <v>0.104</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.397</v>
+        <v>0.413</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.532</v>
+        <v>0.563</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.755</v>
+        <v>2.787</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.032</v>
+        <v>0.044</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.37</v>
+        <v>101.05</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.007</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.049</v>
+        <v>0.06</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.053</v>
+        <v>0.065</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.288</v>
+        <v>0.317</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.897</v>
+        <v>0.916</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.069</v>
+        <v>0.076</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.22</v>
+        <v>89.91</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.057</v>
+        <v>0.073</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="V58" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="W58" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X58" s="1" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="Z58" s="1" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="AA58" s="1" t="n">
         <v>0.088</v>
-      </c>
-      <c r="W58" s="1" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="Y58" s="1" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="Z58" s="1" t="n">
-        <v>1.029</v>
-      </c>
-      <c r="AA58" s="1" t="n">
-        <v>0.08</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>94.87</v>
+        <v>95.52</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.048</v>
+        <v>0.056</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.055</v>
+        <v>0.065</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.059</v>
+        <v>0.07</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.249</v>
+        <v>0.257</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.281</v>
+        <v>0.309</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.823</v>
+        <v>0.845</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.072</v>
+        <v>0.079</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.43</v>
+        <v>22.72</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.005</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.033</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.052</v>
+        <v>0.063</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.21</v>
+        <v>0.226</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.036</v>
+        <v>0.043</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.523</v>
+        <v>0.544</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.011</v>
+        <v>0.024</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>97.48</v>
+        <v>96.28</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.003</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.129</v>
+        <v>0.099</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.134</v>
+        <v>0.112</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.179</v>
+        <v>0.16</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.241</v>
+        <v>0.217</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.485</v>
+        <v>0.467</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.537</v>
+        <v>0.531</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.994</v>
+        <v>1.94</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.147</v>
+        <v>0.133</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/26/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">02/27/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>336.91</v>
+        <v>334.88</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>-0.009</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.005</v>
-      </c>
       <c r="F5" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.029</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.019</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.057</v>
+        <v>0.047</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.169</v>
+        <v>0.185</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.959</v>
+        <v>0.94</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.066</v>
+        <v>1.054</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.529</v>
+        <v>3.501</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.024</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.16</v>
+        <v>59.06</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.017</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.233</v>
+        <v>0.252</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.258</v>
+        <v>0.264</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.271</v>
+        <v>0.287</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.415</v>
+        <v>0.431</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.652</v>
+        <v>1.693</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.558</v>
+        <v>1.598</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.224</v>
+        <v>0.243</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,37 +1744,37 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.07</v>
+        <v>83.18</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>692.41</v>
+        <v>689.38</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.013</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.075</v>
+        <v>0.068</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.174</v>
+        <v>0.188</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.814</v>
+        <v>0.8</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.948</v>
+        <v>0.939</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.17</v>
+        <v>3.152</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>106.19</v>
+        <v>108.4</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.011</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.122</v>
+        <v>0.14</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.159</v>
+        <v>0.183</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.177</v>
+        <v>0.188</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.186</v>
+        <v>0.211</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.598</v>
+        <v>1.652</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.017</v>
+        <v>2.079</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.19</v>
+        <v>0.214</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.38</v>
+        <v>120.72</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.062</v>
+        <v>0.065</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.16</v>
+        <v>0.164</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>72.07</v>
+        <v>71.49</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.009</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.098</v>
+        <v>0.089</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.179</v>
+        <v>0.184</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.451</v>
+        <v>0.436</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.555</v>
+        <v>0.542</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.13</v>
+        <v>2.105</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.092</v>
+        <v>0.083</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.92</v>
+        <v>28.97</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.002</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.138</v>
+        <v>0.124</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.409</v>
+        <v>0.412</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.58</v>
+        <v>0.555</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.499</v>
+        <v>0.496</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.401</v>
+        <v>0.379</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.183</v>
+        <v>1.187</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.386</v>
+        <v>0.388</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.6</v>
+        <v>97.99</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.068</v>
+        <v>0.074</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.136</v>
+        <v>0.137</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.034</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.103</v>
+        <v>0.108</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>265.99</v>
+        <v>261.41</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.017</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.012</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.013</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.079</v>
+        <v>0.061</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.142</v>
+        <v>0.115</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.247</v>
+        <v>0.245</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.473</v>
+        <v>0.443</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.296</v>
+        <v>0.273</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.934</v>
+        <v>1.884</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.081</v>
+        <v>0.062</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.67</v>
+        <v>18.22</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.024</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.036</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.019</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.12</v>
+        <v>0.093</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.308</v>
+        <v>0.28</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.646</v>
+        <v>0.657</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>0.036</v>
+        <v>-0.006</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.226</v>
+        <v>-0.245</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.66</v>
+        <v>1.596</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.136</v>
+        <v>0.109</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>104.48</v>
+        <v>105</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.059</v>
+        <v>0.065</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.048</v>
+        <v>0.056</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.085</v>
+        <v>0.088</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.158</v>
+        <v>-0.154</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.024</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.63</v>
+        <v>26.72</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.003</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.089</v>
+        <v>0.093</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.132</v>
+        <v>0.128</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.216</v>
+        <v>0.221</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.313</v>
+        <v>0.31</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.206</v>
+        <v>1.213</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.554</v>
+        <v>1.563</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.132</v>
+        <v>0.136</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>90.27</v>
+        <v>90.82</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.038</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.064</v>
+        <v>0.072</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.039</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.26</v>
+        <v>-0.256</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.091</v>
+        <v>-0.086</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.04</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>187.16</v>
+        <v>188.56</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.066</v>
+        <v>0.071</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.264</v>
+        <v>0.274</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.271</v>
+        <v>0.275</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.382</v>
+        <v>0.398</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.473</v>
+        <v>0.477</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.761</v>
+        <v>0.775</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.27</v>
+        <v>2.295</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.216</v>
+        <v>0.225</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.71</v>
+        <v>111.88</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,34 +2332,34 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>225.38</v>
+        <v>225.52</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0.029</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.086</v>
+        <v>0.087</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.193</v>
+        <v>0.197</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.548</v>
+        <v>0.549</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.999</v>
+        <v>2.001</v>
       </c>
       <c r="M11" s="1" t="n">
         <v>0.072</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>64.13</v>
+        <v>64.34</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.003</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.065</v>
+        <v>0.047</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.387</v>
+        <v>0.392</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.593</v>
+        <v>0.602</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.706</v>
+        <v>0.696</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.941</v>
+        <v>0.947</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.898</v>
+        <v>4.917</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.249</v>
+        <v>0.253</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,37 +2410,37 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.21</v>
+        <v>103.32</v>
       </c>
       <c r="AF11" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="AJ11" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AK11" s="1" t="n">
         <v>0.051</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.193</v>
+        <v>0.194</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>454.15</v>
+        <v>450.19</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>-0.009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.051</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.05</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.145</v>
+        <v>0.166</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>1.021</v>
+        <v>0.991</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.958</v>
+        <v>0.941</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.245</v>
+        <v>4.199</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.049</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>97.54</v>
+        <v>99.42</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.091</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.41</v>
+        <v>0.437</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.864</v>
+        <v>0.903</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.9</v>
+        <v>2.072</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.828</v>
+        <v>3.898</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>3.132</v>
+        <v>3.212</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>6.024</v>
+        <v>6.159</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.325</v>
+        <v>0.35</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2532,7 +2532,7 @@
         <v>108.92</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="1" t="n">
         <v>0.004</v>
@@ -2544,13 +2544,13 @@
         <v>0.022</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="AM12" s="1" t="n">
         <v>0.072</v>
@@ -2570,34 +2570,34 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>204.8</v>
+        <v>204.86</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>0.041</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.089</v>
+        <v>0.088</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.139</v>
+        <v>0.156</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.785</v>
+        <v>0.782</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>0.871</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.81</v>
+        <v>2.811</v>
       </c>
       <c r="M13" s="1" t="n">
         <v>0.031</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.47</v>
+        <v>47.51</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.11</v>
+        <v>0.097</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.015</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.581</v>
+        <v>0.616</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.28</v>
+        <v>1.312</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.474</v>
+        <v>2.73</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>4.102</v>
+        <v>4.167</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>2.118</v>
+        <v>2.188</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.464</v>
+        <v>6.631</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.356</v>
+        <v>0.386</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.35</v>
+        <v>23.38</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.078</v>
+        <v>0.084</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.131</v>
+        <v>0.134</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.287</v>
+        <v>0.288</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.8</v>
+        <v>97.81</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.433</v>
+        <v>0.448</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.596</v>
+        <v>0.613</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.771</v>
+        <v>1.8</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.039</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.96</v>
+        <v>57.15</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.079</v>
+        <v>0.054</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.071</v>
+        <v>0.053</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.464</v>
+        <v>0.468</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.798</v>
+        <v>0.812</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.231</v>
+        <v>1.274</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.4</v>
+        <v>76.52</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.125</v>
+        <v>0.135</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.169</v>
+        <v>0.165</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.039</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>254.89</v>
+        <v>252.96</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.028</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.032</v>
+        <v>0.024</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.045</v>
+        <v>0.039</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.18</v>
+        <v>0.191</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.872</v>
+        <v>0.857</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.655</v>
+        <v>0.642</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.09</v>
+        <v>3.059</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.43</v>
+        <v>18.07</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.02</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.082</v>
+        <v>0.075</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.059</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.249</v>
+        <v>0.225</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.848</v>
+        <v>0.78</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1.089</v>
+        <v>1.055</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.18</v>
+        <v>0.157</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,34 +2874,34 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.68</v>
+        <v>97.73</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG15" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.067</v>
+        <v>0.069</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.34</v>
+        <v>0.334</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="AO15" s="1" t="n">
         <v>0.019</v>
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.42</v>
+        <v>140.13</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.071</v>
+        <v>0.075</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.134</v>
+        <v>0.148</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.15</v>
+        <v>0.161</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.2</v>
+        <v>0.213</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.522</v>
+        <v>0.539</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.851</v>
+        <v>0.874</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.66</v>
+        <v>1.693</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.138</v>
+        <v>0.152</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>78.58</v>
+        <v>78.38</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.026</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.025</v>
+        <v>0.029</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.154</v>
+        <v>0.138</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.275</v>
+        <v>1.269</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.091</v>
+        <v>0.088</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,34 +2993,34 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.93</v>
+        <v>42.96</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.177</v>
+        <v>0.185</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.278</v>
+        <v>0.273</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.069</v>
+        <v>0.07</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.314</v>
+        <v>0.315</v>
       </c>
       <c r="AO16" s="1" t="n">
         <v>0.033</v>
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.85</v>
+        <v>149.19</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="F17" s="1" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="H17" s="1" t="n">
-        <v>0.069</v>
+        <v>0.061</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.165</v>
+        <v>0.179</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.773</v>
+        <v>0.759</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.824</v>
+        <v>0.816</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.84</v>
+        <v>108.68</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.011</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.091</v>
+        <v>0.082</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.15</v>
+        <v>0.138</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.19</v>
+        <v>0.178</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.52</v>
+        <v>0.537</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.478</v>
+        <v>1.441</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.468</v>
+        <v>1.442</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.055</v>
+        <v>4.002</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.186</v>
+        <v>0.174</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.86</v>
+        <v>42.99</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="AI17" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>-0.173</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="AO17" s="1" t="n">
         <v>0.032</v>
-      </c>
-      <c r="AJ17" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AK17" s="1" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AL17" s="1" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AM17" s="1" t="n">
-        <v>-0.175</v>
-      </c>
-      <c r="AN17" s="1" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="AO17" s="1" t="n">
-        <v>0.029</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,13 +3166,13 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.93</v>
+        <v>160.94</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="T18" s="1" t="n">
         <v>0.044</v>
@@ -3184,10 +3184,10 @@
         <v>0.103</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.195</v>
+        <v>0.198</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.663</v>
+        <v>0.653</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>0.697</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.56</v>
+        <v>36.4</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.079</v>
+        <v>0.058</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.197</v>
+        <v>0.192</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.28</v>
+        <v>0.272</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.502</v>
+        <v>0.514</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>58.15</v>
+        <v>57.98</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.044</v>
+        <v>0.032</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.123</v>
+        <v>0.12</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.222</v>
+        <v>0.209</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.426</v>
+        <v>0.443</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.814</v>
+        <v>0.799</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>1.002</v>
+        <v>0.996</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.317</v>
+        <v>2.307</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>82.22</v>
+        <v>81.78</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.005</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.071</v>
+        <v>0.069</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.137</v>
+        <v>0.131</v>
       </c>
       <c r="V20" s="1" t="n">
         <v>0.151</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.196</v>
+        <v>0.201</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.495</v>
+        <v>0.455</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.481</v>
+        <v>0.474</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.774</v>
+        <v>1.759</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101.2</v>
+        <v>101.4</v>
       </c>
       <c r="AF20" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.063</v>
+        <v>0.067</v>
       </c>
       <c r="AL20" s="1" t="n">
         <v>0.162</v>
       </c>
       <c r="AM20" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AO20" s="1" t="n">
         <v>0.019</v>
-      </c>
-      <c r="AN20" s="1" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="AO20" s="1" t="n">
-        <v>0.017</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.8</v>
+        <v>36.48</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.009</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.016</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.048</v>
+        <v>0.009</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.218</v>
+        <v>0.208</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.417</v>
+        <v>0.392</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.663</v>
+        <v>0.672</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.811</v>
+        <v>0.791</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.983</v>
+        <v>0.965</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.897</v>
+        <v>1.871</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.209</v>
+        <v>0.198</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>242.82</v>
+        <v>243.72</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.192</v>
+        <v>0.196</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.219</v>
+        <v>0.228</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.617</v>
+        <v>0.61</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.156</v>
+        <v>1.164</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.653</v>
+        <v>1.663</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.794</v>
+        <v>3.811</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.131</v>
+        <v>0.135</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.74</v>
+        <v>50.86</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.177</v>
+        <v>0.181</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.066</v>
+        <v>0.068</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.276</v>
+        <v>0.279</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.66</v>
+        <v>80.94</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>0.003</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.004</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.211</v>
+        <v>0.215</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.338</v>
+        <v>0.332</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.625</v>
+        <v>0.66</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.556</v>
+        <v>0.552</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.318</v>
+        <v>1.326</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.186</v>
+        <v>1.194</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.163</v>
+        <v>0.167</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.62</v>
+        <v>103.17</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.019</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.073</v>
+        <v>0.094</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.664</v>
+        <v>0.658</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.461</v>
+        <v>0.469</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.197</v>
+        <v>2.214</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.55</v>
+        <v>49.89</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.069</v>
+        <v>0.077</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.183</v>
+        <v>0.195</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.262</v>
+        <v>0.271</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>39.1</v>
+        <v>38.73</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.009</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.068</v>
+        <v>0.022</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.209</v>
+        <v>0.198</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.415</v>
+        <v>0.381</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.657</v>
+        <v>0.653</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.707</v>
+        <v>0.694</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.82</v>
+        <v>0.803</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.263</v>
+        <v>2.232</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.231</v>
+        <v>0.219</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>107.24</v>
+        <v>107.52</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.031</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.026</v>
+        <v>0.041</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.093</v>
+        <v>0.112</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.649</v>
+        <v>0.643</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.857</v>
+        <v>0.862</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.65</v>
+        <v>3.662</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.75</v>
+        <v>96.91</v>
       </c>
       <c r="AF23" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.161</v>
+        <v>0.163</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>69.06</v>
+        <v>68.58</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.001</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.032</v>
+        <v>0.009</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.117</v>
+        <v>0.109</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.336</v>
+        <v>0.351</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.742</v>
+        <v>0.701</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.766</v>
+        <v>0.754</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.827</v>
+        <v>1.808</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.077</v>
+        <v>0.07</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>41.06</v>
+        <v>40.77</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.096</v>
+        <v>0.088</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.152</v>
+        <v>0.122</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,16 +3839,16 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.72</v>
+        <v>111.68</v>
       </c>
       <c r="AF24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG24" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="AH24" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AI24" s="1" t="n">
         <v>0.008</v>
@@ -3857,19 +3857,19 @@
         <v>0.038</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.067</v>
+        <v>0.071</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="AM24" s="1" t="n">
         <v>0.017</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>47.15</v>
+        <v>46.75</v>
       </c>
       <c r="D25" s="1" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="F25" s="1" t="n">
-        <v>0.041</v>
+        <v>0.027</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.103</v>
+        <v>0.094</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.154</v>
+        <v>0.149</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.212</v>
+        <v>0.214</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.655</v>
+        <v>0.623</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>1.001</v>
+        <v>0.985</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.23</v>
+        <v>2.203</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>87.67</v>
+        <v>86.98</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.019</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.041</v>
+        <v>0.032</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.04</v>
+        <v>0.014</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.18</v>
+        <v>0.195</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.373</v>
+        <v>0.361</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.194</v>
+        <v>0.184</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.353</v>
+        <v>1.334</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.94</v>
+        <v>92.51</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="AG25" s="1" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AH25" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="AI25" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AJ25" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AK25" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AL25" s="1" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AM25" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="AO25" s="1" t="n">
         <v>-0.004</v>
-      </c>
-      <c r="AH25" s="1" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="AI25" s="1" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="AJ25" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="AK25" s="1" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AL25" s="1" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="AM25" s="1" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AN25" s="1" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AO25" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.61</v>
+        <v>48.68</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.061</v>
+        <v>0.047</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.187</v>
+        <v>0.191</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.701</v>
+        <v>0.684</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.95</v>
+        <v>0.953</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.41</v>
+        <v>1.413</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>62.08</v>
+        <v>61.66</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.007</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.136</v>
+        <v>0.15</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.559</v>
+        <v>0.545</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.315</v>
+        <v>0.306</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.877</v>
+        <v>0.864</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.66</v>
+        <v>26.61</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.064</v>
+        <v>0.066</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.134</v>
+        <v>0.132</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>48.35</v>
+        <v>47.87</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.031</v>
+        <v>0.004</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.059</v>
+        <v>0.037</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.141</v>
+        <v>0.13</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.246</v>
+        <v>0.248</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.454</v>
+        <v>0.415</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.669</v>
+        <v>0.652</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.778</v>
+        <v>1.751</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.075</v>
+        <v>0.064</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>27.25</v>
+        <v>26.66</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="T27" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>0.047</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>0.055</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,13 +4188,13 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.19</v>
+        <v>53.23</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH27" s="1" t="n">
         <v>0.008</v>
@@ -4203,19 +4203,19 @@
         <v>0.013</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.203</v>
+        <v>0.202</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.136</v>
+        <v>0.137</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="AO27" s="1" t="n">
         <v>0.01</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.56</v>
+        <v>44.34</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.098</v>
+        <v>0.092</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>0.058</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.234</v>
+        <v>0.252</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.763</v>
+        <v>0.727</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.574</v>
+        <v>0.567</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.402</v>
+        <v>1.39</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.72</v>
+        <v>77.64</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.087</v>
+        <v>0.097</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.12</v>
+        <v>0.133</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.115</v>
+        <v>0.127</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.128</v>
+        <v>0.14</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.274</v>
+        <v>0.292</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.54</v>
+        <v>0.558</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.693</v>
+        <v>1.726</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.146</v>
+        <v>0.16</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.47</v>
+        <v>54.51</v>
       </c>
       <c r="AF28" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AJ28" s="1" t="n">
         <v>0.04</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.085</v>
+        <v>0.088</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.247</v>
+        <v>0.245</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>64.63</v>
+        <v>65.08</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.056</v>
+        <v>0.04</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.123</v>
+        <v>0.131</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.173</v>
+        <v>0.178</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.266</v>
+        <v>0.292</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.571</v>
+        <v>0.569</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.651</v>
+        <v>0.663</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.791</v>
+        <v>1.81</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.078</v>
+        <v>0.085</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.96</v>
+        <v>46.58</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.013</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.012</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.089</v>
+        <v>0.094</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.195</v>
+        <v>0.211</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.146</v>
+        <v>0.157</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.258</v>
+        <v>0.279</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.15</v>
+        <v>0.157</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.321</v>
+        <v>0.338</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.624</v>
+        <v>1.66</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.192</v>
+        <v>0.208</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,28 +4426,28 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.41</v>
+        <v>51.39</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.047</v>
+        <v>0.048</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.057</v>
+        <v>0.065</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="AM29" s="1" t="n">
         <v>-0.061</v>
@@ -4456,7 +4456,7 @@
         <v>0.381</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>106.71</v>
+        <v>106.51</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.062</v>
+        <v>0.04</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.164</v>
+        <v>0.162</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.251</v>
+        <v>0.259</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.427</v>
+        <v>0.452</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.75</v>
+        <v>0.744</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.267</v>
+        <v>0.265</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.759</v>
+        <v>1.754</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.135</v>
+        <v>0.133</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.47</v>
+        <v>50.97</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.072</v>
+        <v>0.067</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.11</v>
+        <v>0.121</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.07</v>
+        <v>0.079</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.091</v>
+        <v>0.112</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.459</v>
+        <v>0.473</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.822</v>
+        <v>0.84</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.127</v>
+        <v>0.138</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.4</v>
+        <v>24.25</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.029</v>
+        <v>0.023</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.265</v>
+        <v>0.263</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.276</v>
+        <v>0.268</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.721</v>
+        <v>0.711</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.46</v>
+        <v>20.38</v>
       </c>
       <c r="D31" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="E31" s="1" t="n">
         <v>-0.009</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="F31" s="1" t="n">
-        <v>0.05</v>
+        <v>0.027</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.21</v>
+        <v>0.204</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.34</v>
+        <v>0.363</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.561</v>
+        <v>0.552</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.699</v>
+        <v>0.692</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.287</v>
+        <v>1.278</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.77</v>
+        <v>66.84</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.016</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.001</v>
+        <v>0.019</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.022</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.147</v>
+        <v>0.166</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.073</v>
+        <v>0.097</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.266</v>
+        <v>0.289</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.415</v>
+        <v>0.438</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.691</v>
+        <v>1.735</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.85</v>
+        <v>80.72</v>
       </c>
       <c r="AF31" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG31" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AH31" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="AG31" s="1" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="AH31" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AI31" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="AK31" s="1" t="n">
         <v>0.07</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.302</v>
+        <v>0.291</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.225</v>
+        <v>0.223</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>37.13</v>
+        <v>37.17</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.001</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.038</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.074</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.082</v>
+        <v>-0.07</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.112</v>
+        <v>0.124</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.306</v>
+        <v>0.308</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.244</v>
+        <v>1.246</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>45.78</v>
+        <v>46.14</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.002</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>-0.085</v>
+        <v>0.021</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.063</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.078</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.091</v>
+        <v>-0.083</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.165</v>
+        <v>1.182</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.038</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.71</v>
+        <v>29.63</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.044</v>
+        <v>0.04</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.089</v>
+        <v>0.088</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.304</v>
+        <v>0.294</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.209</v>
+        <v>0.206</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.105</v>
+        <v>1.099</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.58</v>
+        <v>52.27</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.022</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.044</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.073</v>
+        <v>0.077</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.361</v>
+        <v>0.353</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.377</v>
+        <v>0.369</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.482</v>
+        <v>1.468</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.033</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>90.73</v>
+        <v>91.84</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.012</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.063</v>
+        <v>0.076</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.294</v>
+        <v>0.307</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.276</v>
+        <v>0.305</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.605</v>
+        <v>0.637</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.659</v>
+        <v>0.679</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.258</v>
+        <v>1.285</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.07</v>
+        <v>0.083</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.33</v>
+        <v>48.38</v>
       </c>
       <c r="AF33" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AJ33" s="1" t="n">
         <v>0.031</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="AL33" s="1" t="n">
         <v>0.18</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>92.48</v>
+        <v>92.37</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.093</v>
+        <v>0.076</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.816</v>
+        <v>0.797</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.53</v>
+        <v>0.528</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.557</v>
+        <v>1.554</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>173.88</v>
+        <v>175.37</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.009</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.258</v>
+        <v>0.268</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.272</v>
+        <v>0.298</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.387</v>
+        <v>0.393</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.123</v>
+        <v>0.133</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.048</v>
+        <v>1.065</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.39</v>
+        <v>104.78</v>
       </c>
       <c r="AF34" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG34" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="AG34" s="1" t="n">
-        <v>0.001</v>
-      </c>
       <c r="AH34" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.001</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.24</v>
+        <v>0.243</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.54</v>
+        <v>0.526</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.181</v>
+        <v>0.175</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.525</v>
+        <v>2.504</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.071</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>59.23</v>
+        <v>59.06</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.003</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.032</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.067</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.034</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.004</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.093</v>
+        <v>0.099</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.342</v>
+        <v>0.321</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.242</v>
+        <v>-0.244</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.851</v>
+        <v>0.846</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.017</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>60.32</v>
+        <v>60.2</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.002</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.063</v>
       </c>
       <c r="V35" s="1" t="n">
         <v>-0.028</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.044</v>
       </c>
       <c r="X35" s="1" t="n">
         <v>0.177</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.204</v>
+        <v>2.198</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.031</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.87</v>
+        <v>24.21</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="K36" s="1" t="n">
         <v>0.112</v>
       </c>
-      <c r="H36" s="1" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>0.096</v>
-      </c>
       <c r="L36" s="1" t="n">
-        <v>0.864</v>
+        <v>0.89</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.123</v>
+        <v>0.139</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.89</v>
+        <v>31.13</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="T36" s="1" t="n">
         <v>0.05</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.13</v>
+        <v>0.139</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.389</v>
+        <v>0.399</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.394</v>
+        <v>0.419</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.313</v>
+        <v>-0.308</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.179</v>
+        <v>0.189</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>76.14</v>
+        <v>75.67</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.006</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.048</v>
+        <v>0.017</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.089</v>
+        <v>0.061</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.251</v>
+        <v>0.243</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.338</v>
+        <v>0.324</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.5</v>
+        <v>0.557</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.115</v>
+        <v>1.094</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.918</v>
+        <v>0.906</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.973</v>
+        <v>3.943</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.198</v>
+        <v>0.191</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>125.66</v>
+        <v>122.61</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.024</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.022</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.033</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.015</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.015</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.103</v>
+        <v>0.071</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.668</v>
+        <v>0.627</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.905</v>
+        <v>0.859</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.725</v>
+        <v>2.635</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.049</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>97.79</v>
+        <v>99.07</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.039</v>
+        <v>0.033</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.027</v>
+        <v>0.016</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.247</v>
+        <v>0.263</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.531</v>
+        <v>0.548</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.777</v>
+        <v>0.828</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.849</v>
+        <v>1.876</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.974</v>
+        <v>2.013</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.14</v>
+        <v>3.194</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.205</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>150.41</v>
+        <v>151.37</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.112</v>
+        <v>0.067</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.282</v>
+        <v>0.234</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.68</v>
+        <v>0.691</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.124</v>
+        <v>1.136</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.66</v>
+        <v>1.766</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.757</v>
+        <v>1.769</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.898</v>
+        <v>0.911</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.924</v>
+        <v>2.949</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.547</v>
+        <v>0.557</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>64.23</v>
+        <v>61.05</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.05</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.068</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.036</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.093</v>
+        <v>0.039</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.068</v>
+        <v>0.009</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.171</v>
+        <v>0.11</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.449</v>
+        <v>0.376</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.482</v>
+        <v>0.408</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.829</v>
+        <v>1.688</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.058</v>
+        <v>0.006</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>80.45</v>
+        <v>84.99</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.005</v>
+        <v>0.056</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.133</v>
+        <v>0.109</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.163</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.662</v>
+        <v>0.756</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.297</v>
+        <v>1.429</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.78</v>
+        <v>1.993</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.214</v>
+        <v>3.49</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.262</v>
+        <v>2.446</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.738</v>
+        <v>5.062</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.249</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>30.48</v>
+        <v>30.56</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.037</v>
+        <v>0.025</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.249</v>
+        <v>0.253</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.372</v>
+        <v>0.38</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.82</v>
+        <v>0.863</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.969</v>
+        <v>0.953</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.622</v>
+        <v>0.626</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.358</v>
+        <v>1.364</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.39</v>
+        <v>66.77</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.051</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.071</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>0.036</v>
+        <v>-0.022</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.121</v>
+        <v>0.064</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.093</v>
+        <v>0.028</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.181</v>
+        <v>0.119</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.249</v>
+        <v>0.185</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.254</v>
+        <v>0.19</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.512</v>
+        <v>1.383</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.086</v>
+        <v>0.03</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>207.08</v>
+        <v>214.73</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.037</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.099</v>
+        <v>0.093</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.097</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.429</v>
+        <v>0.482</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.681</v>
+        <v>0.746</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.341</v>
+        <v>1.474</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.455</v>
+        <v>1.469</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.862</v>
+        <v>0.931</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.353</v>
+        <v>1.44</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.111</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>80.76</v>
+        <v>81.6</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.077</v>
+        <v>0.056</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.044</v>
+        <v>0.033</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.256</v>
+        <v>0.269</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.466</v>
+        <v>0.5</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.87</v>
+        <v>0.926</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.33</v>
+        <v>1.344</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.17</v>
+        <v>1.192</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>2.007</v>
+        <v>2.038</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.174</v>
+        <v>0.186</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>136.8</v>
+        <v>136.57</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="T40" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>0.017</v>
       </c>
-      <c r="T40" s="1" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>0.018</v>
-      </c>
       <c r="V40" s="1" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.061</v>
+        <v>0.037</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.537</v>
+        <v>0.534</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.11</v>
+        <v>1.106</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.496</v>
+        <v>2.49</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.73</v>
+        <v>36.88</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.315</v>
+        <v>0.333</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.284</v>
+        <v>0.285</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.527</v>
+        <v>0.509</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.463</v>
+        <v>0.469</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.605</v>
+        <v>1.616</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>30.14</v>
+        <v>30.09</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.091</v>
+        <v>0.066</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.187</v>
+        <v>0.185</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.137</v>
+        <v>0.133</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.274</v>
+        <v>0.291</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.463</v>
+        <v>0.455</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.51</v>
+        <v>0.508</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.632</v>
+        <v>1.627</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.151</v>
+        <v>0.149</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>176.65</v>
+        <v>170.69</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.034</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.032</v>
+        <v>-0.008</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.077</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.019</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.017</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.186</v>
+        <v>0.154</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.802</v>
+        <v>0.752</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.131</v>
+        <v>1.059</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.815</v>
+        <v>4.619</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.048</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>74.63</v>
+        <v>74.45</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.054</v>
+        <v>0.034</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.144</v>
+        <v>0.142</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>0.204</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.369</v>
+        <v>0.385</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.727</v>
+        <v>0.706</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.675</v>
+        <v>1.669</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.7</v>
+        <v>24.42</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.011</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.144</v>
+        <v>-0.149</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.182</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.259</v>
+        <v>-0.27</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.189</v>
+        <v>-0.187</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.437</v>
+        <v>-0.443</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.17</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>105.57</v>
+        <v>105.38</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.051</v>
+        <v>0.032</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>0.17</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.328</v>
+        <v>0.341</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.684</v>
+        <v>0.661</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.666</v>
+        <v>0.663</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.64</v>
+        <v>1.635</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>193.2</v>
+        <v>189.58</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.019</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.017</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.069</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.039</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.063</v>
+        <v>0.037</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.225</v>
+        <v>0.248</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.355</v>
+        <v>1.301</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.263</v>
+        <v>1.221</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.207</v>
+        <v>7.053</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.051</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>54.87</v>
+        <v>54.34</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.061</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.284</v>
+        <v>0.271</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.421</v>
+        <v>0.435</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.236</v>
+        <v>1.303</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.99</v>
+        <v>1.943</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.821</v>
+        <v>2.784</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.11</v>
+        <v>5.051</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.284</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>45.12</v>
+        <v>45.03</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.274</v>
+        <v>0.277</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.728</v>
+        <v>0.711</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1.057</v>
+        <v>1.053</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.301</v>
+        <v>2.294</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.6</v>
+        <v>81.57</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.012</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.164</v>
+        <v>-0.166</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.208</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.225</v>
+        <v>-0.241</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.165</v>
+        <v>-0.153</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.484</v>
+        <v>0.464</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.165</v>
+        <v>0.15</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.495</v>
+        <v>3.439</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.218</v>
+        <v>-0.228</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>79.77</v>
+        <v>81.95</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.001</v>
+        <v>0.027</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.086</v>
+        <v>0.083</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.139</v>
+        <v>0.17</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.077</v>
+        <v>0.097</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.189</v>
+        <v>0.237</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.931</v>
+        <v>0.984</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.136</v>
+        <v>0.167</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.153</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>62.71</v>
+        <v>62.58</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.027</v>
+        <v>0.004</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.173</v>
+        <v>0.17</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.267</v>
+        <v>0.272</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.437</v>
+        <v>0.463</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.763</v>
+        <v>0.75</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.312</v>
+        <v>0.309</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.604</v>
+        <v>1.599</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.146</v>
+        <v>0.144</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>73.7</v>
+        <v>73.16</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.014</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.096</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.111</v>
+        <v>-0.118</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.126</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.031</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.6</v>
+        <v>0.585</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.324</v>
+        <v>0.314</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.468</v>
+        <v>2.442</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.09</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>33.81</v>
+        <v>34.81</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.027</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.173</v>
+        <v>0.208</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.127</v>
+        <v>0.153</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.135</v>
+        <v>0.15</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.23</v>
+        <v>0.282</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.087</v>
+        <v>1.149</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.194</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.73</v>
+        <v>33.52</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.036</v>
+        <v>0.024</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.121</v>
+        <v>0.114</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.165</v>
+        <v>0.153</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.109</v>
+        <v>0.102</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>356.8</v>
+        <v>352.29</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.013</v>
       </c>
       <c r="S46" s="1" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="T46" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="T46" s="1" t="n">
-        <v>0.04</v>
-      </c>
       <c r="U46" s="1" t="n">
-        <v>0.226</v>
+        <v>0.211</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.427</v>
+        <v>0.407</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.649</v>
+        <v>0.729</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.695</v>
+        <v>1.647</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.677</v>
+        <v>1.643</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>13.008</v>
+        <v>12.831</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.185</v>
+        <v>0.17</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.38</v>
+        <v>11.52</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.012</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.041</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.233</v>
+        <v>-0.216</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.201</v>
+        <v>-0.192</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.055</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.462</v>
+        <v>-0.448</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.665</v>
+        <v>-0.679</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.724</v>
+        <v>-0.721</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.888</v>
+        <v>-0.887</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.54</v>
+        <v>49.69</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.016</v>
+        <v>0.009</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.039</v>
+        <v>0.027</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.158</v>
+        <v>0.16</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.258</v>
+        <v>0.28</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.583</v>
+        <v>0.569</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.586</v>
+        <v>0.591</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.648</v>
+        <v>1.656</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.09</v>
+        <v>0.093</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>125.37</v>
+        <v>124.23</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.061</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.038</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.072</v>
+        <v>0.058</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.229</v>
+        <v>0.26</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.465</v>
+        <v>1.434</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.134</v>
+        <v>1.115</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.667</v>
+        <v>6.597</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.038</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.75</v>
+        <v>44.68</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.079</v>
+        <v>0.056</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.252</v>
+        <v>0.254</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.586</v>
+        <v>0.596</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.93</v>
+        <v>0.911</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.986</v>
+        <v>0.982</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.984</v>
+        <v>1.98</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.79</v>
+        <v>51.01</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.005</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.047</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.106</v>
+        <v>0.089</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.231</v>
+        <v>0.192</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.374</v>
+        <v>0.417</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.787</v>
+        <v>0.74</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.172</v>
+        <v>0.154</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.075</v>
+        <v>0.059</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.05</v>
+        <v>26.02</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AI48" s="1" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AJ48" s="1" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="AK48" s="1" t="n">
         <v>0.006</v>
-      </c>
-      <c r="AH48" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AI48" s="1" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AJ48" s="1" t="n">
-        <v>-0.016</v>
-      </c>
-      <c r="AK48" s="1" t="n">
-        <v>-0.005</v>
       </c>
       <c r="AL48" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.706</v>
+        <v>0.704</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.518</v>
+        <v>0.516</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>53.05</v>
+        <v>52.71</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.006</v>
       </c>
       <c r="E49" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F49" s="1" t="n">
         <v>0.019</v>
       </c>
-      <c r="F49" s="1" t="n">
-        <v>0.047</v>
-      </c>
       <c r="G49" s="1" t="n">
-        <v>0.142</v>
+        <v>0.135</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.854</v>
+        <v>0.825</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.695</v>
+        <v>0.684</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.908</v>
+        <v>1.89</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.106</v>
+        <v>0.099</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.25</v>
+        <v>35.01</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.007</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.005</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.012</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.048</v>
+        <v>0.04</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.151</v>
+        <v>0.136</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.355</v>
+        <v>0.406</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.74</v>
+        <v>17.89</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.003</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.079</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.308</v>
+        <v>-0.298</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.148</v>
+        <v>-0.141</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>0.001</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>38.96</v>
+        <v>39.75</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.135</v>
+        <v>0.152</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.208</v>
+        <v>0.233</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.266</v>
+        <v>0.287</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.411</v>
+        <v>0.445</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.82</v>
+        <v>0.858</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.429</v>
+        <v>0.458</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.711</v>
+        <v>0.745</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.149</v>
+        <v>0.173</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.92</v>
+        <v>22.57</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.008</v>
+        <v>0.03</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.068</v>
+        <v>0.101</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.046</v>
+        <v>0.077</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.032</v>
+        <v>0.07</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.128</v>
+        <v>-0.079</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.396</v>
+        <v>-0.37</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.303</v>
+        <v>-0.282</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.494</v>
+        <v>-0.479</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.098</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.84</v>
+        <v>53.02</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.087</v>
+        <v>-0.084</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.115</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.157</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.015</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.512</v>
+        <v>0.518</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.449</v>
+        <v>1.457</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.113</v>
+        <v>-0.11</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.74</v>
+        <v>23.82</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AH51" s="1" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AI51" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AJ51" s="1" t="n">
         <v>0.07</v>
       </c>
-      <c r="AI51" s="1" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="AJ51" s="1" t="n">
-        <v>0.066</v>
-      </c>
       <c r="AK51" s="1" t="n">
-        <v>0.084</v>
+        <v>0.092</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.156</v>
+        <v>-0.15</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.086</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.26</v>
+        <v>37.19</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.028</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.032</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.229</v>
+        <v>-0.265</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.25</v>
+        <v>-0.271</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.394</v>
+        <v>-0.416</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.202</v>
+        <v>-0.215</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.229</v>
+        <v>-0.251</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.45</v>
+        <v>49.33</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.02</v>
       </c>
       <c r="T52" s="1" t="n">
         <v>-0.142</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.105</v>
+        <v>-0.108</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.149</v>
+        <v>-0.136</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.035</v>
+        <v>0.058</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.49</v>
+        <v>0.467</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.297</v>
+        <v>-0.298</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.964</v>
+        <v>1.957</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.104</v>
+        <v>-0.107</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>15.29</v>
+        <v>14.52</v>
       </c>
       <c r="D53" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E53" s="1" t="n">
         <v>-0.025</v>
       </c>
-      <c r="E53" s="1" t="n">
-        <v>0.039</v>
-      </c>
       <c r="F53" s="1" t="n">
-        <v>-0.302</v>
+        <v>-0.364</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.332</v>
+        <v>-0.366</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.561</v>
+        <v>-0.58</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.134</v>
+        <v>-0.148</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.318</v>
+        <v>-0.353</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>94.52</v>
+        <v>93.78</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.118</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.129</v>
+        <v>-0.136</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.169</v>
+        <v>-0.168</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.035</v>
+        <v>0.046</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>1.093</v>
+        <v>1.061</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.403</v>
+        <v>0.392</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.095</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.32</v>
+        <v>9.29</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.031</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.046</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.155</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.257</v>
+        <v>-0.235</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.087</v>
+        <v>-0.111</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.251</v>
+        <v>0.247</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.019</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>61.79</v>
+        <v>60.38</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.023</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.033</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.098</v>
+        <v>-0.122</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.057</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.127</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.057</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.434</v>
+        <v>0.375</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.172</v>
+        <v>0.145</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.415</v>
+        <v>1.359</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.079</v>
+        <v>-0.1</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.25</v>
+        <v>120.7</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.012</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.057</v>
+        <v>0.07</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.111</v>
+        <v>0.122</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.194</v>
+        <v>0.234</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.566</v>
+        <v>0.594</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.862</v>
+        <v>0.885</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.72</v>
+        <v>1.753</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.1</v>
+        <v>0.114</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.54</v>
+        <v>39.63</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.113</v>
+        <v>0.112</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.181</v>
+        <v>0.183</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.376</v>
+        <v>0.379</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.18</v>
+        <v>47.73</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.012</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.056</v>
+        <v>0.069</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.123</v>
+        <v>0.135</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.216</v>
+        <v>0.258</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.553</v>
+        <v>0.582</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.883</v>
+        <v>0.905</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.811</v>
+        <v>1.844</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.105</v>
+        <v>0.118</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>27.72</v>
+        <v>28.9</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.012</v>
+        <v>0.043</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>-0.043</v>
+        <v>0.019</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.043</v>
+        <v>0.073</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.154</v>
+        <v>-0.118</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.227</v>
+        <v>-0.197</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.371</v>
+        <v>-0.379</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.859</v>
+        <v>-0.847</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.973</v>
+        <v>-0.972</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.047</v>
+        <v>0.092</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>73.52</v>
+        <v>73.04</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.007</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.413</v>
+        <v>0.403</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.563</v>
+        <v>0.553</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.787</v>
+        <v>2.762</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.044</v>
+        <v>0.037</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>101.05</v>
+        <v>101.28</v>
       </c>
       <c r="R57" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S57" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="S57" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="T57" s="1" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="U57" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="V57" s="1" t="n">
         <v>0.057</v>
       </c>
-      <c r="V57" s="1" t="n">
-        <v>0.06</v>
-      </c>
       <c r="W57" s="1" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="X57" s="1" t="n">
         <v>0.258</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.317</v>
+        <v>0.32</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.916</v>
+        <v>0.92</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.91</v>
+        <v>89.57</v>
       </c>
       <c r="R58" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="S58" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="S58" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="T58" s="1" t="n">
-        <v>0.073</v>
+        <v>0.072</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.097</v>
+        <v>0.081</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.328</v>
+        <v>0.329</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.454</v>
+        <v>0.449</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.046</v>
+        <v>1.038</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.088</v>
+        <v>0.084</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.52</v>
+        <v>95.69</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.07</v>
+        <v>0.068</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.309</v>
+        <v>0.311</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.845</v>
+        <v>0.848</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.72</v>
+        <v>22.62</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.052</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.226</v>
+        <v>0.228</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.043</v>
+        <v>0.038</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.544</v>
+        <v>0.537</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.28</v>
+        <v>97.34</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.011</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.112</v>
+        <v>0.124</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.16</v>
+        <v>0.169</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.217</v>
+        <v>0.257</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.467</v>
+        <v>0.481</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.531</v>
+        <v>0.548</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.94</v>
+        <v>1.972</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.133</v>
+        <v>0.145</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">02/27/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">03/02/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>334.88</v>
+        <v>334.94</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.006</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.002</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.03</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.023</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.047</v>
+        <v>0.059</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.185</v>
+        <v>0.164</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.94</v>
+        <v>0.944</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.054</v>
+        <v>1.022</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.501</v>
+        <v>3.412</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.06</v>
+        <v>60.29</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.123</v>
+        <v>0.138</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.252</v>
+        <v>0.267</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.264</v>
+        <v>0.272</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.287</v>
+        <v>0.294</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.431</v>
+        <v>0.439</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.693</v>
+        <v>1.691</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.598</v>
+        <v>1.56</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.243</v>
+        <v>0.268</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,37 +1744,37 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>83.18</v>
+        <v>82.81</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>689.38</v>
+        <v>689.45</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.006</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>-0.013</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.188</v>
+        <v>0.17</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.939</v>
+        <v>0.908</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.152</v>
+        <v>3.071</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>108.4</v>
+        <v>112.3</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.021</v>
+        <v>0.036</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.061</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.14</v>
+        <v>0.174</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.183</v>
+        <v>0.209</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.188</v>
+        <v>0.205</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.211</v>
+        <v>0.24</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.32</v>
+        <v>0.336</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.652</v>
+        <v>1.715</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.079</v>
+        <v>2.014</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.214</v>
+        <v>0.258</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>120.72</v>
+        <v>119.88</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.065</v>
+        <v>0.057</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.164</v>
+        <v>0.165</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>71.49</v>
+        <v>72.1</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.009</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.017</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.027</v>
+        <v>0.041</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.089</v>
+        <v>0.102</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.436</v>
+        <v>0.44</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.542</v>
+        <v>0.535</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.105</v>
+        <v>2.051</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.083</v>
+        <v>0.092</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.97</v>
+        <v>28.98</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.124</v>
+        <v>0.134</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.412</v>
+        <v>0.388</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.555</v>
+        <v>0.547</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.496</v>
+        <v>0.483</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.379</v>
+        <v>0.334</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.187</v>
+        <v>1.154</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.075</v>
+        <v>0.011</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.99</v>
+        <v>97.12</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0.009</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.074</v>
+        <v>0.061</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.04</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.108</v>
+        <v>0.11</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>261.41</v>
+        <v>263.81</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.009</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.006</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.061</v>
+        <v>0.08</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.115</v>
+        <v>0.135</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.443</v>
+        <v>0.45</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.273</v>
+        <v>0.265</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.884</v>
+        <v>1.833</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.062</v>
+        <v>0.072</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.22</v>
+        <v>18.33</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.024</v>
+        <v>0.006</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.034</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.005</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.093</v>
+        <v>0.105</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.28</v>
+        <v>0.305</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.657</v>
+        <v>0.68</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>-0.006</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.245</v>
+        <v>-0.244</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.596</v>
+        <v>1.516</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.109</v>
+        <v>0.116</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>105</v>
+        <v>103.78</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.056</v>
+        <v>0.039</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.088</v>
+        <v>0.097</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.154</v>
+        <v>-0.155</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.025</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.037</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,34 +2157,34 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.72</v>
+        <v>26.73</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.089</v>
+        <v>0.091</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.093</v>
+        <v>0.11</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.221</v>
+        <v>0.216</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.31</v>
+        <v>0.298</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.213</v>
+        <v>1.173</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.563</v>
+        <v>1.492</v>
       </c>
       <c r="AA9" s="1" t="n">
         <v>0.136</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>90.82</v>
+        <v>89.61</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="AG9" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="AK9" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="AH9" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AI9" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AJ9" s="1" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="AK9" s="1" t="n">
-        <v>0.039</v>
-      </c>
       <c r="AL9" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.256</v>
+        <v>-0.254</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.086</v>
+        <v>-0.087</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.046</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>188.56</v>
+        <v>189.59</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.071</v>
+        <v>0.105</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.274</v>
+        <v>0.284</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.275</v>
+        <v>0.29</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.398</v>
+        <v>0.393</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.477</v>
+        <v>0.442</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.775</v>
+        <v>0.724</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.295</v>
+        <v>2.251</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.225</v>
+        <v>0.231</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.88</v>
+        <v>111.57</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AH10" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.057</v>
+        <v>0.047</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.324</v>
+        <v>0.316</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>225.52</v>
+        <v>225.15</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.009</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.029</v>
+        <v>0.016</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.087</v>
+        <v>0.085</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.197</v>
+        <v>0.179</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.549</v>
+        <v>0.544</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.731</v>
+        <v>0.696</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.001</v>
+        <v>1.927</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.072</v>
+        <v>0.07</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>64.34</v>
+        <v>64.36</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.047</v>
+        <v>0.038</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.056</v>
+        <v>0.104</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.392</v>
+        <v>0.367</v>
       </c>
       <c r="V11" s="1" t="n">
         <v>0.602</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.85</v>
+        <v>0.856</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.696</v>
+        <v>0.606</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.947</v>
+        <v>0.863</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.917</v>
+        <v>4.41</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.253</v>
+        <v>0.254</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,16 +2410,16 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.32</v>
+        <v>103.26</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>0.009</v>
@@ -2428,19 +2428,19 @@
         <v>0.012</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.171</v>
+        <v>0.167</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.194</v>
+        <v>0.189</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>450.19</v>
+        <v>451.47</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.003</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.034</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.052</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.166</v>
+        <v>0.149</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.991</v>
+        <v>0.998</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.941</v>
+        <v>0.92</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.199</v>
+        <v>4.124</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.046</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>99.42</v>
+        <v>99.05</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.004</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.091</v>
+        <v>0.048</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.061</v>
+        <v>0.225</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.437</v>
+        <v>0.432</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.903</v>
+        <v>0.794</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>2.072</v>
+        <v>2.038</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.898</v>
+        <v>3.735</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>3.212</v>
+        <v>3.036</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>6.159</v>
+        <v>5.94</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.35</v>
+        <v>0.345</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.92</v>
+        <v>108.27</v>
       </c>
       <c r="AF12" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AG12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG12" s="1" t="n">
-        <v>0.004</v>
-      </c>
       <c r="AH12" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>0.022</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.072</v>
+        <v>0.067</v>
       </c>
       <c r="AN12" s="1" t="n">
         <v>0.247</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>204.86</v>
+        <v>204.47</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.088</v>
+        <v>0.096</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.156</v>
+        <v>0.137</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.782</v>
+        <v>0.769</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.871</v>
+        <v>0.84</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.811</v>
+        <v>2.741</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>47.51</v>
+        <v>46.66</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.018</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.097</v>
+        <v>0.049</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.22</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.616</v>
+        <v>0.491</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.312</v>
+        <v>1.089</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.73</v>
+        <v>2.643</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>4.167</v>
+        <v>3.92</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>2.188</v>
+        <v>2.151</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.631</v>
+        <v>6.516</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.386</v>
+        <v>0.362</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.38</v>
+        <v>23.22</v>
       </c>
       <c r="AF13" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG13" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG13" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="AH13" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.039</v>
+        <v>0.033</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.058</v>
+        <v>0.048</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.084</v>
+        <v>0.077</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.134</v>
+        <v>0.115</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.108</v>
+        <v>0.096</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>97.81</v>
+        <v>97.68</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="H14" s="1" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>0.048</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <v>0.064</v>
-      </c>
       <c r="J14" s="1" t="n">
-        <v>0.448</v>
+        <v>0.451</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.613</v>
+        <v>0.589</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.8</v>
+        <v>1.764</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>57.15</v>
+        <v>56.61</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.009</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.054</v>
+        <v>0.032</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.053</v>
+        <v>0.098</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.468</v>
+        <v>0.425</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.812</v>
+        <v>0.769</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.274</v>
+        <v>1.284</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.29</v>
+        <v>0.278</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>76.52</v>
+        <v>75.67</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.009</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.007</v>
       </c>
       <c r="AI14" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AN14" s="1" t="n">
         <v>0.032</v>
       </c>
-      <c r="AJ14" s="1" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="AK14" s="1" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AL14" s="1" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="AM14" s="1" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="AN14" s="1" t="n">
-        <v>0.045</v>
-      </c>
       <c r="AO14" s="1" t="n">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>252.96</v>
+        <v>253.7</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.003</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.016</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.018</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.039</v>
+        <v>0.052</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.191</v>
+        <v>0.173</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.857</v>
+        <v>0.863</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.642</v>
+        <v>0.628</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.059</v>
+        <v>3.025</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.07</v>
+        <v>18.01</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.003</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.075</v>
+        <v>0.047</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.059</v>
+        <v>0.088</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.78</v>
+        <v>0.839</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1.055</v>
+        <v>1.113</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.157</v>
+        <v>0.153</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>97.73</v>
+        <v>96.99</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.023</v>
+        <v>0.018</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.069</v>
+        <v>0.065</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.124</v>
+        <v>0.114</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.334</v>
+        <v>0.349</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.471</v>
+        <v>0.45</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>140.13</v>
+        <v>140.18</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.148</v>
+        <v>0.157</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.161</v>
+        <v>0.158</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.213</v>
+        <v>0.199</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.539</v>
+        <v>0.542</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.874</v>
+        <v>0.848</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.693</v>
+        <v>1.656</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>78.38</v>
+        <v>76.56</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.023</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.029</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>0.019</v>
+        <v>0.032</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.138</v>
+        <v>0.118</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.054</v>
+        <v>0.038</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.138</v>
+        <v>0.092</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>0.037</v>
+        <v>0.005</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.269</v>
+        <v>1.126</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.088</v>
+        <v>0.063</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.96</v>
+        <v>42.52</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.082</v>
+        <v>0.074</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.185</v>
+        <v>0.176</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.273</v>
+        <v>0.263</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.07</v>
+        <v>0.052</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.315</v>
+        <v>0.28</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.19</v>
+        <v>149.27</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.008</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.015</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.061</v>
+        <v>0.073</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.179</v>
+        <v>0.162</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>0.759</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.816</v>
+        <v>0.789</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.68</v>
+        <v>108.01</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.008</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.082</v>
+        <v>0.075</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.138</v>
+        <v>0.152</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.178</v>
+        <v>0.189</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.537</v>
+        <v>0.494</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.441</v>
+        <v>1.406</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.442</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>4.002</v>
+        <v>3.875</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.174</v>
+        <v>0.167</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.99</v>
+        <v>42.49</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.173</v>
+        <v>-0.189</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.051</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>160.94</v>
+        <v>162.04</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.023</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.113</v>
+        <v>0.122</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.103</v>
+        <v>0.125</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.198</v>
+        <v>0.192</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.653</v>
+        <v>0.647</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.697</v>
+        <v>0.67</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.603</v>
+        <v>2.566</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.086</v>
+        <v>0.094</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.4</v>
+        <v>36.62</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.007</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.192</v>
+        <v>0.198</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.272</v>
+        <v>0.304</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.98</v>
+        <v>58.16</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.032</v>
+        <v>0.066</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.209</v>
+        <v>0.208</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.443</v>
+        <v>0.433</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>0.799</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.996</v>
+        <v>0.938</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.307</v>
+        <v>2.24</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.78</v>
+        <v>81.95</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.024</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.069</v>
+        <v>0.04</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.131</v>
+        <v>0.119</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.151</v>
+        <v>0.167</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.201</v>
+        <v>0.186</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.474</v>
+        <v>0.45</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.759</v>
+        <v>1.723</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.098</v>
+        <v>0.1</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>101.4</v>
+        <v>100.68</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="AH20" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AI20" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="AI20" s="1" t="n">
+      <c r="AJ20" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="AO20" s="1" t="n">
         <v>0.014</v>
-      </c>
-      <c r="AJ20" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AK20" s="1" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="AL20" s="1" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AM20" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="AN20" s="1" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AO20" s="1" t="n">
-        <v>0.019</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.48</v>
+        <v>36.26</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.006</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.208</v>
+        <v>0.179</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.392</v>
+        <v>0.374</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.672</v>
+        <v>0.697</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.791</v>
+        <v>0.784</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.965</v>
+        <v>0.91</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.871</v>
+        <v>1.634</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.198</v>
+        <v>0.191</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>243.72</v>
+        <v>250.58</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.028</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.028</v>
+        <v>0.084</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.196</v>
+        <v>0.245</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.228</v>
+        <v>0.267</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.61</v>
+        <v>0.629</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.164</v>
+        <v>1.195</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.663</v>
+        <v>1.658</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.811</v>
+        <v>3.897</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.135</v>
+        <v>0.167</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.86</v>
+        <v>50.66</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AH21" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AJ21" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AK21" s="1" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AL21" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AM21" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AN21" s="1" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AO21" s="1" t="n">
         <v>0.015</v>
-      </c>
-      <c r="AI21" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="AJ21" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="AK21" s="1" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="AL21" s="1" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="AM21" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="AN21" s="1" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="AO21" s="1" t="n">
-        <v>0.019</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>80.94</v>
+        <v>79.46</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.018</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.04</v>
+        <v>0.053</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.215</v>
+        <v>0.179</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.332</v>
+        <v>0.287</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.66</v>
+        <v>0.632</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.552</v>
+        <v>0.493</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.326</v>
+        <v>1.2</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.194</v>
+        <v>1.035</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.167</v>
+        <v>0.146</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>103.17</v>
+        <v>102.11</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.009</v>
+        <v>0.018</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.025</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.005</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.094</v>
+        <v>0.065</v>
       </c>
       <c r="X22" s="1" t="n">
         <v>0.658</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.469</v>
+        <v>0.436</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.214</v>
+        <v>2.126</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.89</v>
+        <v>49.47</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.005</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="AH22" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="AI22" s="1" t="n">
         <v>0.016</v>
       </c>
-      <c r="AI22" s="1" t="n">
-        <v>0.019</v>
-      </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.037</v>
+        <v>0.03</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.195</v>
+        <v>0.197</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.065</v>
+        <v>0.057</v>
       </c>
       <c r="AN22" s="1" t="n">
         <v>0.271</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.019</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.73</v>
+        <v>38.64</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.002</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.003</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.198</v>
+        <v>0.175</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.653</v>
+        <v>0.69</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.694</v>
+        <v>0.726</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.803</v>
+        <v>0.787</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>2.232</v>
+        <v>1.918</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.219</v>
+        <v>0.216</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>107.52</v>
+        <v>104.96</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.024</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.042</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.041</v>
+        <v>0.022</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.037</v>
+        <v>0.016</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.045</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.643</v>
+        <v>0.603</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.862</v>
+        <v>0.778</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.662</v>
+        <v>3.416</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.117</v>
+        <v>0.09</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.91</v>
+        <v>96.05</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="AH23" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AI23" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="AJ23" s="1" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AK23" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="AL23" s="1" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AM23" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AN23" s="1" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AO23" s="1" t="n">
         <v>0.016</v>
-      </c>
-      <c r="AI23" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ23" s="1" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="AK23" s="1" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AL23" s="1" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="AM23" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="AN23" s="1" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AO23" s="1" t="n">
-        <v>0.021</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>68.58</v>
+        <v>66.81</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F24" s="1" t="n">
         <v>-0.007</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>0.009</v>
-      </c>
       <c r="G24" s="1" t="n">
-        <v>0.109</v>
+        <v>0.071</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.155</v>
+        <v>0.142</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.351</v>
+        <v>0.315</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.701</v>
+        <v>0.655</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.754</v>
+        <v>0.678</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.808</v>
+        <v>1.662</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.07</v>
+        <v>0.042</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>40.77</v>
+        <v>40.04</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.027</v>
+        <v>0.011</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.056</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.088</v>
+        <v>0.067</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.149</v>
+        <v>0.158</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.332</v>
+        <v>0.335</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.122</v>
+        <v>0.095</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.075</v>
+        <v>0.056</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>111.68</v>
+        <v>110.92</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AI24" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>0.071</v>
+        <v>0.059</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.375</v>
+        <v>0.369</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.75</v>
+        <v>46.02</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.094</v>
+        <v>0.07</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>0.149</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.214</v>
+        <v>0.187</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.623</v>
+        <v>0.595</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.985</v>
+        <v>0.92</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.203</v>
+        <v>2.048</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.068</v>
+        <v>0.052</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.98</v>
+        <v>86.16</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.007</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.02</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.032</v>
+        <v>0.024</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.195</v>
+        <v>0.172</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.184</v>
+        <v>0.136</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.334</v>
+        <v>1.267</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.51</v>
+        <v>92.68</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.009</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.248</v>
+        <v>0.244</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="AN25" s="1" t="n">
         <v>0.608</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.68</v>
+        <v>48.12</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.154</v>
+        <v>0.14</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.191</v>
+        <v>0.199</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.38</v>
+        <v>0.351</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.684</v>
+        <v>0.671</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.953</v>
+        <v>0.888</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.413</v>
+        <v>1.318</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>61.66</v>
+        <v>60.89</v>
       </c>
       <c r="R26" s="1" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="V26" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="W26" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="Y26" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="Z26" s="1" t="n">
+        <v>0.817</v>
+      </c>
+      <c r="AA26" s="1" t="n">
         <v>-0.007</v>
-      </c>
-      <c r="S26" s="1" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="T26" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="U26" s="1" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="V26" s="1" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="Z26" s="1" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="AA26" s="1" t="n">
-        <v>0.005</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.61</v>
+        <v>26.67</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.201</v>
+        <v>0.198</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>47.87</v>
+        <v>46.57</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.019</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.037</v>
+        <v>0.019</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.083</v>
+        <v>0.053</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.13</v>
+        <v>0.107</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.248</v>
+        <v>0.211</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.415</v>
+        <v>0.378</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.652</v>
+        <v>0.577</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.751</v>
+        <v>1.62</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.064</v>
+        <v>0.035</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.66</v>
+        <v>26.74</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.003</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.01</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.023</v>
+        <v>0.032</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="V27" s="1" t="n">
         <v>0.058</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,37 +4188,37 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>53.23</v>
+        <v>52.92</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AH27" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AI27" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AJ27" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AK27" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AL27" s="1" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AM27" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AO27" s="1" t="n">
         <v>0.008</v>
-      </c>
-      <c r="AI27" s="1" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="AJ27" s="1" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="AK27" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AL27" s="1" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="AM27" s="1" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AN27" s="1" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="AO27" s="1" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>44.34</v>
+        <v>42.91</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.032</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.013</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.092</v>
+        <v>0.049</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.058</v>
+        <v>0.046</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.252</v>
+        <v>0.209</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.727</v>
+        <v>0.676</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.567</v>
+        <v>0.49</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.39</v>
+        <v>1.259</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.043</v>
+        <v>0.01</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>77.64</v>
+        <v>76.77</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.011</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.029</v>
+        <v>0.003</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.097</v>
+        <v>0.068</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.127</v>
+        <v>0.109</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.14</v>
+        <v>0.114</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.292</v>
+        <v>0.283</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.558</v>
+        <v>0.514</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.726</v>
+        <v>1.66</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.16</v>
+        <v>0.147</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.51</v>
+        <v>54.11</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AI28" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.088</v>
+        <v>0.08</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.245</v>
+        <v>0.25</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.09</v>
+        <v>0.083</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.404</v>
+        <v>0.401</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>65.08</v>
+        <v>63.59</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.023</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.011</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.131</v>
+        <v>0.098</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.178</v>
+        <v>0.163</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.292</v>
+        <v>0.252</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.569</v>
+        <v>0.545</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.663</v>
+        <v>0.594</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.81</v>
+        <v>1.686</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.085</v>
+        <v>0.061</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.58</v>
+        <v>46.44</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.094</v>
+        <v>0.087</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.211</v>
+        <v>0.205</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.279</v>
+        <v>0.275</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.157</v>
+        <v>0.143</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.338</v>
+        <v>0.307</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.66</v>
+        <v>1.615</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.208</v>
+        <v>0.204</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>51.39</v>
+        <v>50.94</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.048</v>
+        <v>0.052</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.186</v>
+        <v>0.189</v>
       </c>
       <c r="AM29" s="1" t="n">
         <v>-0.061</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>106.51</v>
+        <v>104.66</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>-0.002</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>0.003</v>
-      </c>
       <c r="F30" s="1" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.162</v>
+        <v>0.141</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.259</v>
+        <v>0.239</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>0.452</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.744</v>
+        <v>0.67</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.265</v>
+        <v>0.225</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.754</v>
+        <v>1.572</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.133</v>
+        <v>0.113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.97</v>
+        <v>50.54</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.067</v>
+        <v>0.049</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.121</v>
+        <v>0.119</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.079</v>
+        <v>0.072</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.112</v>
+        <v>0.09</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.174</v>
+        <v>0.164</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.473</v>
+        <v>0.436</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.84</v>
+        <v>0.811</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.138</v>
+        <v>0.128</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.25</v>
+        <v>24.3</v>
       </c>
       <c r="AF30" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="AG30" s="1" t="n">
         <v>-0.006</v>
       </c>
-      <c r="AG30" s="1" t="n">
-        <v>-0.014</v>
-      </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.019</v>
       </c>
       <c r="AI30" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.263</v>
+        <v>0.257</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.268</v>
+        <v>0.261</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.711</v>
+        <v>0.706</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>20.38</v>
+        <v>19.81</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.032</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.139</v>
+        <v>0.11</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.204</v>
+        <v>0.174</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.363</v>
+        <v>0.336</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.552</v>
+        <v>0.514</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.692</v>
+        <v>0.614</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.278</v>
+        <v>1.119</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.112</v>
+        <v>0.081</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.84</v>
+        <v>66.08</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.011</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.002</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.166</v>
+        <v>0.148</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.097</v>
+        <v>0.072</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.289</v>
+        <v>0.276</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.735</v>
+        <v>1.679</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.027</v>
+        <v>0.015</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.72</v>
+        <v>80.28</v>
       </c>
       <c r="AF31" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG31" s="1" t="n">
         <v>-0.002</v>
-      </c>
-      <c r="AG31" s="1" t="n">
-        <v>-0.003</v>
       </c>
       <c r="AH31" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.07</v>
+        <v>0.067</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.291</v>
+        <v>0.295</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.223</v>
+        <v>0.21</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.728</v>
+        <v>0.693</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>37.17</v>
+        <v>36.58</v>
       </c>
       <c r="D32" s="1" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.001</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>-0.074</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="H32" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.084</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.124</v>
+        <v>0.075</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.308</v>
+        <v>0.248</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.246</v>
+        <v>1.119</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46.14</v>
+        <v>46</v>
       </c>
       <c r="R32" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="S32" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="S32" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="T32" s="1" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.046</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.022</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.078</v>
+        <v>-0.086</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.07</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.182</v>
+        <v>1.167</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.04</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.63</v>
+        <v>29.5</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="AH32" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.088</v>
+        <v>0.086</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.294</v>
+        <v>0.298</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.099</v>
+        <v>1.051</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>52.27</v>
+        <v>50.95</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.025</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.044</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.054</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.027</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.077</v>
+        <v>0.059</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.353</v>
+        <v>0.307</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.369</v>
+        <v>0.29</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.468</v>
+        <v>1.228</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.057</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>91.84</v>
+        <v>91.31</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.006</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.022</v>
+        <v>0.003</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.055</v>
+        <v>0.037</v>
       </c>
       <c r="U33" s="1" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="V33" s="1" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="W33" s="1" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="X33" s="1" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="Y33" s="1" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="Z33" s="1" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="AA33" s="1" t="n">
         <v>0.076</v>
-      </c>
-      <c r="V33" s="1" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="W33" s="1" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="X33" s="1" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="Y33" s="1" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="Z33" s="1" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="AA33" s="1" t="n">
-        <v>0.083</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.38</v>
+        <v>48.04</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="AH33" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AI33" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="AI33" s="1" t="n">
-        <v>0.012</v>
-      </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.068</v>
+        <v>0.059</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.18</v>
+        <v>0.182</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.013</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>92.37</v>
+        <v>90.2</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.076</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.151</v>
+        <v>0.135</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.219</v>
+        <v>0.197</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.4</v>
+        <v>0.378</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.797</v>
+        <v>0.757</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.528</v>
+        <v>0.482</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.554</v>
+        <v>1.437</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.144</v>
+        <v>0.117</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>175.37</v>
+        <v>173.92</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.008</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.001</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.268</v>
+        <v>0.241</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.298</v>
+        <v>0.272</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.393</v>
+        <v>0.366</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.133</v>
+        <v>0.127</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.065</v>
+        <v>0.997</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.78</v>
+        <v>105.61</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.009</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.013</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.017</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.057</v>
+        <v>0.072</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.243</v>
+        <v>0.248</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.526</v>
+        <v>0.532</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.175</v>
+        <v>0.179</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.504</v>
+        <v>2.404</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.065</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>59.06</v>
+        <v>58.51</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.009</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.037</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.05</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.048</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.039</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.099</v>
+        <v>0.116</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.321</v>
+        <v>0.256</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.244</v>
+        <v>-0.258</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.846</v>
+        <v>0.742</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.026</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>60.2</v>
+        <v>59.63</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.009</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.055</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.031</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.062</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.177</v>
+        <v>0.151</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.12</v>
+        <v>0.093</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.198</v>
+        <v>2.155</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.041</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>24.21</v>
+        <v>23.94</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.011</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.128</v>
+        <v>0.114</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.178</v>
+        <v>0.161</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.446</v>
+        <v>0.435</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.354</v>
+        <v>0.298</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.112</v>
+        <v>0.099</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.89</v>
+        <v>0.803</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.139</v>
+        <v>0.127</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.13</v>
+        <v>30.91</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.007</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.051</v>
+        <v>0.016</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.05</v>
+        <v>0.071</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.139</v>
+        <v>0.191</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.399</v>
+        <v>0.391</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.419</v>
+        <v>0.392</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.344</v>
+        <v>0.331</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.308</v>
+        <v>-0.312</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.189</v>
+        <v>0.18</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>75.67</v>
+        <v>75.07</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.061</v>
+        <v>0.089</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.243</v>
+        <v>0.215</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.324</v>
+        <v>0.353</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.557</v>
+        <v>0.545</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.094</v>
+        <v>1.055</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.906</v>
+        <v>0.879</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.943</v>
+        <v>3.74</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.191</v>
+        <v>0.182</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>122.61</v>
+        <v>122.54</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.001</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.007</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.047</v>
       </c>
       <c r="U37" s="1" t="n">
         <v>-0.015</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.011</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.071</v>
+        <v>0.05</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.627</v>
+        <v>0.637</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.859</v>
+        <v>0.819</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.635</v>
+        <v>2.519</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.05</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>99.07</v>
+        <v>100.38</v>
       </c>
       <c r="AF37" s="1" t="n">
         <v>0.013</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.016</v>
+        <v>0.146</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.263</v>
+        <v>0.266</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.548</v>
+        <v>0.506</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.828</v>
+        <v>0.863</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.876</v>
+        <v>1.882</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>2.013</v>
+        <v>2.04</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.194</v>
+        <v>3.193</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.221</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>151.37</v>
+        <v>147.54</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.025</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.067</v>
+        <v>0.059</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.234</v>
+        <v>0.22</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.691</v>
+        <v>0.638</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.136</v>
+        <v>1.098</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.766</v>
+        <v>1.759</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.769</v>
+        <v>1.67</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.911</v>
+        <v>0.832</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.949</v>
+        <v>2.691</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.557</v>
+        <v>0.518</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>61.05</v>
+        <v>61.89</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.014</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.012</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.04</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.039</v>
+        <v>0.054</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.009</v>
+        <v>0.035</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.376</v>
+        <v>0.428</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.408</v>
+        <v>0.374</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.688</v>
+        <v>1.624</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>84.99</v>
+        <v>81.57</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.056</v>
+        <v>-0.04</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.109</v>
+        <v>0.012</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.163</v>
+        <v>0.126</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.756</v>
+        <v>0.535</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.429</v>
+        <v>1.196</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.993</v>
+        <v>1.881</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.49</v>
+        <v>3.24</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.446</v>
+        <v>2.289</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>5.062</v>
+        <v>4.724</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.319</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>30.56</v>
+        <v>29.82</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.024</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.009</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.034</v>
+        <v>0.062</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.253</v>
+        <v>0.218</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.38</v>
+        <v>0.342</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.863</v>
+        <v>0.83</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.953</v>
+        <v>0.888</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.626</v>
+        <v>0.546</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.364</v>
+        <v>1.217</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.142</v>
+        <v>0.115</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>66.77</v>
+        <v>67.76</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.051</v>
+        <v>0.015</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.014</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.033</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.064</v>
+        <v>0.077</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.028</v>
+        <v>0.054</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.185</v>
+        <v>0.243</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.19</v>
+        <v>0.177</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.383</v>
+        <v>1.332</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>214.73</v>
+        <v>209.78</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.037</v>
+        <v>-0.023</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.093</v>
+        <v>0.063</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.097</v>
+        <v>0.078</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.482</v>
+        <v>0.401</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.746</v>
+        <v>0.638</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.474</v>
+        <v>1.428</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.469</v>
+        <v>1.355</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.931</v>
+        <v>0.857</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.44</v>
+        <v>1.322</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.152</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>81.6</v>
+        <v>79.9</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.021</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.056</v>
+        <v>0.026</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.033</v>
+        <v>0.091</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.5</v>
+        <v>0.472</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.926</v>
+        <v>0.921</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.344</v>
+        <v>1.244</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.192</v>
+        <v>1.045</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>2.038</v>
+        <v>1.707</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.186</v>
+        <v>0.161</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>136.57</v>
+        <v>137.56</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0.007</v>
+        <v>0.025</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.017</v>
+        <v>0.038</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.038</v>
+        <v>0.049</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.534</v>
+        <v>0.556</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.106</v>
+        <v>1.076</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.49</v>
+        <v>2.438</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.88</v>
+        <v>36.39</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="AG40" s="1" t="n">
         <v>0.02</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.158</v>
+        <v>0.132</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.333</v>
+        <v>0.277</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.285</v>
+        <v>0.282</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.509</v>
+        <v>0.467</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.469</v>
+        <v>0.401</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.616</v>
+        <v>1.517</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.055</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>30.09</v>
+        <v>29.93</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.066</v>
+        <v>0.071</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.185</v>
+        <v>0.174</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.133</v>
+        <v>0.137</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.291</v>
+        <v>0.288</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.455</v>
+        <v>0.441</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.508</v>
+        <v>0.451</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.627</v>
+        <v>1.463</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.149</v>
+        <v>0.143</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>170.69</v>
+        <v>171.99</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.008</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="T41" s="1" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>-0.008</v>
       </c>
-      <c r="T41" s="1" t="n">
-        <v>-0.077</v>
-      </c>
-      <c r="U41" s="1" t="n">
-        <v>-0.019</v>
-      </c>
       <c r="V41" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.005</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.154</v>
+        <v>0.138</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.752</v>
+        <v>0.78</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.059</v>
+        <v>1.012</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.619</v>
+        <v>4.535</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.041</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>74.45</v>
+        <v>73.18</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.017</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.142</v>
+        <v>0.12</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.204</v>
+        <v>0.193</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.385</v>
+        <v>0.363</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.706</v>
+        <v>0.668</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.58</v>
+        <v>0.523</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.669</v>
+        <v>1.54</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.109</v>
+        <v>0.09</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.42</v>
+        <v>24.78</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.015</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.026</v>
+        <v>0.085</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.149</v>
+        <v>-0.07</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.172</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.27</v>
+        <v>-0.253</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.187</v>
+        <v>-0.188</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.189</v>
+        <v>0.196</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.443</v>
+        <v>-0.448</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.158</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>105.38</v>
+        <v>103.3</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.02</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.011</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.131</v>
+        <v>0.107</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.17</v>
+        <v>0.161</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.341</v>
+        <v>0.312</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.661</v>
+        <v>0.629</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.663</v>
+        <v>0.602</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.635</v>
+        <v>1.515</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.097</v>
+        <v>0.076</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>189.58</v>
+        <v>191.17</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.008</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.007</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.042</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.048</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.037</v>
+        <v>0.063</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.248</v>
+        <v>0.238</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.301</v>
+        <v>1.302</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.221</v>
+        <v>1.21</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>7.053</v>
+        <v>6.902</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.043</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>54.34</v>
+        <v>56.45</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.039</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.061</v>
+        <v>0.06</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.271</v>
+        <v>0.307</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.435</v>
+        <v>0.456</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.303</v>
+        <v>1.385</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.943</v>
+        <v>2.033</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.784</v>
+        <v>2.636</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.051</v>
+        <v>5.091</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.272</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>45.03</v>
+        <v>44.5</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.055</v>
+        <v>0.027</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.123</v>
+        <v>0.099</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.189</v>
+        <v>0.182</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.277</v>
+        <v>0.254</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.711</v>
+        <v>0.686</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>1.053</v>
+        <v>0.997</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.294</v>
+        <v>2.179</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.089</v>
+        <v>0.076</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>81.57</v>
+        <v>82.77</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.015</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.01</v>
+        <v>0.076</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.075</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.213</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.241</v>
+        <v>-0.228</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.151</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.15</v>
+        <v>0.155</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.439</v>
+        <v>3.377</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.228</v>
+        <v>-0.217</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>81.95</v>
+        <v>87.19</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.027</v>
+        <v>0.064</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.014</v>
+        <v>0.078</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.083</v>
+        <v>0.157</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.17</v>
+        <v>0.242</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.097</v>
+        <v>0.136</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.089</v>
+        <v>0.159</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.237</v>
+        <v>0.277</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>0.984</v>
+        <v>1.176</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.167</v>
+        <v>0.172</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.185</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>62.58</v>
+        <v>61.5</v>
       </c>
       <c r="D45" s="1" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="E45" s="1" t="n">
         <v>-0.002</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>0.004</v>
       </c>
       <c r="F45" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.17</v>
+        <v>0.149</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.272</v>
+        <v>0.252</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.463</v>
+        <v>0.458</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.75</v>
+        <v>0.69</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.599</v>
+        <v>1.413</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.144</v>
+        <v>0.124</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>73.16</v>
+        <v>74.69</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.021</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.057</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.038</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.102</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.126</v>
+        <v>-0.102</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.021</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.585</v>
+        <v>0.603</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.314</v>
+        <v>0.321</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.442</v>
+        <v>2.407</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.09</v>
+        <v>-0.071</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>34.81</v>
+        <v>37.34</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.03</v>
+        <v>0.073</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.027</v>
+        <v>0.102</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.108</v>
+        <v>0.194</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.208</v>
+        <v>0.295</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.153</v>
+        <v>0.201</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.15</v>
+        <v>0.238</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.282</v>
+        <v>0.333</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.149</v>
+        <v>1.374</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.15</v>
+        <v>2.236</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.229</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.52</v>
+        <v>33.42</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.153</v>
+        <v>0.162</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.102</v>
+        <v>0.098</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.29</v>
+        <v>352.05</v>
       </c>
       <c r="R46" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="S46" s="1" t="n">
         <v>-0.013</v>
       </c>
-      <c r="S46" s="1" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="T46" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.211</v>
+        <v>0.164</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.407</v>
+        <v>0.455</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.729</v>
+        <v>0.7</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.647</v>
+        <v>1.615</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.643</v>
+        <v>1.639</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>12.831</v>
+        <v>12.407</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.52</v>
+        <v>12</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>-0.041</v>
+        <v>0.022</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.055</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.192</v>
+        <v>-0.198</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.061</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.448</v>
+        <v>-0.41</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.679</v>
+        <v>-0.673</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.721</v>
+        <v>-0.718</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.887</v>
+        <v>-0.873</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>49.69</v>
+        <v>48.88</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.004</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.122</v>
+        <v>0.102</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.28</v>
+        <v>0.256</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.569</v>
+        <v>0.537</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.591</v>
+        <v>0.536</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.656</v>
+        <v>1.6</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.093</v>
+        <v>0.075</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.23</v>
+        <v>124.79</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.005</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.016</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.041</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.047</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.058</v>
+        <v>0.073</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.26</v>
+        <v>0.249</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.434</v>
+        <v>1.432</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.115</v>
+        <v>1.098</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.597</v>
+        <v>6.431</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.034</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.68</v>
+        <v>44.16</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.012</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.001</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.183</v>
+        <v>0.151</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.254</v>
+        <v>0.252</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.596</v>
+        <v>0.578</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.911</v>
+        <v>0.88</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.982</v>
+        <v>0.921</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.98</v>
+        <v>1.844</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.133</v>
+        <v>0.119</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>51.01</v>
+        <v>50.6</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.014</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.027</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.089</v>
+        <v>0.049</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.417</v>
+        <v>0.406</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.154</v>
+        <v>0.145</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.059</v>
+        <v>0.05</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.02</v>
+        <v>25.99</v>
       </c>
       <c r="AF48" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.019</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>0.006</v>
+        <v>0.017</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.704</v>
+        <v>0.705</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.516</v>
+        <v>0.513</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>52.71</v>
+        <v>51.9</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.015</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.01</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.135</v>
+        <v>0.115</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.175</v>
+        <v>0.167</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.391</v>
+        <v>0.359</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.825</v>
+        <v>0.798</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.684</v>
+        <v>0.634</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.89</v>
+        <v>1.867</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.099</v>
+        <v>0.082</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.01</v>
+        <v>35.32</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.009</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.021</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.019</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.04</v>
+        <v>0.038</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.136</v>
+        <v>0.158</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.406</v>
+        <v>0.403</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.89</v>
+        <v>17.83</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.012</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.046</v>
+        <v>0.006</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.079</v>
+        <v>-0.065</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.291</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.141</v>
+        <v>-0.132</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.75</v>
+        <v>40.2</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.152</v>
+        <v>0.112</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.233</v>
+        <v>0.248</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.287</v>
+        <v>0.296</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.445</v>
+        <v>0.448</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.858</v>
+        <v>0.892</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.745</v>
+        <v>0.697</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.173</v>
+        <v>0.186</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>22.57</v>
+        <v>21.99</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>0.03</v>
+        <v>-0.026</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="AH50" s="1" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="AI50" s="1" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AJ50" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AK50" s="1" t="n">
+        <v>-0.089</v>
+      </c>
+      <c r="AL50" s="1" t="n">
+        <v>-0.389</v>
+      </c>
+      <c r="AM50" s="1" t="n">
+        <v>-0.308</v>
+      </c>
+      <c r="AN50" s="1" t="n">
+        <v>-0.489</v>
+      </c>
+      <c r="AO50" s="1" t="n">
         <v>0.101</v>
-      </c>
-      <c r="AI50" s="1" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AJ50" s="1" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="AK50" s="1" t="n">
-        <v>-0.079</v>
-      </c>
-      <c r="AL50" s="1" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="AM50" s="1" t="n">
-        <v>-0.282</v>
-      </c>
-      <c r="AN50" s="1" t="n">
-        <v>-0.479</v>
-      </c>
-      <c r="AO50" s="1" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>53.02</v>
+        <v>53.05</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.017</v>
+        <v>0.039</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.058</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.115</v>
+        <v>-0.13</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.157</v>
+        <v>-0.153</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.02</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.518</v>
+        <v>0.548</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>0.031</v>
+        <v>0.007</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.457</v>
+        <v>1.405</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.11</v>
+        <v>-0.109</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.82</v>
+        <v>23.69</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.068</v>
+        <v>0.071</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.07</v>
+        <v>0.069</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.092</v>
+        <v>0.1</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.153</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.131</v>
+        <v>0.12</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.39</v>
+        <v>0.384</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.09</v>
+        <v>0.084</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>37.19</v>
+        <v>39.19</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.054</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.072</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.265</v>
+        <v>-0.114</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.271</v>
+        <v>-0.241</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.416</v>
+        <v>-0.378</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.215</v>
+        <v>-0.182</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.251</v>
+        <v>-0.211</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.33</v>
+        <v>48.83</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.01</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.009</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.142</v>
+        <v>-0.118</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.108</v>
+        <v>-0.118</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.136</v>
+        <v>-0.14</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.058</v>
+        <v>0.053</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.467</v>
+        <v>0.409</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.298</v>
+        <v>-0.321</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.957</v>
+        <v>1.833</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.116</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.52</v>
+        <v>15.37</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.059</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-0.025</v>
+        <v>0.094</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.364</v>
+        <v>-0.122</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.366</v>
+        <v>-0.317</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.524</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.148</v>
+        <v>-0.085</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.353</v>
+        <v>-0.315</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>93.78</v>
+        <v>92.71</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.011</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>0.009</v>
+        <v>0</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.08</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.136</v>
+        <v>-0.147</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.175</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>1.061</v>
+        <v>0.99</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.392</v>
+        <v>0.354</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.095</v>
+        <v>-0.105</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.29</v>
+        <v>9.28</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.008</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.035</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.155</v>
+        <v>-0.142</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.235</v>
+        <v>-0.216</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.111</v>
+        <v>-0.115</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.247</v>
+        <v>0.236</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.061</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.049</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>60.38</v>
+        <v>60.17</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.004</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.122</v>
+        <v>-0.107</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.058</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.117</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.068</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.145</v>
+        <v>0.113</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.359</v>
+        <v>1.286</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.103</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>120.7</v>
+        <v>119.96</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.006</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.092</v>
+        <v>0.107</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.07</v>
+        <v>0.087</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.122</v>
+        <v>0.131</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.234</v>
+        <v>0.208</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.594</v>
+        <v>0.608</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.885</v>
+        <v>0.842</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.753</v>
+        <v>1.721</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.114</v>
+        <v>0.107</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.63</v>
+        <v>39.73</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.112</v>
+        <v>0.114</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.183</v>
+        <v>0.179</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.379</v>
+        <v>0.369</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.358</v>
+        <v>0.365</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.325</v>
+        <v>0.33</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.73</v>
+        <v>47.37</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.099</v>
+        <v>0.111</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.069</v>
+        <v>0.086</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.135</v>
+        <v>0.143</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.258</v>
+        <v>0.23</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.582</v>
+        <v>0.595</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.905</v>
+        <v>0.855</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.844</v>
+        <v>1.814</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.118</v>
+        <v>0.11</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>28.9</v>
+        <v>29.26</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.043</v>
+        <v>0.012</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.006</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.073</v>
+        <v>0.12</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.077</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.197</v>
+        <v>-0.217</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.379</v>
+        <v>-0.362</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.847</v>
+        <v>-0.837</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.972</v>
+        <v>-0.969</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>73.04</v>
+        <v>72.78</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.011</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.102</v>
+        <v>0.089</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.403</v>
+        <v>0.39</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.553</v>
+        <v>0.535</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.762</v>
+        <v>2.598</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>101.28</v>
+        <v>101.54</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.059</v>
+        <v>0.073</v>
       </c>
       <c r="V57" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="W57" s="1" t="n">
         <v>0.057</v>
       </c>
-      <c r="W57" s="1" t="n">
-        <v>0.063</v>
-      </c>
       <c r="X57" s="1" t="n">
-        <v>0.258</v>
+        <v>0.265</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.32</v>
+        <v>0.331</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.92</v>
+        <v>0.865</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.57</v>
+        <v>90.11</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.072</v>
+        <v>0.084</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.039</v>
+        <v>0.052</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.081</v>
+        <v>0.099</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.329</v>
+        <v>0.345</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>1.038</v>
+        <v>0.984</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.084</v>
+        <v>0.09</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.69</v>
+        <v>95.93</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.059</v>
+        <v>0.068</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.061</v>
+        <v>0.076</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.06</v>
+        <v>0.077</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.258</v>
+        <v>0.264</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.311</v>
+        <v>0.321</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.848</v>
+        <v>0.796</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.081</v>
+        <v>0.084</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.62</v>
+        <v>22.76</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.018</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.052</v>
+        <v>0.008</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.054</v>
+        <v>0.048</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.228</v>
+        <v>0.272</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.038</v>
+        <v>0.024</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.537</v>
+        <v>0.539</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.02</v>
+        <v>0.026</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>97.34</v>
+        <v>98.48</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.092</v>
+        <v>0.129</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.124</v>
+        <v>0.135</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.169</v>
+        <v>0.211</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.257</v>
+        <v>0.271</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.481</v>
+        <v>0.498</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.548</v>
+        <v>0.549</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.972</v>
+        <v>1.957</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.145</v>
+        <v>0.159</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">03/02/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">03/03/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>334.94</v>
+        <v>333.33</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>-0.023</v>
-      </c>
       <c r="H5" s="1" t="n">
-        <v>0.059</v>
+        <v>0.045</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.164</v>
+        <v>0.183</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.944</v>
+        <v>0.901</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.022</v>
+        <v>1.041</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.412</v>
+        <v>3.384</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.028</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.29</v>
+        <v>59.7</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.01</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.138</v>
+        <v>0.093</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.267</v>
+        <v>0.232</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.272</v>
+        <v>0.286</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.294</v>
+        <v>0.329</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.439</v>
+        <v>0.404</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.691</v>
+        <v>1.629</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.56</v>
+        <v>1.494</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.268</v>
+        <v>0.256</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,10 +1744,10 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.81</v>
+        <v>82.8</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
         <v>0</v>
@@ -1756,25 +1756,25 @@
         <v>0.004</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="AL5" s="1" t="n">
         <v>0.144</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>689.45</v>
+        <v>683.37</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0</v>
+        <v>-0.009</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>-0.013</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.079</v>
+        <v>0.063</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.799</v>
+        <v>0.755</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.908</v>
+        <v>0.917</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.071</v>
+        <v>3.021</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.002</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>112.3</v>
+        <v>111.99</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.036</v>
+        <v>-0.003</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.174</v>
+        <v>0.135</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.209</v>
+        <v>0.178</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.205</v>
+        <v>0.238</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.24</v>
+        <v>0.295</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.336</v>
+        <v>0.312</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.715</v>
+        <v>1.644</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>2.014</v>
+        <v>1.899</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.258</v>
+        <v>0.255</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,34 +1863,34 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.88</v>
+        <v>119.82</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AG6" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.158</v>
+        <v>0.154</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="AO6" s="1" t="n">
         <v>0.01</v>
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>72.1</v>
+        <v>70.86</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.017</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.009</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.041</v>
+        <v>0.021</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>0.102</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>0.12</v>
-      </c>
       <c r="I7" s="1" t="n">
-        <v>0.182</v>
+        <v>0.188</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.44</v>
+        <v>0.399</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.535</v>
+        <v>0.521</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>2.051</v>
+        <v>1.965</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.092</v>
+        <v>0.074</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.98</v>
+        <v>28.12</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.036</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.134</v>
+        <v>0.075</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.388</v>
+        <v>0.294</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.547</v>
+        <v>0.525</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.483</v>
+        <v>0.509</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.334</v>
+        <v>0.277</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.154</v>
+        <v>1.076</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.059</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.389</v>
+        <v>0.347</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.12</v>
+        <v>97.01</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.142</v>
+        <v>0.132</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.036</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>263.81</v>
+        <v>259.24</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.017</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.08</v>
+        <v>0.042</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.135</v>
+        <v>0.116</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.243</v>
+        <v>0.256</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.45</v>
+        <v>0.406</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.265</v>
+        <v>0.257</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.833</v>
+        <v>1.755</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.072</v>
+        <v>0.053</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.33</v>
+        <v>17.72</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.033</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.077</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.055</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.105</v>
+        <v>0.073</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.305</v>
+        <v>0.258</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.059</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.244</v>
+        <v>-0.218</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.516</v>
+        <v>1.394</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.116</v>
+        <v>0.079</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.78</v>
+        <v>103.59</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AH8" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AK8" s="1" t="n">
         <v>0.032</v>
       </c>
-      <c r="AI8" s="1" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="AJ8" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AK8" s="1" t="n">
-        <v>0.039</v>
-      </c>
       <c r="AL8" s="1" t="n">
-        <v>0.097</v>
+        <v>0.076</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.155</v>
+        <v>-0.15</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.73</v>
+        <v>26.25</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.022</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.091</v>
+        <v>0.052</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.11</v>
+        <v>0.085</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.216</v>
+        <v>0.232</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.298</v>
+        <v>0.254</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.173</v>
+        <v>1.103</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.492</v>
+        <v>1.371</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.136</v>
+        <v>0.116</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.61</v>
+        <v>89.43</v>
       </c>
       <c r="AF9" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AL9" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG9" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AH9" s="1" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="AI9" s="1" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9" s="1" t="n">
-        <v>0.069</v>
-      </c>
-      <c r="AK9" s="1" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="AL9" s="1" t="n">
-        <v>0.016</v>
-      </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.254</v>
+        <v>-0.247</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.087</v>
+        <v>-0.092</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>189.59</v>
+        <v>183.37</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.033</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.02</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.105</v>
+        <v>0.039</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.284</v>
+        <v>0.234</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.29</v>
+        <v>0.254</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.393</v>
+        <v>0.376</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.442</v>
+        <v>0.373</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.724</v>
+        <v>0.684</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.251</v>
+        <v>2.126</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.231</v>
+        <v>0.191</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.57</v>
+        <v>111.5</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.047</v>
+        <v>0.043</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.139</v>
+        <v>0.126</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.316</v>
+        <v>0.313</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>225.15</v>
+        <v>222.27</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.013</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.009</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.085</v>
+        <v>0.062</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.133</v>
+        <v>0.119</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.179</v>
+        <v>0.176</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.544</v>
+        <v>0.503</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.696</v>
+        <v>0.678</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.927</v>
+        <v>1.871</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.07</v>
+        <v>0.057</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>64.36</v>
+        <v>60.54</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0</v>
+        <v>-0.059</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.104</v>
+        <v>-0.008</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.367</v>
+        <v>0.254</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.602</v>
+        <v>0.488</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.856</v>
+        <v>0.755</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.606</v>
+        <v>0.487</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.863</v>
+        <v>0.75</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>4.41</v>
+        <v>3.895</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.254</v>
+        <v>0.179</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2413,31 +2413,31 @@
         <v>103.26</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AJ11" s="1" t="n">
         <v>0.012</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.167</v>
+        <v>0.163</v>
       </c>
       <c r="AM11" s="1" t="n">
         <v>0.189</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="AO11" s="1" t="n">
         <v>0.008</v>
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>451.47</v>
+        <v>448.66</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>-0.009</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>0.008</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="G12" s="1" t="n">
+      <c r="I12" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>4.079</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>-0.052</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>4.124</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>-0.046</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>99.05</v>
+        <v>90.42</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.087</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>0.048</v>
+        <v>-0.051</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.225</v>
+        <v>0.071</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.432</v>
+        <v>0.316</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.794</v>
+        <v>0.628</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>2.038</v>
+        <v>1.775</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.735</v>
+        <v>3.26</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>3.036</v>
+        <v>2.776</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.94</v>
+        <v>5.104</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.345</v>
+        <v>0.228</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>108.27</v>
+        <v>107.76</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.05</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.041</v>
+        <v>0.037</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.067</v>
+        <v>0.063</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.247</v>
+        <v>0.24</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>204.47</v>
+        <v>202.29</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.011</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.034</v>
+        <v>0.019</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.096</v>
+        <v>0.078</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.137</v>
+        <v>0.141</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.769</v>
+        <v>0.724</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.84</v>
+        <v>0.846</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.741</v>
+        <v>2.697</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.66</v>
+        <v>42.26</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.094</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0.049</v>
+        <v>-0.059</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.22</v>
+        <v>0.036</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.491</v>
+        <v>0.364</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>1.089</v>
+        <v>0.847</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.643</v>
+        <v>2.333</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.92</v>
+        <v>3.324</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>2.151</v>
+        <v>1.958</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>6.516</v>
+        <v>5.484</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.362</v>
+        <v>0.233</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.22</v>
+        <v>23.04</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.009</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.033</v>
+        <v>0.025</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.048</v>
+        <v>0.039</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.096</v>
+        <v>0.089</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.291</v>
+        <v>0.276</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>97.68</v>
+        <v>97.21</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.009</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.047</v>
+        <v>0.042</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.451</v>
+        <v>0.431</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.589</v>
+        <v>0.6</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.764</v>
+        <v>1.745</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>56.61</v>
+        <v>52.8</v>
       </c>
       <c r="R14" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.067</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0.032</v>
+        <v>-0.058</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>0.098</v>
+        <v>-0.038</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.425</v>
+        <v>0.283</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.769</v>
+        <v>0.623</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.284</v>
+        <v>1.148</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.278</v>
+        <v>0.192</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>75.67</v>
+        <v>75.27</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.005</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.013</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.015</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.157</v>
+        <v>0.144</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.051</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.021</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>253.7</v>
+        <v>247.01</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.026</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.037</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.008</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.052</v>
+        <v>0.023</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.173</v>
+        <v>0.164</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.863</v>
+        <v>0.797</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.628</v>
+        <v>0.651</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>3.025</v>
+        <v>2.922</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.013</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.01</v>
+        <v>16.42</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.088</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.047</v>
+        <v>-0.083</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.088</v>
+        <v>-0.042</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.224</v>
+        <v>0.129</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.839</v>
+        <v>0.67</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>1.113</v>
+        <v>0.932</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.153</v>
+        <v>0.051</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>96.99</v>
+        <v>96.55</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="AH15" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AI15" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="AI15" s="1" t="n">
-        <v>0.018</v>
-      </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.349</v>
+        <v>0.323</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.45</v>
+        <v>0.442</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>140.18</v>
+        <v>138.39</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.157</v>
+        <v>0.133</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.158</v>
+        <v>0.153</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.199</v>
+        <v>0.187</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.542</v>
+        <v>0.504</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.848</v>
+        <v>0.821</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.656</v>
+        <v>1.617</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.153</v>
+        <v>0.138</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>76.56</v>
+        <v>74.83</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>-0.023</v>
       </c>
       <c r="S16" s="1" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="Y16" s="1" t="n">
         <v>-0.029</v>
       </c>
-      <c r="T16" s="1" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="U16" s="1" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="V16" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="W16" s="1" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="X16" s="1" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="Y16" s="1" t="n">
-        <v>0.005</v>
-      </c>
       <c r="Z16" s="1" t="n">
-        <v>1.126</v>
+        <v>1.066</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.063</v>
+        <v>0.039</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.52</v>
+        <v>41.77</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.018</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.017</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.037</v>
+        <v>0.015</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.074</v>
+        <v>0.053</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.176</v>
+        <v>0.151</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.263</v>
+        <v>0.234</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.28</v>
+        <v>0.246</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.023</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149.27</v>
+        <v>147.94</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.009</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.012</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.162</v>
+        <v>0.172</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.759</v>
+        <v>0.716</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.789</v>
+        <v>0.801</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>108.01</v>
+        <v>105.31</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.025</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.045</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.075</v>
+        <v>0.029</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.152</v>
+        <v>0.111</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.189</v>
+        <v>0.163</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.494</v>
+        <v>0.501</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.406</v>
+        <v>1.305</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.38</v>
+        <v>1.334</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>3.875</v>
+        <v>3.712</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.167</v>
+        <v>0.137</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.49</v>
+        <v>42.13</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.008</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.014</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.006</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.109</v>
+        <v>0.093</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.136</v>
+        <v>0.117</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.189</v>
+        <v>-0.191</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.066</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>162.04</v>
+        <v>159.26</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.017</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.007</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.122</v>
+        <v>0.092</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.192</v>
+        <v>0.187</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.647</v>
+        <v>0.597</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.67</v>
+        <v>0.654</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.566</v>
+        <v>2.479</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>36.62</v>
+        <v>35.53</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.03</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.04</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.057</v>
+        <v>0.013</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.198</v>
+        <v>0.154</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.304</v>
+        <v>0.272</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.507</v>
+        <v>0.498</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.174</v>
+        <v>0.139</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>58.16</v>
+        <v>57.07</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.019</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.001</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.066</v>
+        <v>0.041</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.125</v>
+        <v>0.097</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.208</v>
+        <v>0.178</v>
       </c>
       <c r="I20" s="1" t="n">
         <v>0.433</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.799</v>
+        <v>0.742</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.938</v>
+        <v>0.917</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.24</v>
+        <v>2.145</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.078</v>
+        <v>0.058</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.95</v>
+        <v>81.61</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.04</v>
+        <v>0.023</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.119</v>
+        <v>0.086</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.167</v>
+        <v>0.162</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.186</v>
+        <v>0.2</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.44</v>
+        <v>0.427</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.45</v>
+        <v>0.447</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.723</v>
+        <v>1.683</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.68</v>
+        <v>100.57</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH20" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="AJ20" s="1" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AK20" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AL20" s="1" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="AM20" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AN20" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AO20" s="1" t="n">
         <v>0.013</v>
-      </c>
-      <c r="AI20" s="1" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="AJ20" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AK20" s="1" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="AL20" s="1" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="AM20" s="1" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="AN20" s="1" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="AO20" s="1" t="n">
-        <v>0.014</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>36.26</v>
+        <v>34.52</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.048</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.068</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.059</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.179</v>
+        <v>0.122</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.374</v>
+        <v>0.31</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.697</v>
+        <v>0.622</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.784</v>
+        <v>0.672</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.91</v>
+        <v>0.824</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.634</v>
+        <v>1.405</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.191</v>
+        <v>0.134</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>250.58</v>
+        <v>244.98</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.028</v>
+        <v>-0.022</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.039</v>
+        <v>0.008</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.084</v>
+        <v>0.045</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.245</v>
+        <v>0.215</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.267</v>
+        <v>0.249</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.629</v>
+        <v>0.611</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.195</v>
+        <v>1.134</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.658</v>
+        <v>1.591</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.897</v>
+        <v>3.771</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.167</v>
+        <v>0.141</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.66</v>
+        <v>50.6</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.184</v>
+        <v>0.177</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.276</v>
+        <v>0.271</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>79.46</v>
+        <v>75.37</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.051</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.062</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.053</v>
+        <v>-0.043</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.179</v>
+        <v>0.123</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.287</v>
+        <v>0.223</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.632</v>
+        <v>0.569</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.493</v>
+        <v>0.379</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.2</v>
+        <v>1.092</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>1.035</v>
+        <v>0.938</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.146</v>
+        <v>0.087</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.11</v>
+        <v>101.64</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.002</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.022</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.016</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.014</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.065</v>
+        <v>0.078</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.658</v>
+        <v>0.624</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.436</v>
+        <v>0.45</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.126</v>
+        <v>2.098</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.014</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.47</v>
+        <v>49.3</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.066</v>
+        <v>0.061</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.197</v>
+        <v>0.187</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.271</v>
+        <v>0.269</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>38.64</v>
+        <v>36.82</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.047</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.067</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.032</v>
+        <v>-0.032</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.175</v>
+        <v>0.114</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.379</v>
+        <v>0.315</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.69</v>
+        <v>0.608</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.726</v>
+        <v>0.634</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.787</v>
+        <v>0.699</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>1.918</v>
+        <v>1.59</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.216</v>
+        <v>0.159</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>104.96</v>
+        <v>103.69</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.012</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.059</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>0.022</v>
+        <v>-0.013</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.016</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.062</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.08</v>
+        <v>0.086</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.603</v>
+        <v>0.555</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.778</v>
+        <v>0.81</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.416</v>
+        <v>3.309</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.09</v>
+        <v>0.077</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>96.05</v>
+        <v>95.98</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.069</v>
+        <v>0.067</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.178</v>
+        <v>0.168</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.159</v>
+        <v>0.157</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>66.81</v>
+        <v>64.53</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.034</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.059</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.038</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.071</v>
+        <v>0.028</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.142</v>
+        <v>0.101</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.315</v>
+        <v>0.243</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.655</v>
+        <v>0.574</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.678</v>
+        <v>0.633</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.662</v>
+        <v>1.546</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.042</v>
+        <v>0.007</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>40.04</v>
+        <v>37.69</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.059</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.078</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>0.056</v>
+        <v>-0.011</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.067</v>
+        <v>0.002</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.158</v>
+        <v>0.095</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.335</v>
+        <v>0.295</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.095</v>
+        <v>0.003</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.077</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>0.056</v>
+        <v>-0.006</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>110.92</v>
+        <v>110.87</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="AI24" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AK24" s="1" t="n">
         <v>0.059</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>46.02</v>
+        <v>44.83</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.026</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.044</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.017</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.07</v>
+        <v>0.038</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.149</v>
+        <v>0.119</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.187</v>
+        <v>0.146</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.595</v>
+        <v>0.535</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>2.048</v>
+        <v>1.964</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.052</v>
+        <v>0.024</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16</v>
+        <v>85.65</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.006</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.028</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.024</v>
+        <v>0.004</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.172</v>
+        <v>0.2</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.358</v>
+        <v>0.33</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.136</v>
+        <v>0.133</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.267</v>
+        <v>1.234</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.68</v>
+        <v>92.45</v>
       </c>
       <c r="AF25" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.006</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AJ25" s="1" t="n">
         <v>0.029</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.244</v>
+        <v>0.242</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.267</v>
+        <v>0.271</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.608</v>
+        <v>0.607</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>48.12</v>
+        <v>46.76</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.028</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.034</v>
+        <v>0.006</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.14</v>
+        <v>0.097</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.199</v>
+        <v>0.157</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.351</v>
+        <v>0.3</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.671</v>
+        <v>0.613</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.888</v>
+        <v>0.832</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.318</v>
+        <v>1.234</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.094</v>
+        <v>0.063</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.89</v>
+        <v>60.37</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.009</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.004</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.027</v>
+        <v>0.014</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.117</v>
+        <v>0.135</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.495</v>
+        <v>0.473</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.239</v>
+        <v>0.23</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.817</v>
+        <v>0.791</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.67</v>
+        <v>26.46</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.063</v>
+        <v>0.055</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.198</v>
+        <v>0.181</v>
       </c>
       <c r="AM26" s="1" t="n">
         <v>0.131</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>46.57</v>
+        <v>45.07</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.032</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.054</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.053</v>
+        <v>0.011</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.107</v>
+        <v>0.065</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.211</v>
+        <v>0.148</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.378</v>
+        <v>0.317</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.577</v>
+        <v>0.533</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.62</v>
+        <v>1.508</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.035</v>
+        <v>0.002</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.74</v>
+        <v>26.51</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.027</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.001</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.058</v>
+        <v>0.042</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,10 +4188,10 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>52.92</v>
+        <v>52.91</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="1" t="n">
         <v>-0.001</v>
@@ -4200,19 +4200,19 @@
         <v>0.005</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="AK27" s="1" t="n">
         <v>0.061</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
       <c r="AN27" s="1" t="n">
         <v>0.325</v>
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>42.91</v>
+        <v>41.57</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.054</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.045</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.049</v>
+        <v>0.015</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.046</v>
+        <v>0.013</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.209</v>
+        <v>0.137</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.676</v>
+        <v>0.592</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.49</v>
+        <v>0.449</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.259</v>
+        <v>1.167</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.022</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>76.77</v>
+        <v>75.46</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.017</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.019</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.068</v>
+        <v>0.035</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.138</v>
+        <v>0.127</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.109</v>
+        <v>0.096</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.114</v>
+        <v>0.085</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.283</v>
+        <v>0.258</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.66</v>
+        <v>1.592</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.147</v>
+        <v>0.128</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.11</v>
+        <v>54.07</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG28" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AH28" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AI28" s="1" t="n">
         <v>0.011</v>
       </c>
-      <c r="AI28" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.25</v>
+        <v>0.239</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.083</v>
+        <v>0.087</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>63.59</v>
+        <v>62.21</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.022</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.04</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.098</v>
+        <v>0.071</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.163</v>
+        <v>0.129</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.252</v>
+        <v>0.212</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.545</v>
+        <v>0.498</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.594</v>
+        <v>0.579</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.686</v>
+        <v>1.609</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.061</v>
+        <v>0.038</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.44</v>
+        <v>45.65</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.017</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.025</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.087</v>
+        <v>0.052</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.205</v>
+        <v>0.174</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.174</v>
+        <v>0.159</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.275</v>
+        <v>0.292</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.143</v>
+        <v>0.114</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.307</v>
+        <v>0.297</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.615</v>
+        <v>1.539</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.204</v>
+        <v>0.184</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>50.94</v>
+        <v>50.91</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.189</v>
+        <v>0.167</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.052</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>104.66</v>
+        <v>99.69</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.047</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.064</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.038</v>
+        <v>-0.013</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.141</v>
+        <v>0.087</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.239</v>
+        <v>0.176</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.452</v>
+        <v>0.399</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.67</v>
+        <v>0.578</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.225</v>
+        <v>0.169</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.572</v>
+        <v>1.442</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.113</v>
+        <v>0.06</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>50.54</v>
+        <v>49.52</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.02</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.028</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.049</v>
+        <v>0.012</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.119</v>
+        <v>0.099</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.072</v>
+        <v>0.052</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.09</v>
+        <v>0.082</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.164</v>
+        <v>0.137</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.436</v>
+        <v>0.41</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.811</v>
+        <v>0.771</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.128</v>
+        <v>0.105</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.3</v>
+        <v>24.18</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.018</v>
       </c>
       <c r="AI30" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.257</v>
+        <v>0.251</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.261</v>
+        <v>0.266</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>19.81</v>
+        <v>19.5</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.016</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.05</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.006</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.174</v>
+        <v>0.158</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.336</v>
+        <v>0.305</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.514</v>
+        <v>0.486</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.614</v>
+        <v>0.585</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.119</v>
+        <v>1.053</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.081</v>
+        <v>0.064</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.08</v>
+        <v>65.36</v>
       </c>
       <c r="R31" s="1" t="n">
         <v>-0.011</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.01</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.148</v>
+        <v>0.14</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.072</v>
+        <v>0.058</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.276</v>
+        <v>0.247</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.412</v>
+        <v>0.42</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.679</v>
+        <v>1.659</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.28</v>
+        <v>80.12</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG31" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AH31" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="AK31" s="1" t="n">
         <v>0.067</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.295</v>
+        <v>0.279</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.693</v>
+        <v>0.684</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>36.58</v>
+        <v>36.68</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.003</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.039</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.073</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.08</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.248</v>
+        <v>0.245</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.119</v>
+        <v>1.125</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>45.49</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.061</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.086</v>
+        <v>-0.088</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.089</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.167</v>
+        <v>1.114</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.051</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.5</v>
+        <v>29.32</v>
       </c>
       <c r="AF32" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AH32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AG32" s="1" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="AH32" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="AI32" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.086</v>
+        <v>0.081</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.298</v>
+        <v>0.278</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.051</v>
+        <v>1.027</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.015</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>50.95</v>
+        <v>50.22</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.014</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.047</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.055</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.06</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.046</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.307</v>
+        <v>0.264</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.29</v>
+        <v>0.261</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.228</v>
+        <v>1.177</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.071</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>91.31</v>
+        <v>89.7</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.018</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.021</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>0.037</v>
+        <v>0.025</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.103</v>
+        <v>0.078</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.294</v>
+        <v>0.273</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.282</v>
+        <v>0.256</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.629</v>
+        <v>0.582</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.261</v>
+        <v>1.235</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.076</v>
+        <v>0.057</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>48.04</v>
+        <v>47.99</v>
       </c>
       <c r="AF33" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AG33" s="1" t="n">
         <v>-0.003</v>
       </c>
-      <c r="AG33" s="1" t="n">
-        <v>-0.002</v>
-      </c>
       <c r="AH33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.182</v>
+        <v>0.173</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>90.2</v>
+        <v>86.83</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.048</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.135</v>
+        <v>0.09</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.197</v>
+        <v>0.156</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.378</v>
+        <v>0.312</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.757</v>
+        <v>0.653</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.482</v>
+        <v>0.435</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.437</v>
+        <v>1.329</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.117</v>
+        <v>0.075</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>173.92</v>
+        <v>170.1</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.022</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.035</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.021</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>0.029</v>
+        <v>-0.011</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.241</v>
+        <v>0.214</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.366</v>
+        <v>0.314</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.127</v>
+        <v>0.143</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>0.997</v>
+        <v>0.982</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>105.61</v>
+        <v>103.31</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.022</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.008</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.072</v>
+        <v>0.043</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.129</v>
+        <v>0.106</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.248</v>
+        <v>0.232</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.532</v>
+        <v>0.488</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.179</v>
+        <v>0.181</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.404</v>
+        <v>2.33</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.075</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>58.51</v>
+        <v>56.9</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.028</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.058</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.068</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.069</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.061</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.116</v>
+        <v>0.101</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.256</v>
+        <v>0.219</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.258</v>
+        <v>-0.275</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.742</v>
+        <v>0.695</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.053</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.63</v>
+        <v>59</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.011</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.066</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.035</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.074</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.151</v>
+        <v>0.119</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.093</v>
+        <v>0.107</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.155</v>
+        <v>2.117</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.051</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.94</v>
+        <v>23.51</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.114</v>
+        <v>0.092</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.161</v>
+        <v>0.148</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.435</v>
+        <v>0.432</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.298</v>
+        <v>0.276</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.099</v>
+        <v>0.069</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.803</v>
+        <v>0.768</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.127</v>
+        <v>0.106</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.91</v>
+        <v>29.83</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.035</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.041</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.071</v>
+        <v>0.033</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.191</v>
+        <v>0.12</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.391</v>
+        <v>0.326</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.392</v>
+        <v>0.379</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.331</v>
+        <v>0.262</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.312</v>
+        <v>-0.299</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.18</v>
+        <v>0.139</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>75.07</v>
+        <v>71.29</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.05</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.059</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.089</v>
+        <v>0.036</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.215</v>
+        <v>0.15</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.353</v>
+        <v>0.27</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.545</v>
+        <v>0.484</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>1.055</v>
+        <v>0.932</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.879</v>
+        <v>0.788</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.74</v>
+        <v>3.468</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.182</v>
+        <v>0.122</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>122.54</v>
+        <v>122.04</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.044</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.032</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.014</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.637</v>
+        <v>0.606</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.819</v>
+        <v>0.808</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.519</v>
+        <v>2.481</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.053</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>100.38</v>
+        <v>95.92</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.044</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.146</v>
+        <v>0.031</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.266</v>
+        <v>0.211</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.506</v>
+        <v>0.427</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.863</v>
+        <v>0.758</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.882</v>
+        <v>1.726</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>2.04</v>
+        <v>1.935</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>3.193</v>
+        <v>2.941</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.237</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>147.54</v>
+        <v>132.34</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.103</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>0.059</v>
+        <v>-0.084</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.22</v>
+        <v>0.065</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.638</v>
+        <v>0.455</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>1.098</v>
+        <v>0.856</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.759</v>
+        <v>1.491</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.67</v>
+        <v>1.346</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.832</v>
+        <v>0.648</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.691</v>
+        <v>2.266</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.518</v>
+        <v>0.361</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>61.89</v>
+        <v>61.51</v>
       </c>
       <c r="R38" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="S38" s="1" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="T38" s="1" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="U38" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="V38" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="W38" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="X38" s="1" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="Y38" s="1" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="Z38" s="1" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="AA38" s="1" t="n">
         <v>0.014</v>
-      </c>
-      <c r="S38" s="1" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="T38" s="1" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="U38" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="V38" s="1" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="W38" s="1" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="X38" s="1" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="Y38" s="1" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="Z38" s="1" t="n">
-        <v>1.624</v>
-      </c>
-      <c r="AA38" s="1" t="n">
-        <v>0.02</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>81.57</v>
+        <v>74.68</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.084</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.056</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>0.126</v>
+        <v>-0.03</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.535</v>
+        <v>0.407</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.196</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.881</v>
+        <v>1.598</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>3.24</v>
+        <v>2.82</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.289</v>
+        <v>2.076</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.724</v>
+        <v>4.15</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.266</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>29.82</v>
+        <v>27.6</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.074</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.085</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.062</v>
+        <v>-0.031</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.218</v>
+        <v>0.116</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.342</v>
+        <v>0.241</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.83</v>
+        <v>0.705</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.888</v>
+        <v>0.73</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.546</v>
+        <v>0.447</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.217</v>
+        <v>1.023</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.115</v>
+        <v>0.032</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>67.76</v>
+        <v>67.3</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.007</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.02</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.055</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.077</v>
+        <v>0.048</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.054</v>
+        <v>0.046</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.12</v>
+        <v>0.129</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.243</v>
+        <v>0.22</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.177</v>
+        <v>0.159</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.332</v>
+        <v>1.273</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>209.78</v>
+        <v>190.89</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.09</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>0.063</v>
+        <v>-0.034</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>0.078</v>
+        <v>-0.058</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.401</v>
+        <v>0.259</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.638</v>
+        <v>0.473</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.428</v>
+        <v>1.19</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.355</v>
+        <v>1.113</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.857</v>
+        <v>0.735</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.322</v>
+        <v>1.086</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.125</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>79.9</v>
+        <v>73.56</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.072</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.091</v>
+        <v>-0.013</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.267</v>
+        <v>0.159</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.472</v>
+        <v>0.345</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.921</v>
+        <v>0.763</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.244</v>
+        <v>1.049</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>1.045</v>
+        <v>0.903</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.707</v>
+        <v>1.471</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.161</v>
+        <v>0.069</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>137.56</v>
+        <v>136.46</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="T40" s="1" t="n">
         <v>0.025</v>
       </c>
-      <c r="T40" s="1" t="n">
-        <v>0.033</v>
-      </c>
       <c r="U40" s="1" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.049</v>
+        <v>0.035</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.556</v>
+        <v>0.531</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.076</v>
+        <v>1.049</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.438</v>
+        <v>2.404</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>36.39</v>
+        <v>35.6</v>
       </c>
       <c r="AF40" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.022</v>
       </c>
       <c r="AG40" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.019</v>
       </c>
       <c r="AH40" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.05</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.132</v>
+        <v>0.078</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.277</v>
+        <v>0.255</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.282</v>
+        <v>0.246</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.467</v>
+        <v>0.433</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.401</v>
+        <v>0.398</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.517</v>
+        <v>1.425</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.041</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.93</v>
+        <v>29.09</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.028</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.017</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.071</v>
+        <v>0.034</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.174</v>
+        <v>0.132</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.137</v>
+        <v>0.112</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.288</v>
+        <v>0.254</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.441</v>
+        <v>0.378</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.451</v>
+        <v>0.42</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.463</v>
+        <v>1.347</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.143</v>
+        <v>0.111</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>171.99</v>
+        <v>171.17</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.005</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.029</v>
+        <v>0.009</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.047</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.032</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.138</v>
+        <v>0.153</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.78</v>
+        <v>0.746</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.012</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.535</v>
+        <v>4.44</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.046</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>73.18</v>
+        <v>70.63</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.035</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.047</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.028</v>
+        <v>-0.01</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.12</v>
+        <v>0.077</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.193</v>
+        <v>0.149</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.363</v>
+        <v>0.312</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.668</v>
+        <v>0.59</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.523</v>
+        <v>0.476</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.54</v>
+        <v>1.426</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.09</v>
+        <v>0.052</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.78</v>
+        <v>24.7</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.003</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.085</v>
+        <v>0.06</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.012</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.186</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.253</v>
+        <v>-0.252</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.188</v>
+        <v>-0.177</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.196</v>
+        <v>0.171</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.448</v>
+        <v>-0.429</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.158</v>
+        <v>-0.161</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>103.3</v>
+        <v>100.09</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.031</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.044</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.013</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.107</v>
+        <v>0.066</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.161</v>
+        <v>0.123</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.312</v>
+        <v>0.257</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.629</v>
+        <v>0.555</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.602</v>
+        <v>0.562</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.515</v>
+        <v>1.413</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.076</v>
+        <v>0.042</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>191.17</v>
+        <v>188.91</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.017</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.031</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.06</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.063</v>
+        <v>0.04</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.238</v>
+        <v>0.262</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.302</v>
+        <v>1.224</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>6.902</v>
+        <v>6.81</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.054</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>56.45</v>
+        <v>52</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.039</v>
+        <v>-0.079</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>0.056</v>
+        <v>-0.054</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>0.06</v>
+        <v>-0.076</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.307</v>
+        <v>0.169</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.456</v>
+        <v>0.318</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.385</v>
+        <v>1.319</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>2.033</v>
+        <v>1.741</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.636</v>
+        <v>2.351</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>5.091</v>
+        <v>4.438</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.321</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>44.5</v>
+        <v>43.35</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.026</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.032</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.027</v>
+        <v>0.003</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.099</v>
+        <v>0.069</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.182</v>
+        <v>0.157</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.254</v>
+        <v>0.218</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.686</v>
+        <v>0.627</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.997</v>
+        <v>0.953</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.179</v>
+        <v>2.084</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.076</v>
+        <v>0.048</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.77</v>
+        <v>84.12</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.075</v>
+        <v>-0.015</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.213</v>
+        <v>-0.211</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.228</v>
+        <v>-0.216</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.151</v>
+        <v>-0.12</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.155</v>
+        <v>0.225</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.377</v>
+        <v>3.448</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.217</v>
+        <v>-0.204</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>87.19</v>
+        <v>90.2</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.064</v>
+        <v>0.035</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.078</v>
+        <v>0.117</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.157</v>
+        <v>0.164</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.242</v>
+        <v>0.277</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.136</v>
+        <v>0.205</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.159</v>
+        <v>0.23</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.277</v>
+        <v>0.291</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>1.176</v>
+        <v>1.193</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.172</v>
+        <v>0.219</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.261</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>61.5</v>
+        <v>58.42</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.05</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.067</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.037</v>
+        <v>-0.02</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.149</v>
+        <v>0.09</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.252</v>
+        <v>0.185</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.458</v>
+        <v>0.397</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.69</v>
+        <v>0.591</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.265</v>
+        <v>0.204</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.413</v>
+        <v>1.266</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.124</v>
+        <v>0.068</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>74.69</v>
+        <v>75.25</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>-0.038</v>
+        <v>0.002</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.107</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.094</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.008</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.603</v>
+        <v>0.6</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.321</v>
+        <v>0.371</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.407</v>
+        <v>2.404</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.064</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>37.34</v>
+        <v>38.61</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.073</v>
+        <v>0.034</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.102</v>
+        <v>0.139</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.194</v>
+        <v>0.202</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.295</v>
+        <v>0.331</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.201</v>
+        <v>0.271</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.238</v>
+        <v>0.311</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.333</v>
+        <v>0.356</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.374</v>
+        <v>1.397</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.236</v>
+        <v>2.346</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.319</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>33.42</v>
+        <v>32.72</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.021</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.033</v>
+        <v>0.005</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.162</v>
+        <v>0.137</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.098</v>
+        <v>0.075</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.05</v>
+        <v>334.78</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.049</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.075</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.031</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.164</v>
+        <v>0.084</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.455</v>
+        <v>0.39</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.7</v>
+        <v>0.676</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.615</v>
+        <v>1.449</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.639</v>
+        <v>1.589</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>12.407</v>
+        <v>11.735</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.169</v>
+        <v>0.112</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>12</v>
+        <v>12.28</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.042</v>
+        <v>0.023</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>0.022</v>
+        <v>0.072</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.054</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.206</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.06</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.41</v>
+        <v>-0.441</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.673</v>
+        <v>-0.689</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.718</v>
+        <v>-0.708</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.873</v>
+        <v>-0.867</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.88</v>
+        <v>47.46</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.038</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.003</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.102</v>
+        <v>0.062</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.156</v>
+        <v>0.118</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.256</v>
+        <v>0.21</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.537</v>
+        <v>0.476</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.536</v>
+        <v>0.509</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.6</v>
+        <v>1.476</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.075</v>
+        <v>0.044</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.79</v>
+        <v>123.03</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.014</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.01</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.032</v>
       </c>
       <c r="U47" s="1" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="V47" s="1" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="W47" s="1" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="X47" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="Y47" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z47" s="1" t="n">
+        <v>6.326</v>
+      </c>
+      <c r="AA47" s="1" t="n">
         <v>-0.047</v>
-      </c>
-      <c r="V47" s="1" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="W47" s="1" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="X47" s="1" t="n">
-        <v>1.432</v>
-      </c>
-      <c r="Y47" s="1" t="n">
-        <v>1.098</v>
-      </c>
-      <c r="Z47" s="1" t="n">
-        <v>6.431</v>
-      </c>
-      <c r="AA47" s="1" t="n">
-        <v>-0.034</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>44.16</v>
+        <v>42.65</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.036</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.049</v>
+        <v>0.002</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.151</v>
+        <v>0.109</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.252</v>
+        <v>0.212</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.578</v>
+        <v>0.512</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.921</v>
+        <v>0.864</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.844</v>
+        <v>1.7</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.119</v>
+        <v>0.081</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>50.6</v>
+        <v>48.13</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.049</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.058</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.059</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.049</v>
+        <v>-0.017</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.202</v>
+        <v>0.142</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.406</v>
+        <v>0.394</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.7</v>
+        <v>0.591</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.145</v>
+        <v>0.12</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.05</v>
+        <v>-0.001</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>25.99</v>
+        <v>26.02</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AI48" s="1" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AJ48" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="AK48" s="1" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="AL48" s="1" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AM48" s="1" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="AN48" s="1" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="AO48" s="1" t="n">
         <v>0.02</v>
-      </c>
-      <c r="AJ48" s="1" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="AK48" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AL48" s="1" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="AM48" s="1" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="AN48" s="1" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="AO48" s="1" t="n">
-        <v>0.018</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>51.9</v>
+        <v>50.01</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.036</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.046</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.115</v>
+        <v>0.071</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.167</v>
+        <v>0.126</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.359</v>
+        <v>0.301</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.798</v>
+        <v>0.712</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.634</v>
+        <v>0.604</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.867</v>
+        <v>1.678</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.082</v>
+        <v>0.043</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>35.32</v>
+        <v>33.49</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.052</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.05</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.022</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.038</v>
+        <v>-0.016</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.158</v>
+        <v>0.091</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.403</v>
+        <v>0.379</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.061</v>
+        <v>0.006</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.83</v>
+        <v>17.89</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.004</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.065</v>
+        <v>-0.042</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.291</v>
+        <v>-0.295</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.037</v>
+        <v>0.054</v>
       </c>
       <c r="AN49" s="1" t="n">
         <v>-0.132</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>0.006</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>40.2</v>
+        <v>39.72</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.03</v>
+        <v>0.008</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.112</v>
+        <v>0.072</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.248</v>
+        <v>0.231</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.296</v>
+        <v>0.281</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.448</v>
+        <v>0.44</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.892</v>
+        <v>0.85</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.459</v>
+        <v>0.44</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.697</v>
+        <v>0.68</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.186</v>
+        <v>0.172</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.99</v>
+        <v>21.85</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.006</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.069</v>
+        <v>0.057</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.042</v>
+        <v>0.048</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.082</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.389</v>
+        <v>-0.392</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.308</v>
+        <v>-0.304</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.489</v>
+        <v>-0.501</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.101</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>53.05</v>
+        <v>52.68</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.039</v>
+        <v>0.011</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.034</v>
       </c>
       <c r="U51" s="1" t="n">
         <v>-0.13</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.162</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.548</v>
+        <v>0.524</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.405</v>
+        <v>1.351</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.109</v>
+        <v>-0.116</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.69</v>
+        <v>23.94</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.009</v>
+        <v>0.016</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.071</v>
+        <v>0.076</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.011</v>
+        <v>0.028</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.069</v>
+        <v>0.088</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.15</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.12</v>
+        <v>0.138</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.384</v>
+        <v>0.393</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.084</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>39.19</v>
+        <v>38.7</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.054</v>
+        <v>-0.013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.072</v>
+        <v>0.059</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.114</v>
+        <v>-0.106</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.241</v>
+        <v>-0.266</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.378</v>
+        <v>-0.393</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.209</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.211</v>
+        <v>-0.221</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>48.83</v>
+        <v>47.36</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.036</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.116</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.141</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.172</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.409</v>
+        <v>0.336</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.321</v>
+        <v>-0.322</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.833</v>
+        <v>1.754</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.116</v>
+        <v>-0.142</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>15.37</v>
+        <v>14.93</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.059</v>
+        <v>-0.029</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.094</v>
+        <v>0.064</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.122</v>
+        <v>-0.139</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.317</v>
+        <v>-0.371</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.524</v>
+        <v>-0.559</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.072</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.315</v>
+        <v>-0.334</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.71</v>
+        <v>90.87</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>0</v>
+        <v>-0.017</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.073</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.147</v>
+        <v>-0.16</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.175</v>
+        <v>-0.194</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.99</v>
+        <v>0.915</v>
       </c>
       <c r="Y53" s="1" t="n">
         <v>0.354</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.105</v>
+        <v>-0.123</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.28</v>
+        <v>9.29</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="AH53" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.016</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.032</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.142</v>
+        <v>-0.137</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.207</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.115</v>
+        <v>-0.133</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.236</v>
+        <v>0.259</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.063</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>60.17</v>
+        <v>59.09</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.018</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.026</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.08</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.088</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.117</v>
+        <v>-0.127</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.085</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.376</v>
+        <v>0.328</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.113</v>
+        <v>0.095</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.286</v>
+        <v>1.227</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.119</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.96</v>
+        <v>119.25</v>
       </c>
       <c r="R54" s="1" t="n">
         <v>-0.006</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.107</v>
+        <v>0.085</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.087</v>
+        <v>0.084</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.131</v>
+        <v>0.127</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.208</v>
+        <v>0.198</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.608</v>
+        <v>0.574</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.842</v>
+        <v>0.849</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.721</v>
+        <v>1.689</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.73</v>
+        <v>39.32</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.01</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.114</v>
+        <v>0.1</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.179</v>
+        <v>0.18</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.369</v>
+        <v>0.348</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.365</v>
+        <v>0.344</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.33</v>
+        <v>0.321</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.045</v>
+        <v>0.034</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.37</v>
+        <v>47.07</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.003</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.111</v>
+        <v>0.089</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.086</v>
+        <v>0.083</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.23</v>
+        <v>0.221</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.595</v>
+        <v>0.558</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.855</v>
+        <v>0.865</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.814</v>
+        <v>1.779</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>29.26</v>
+        <v>30.48</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.07</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.03</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.217</v>
+        <v>-0.164</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.362</v>
+        <v>-0.382</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.837</v>
+        <v>-0.825</v>
       </c>
       <c r="K56" s="1" t="n">
         <v>-0.969</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.105</v>
+        <v>0.151</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.78</v>
+        <v>72.03</v>
       </c>
       <c r="R56" s="1" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="S56" s="1" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="U56" s="1" t="n">
         <v>-0.004</v>
       </c>
-      <c r="S56" s="1" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="T56" s="1" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="U56" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="V56" s="1" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.089</v>
+        <v>0.088</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.39</v>
+        <v>0.362</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.535</v>
+        <v>0.541</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.598</v>
+        <v>2.582</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.034</v>
+        <v>0.023</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>101.54</v>
+        <v>100.96</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.073</v>
+        <v>0.064</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.074</v>
+        <v>0.068</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.057</v>
+        <v>0.046</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.265</v>
+        <v>0.238</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.331</v>
+        <v>0.335</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.865</v>
+        <v>0.845</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.081</v>
+        <v>0.075</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>90.11</v>
+        <v>89.41</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.009</v>
+        <v>0.001</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.084</v>
+        <v>0.07</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.099</v>
+        <v>0.087</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.06</v>
+        <v>0.038</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.345</v>
+        <v>0.312</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.448</v>
+        <v>0.438</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>0.984</v>
+        <v>0.966</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.09</v>
+        <v>0.082</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.93</v>
+        <v>95.42</v>
       </c>
       <c r="R59" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="S59" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="S59" s="1" t="n">
-        <v>0.011</v>
-      </c>
       <c r="T59" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="U59" s="1" t="n">
         <v>0.068</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>0.076</v>
-      </c>
       <c r="V59" s="1" t="n">
-        <v>0.077</v>
+        <v>0.071</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.062</v>
+        <v>0.051</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.264</v>
+        <v>0.238</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.796</v>
+        <v>0.777</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.084</v>
+        <v>0.078</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.76</v>
+        <v>22.55</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.009</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.034</v>
+        <v>0.017</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.064</v>
+        <v>0.039</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.048</v>
+        <v>0.062</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.272</v>
+        <v>0.24</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.539</v>
+        <v>0.496</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>98.48</v>
+        <v>96.92</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.001</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.129</v>
+        <v>0.112</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.135</v>
+        <v>0.11</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.211</v>
+        <v>0.197</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.498</v>
+        <v>0.459</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.549</v>
+        <v>0.544</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.957</v>
+        <v>1.933</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.159</v>
+        <v>0.14</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">03/03/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">03/04/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>333.33</v>
+        <v>335.85</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.008</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.012</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.013</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.023</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.183</v>
+        <v>0.206</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.901</v>
+        <v>0.915</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.041</v>
+        <v>1.077</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.384</v>
+        <v>3.405</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.021</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.7</v>
+        <v>59.37</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.093</v>
+        <v>0.063</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.232</v>
+        <v>0.22</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.286</v>
+        <v>0.271</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.404</v>
+        <v>0.397</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.629</v>
+        <v>1.551</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.494</v>
+        <v>1.456</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.256</v>
+        <v>0.249</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,37 +1744,37 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.8</v>
+        <v>82.75</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>0.043</v>
+        <v>0.039</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.091</v>
+        <v>0.087</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.183</v>
+        <v>0.18</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>683.37</v>
+        <v>688.28</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.007</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.011</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.18</v>
+        <v>0.203</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.755</v>
+        <v>0.768</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.917</v>
+        <v>0.955</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.021</v>
+        <v>3.036</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>111.99</v>
+        <v>112.42</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.054</v>
+        <v>0.066</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.135</v>
+        <v>0.104</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.238</v>
+        <v>0.231</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.295</v>
+        <v>0.31</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.312</v>
+        <v>0.317</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.644</v>
+        <v>1.566</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>1.899</v>
+        <v>1.835</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.82</v>
+        <v>119.6</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.154</v>
+        <v>0.148</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.164</v>
+        <v>0.16</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1907,31 +1907,31 @@
         <v>70.86</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-0.017</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.013</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.076</v>
+        <v>0.071</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.102</v>
+        <v>0.087</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.188</v>
+        <v>0.207</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>0.399</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.521</v>
+        <v>0.555</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>1.965</v>
+        <v>1.946</v>
       </c>
       <c r="M7" s="1" t="n">
         <v>0.074</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>28.12</v>
+        <v>27.91</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.007</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.039</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.075</v>
+        <v>0.049</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.294</v>
+        <v>0.276</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.525</v>
+        <v>0.47</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.509</v>
+        <v>0.527</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.277</v>
+        <v>0.267</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.076</v>
+        <v>1.038</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.085</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.347</v>
+        <v>0.337</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>97.01</v>
+        <v>96.81</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.003</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AI7" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>-0.037</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AO7" s="1" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AJ7" s="1" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AK7" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AL7" s="1" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="AM7" s="1" t="n">
-        <v>-0.036</v>
-      </c>
-      <c r="AN7" s="1" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AO7" s="1" t="n">
-        <v>0.015</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>259.24</v>
+        <v>261.76</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.011</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.005</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.256</v>
+        <v>0.282</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.406</v>
+        <v>0.419</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.257</v>
+        <v>0.306</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.755</v>
+        <v>1.766</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.72</v>
+        <v>18.09</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.033</v>
+        <v>0.021</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.052</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.035</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.258</v>
+        <v>0.272</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.65</v>
+        <v>0.655</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.039</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.218</v>
+        <v>-0.168</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.394</v>
+        <v>1.419</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.079</v>
+        <v>0.101</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.59</v>
+        <v>103.33</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.051</v>
+        <v>0.038</v>
       </c>
       <c r="AK8" s="1" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.076</v>
+        <v>0.07</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.15</v>
+        <v>-0.149</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.03</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2196,28 +2196,28 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.43</v>
+        <v>89.15</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="AH9" s="1" t="n">
         <v>0.034</v>
       </c>
       <c r="AI9" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AK9" s="1" t="n">
         <v>0.015</v>
       </c>
-      <c r="AJ9" s="1" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AK9" s="1" t="n">
-        <v>0.01</v>
-      </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.017</v>
       </c>
       <c r="AM9" s="1" t="n">
         <v>-0.247</v>
@@ -2226,7 +2226,7 @@
         <v>-0.092</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.37</v>
+        <v>183.25</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.001</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.022</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.039</v>
+        <v>0.029</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.254</v>
+        <v>0.249</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.376</v>
+        <v>0.394</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.684</v>
+        <v>0.72</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.126</v>
+        <v>2.083</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.5</v>
+        <v>111.25</v>
       </c>
       <c r="AF10" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AG10" s="1" t="n">
         <v>-0.001</v>
       </c>
-      <c r="AG10" s="1" t="n">
-        <v>0.002</v>
-      </c>
       <c r="AH10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>222.27</v>
+        <v>223.25</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.004</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.008</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.176</v>
+        <v>0.204</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.503</v>
+        <v>0.51</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.678</v>
+        <v>0.705</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.871</v>
+        <v>1.869</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.057</v>
+        <v>0.061</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.54</v>
+        <v>61.23</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.059</v>
+        <v>0.011</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.05</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.254</v>
+        <v>0.267</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.488</v>
+        <v>0.508</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.755</v>
+        <v>0.78</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.487</v>
+        <v>0.504</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.75</v>
+        <v>0.848</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>3.895</v>
+        <v>3.754</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.179</v>
+        <v>0.193</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,37 +2410,37 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.26</v>
+        <v>103.15</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AH11" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ11" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.163</v>
+        <v>0.162</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>448.66</v>
+        <v>453.06</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.01</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.012</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.002</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.05</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.949</v>
+        <v>0.968</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.962</v>
+        <v>1.016</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.079</v>
+        <v>4.118</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.043</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>90.42</v>
+        <v>91.08</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>-0.087</v>
+        <v>0.007</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.045</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.071</v>
+        <v>0.08</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.316</v>
+        <v>0.314</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.628</v>
+        <v>0.658</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.775</v>
+        <v>1.765</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.26</v>
+        <v>3.291</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.776</v>
+        <v>2.764</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.104</v>
+        <v>5.222</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.228</v>
+        <v>0.237</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>107.76</v>
+        <v>107.75</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="AH12" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.05</v>
+        <v>0.044</v>
       </c>
       <c r="AK12" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.24</v>
+        <v>0.239</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>202.29</v>
+        <v>203.44</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.006</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.005</v>
+        <v>0.009</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.141</v>
+        <v>0.159</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.724</v>
+        <v>0.733</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.846</v>
+        <v>0.883</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.697</v>
+        <v>2.709</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.26</v>
+        <v>42.76</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>-0.094</v>
+        <v>0.012</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.055</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.036</v>
+        <v>0.051</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.364</v>
+        <v>0.394</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.847</v>
+        <v>0.908</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.333</v>
+        <v>2.339</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.324</v>
+        <v>3.376</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.958</v>
+        <v>2.068</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.484</v>
+        <v>5.458</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.233</v>
+        <v>0.248</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.04</v>
+        <v>23.15</v>
       </c>
       <c r="AF13" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AG13" s="1" t="n">
         <v>-0.008</v>
       </c>
-      <c r="AG13" s="1" t="n">
-        <v>-0.009</v>
-      </c>
       <c r="AH13" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.089</v>
+        <v>0.102</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.276</v>
+        <v>0.273</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>97.21</v>
+        <v>97.36</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>0.042</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.745</v>
+        <v>1.744</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>52.8</v>
+        <v>53.48</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>-0.067</v>
       </c>
-      <c r="S14" s="1" t="n">
-        <v>-0.058</v>
-      </c>
       <c r="T14" s="1" t="n">
-        <v>-0.038</v>
+        <v>0.015</v>
       </c>
       <c r="U14" s="1" t="n">
-        <v>0.283</v>
+        <v>0.297</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.623</v>
+        <v>0.661</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.148</v>
+        <v>1.18</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.192</v>
+        <v>0.207</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>75.27</v>
+        <v>75.56</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.012</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.009</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.144</v>
+        <v>0.148</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.041</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>247.01</v>
+        <v>250.71</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.015</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.022</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>-0.037</v>
+        <v>0.015</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.164</v>
+        <v>0.206</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.797</v>
+        <v>0.823</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.651</v>
+        <v>0.723</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>2.922</v>
+        <v>2.986</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.002</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.42</v>
+        <v>16.57</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.088</v>
+        <v>0.009</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.118</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>-0.042</v>
+        <v>0.005</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.129</v>
+        <v>0.157</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.932</v>
+        <v>0.966</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>96.55</v>
+        <v>96.87</v>
       </c>
       <c r="AF15" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AG15" s="1" t="n">
         <v>-0.005</v>
       </c>
-      <c r="AG15" s="1" t="n">
-        <v>-0.007</v>
-      </c>
       <c r="AH15" s="1" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.056</v>
+        <v>0.05</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.111</v>
+        <v>0.112</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.124</v>
+        <v>0.133</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.442</v>
+        <v>0.437</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>138.39</v>
+        <v>137.92</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.153</v>
+        <v>0.147</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.187</v>
+        <v>0.198</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.504</v>
+        <v>0.499</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.821</v>
+        <v>0.815</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.617</v>
+        <v>1.601</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.138</v>
+        <v>0.134</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.83</v>
+        <v>75.3</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.023</v>
+        <v>0.006</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.041</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.058</v>
+        <v>0.064</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.007</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.066</v>
+        <v>1.055</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>41.77</v>
+        <v>42.01</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.006</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.011</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.151</v>
+        <v>0.152</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.234</v>
+        <v>0.242</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.04</v>
+        <v>0.054</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.246</v>
+        <v>0.241</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>147.94</v>
+        <v>149</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.007</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.011</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>-0.012</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.172</v>
+        <v>0.195</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.716</v>
+        <v>0.728</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.801</v>
+        <v>0.841</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>105.31</v>
+        <v>105.96</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.025</v>
+        <v>0.006</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.03</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.029</v>
+        <v>0.036</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.111</v>
+        <v>0.11</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.163</v>
+        <v>0.147</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.501</v>
+        <v>0.534</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.305</v>
+        <v>1.32</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.334</v>
+        <v>1.406</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>3.712</v>
+        <v>3.692</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.137</v>
+        <v>0.144</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.13</v>
+        <v>42.22</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.002</v>
       </c>
       <c r="AG17" s="1" t="n">
         <v>-0.014</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.001</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.012</v>
+        <v>0.017</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.015</v>
+        <v>0.017</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.191</v>
+        <v>-0.182</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.064</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>159.26</v>
+        <v>159.78</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.003</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.11</v>
+        <v>0.102</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.187</v>
+        <v>0.221</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.597</v>
+        <v>0.602</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.654</v>
+        <v>0.697</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.479</v>
+        <v>2.473</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.075</v>
+        <v>0.078</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.53</v>
+        <v>35.8</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.008</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.027</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.013</v>
+        <v>0.028</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.154</v>
+        <v>0.15</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.272</v>
+        <v>0.264</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.498</v>
+        <v>0.543</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.139</v>
+        <v>0.147</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.07</v>
+        <v>57.47</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>-0.019</v>
+        <v>0.007</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.097</v>
+        <v>0.093</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.433</v>
+        <v>0.468</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.742</v>
+        <v>0.754</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.917</v>
+        <v>0.951</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.145</v>
+        <v>2.135</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.058</v>
+        <v>0.066</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,34 +3326,34 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.61</v>
+        <v>81.6</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.023</v>
+        <v>0.008</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.086</v>
+        <v>0.085</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.2</v>
+        <v>0.221</v>
       </c>
       <c r="X20" s="1" t="n">
         <v>0.427</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.447</v>
+        <v>0.484</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.683</v>
+        <v>1.665</v>
       </c>
       <c r="AA20" s="1" t="n">
         <v>0.095</v>
@@ -3365,10 +3365,10 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.57</v>
+        <v>100.53</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="1" t="n">
         <v>-0.002</v>
@@ -3377,25 +3377,25 @@
         <v>0.012</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.033</v>
+        <v>0.026</v>
       </c>
       <c r="AK20" s="1" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AM20" s="1" t="n">
         <v>0.02</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.21</v>
+        <v>0.207</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>34.52</v>
+        <v>35.18</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.048</v>
+        <v>0.019</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.057</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.01</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.31</v>
+        <v>0.326</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.622</v>
+        <v>0.658</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.672</v>
+        <v>0.704</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.824</v>
+        <v>0.875</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.405</v>
+        <v>1.364</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.134</v>
+        <v>0.155</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>244.98</v>
+        <v>246.97</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.008</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.008</v>
+        <v>0.024</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.045</v>
+        <v>0.083</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.215</v>
+        <v>0.207</v>
       </c>
       <c r="V21" s="1" t="n">
         <v>0.249</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.611</v>
+        <v>0.664</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.134</v>
+        <v>1.151</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.591</v>
+        <v>1.662</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.771</v>
+        <v>3.779</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.141</v>
+        <v>0.15</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3487,7 +3487,7 @@
         <v>50.6</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="1" t="n">
         <v>-0.002</v>
@@ -3496,22 +3496,22 @@
         <v>0.009</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="AL21" s="1" t="n">
         <v>0.177</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.271</v>
+        <v>0.274</v>
       </c>
       <c r="AO21" s="1" t="n">
         <v>0.014</v>
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>75.37</v>
+        <v>77.91</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.051</v>
+        <v>0.034</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.032</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>-0.043</v>
+        <v>0.009</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.123</v>
+        <v>0.154</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.223</v>
+        <v>0.259</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.569</v>
+        <v>0.616</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.379</v>
+        <v>0.426</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.092</v>
+        <v>1.183</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>0.938</v>
+        <v>0.982</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.087</v>
+        <v>0.124</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>101.64</v>
+        <v>102.69</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.009</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.003</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.017</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.078</v>
+        <v>0.107</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.624</v>
+        <v>0.641</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.45</v>
+        <v>0.489</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.098</v>
+        <v>2.132</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.004</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.3</v>
+        <v>49.54</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.005</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="AI22" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AJ22" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="AK22" s="1" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AL22" s="1" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="AM22" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AN22" s="1" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AO22" s="1" t="n">
         <v>0.012</v>
-      </c>
-      <c r="AJ22" s="1" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="AK22" s="1" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AL22" s="1" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AM22" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="AN22" s="1" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="AO22" s="1" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>36.82</v>
+        <v>37.49</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>-0.047</v>
+        <v>0.018</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.053</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.014</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.114</v>
+        <v>0.118</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.608</v>
+        <v>0.653</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.634</v>
+        <v>0.663</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.699</v>
+        <v>0.723</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>1.59</v>
+        <v>1.505</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.159</v>
+        <v>0.18</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>103.69</v>
+        <v>103.17</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.005</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.031</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.051</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.062</v>
+        <v>-0.094</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.086</v>
+        <v>0.087</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.555</v>
+        <v>0.547</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.81</v>
+        <v>0.831</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.309</v>
+        <v>3.304</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.077</v>
+        <v>0.071</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,10 +3722,10 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>95.98</v>
+        <v>95.95</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="1" t="n">
         <v>-0.003</v>
@@ -3734,25 +3734,25 @@
         <v>0.011</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.168</v>
+        <v>0.163</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.157</v>
+        <v>0.154</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>64.53</v>
+        <v>65.33</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.012</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.056</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.023</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.028</v>
+        <v>0.041</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.101</v>
+        <v>0.109</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.243</v>
+        <v>0.256</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.574</v>
+        <v>0.593</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.633</v>
+        <v>0.669</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.546</v>
+        <v>1.569</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>37.69</v>
+        <v>37.85</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>-0.059</v>
+        <v>0.004</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.078</v>
+        <v>-0.083</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.095</v>
+        <v>0.105</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.295</v>
+        <v>0.309</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.047</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>110.87</v>
+        <v>110.97</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>0.033</v>
+        <v>0.023</v>
       </c>
       <c r="AK24" s="1" t="n">
         <v>0.059</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>0.021</v>
+        <v>0.026</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.367</v>
+        <v>0.363</v>
       </c>
       <c r="AO24" s="1" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>44.83</v>
+        <v>45.29</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.01</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.042</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.006</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.038</v>
+        <v>0.048</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.119</v>
+        <v>0.123</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.146</v>
+        <v>0.169</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.535</v>
+        <v>0.551</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.88</v>
+        <v>0.907</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>1.964</v>
+        <v>1.993</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>85.65</v>
+        <v>85.94</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.009</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.038</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.009</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.2</v>
+        <v>0.224</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.133</v>
+        <v>0.159</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.234</v>
+        <v>1.23</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,37 +3958,37 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.45</v>
+        <v>92.57</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.242</v>
+        <v>0.244</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.271</v>
+        <v>0.28</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>46.76</v>
+        <v>47.24</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.01</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.097</v>
+        <v>0.109</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.3</v>
+        <v>0.309</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.613</v>
+        <v>0.63</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.832</v>
+        <v>0.864</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.234</v>
+        <v>1.242</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.063</v>
+        <v>0.074</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.37</v>
+        <v>60.58</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.003</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.135</v>
+        <v>0.157</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.473</v>
+        <v>0.478</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.23</v>
+        <v>0.255</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.791</v>
+        <v>0.8</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.46</v>
+        <v>26.59</v>
       </c>
       <c r="AF26" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="AJ26" s="1" t="n">
         <v>0.019</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>0.055</v>
+        <v>0.059</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.131</v>
+        <v>0.147</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>45.07</v>
+        <v>45.23</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.004</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.058</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.017</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.148</v>
+        <v>0.14</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.317</v>
+        <v>0.321</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.533</v>
+        <v>0.551</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.508</v>
+        <v>1.503</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4155,31 +4155,31 @@
         <v>159</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.51</v>
+        <v>26.42</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.024</v>
       </c>
       <c r="T27" s="1" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="W27" s="1" t="n">
         <v>0.037</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="V27" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>0.036</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="AC27" s="6" t="s">
         <v>270</v>
@@ -4188,37 +4188,37 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>52.91</v>
+        <v>52.87</v>
       </c>
       <c r="AF27" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.199</v>
+        <v>0.194</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.135</v>
+        <v>0.131</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.325</v>
+        <v>0.319</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>41.57</v>
+        <v>42.1</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.013</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.051</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.027</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.015</v>
+        <v>0.023</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.137</v>
+        <v>0.156</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.592</v>
+        <v>0.612</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.449</v>
+        <v>0.482</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.167</v>
+        <v>1.185</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.009</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>75.46</v>
+        <v>74.82</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.008</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.022</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.035</v>
+        <v>0.019</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.127</v>
+        <v>0.123</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.096</v>
+        <v>0.088</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.085</v>
+        <v>0.093</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.258</v>
+        <v>0.247</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.513</v>
+        <v>0.526</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.592</v>
+        <v>1.556</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4310,34 +4310,34 @@
         <v>54.07</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="AH28" s="1" t="n">
         <v>0.01</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.239</v>
+        <v>0.234</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.087</v>
+        <v>0.09</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.399</v>
+        <v>0.394</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>62.21</v>
+        <v>62.56</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.006</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.035</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.071</v>
+        <v>0.08</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.212</v>
+        <v>0.209</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.498</v>
+        <v>0.506</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.579</v>
+        <v>0.606</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.609</v>
+        <v>1.636</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.65</v>
+        <v>45.55</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.002</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.011</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.052</v>
+        <v>0.03</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.159</v>
+        <v>0.155</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.292</v>
+        <v>0.301</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.297</v>
+        <v>0.325</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.539</v>
+        <v>1.5</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.184</v>
+        <v>0.181</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>50.91</v>
+        <v>50.94</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="AH29" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AI29" s="1" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AJ29" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AK29" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AL29" s="1" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AM29" s="1" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AN29" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO29" s="1" t="n">
         <v>0.014</v>
-      </c>
-      <c r="AI29" s="1" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="AJ29" s="1" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AK29" s="1" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AL29" s="1" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AM29" s="1" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="AN29" s="1" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AO29" s="1" t="n">
-        <v>0.018</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>99.69</v>
+        <v>100.16</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>-0.047</v>
+        <v>0.005</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.071</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.006</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.087</v>
+        <v>0.096</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.176</v>
+        <v>0.186</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.399</v>
+        <v>0.388</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.578</v>
+        <v>0.586</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.169</v>
+        <v>0.202</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.442</v>
+        <v>1.409</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>49.52</v>
+        <v>49.32</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.004</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.019</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.001</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.052</v>
+        <v>0.046</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.082</v>
+        <v>0.094</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.137</v>
+        <v>0.132</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.771</v>
+        <v>0.767</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.18</v>
+        <v>24.28</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.014</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.062</v>
+        <v>0.067</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.251</v>
+        <v>0.256</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.266</v>
+        <v>0.279</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.705</v>
+        <v>0.689</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>19.5</v>
+        <v>19.49</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.056</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.158</v>
+        <v>0.16</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>0.305</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.585</v>
+        <v>0.591</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.053</v>
+        <v>1.01</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.36</v>
+        <v>65.51</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.002</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.007</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.14</v>
+        <v>0.138</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.058</v>
+        <v>0.07</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.42</v>
+        <v>0.448</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.659</v>
+        <v>1.67</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.12</v>
+        <v>80.4</v>
       </c>
       <c r="AF31" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AG31" s="1" t="n">
         <v>-0.002</v>
       </c>
-      <c r="AG31" s="1" t="n">
-        <v>-0.004</v>
-      </c>
       <c r="AH31" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AI31" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AJ31" s="1" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="AK31" s="1" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="AL31" s="1" t="n">
-        <v>0.279</v>
+        <v>0.277</v>
       </c>
       <c r="AM31" s="1" t="n">
-        <v>0.212</v>
+        <v>0.215</v>
       </c>
       <c r="AN31" s="1" t="n">
-        <v>0.684</v>
+        <v>0.677</v>
       </c>
       <c r="AO31" s="1" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>36.68</v>
+        <v>37.46</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.012</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.055</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.051</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.073</v>
+        <v>0.096</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.245</v>
+        <v>0.276</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.125</v>
+        <v>1.17</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.007</v>
+        <v>0.029</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>45.49</v>
+        <v>45.87</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.008</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.002</v>
+        <v>0.025</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.052</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.025</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.081</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.081</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.016</v>
+        <v>0.032</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.114</v>
+        <v>1.145</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.043</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.32</v>
+        <v>29.41</v>
       </c>
       <c r="AF32" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AG32" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.005</v>
       </c>
       <c r="AH32" s="1" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AI32" s="1" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.199</v>
+        <v>0.202</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.027</v>
+        <v>1.006</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>50.22</v>
+        <v>50.27</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>-0.014</v>
+        <v>0.001</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>-0.047</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.059</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.065</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.044</v>
       </c>
       <c r="I33" s="1" t="n">
         <v>0.051</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.264</v>
+        <v>0.265</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.261</v>
+        <v>0.275</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.177</v>
+        <v>1.149</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.07</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>89.7</v>
+        <v>89.84</v>
       </c>
       <c r="R33" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="S33" s="1" t="n">
         <v>-0.018</v>
       </c>
-      <c r="S33" s="1" t="n">
-        <v>-0.021</v>
-      </c>
       <c r="T33" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.002</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.078</v>
+        <v>0.089</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.273</v>
+        <v>0.275</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.256</v>
+        <v>0.272</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.582</v>
+        <v>0.585</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.667</v>
+        <v>0.712</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.235</v>
+        <v>1.254</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>47.99</v>
+        <v>47.98</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="1" t="n">
         <v>-0.003</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.009</v>
+        <v>0.006</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.173</v>
+        <v>0.169</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>86.83</v>
+        <v>88.59</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>-0.037</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.042</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.09</v>
+        <v>0.099</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.156</v>
+        <v>0.167</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.312</v>
+        <v>0.35</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.653</v>
+        <v>0.687</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.435</v>
+        <v>0.479</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.329</v>
+        <v>1.352</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.075</v>
+        <v>0.097</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>170.1</v>
+        <v>172.97</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.017</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.013</v>
       </c>
       <c r="T34" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.006</v>
       </c>
       <c r="U34" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.006</v>
       </c>
       <c r="V34" s="1" t="n">
-        <v>0.214</v>
+        <v>0.234</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.27</v>
+        <v>0.291</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.314</v>
+        <v>0.336</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.143</v>
+        <v>0.191</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>0.982</v>
+        <v>1.024</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>103.31</v>
+        <v>104.42</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.011</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.011</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.017</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.106</v>
+        <v>0.115</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.232</v>
+        <v>0.247</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.488</v>
+        <v>0.503</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.181</v>
+        <v>0.231</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.33</v>
+        <v>2.373</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>56.9</v>
+        <v>57.13</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.004</v>
       </c>
       <c r="E35" s="1" t="n">
         <v>-0.058</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.053</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.069</v>
+        <v>-0.067</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.061</v>
+        <v>-0.041</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.101</v>
+        <v>0.09</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.219</v>
+        <v>0.224</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.275</v>
+        <v>-0.249</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.695</v>
+        <v>0.657</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.049</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>59</v>
+        <v>58.81</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.003</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.014</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.015</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.066</v>
+        <v>-0.07</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.049</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.074</v>
+        <v>-0.065</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.107</v>
+        <v>0.132</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.117</v>
+        <v>2.093</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.054</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.51</v>
+        <v>23.31</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.009</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.023</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.432</v>
+        <v>0.401</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.276</v>
+        <v>0.265</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.069</v>
+        <v>0.065</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.768</v>
+        <v>0.725</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.106</v>
+        <v>0.097</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>29.83</v>
+        <v>30.47</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>-0.035</v>
+        <v>0.021</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.011</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.033</v>
+        <v>0.055</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.12</v>
+        <v>0.135</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.326</v>
+        <v>0.358</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.379</v>
+        <v>0.402</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.262</v>
+        <v>0.289</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.299</v>
+        <v>-0.264</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.139</v>
+        <v>0.163</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>71.29</v>
+        <v>71.62</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.005</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.071</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.036</v>
+        <v>0.051</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.15</v>
+        <v>0.161</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.27</v>
+        <v>0.263</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.484</v>
+        <v>0.468</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.932</v>
+        <v>0.941</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.788</v>
+        <v>0.836</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.468</v>
+        <v>3.412</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.122</v>
+        <v>0.127</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>122.04</v>
+        <v>122.77</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.006</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.046</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.019</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.057</v>
+        <v>0.101</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.606</v>
+        <v>0.615</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.808</v>
+        <v>0.842</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.481</v>
+        <v>2.489</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.048</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>95.92</v>
+        <v>96.65</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>-0.044</v>
+        <v>0.008</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.031</v>
+        <v>0.04</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.211</v>
+        <v>0.219</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.427</v>
+        <v>0.444</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.726</v>
+        <v>1.747</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.935</v>
+        <v>1.989</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.941</v>
+        <v>2.971</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.182</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>132.34</v>
+        <v>134.37</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>-0.103</v>
+        <v>0.015</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.098</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.065</v>
+        <v>0.117</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.455</v>
+        <v>0.495</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.856</v>
+        <v>0.88</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.491</v>
+        <v>1.518</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.346</v>
+        <v>1.382</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.648</v>
+        <v>0.704</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.266</v>
+        <v>2.263</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.361</v>
+        <v>0.382</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>61.51</v>
+        <v>61.83</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.031</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.067</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.027</v>
+        <v>0.016</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.115</v>
+        <v>0.164</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.399</v>
+        <v>0.406</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.365</v>
+        <v>0.391</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.567</v>
+        <v>1.549</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>74.68</v>
+        <v>75.34</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>-0.084</v>
+        <v>0.009</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.059</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.048</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.407</v>
+        <v>0.456</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" s="1" t="n">
         <v>1.598</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.82</v>
+        <v>2.854</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.076</v>
+        <v>2.198</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.15</v>
+        <v>4.104</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.159</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>27.6</v>
+        <v>27.97</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>-0.074</v>
+        <v>0.013</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.084</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.011</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.241</v>
+        <v>0.266</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.705</v>
+        <v>0.718</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.73</v>
+        <v>0.753</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.447</v>
+        <v>0.501</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>1.023</v>
+        <v>0.986</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.032</v>
+        <v>0.046</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.003</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.034</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.067</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.046</v>
+        <v>0.033</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.129</v>
+        <v>0.173</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.22</v>
+        <v>0.223</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.159</v>
+        <v>0.178</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.273</v>
+        <v>1.253</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>190.89</v>
+        <v>195.25</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>-0.09</v>
+        <v>0.023</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.058</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.031</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.259</v>
+        <v>0.3</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.473</v>
+        <v>0.558</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.19</v>
+        <v>1.225</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.113</v>
+        <v>1.161</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.735</v>
+        <v>0.849</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.086</v>
+        <v>1.066</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.024</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>73.56</v>
+        <v>74.34</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>-0.079</v>
+        <v>0.011</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.074</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.005</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.159</v>
+        <v>0.169</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.345</v>
+        <v>0.386</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.049</v>
+        <v>1.07</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.903</v>
+        <v>0.955</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.471</v>
+        <v>1.45</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.069</v>
+        <v>0.081</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>136.46</v>
+        <v>136.12</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.002</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="U40" s="1" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.035</v>
+        <v>0.021</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.013</v>
+        <v>0.034</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.531</v>
+        <v>0.527</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.049</v>
+        <v>1.078</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.404</v>
+        <v>2.388</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.6</v>
+        <v>35.97</v>
       </c>
       <c r="AF40" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG40" s="1" t="n">
         <v>-0.022</v>
       </c>
-      <c r="AG40" s="1" t="n">
-        <v>-0.019</v>
-      </c>
       <c r="AH40" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.009</v>
       </c>
       <c r="AI40" s="1" t="n">
-        <v>0.078</v>
+        <v>0.095</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.255</v>
+        <v>0.281</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.246</v>
+        <v>0.263</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.433</v>
+        <v>0.447</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.398</v>
+        <v>0.475</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.425</v>
+        <v>1.4</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.09</v>
+        <v>29.35</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.009</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.027</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.254</v>
+        <v>0.267</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.378</v>
+        <v>0.391</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.42</v>
+        <v>0.442</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.347</v>
+        <v>1.327</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.111</v>
+        <v>0.121</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>171.17</v>
+        <v>173.29</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.012</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0.009</v>
+        <v>0</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.026</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.025</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.153</v>
+        <v>0.209</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.746</v>
+        <v>0.768</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1</v>
+        <v>1.048</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.44</v>
+        <v>4.469</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.034</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>70.63</v>
+        <v>71.42</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>-0.035</v>
+        <v>0.011</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.046</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.003</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.077</v>
+        <v>0.086</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.59</v>
+        <v>0.608</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.476</v>
+        <v>0.515</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.426</v>
+        <v>1.429</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.052</v>
+        <v>0.064</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.024</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.06</v>
+        <v>0.044</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.027</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.186</v>
+        <v>-0.171</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.252</v>
+        <v>-0.239</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.177</v>
+        <v>-0.137</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.171</v>
+        <v>0.2</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.429</v>
+        <v>-0.391</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.14</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>100.09</v>
+        <v>101.38</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.013</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.041</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.066</v>
+        <v>0.077</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.257</v>
+        <v>0.273</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.555</v>
+        <v>0.575</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.562</v>
+        <v>0.597</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.413</v>
+        <v>1.426</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.042</v>
+        <v>0.056</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>188.91</v>
+        <v>191.44</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.013</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.023</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.006</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.051</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.04</v>
+        <v>0.047</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.262</v>
+        <v>0.278</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.224</v>
+        <v>1.254</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.25</v>
+        <v>1.326</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>6.81</v>
+        <v>6.887</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.041</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>52</v>
+        <v>52.77</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>-0.079</v>
+        <v>0.015</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.044</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>-0.076</v>
+        <v>0.007</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.169</v>
+        <v>0.124</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.318</v>
+        <v>0.369</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.319</v>
+        <v>1.299</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.741</v>
+        <v>1.782</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.351</v>
+        <v>2.635</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.438</v>
+        <v>4.498</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.217</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>43.35</v>
+        <v>43.76</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>-0.026</v>
+        <v>0.009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.069</v>
+        <v>0.075</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.218</v>
+        <v>0.239</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.627</v>
+        <v>0.642</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.953</v>
+        <v>0.975</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.084</v>
+        <v>2.095</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.048</v>
+        <v>0.058</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>84.12</v>
+        <v>85.65</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.073</v>
+        <v>0.059</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>-0.015</v>
+        <v>0.022</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.211</v>
+        <v>-0.207</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.216</v>
+        <v>-0.198</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.12</v>
+        <v>-0.103</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.457</v>
+        <v>0.484</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.225</v>
+        <v>0.282</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.448</v>
+        <v>3.533</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.204</v>
+        <v>-0.19</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>90.2</v>
+        <v>91.56</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.117</v>
+        <v>0.148</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.164</v>
+        <v>0.176</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.277</v>
+        <v>0.283</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.205</v>
+        <v>0.234</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.23</v>
+        <v>0.249</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.291</v>
+        <v>0.311</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>1.193</v>
+        <v>1.126</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.219</v>
+        <v>0.186</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.304</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>58.42</v>
+        <v>59.05</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>-0.05</v>
+        <v>0.011</v>
       </c>
       <c r="E45" s="1" t="n">
         <v>-0.067</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.004</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.09</v>
+        <v>0.102</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.185</v>
+        <v>0.202</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.591</v>
+        <v>0.608</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.204</v>
+        <v>0.246</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.266</v>
+        <v>1.246</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>75.25</v>
+        <v>75.9</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0.056</v>
+        <v>0.045</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.107</v>
+        <v>-0.099</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.094</v>
+        <v>-0.089</v>
       </c>
       <c r="W45" s="1" t="n">
         <v>0.008</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.6</v>
+        <v>0.614</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.371</v>
+        <v>0.414</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.404</v>
+        <v>2.416</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.056</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>38.61</v>
+        <v>38.9</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.034</v>
+        <v>0.008</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.139</v>
+        <v>0.156</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.202</v>
+        <v>0.204</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.271</v>
+        <v>0.294</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.311</v>
+        <v>0.326</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.356</v>
+        <v>0.366</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.397</v>
+        <v>1.302</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.346</v>
+        <v>2.22</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.363</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>32.72</v>
+        <v>32.95</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>-0.021</v>
+        <v>0.007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.018</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>0.081</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.137</v>
+        <v>0.134</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>334.78</v>
+        <v>341.54</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>-0.049</v>
+        <v>0.02</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-0.075</v>
+        <v>-0.072</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.034</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.084</v>
+        <v>0.117</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.39</v>
+        <v>0.404</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.676</v>
+        <v>0.7</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.449</v>
+        <v>1.498</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.589</v>
+        <v>1.774</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>11.735</v>
+        <v>11.859</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.112</v>
+        <v>0.134</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>12.28</v>
+        <v>11.78</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.041</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>0.072</v>
+        <v>0.016</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.125</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.206</v>
+        <v>-0.248</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.06</v>
+        <v>-0.101</v>
       </c>
       <c r="AK46" s="1" t="n">
-        <v>-0.441</v>
+        <v>-0.49</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.689</v>
+        <v>-0.702</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.708</v>
+        <v>-0.713</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.867</v>
+        <v>-0.876</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>47.46</v>
+        <v>48.07</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.013</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.033</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.009</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.062</v>
+        <v>0.075</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.21</v>
+        <v>0.224</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.476</v>
+        <v>0.494</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.509</v>
+        <v>0.549</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.476</v>
+        <v>1.475</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>123.03</v>
+        <v>124.91</v>
       </c>
       <c r="R47" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S47" s="1" t="n">
         <v>-0.014</v>
       </c>
-      <c r="S47" s="1" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="T47" s="1" t="n">
-        <v>-0.032</v>
+        <v>0.011</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.052</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.268</v>
+        <v>0.288</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.346</v>
+        <v>1.382</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.13</v>
+        <v>1.212</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.326</v>
+        <v>6.421</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.033</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>42.65</v>
+        <v>42.75</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.046</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.212</v>
+        <v>0.209</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.512</v>
+        <v>0.507</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.8</v>
+        <v>0.804</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.864</v>
+        <v>0.876</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.7</v>
+        <v>1.672</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.081</v>
+        <v>0.084</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>48.13</v>
+        <v>49.38</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>-0.049</v>
+        <v>0.026</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>-0.058</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>-0.059</v>
+        <v>0.014</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>-0.017</v>
+        <v>0.003</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.142</v>
+        <v>0.161</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.394</v>
+        <v>0.424</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.591</v>
+        <v>0.632</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.12</v>
+        <v>0.191</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.025</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.02</v>
+        <v>26.12</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG48" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.007</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.444</v>
+        <v>0.45</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.717</v>
+        <v>0.729</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.504</v>
+        <v>0.492</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>50.01</v>
+        <v>50.83</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>-0.036</v>
+        <v>0.016</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.042</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.071</v>
+        <v>0.082</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.126</v>
+        <v>0.133</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.301</v>
+        <v>0.328</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.712</v>
+        <v>0.74</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.604</v>
+        <v>0.67</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.678</v>
+        <v>1.74</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.043</v>
+        <v>0.06</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>33.49</v>
+        <v>34.25</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>-0.052</v>
+        <v>0.023</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.051</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>-0.022</v>
+        <v>0.049</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.002</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.091</v>
+        <v>0.099</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.379</v>
+        <v>0.415</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.006</v>
+        <v>0.029</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.89</v>
+        <v>17.79</v>
       </c>
       <c r="AF49" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG49" s="1" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AH49" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AI49" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AJ49" s="1" t="n">
+        <v>0.009</v>
+      </c>
+      <c r="AK49" s="1" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="AL49" s="1" t="n">
+        <v>-0.299</v>
+      </c>
+      <c r="AM49" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN49" s="1" t="n">
+        <v>-0.144</v>
+      </c>
+      <c r="AO49" s="1" t="n">
         <v>0.003</v>
-      </c>
-      <c r="AG49" s="1" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AH49" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AI49" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AJ49" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AK49" s="1" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="AL49" s="1" t="n">
-        <v>-0.295</v>
-      </c>
-      <c r="AM49" s="1" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="AN49" s="1" t="n">
-        <v>-0.132</v>
-      </c>
-      <c r="AO49" s="1" t="n">
-        <v>0.009</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.72</v>
+        <v>40.54</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.021</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.008</v>
+        <v>0.03</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.072</v>
+        <v>0.097</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.231</v>
+        <v>0.236</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.281</v>
+        <v>0.286</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.44</v>
+        <v>0.497</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.85</v>
+        <v>0.888</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.44</v>
+        <v>0.492</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.68</v>
+        <v>0.719</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.172</v>
+        <v>0.196</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.85</v>
+        <v>21.79</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.082</v>
+        <v>-0.073</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.392</v>
+        <v>-0.394</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.304</v>
+        <v>-0.3</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.501</v>
+        <v>-0.505</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.94</v>
+        <v>23.79</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.076</v>
+        <v>0.052</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="AJ51" s="1" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AK51" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="AL51" s="1" t="n">
+        <v>-0.156</v>
+      </c>
+      <c r="AM51" s="1" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="AN51" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO51" s="1" t="n">
         <v>0.088</v>
-      </c>
-      <c r="AK51" s="1" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="AL51" s="1" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AM51" s="1" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AN51" s="1" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="AO51" s="1" t="n">
-        <v>0.095</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>38.7</v>
+        <v>41.44</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>-0.013</v>
+        <v>0.071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.003</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.266</v>
+        <v>-0.211</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.393</v>
+        <v>-0.335</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.209</v>
+        <v>-0.161</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.221</v>
+        <v>-0.165</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>47.36</v>
+        <v>47.77</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>-0.03</v>
+        <v>0.009</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.036</v>
+        <v>-0.035</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.116</v>
+        <v>-0.074</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.141</v>
+        <v>-0.135</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.172</v>
+        <v>-0.166</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.043</v>
+        <v>0.049</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.336</v>
+        <v>0.348</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.322</v>
+        <v>-0.289</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.754</v>
+        <v>1.753</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.142</v>
+        <v>-0.135</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>14.93</v>
+        <v>16.25</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>-0.029</v>
+        <v>0.088</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.064</v>
+        <v>0.036</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.139</v>
+        <v>-0.006</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.371</v>
+        <v>-0.316</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.559</v>
+        <v>-0.497</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>-0.072</v>
+        <v>0.003</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.334</v>
+        <v>-0.276</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>90.87</v>
+        <v>92.76</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>-0.02</v>
+        <v>0.021</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.011</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.019</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.194</v>
+        <v>-0.178</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.915</v>
+        <v>0.955</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.354</v>
+        <v>0.443</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.123</v>
+        <v>-0.105</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.29</v>
+        <v>9.2</v>
       </c>
       <c r="AF53" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="AG53" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.014</v>
       </c>
       <c r="AH53" s="1" t="n">
         <v>-0.016</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.043</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.137</v>
+        <v>-0.13</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.207</v>
+        <v>-0.208</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.133</v>
+        <v>-0.142</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.259</v>
+        <v>0.243</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.063</v>
+        <v>-0.081</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>59.09</v>
+        <v>60.21</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>-0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.021</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.08</v>
+        <v>-0.064</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.088</v>
+        <v>-0.077</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.127</v>
+        <v>-0.119</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.045</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.328</v>
+        <v>0.354</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.095</v>
+        <v>0.139</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.227</v>
+        <v>1.246</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.119</v>
+        <v>-0.102</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.25</v>
+        <v>119.69</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>0.002</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.085</v>
+        <v>0.094</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.084</v>
+        <v>0.09</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.198</v>
+        <v>0.222</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.574</v>
+        <v>0.58</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.849</v>
+        <v>0.855</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.689</v>
+        <v>1.67</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.32</v>
+        <v>39.64</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.008</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.034</v>
+        <v>0.044</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.18</v>
+        <v>0.186</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.348</v>
+        <v>0.359</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.321</v>
+        <v>0.338</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.034</v>
+        <v>0.043</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.07</v>
+        <v>47.27</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.004</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.089</v>
+        <v>0.097</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.083</v>
+        <v>0.09</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.139</v>
+        <v>0.145</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.221</v>
+        <v>0.246</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.558</v>
+        <v>0.565</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.865</v>
+        <v>0.875</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.779</v>
+        <v>1.76</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>30.48</v>
+        <v>29.47</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>0.042</v>
+        <v>-0.033</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.07</v>
+        <v>0.076</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.118</v>
+        <v>0.066</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.052</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.164</v>
+        <v>-0.167</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.382</v>
+        <v>-0.417</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.825</v>
+        <v>-0.831</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.969</v>
+        <v>-0.972</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.151</v>
+        <v>0.113</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.03</v>
+        <v>72.09</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>-0.01</v>
+        <v>0.001</v>
       </c>
       <c r="S56" s="1" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="T56" s="1" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="U56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1" t="n">
         <v>-0.013</v>
       </c>
-      <c r="T56" s="1" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="U56" s="1" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>0.003</v>
-      </c>
       <c r="W56" s="1" t="n">
-        <v>0.088</v>
+        <v>0.104</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.541</v>
+        <v>0.577</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.582</v>
+        <v>2.546</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>100.96</v>
+        <v>101.06</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.001</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.068</v>
+        <v>0.061</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.046</v>
+        <v>0.059</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.238</v>
+        <v>0.239</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.335</v>
+        <v>0.35</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.845</v>
+        <v>0.842</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.41</v>
+        <v>89.58</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>-0.008</v>
+        <v>0.002</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.07</v>
+        <v>0.061</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.049</v>
+        <v>0.055</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.087</v>
+        <v>0.081</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.038</v>
+        <v>0.057</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.312</v>
+        <v>0.314</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.438</v>
+        <v>0.455</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>0.966</v>
+        <v>0.975</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.082</v>
+        <v>0.084</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.42</v>
+        <v>95.54</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>-0.005</v>
+        <v>0.001</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="T59" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U59" s="1" t="n">
+        <v>0.071</v>
+      </c>
+      <c r="V59" s="1" t="n">
         <v>0.064</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>0.071</v>
-      </c>
       <c r="W59" s="1" t="n">
-        <v>0.051</v>
+        <v>0.065</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.238</v>
+        <v>0.24</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.322</v>
+        <v>0.339</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.55</v>
+        <v>22.6</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.002</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.017</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="V60" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="W60" s="1" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="X60" s="1" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="Y60" s="1" t="n">
         <v>0.039</v>
       </c>
-      <c r="W60" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="X60" s="1" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Y60" s="1" t="n">
-        <v>0.017</v>
-      </c>
       <c r="Z60" s="1" t="n">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>96.92</v>
+        <v>98.15</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>-0.016</v>
+        <v>0.013</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.112</v>
+        <v>0.135</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.11</v>
+        <v>0.128</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.197</v>
+        <v>0.19</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.27</v>
+        <v>0.289</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.459</v>
+        <v>0.478</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.544</v>
+        <v>0.609</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.933</v>
+        <v>1.964</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.14</v>
+        <v>0.155</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">03/04/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">03/05/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>335.85</v>
+        <v>334.51</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.007</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.028</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.206</v>
+        <v>0.187</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.915</v>
+        <v>0.907</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.077</v>
+        <v>1.035</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.405</v>
+        <v>3.387</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.025</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.37</v>
+        <v>59.68</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.005</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.063</v>
+        <v>0.081</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.22</v>
+        <v>0.231</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.271</v>
+        <v>0.302</v>
       </c>
       <c r="W5" s="1" t="n">
-        <v>0.333</v>
+        <v>0.358</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.397</v>
+        <v>0.404</v>
       </c>
       <c r="Y5" s="1" t="n">
-        <v>1.551</v>
+        <v>1.471</v>
       </c>
       <c r="Z5" s="1" t="n">
-        <v>1.456</v>
+        <v>1.469</v>
       </c>
       <c r="AA5" s="1" t="n">
-        <v>0.249</v>
+        <v>0.256</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,22 +1744,22 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.75</v>
+        <v>82.69</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AK5" s="1" t="n">
         <v>0.039</v>
@@ -1768,13 +1768,13 @@
         <v>0.139</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.087</v>
+        <v>0.086</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>688.28</v>
+        <v>684.46</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>-0.011</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>3.013</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>-0.001</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>3.036</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>0.005</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>112.42</v>
+        <v>113.86</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.066</v>
+        <v>0.072</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.104</v>
+        <v>0.135</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.18</v>
+        <v>0.193</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.231</v>
+        <v>0.269</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.31</v>
+        <v>0.347</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.317</v>
+        <v>0.334</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.566</v>
+        <v>1.502</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>1.835</v>
+        <v>1.871</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.259</v>
+        <v>0.276</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,37 +1863,37 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.6</v>
+        <v>119.4</v>
       </c>
       <c r="AF6" s="1" t="n">
         <v>-0.002</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.009</v>
+        <v>0.003</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>0.006</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.148</v>
+        <v>0.146</v>
       </c>
       <c r="AM6" s="1" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>70.86</v>
+        <v>69.86</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.031</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.071</v>
+        <v>0.055</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.087</v>
+        <v>0.066</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.207</v>
+        <v>0.175</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.399</v>
+        <v>0.38</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.555</v>
+        <v>0.497</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>1.946</v>
+        <v>1.904</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.074</v>
+        <v>0.058</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.91</v>
+        <v>27.55</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.013</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.047</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.049</v>
+        <v>0.064</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.276</v>
+        <v>0.268</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.47</v>
+        <v>0.466</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.527</v>
+        <v>0.511</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.267</v>
+        <v>0.251</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>1.038</v>
+        <v>0.888</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>-0.085</v>
+        <v>-0.097</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.337</v>
+        <v>0.32</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>96.81</v>
+        <v>96.51</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.021</v>
+        <v>0.013</v>
       </c>
       <c r="AK7" s="1" t="n">
-        <v>0.054</v>
+        <v>0.057</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.126</v>
+        <v>0.122</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.038</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>261.76</v>
+        <v>256.76</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.035</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.087</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.043</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>1.766</v>
-      </c>
-      <c r="M8" s="1" t="n">
-        <v>0.063</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>18.09</v>
+        <v>17.79</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.017</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.047</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.018</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.272</v>
+        <v>0.221</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.655</v>
+        <v>0.605</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.055</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.168</v>
+        <v>-0.17</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.419</v>
+        <v>1.379</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.101</v>
+        <v>0.083</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>103.33</v>
+        <v>102.84</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="AI8" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>-0.153</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="AO8" s="1" t="n">
         <v>0.015</v>
-      </c>
-      <c r="AJ8" s="1" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="AK8" s="1" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="AL8" s="1" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="AM8" s="1" t="n">
-        <v>-0.149</v>
-      </c>
-      <c r="AN8" s="1" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AO8" s="1" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.25</v>
+        <v>26.03</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.023</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.085</v>
+        <v>0.078</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="W9" s="1" t="n">
         <v>0.232</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.254</v>
+        <v>0.243</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.103</v>
+        <v>0.983</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.371</v>
+        <v>1.332</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.116</v>
+        <v>0.106</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>89.15</v>
+        <v>88.79</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.013</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.034</v>
+        <v>0.018</v>
       </c>
       <c r="AI9" s="1" t="n">
         <v>0.014</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.04</v>
+        <v>0.021</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.021</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.247</v>
+        <v>-0.252</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.092</v>
+        <v>-0.096</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.25</v>
+        <v>179.57</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.041</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.029</v>
+        <v>0.039</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.237</v>
+        <v>0.219</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.249</v>
+        <v>0.219</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.394</v>
+        <v>0.331</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.372</v>
+        <v>0.345</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.083</v>
+        <v>2.021</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.19</v>
+        <v>0.166</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,31 +2291,31 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.25</v>
+        <v>111.22</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="AH10" s="1" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
         <v>0.009</v>
       </c>
-      <c r="AI10" s="1" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="AJ10" s="1" t="n">
-        <v>0.014</v>
-      </c>
       <c r="AK10" s="1" t="n">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.079</v>
+        <v>0.077</v>
       </c>
       <c r="AN10" s="1" t="n">
         <v>0.314</v>
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>223.25</v>
+        <v>220.59</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.021</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.067</v>
+        <v>0.053</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.115</v>
+        <v>0.104</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.204</v>
+        <v>0.18</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.51</v>
+        <v>0.492</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.705</v>
+        <v>0.648</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.869</v>
+        <v>1.834</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>61.23</v>
+        <v>58.79</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.04</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.083</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.267</v>
+        <v>0.215</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.508</v>
+        <v>0.428</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.78</v>
+        <v>0.633</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.504</v>
+        <v>0.444</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.848</v>
+        <v>0.736</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>3.754</v>
+        <v>3.565</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.193</v>
+        <v>0.145</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,37 +2410,37 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.15</v>
+        <v>103.26</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="1" t="n">
         <v>0.004</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.009</v>
       </c>
       <c r="AJ11" s="1" t="n">
         <v>0.011</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AM11" s="1" t="n">
         <v>0.19</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,34 +2451,34 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>453.06</v>
+        <v>453.02</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>0.009</v>
-      </c>
       <c r="I12" s="1" t="n">
-        <v>0.19</v>
+        <v>0.172</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>0.968</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>1.016</v>
+        <v>0.987</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.118</v>
+        <v>4.117</v>
       </c>
       <c r="M12" s="1" t="n">
         <v>-0.043</v>
@@ -2490,37 +2490,37 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>91.08</v>
+        <v>87.22</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.042</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.106</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.08</v>
+        <v>0.107</v>
       </c>
       <c r="U12" s="1" t="n">
-        <v>0.314</v>
+        <v>0.263</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.658</v>
+        <v>0.54</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.765</v>
+        <v>1.55</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.291</v>
+        <v>3.109</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.764</v>
+        <v>2.553</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>5.222</v>
+        <v>4.958</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>0.237</v>
+        <v>0.184</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>243</v>
@@ -2529,37 +2529,37 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>107.75</v>
+        <v>107.62</v>
       </c>
       <c r="AF12" s="1" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.009</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ12" s="1" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="AL12" s="1" t="n">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
       <c r="AO12" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>203.44</v>
+        <v>201.68</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.009</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.009</v>
+        <v>0.012</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.075</v>
+        <v>0.072</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.159</v>
+        <v>0.137</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.733</v>
+        <v>0.718</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.883</v>
+        <v>0.824</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.709</v>
+        <v>2.677</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.024</v>
+        <v>0.015</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.76</v>
+        <v>40.47</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.054</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.129</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.051</v>
+        <v>0.077</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.394</v>
+        <v>0.32</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.908</v>
+        <v>0.765</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>2.339</v>
+        <v>1.988</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.376</v>
+        <v>3.141</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>2.068</v>
+        <v>1.878</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.458</v>
+        <v>5.112</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.248</v>
+        <v>0.181</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.15</v>
+        <v>23.07</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.011</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.273</v>
+        <v>0.269</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>97.36</v>
+        <v>96.81</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.042</v>
+        <v>0.038</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.059</v>
+        <v>0.049</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.433</v>
+        <v>0.425</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.62</v>
+        <v>0.575</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.744</v>
+        <v>1.728</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.034</v>
+        <v>0.028</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.48</v>
+        <v>50.69</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="S14" s="1" t="n">
-        <v>-0.067</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.015</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>0.297</v>
+        <v>0.226</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.661</v>
+        <v>0.555</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>1.18</v>
+        <v>0.938</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.207</v>
+        <v>0.144</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,37 +2761,37 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>75.56</v>
+        <v>75.19</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.011</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.009</v>
       </c>
       <c r="AJ14" s="1" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.105</v>
+        <v>0.086</v>
       </c>
       <c r="AL14" s="1" t="n">
-        <v>0.148</v>
+        <v>0.143</v>
       </c>
       <c r="AM14" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.042</v>
       </c>
       <c r="AN14" s="1" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="AO14" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>250.71</v>
+        <v>247.03</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.031</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.02</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.029</v>
+        <v>0.016</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.206</v>
+        <v>0.173</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.823</v>
+        <v>0.797</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.723</v>
+        <v>0.683</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>2.986</v>
+        <v>2.928</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.013</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.57</v>
+        <v>16.21</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.021</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-0.118</v>
+        <v>-0.121</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.005</v>
+        <v>0.042</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.157</v>
+        <v>0.117</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.675</v>
+        <v>0.558</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.966</v>
+        <v>0.874</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>96.87</v>
+        <v>96.38</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.009</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.012</v>
+        <v>0.009</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.05</v>
+        <v>0.038</v>
       </c>
       <c r="AK15" s="1" t="n">
-        <v>0.112</v>
+        <v>0.106</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.321</v>
+        <v>0.315</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.133</v>
+        <v>0.127</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.437</v>
+        <v>0.43</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>137.92</v>
+        <v>136.52</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.01</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.014</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.147</v>
+        <v>0.14</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.198</v>
+        <v>0.189</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.499</v>
+        <v>0.484</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.815</v>
+        <v>0.751</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.601</v>
+        <v>1.574</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.134</v>
+        <v>0.123</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>75.3</v>
+        <v>74.16</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.015</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.056</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.034</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0</v>
+        <v>-0.037</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.035</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.055</v>
+        <v>1.024</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>42.01</v>
+        <v>41.73</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.028</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.014</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="AJ16" s="1" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="AK16" s="1" t="n">
-        <v>0.152</v>
+        <v>0.127</v>
       </c>
       <c r="AL16" s="1" t="n">
-        <v>0.242</v>
+        <v>0.233</v>
       </c>
       <c r="AM16" s="1" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="AN16" s="1" t="n">
-        <v>0.241</v>
+        <v>0.232</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>149</v>
+        <v>148.11</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>0.007</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>-0.011</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.01</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.728</v>
+        <v>0.718</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.841</v>
+        <v>0.796</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>105.96</v>
+        <v>102.4</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.034</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.068</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>0.036</v>
+        <v>-0.004</v>
       </c>
       <c r="U17" s="1" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>0.11</v>
       </c>
-      <c r="V17" s="1" t="n">
-        <v>0.147</v>
-      </c>
       <c r="W17" s="1" t="n">
-        <v>0.534</v>
+        <v>0.453</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.32</v>
+        <v>1.242</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.406</v>
+        <v>1.247</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>3.692</v>
+        <v>3.535</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.144</v>
+        <v>0.106</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>42.22</v>
+        <v>41.88</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.008</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.023</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.003</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="AL17" s="1" t="n">
-        <v>0.119</v>
+        <v>0.11</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.182</v>
+        <v>-0.184</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.072</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>159.78</v>
+        <v>156.83</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.018</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.093</v>
+        <v>0.073</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.102</v>
+        <v>0.085</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.221</v>
+        <v>0.181</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.602</v>
+        <v>0.573</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.697</v>
+        <v>0.629</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.473</v>
+        <v>2.409</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.078</v>
+        <v>0.058</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.8</v>
+        <v>34.94</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.024</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.044</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.15</v>
+        <v>0.121</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.264</v>
+        <v>0.229</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.543</v>
+        <v>0.473</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.147</v>
+        <v>0.12</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>57.47</v>
+        <v>56.91</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.093</v>
+        <v>0.077</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.18</v>
+        <v>0.168</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.468</v>
+        <v>0.419</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.754</v>
+        <v>0.737</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.951</v>
+        <v>0.904</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.135</v>
+        <v>2.104</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.066</v>
+        <v>0.055</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>81.6</v>
+        <v>78.96</v>
       </c>
       <c r="R20" s="1" t="n">
-        <v>0</v>
+        <v>-0.032</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.04</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.021</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.085</v>
+        <v>0.044</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.163</v>
+        <v>0.128</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.221</v>
+        <v>0.166</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.427</v>
+        <v>0.381</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.484</v>
+        <v>0.391</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.665</v>
+        <v>1.578</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.095</v>
+        <v>0.06</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.53</v>
+        <v>100.24</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.026</v>
+        <v>0.018</v>
       </c>
       <c r="AK20" s="1" t="n">
         <v>0.054</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.207</v>
+        <v>0.204</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>35.18</v>
+        <v>34.15</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.029</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.072</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.126</v>
+        <v>0.141</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.326</v>
+        <v>0.278</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.658</v>
+        <v>0.574</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.704</v>
+        <v>0.654</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.875</v>
+        <v>0.789</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.364</v>
+        <v>1.295</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.155</v>
+        <v>0.122</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>246.97</v>
+        <v>240.04</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.028</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.011</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.083</v>
+        <v>0.061</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.207</v>
+        <v>0.186</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.249</v>
+        <v>0.216</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.664</v>
+        <v>0.584</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.151</v>
+        <v>1.091</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.662</v>
+        <v>1.557</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.779</v>
+        <v>3.645</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.15</v>
+        <v>0.118</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.6</v>
+        <v>50.41</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.009</v>
+        <v>0.004</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="AK21" s="1" t="n">
         <v>0.044</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.064</v>
+        <v>0.059</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.274</v>
+        <v>0.269</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>77.91</v>
+        <v>75.25</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0.034</v>
+        <v>-0.034</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.032</v>
+        <v>-0.067</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.021</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.154</v>
+        <v>0.117</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.259</v>
+        <v>0.202</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.616</v>
+        <v>0.53</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.426</v>
+        <v>0.377</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.183</v>
+        <v>1.114</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>0.982</v>
+        <v>0.914</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.124</v>
+        <v>0.085</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.69</v>
+        <v>102.37</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>-0.009</v>
+        <v>0.005</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.011</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.019</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.107</v>
+        <v>0.089</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.641</v>
+        <v>0.636</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.489</v>
+        <v>0.464</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.132</v>
+        <v>2.122</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.54</v>
+        <v>49.35</v>
       </c>
       <c r="AF22" s="1" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="AG22" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AH22" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="AG22" s="1" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="AH22" s="1" t="n">
-        <v>0.014</v>
-      </c>
       <c r="AI22" s="1" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="AK22" s="1" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.189</v>
+        <v>0.185</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.27</v>
+        <v>0.265</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
@@ -3644,37 +3644,37 @@
         <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>37.49</v>
+        <v>36.36</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.03</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.07</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0.118</v>
+        <v>0.157</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>0.653</v>
+        <v>0.56</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>0.663</v>
+        <v>0.613</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>0.723</v>
+        <v>0.637</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>1.505</v>
+        <v>1.429</v>
       </c>
       <c r="M23" s="1" t="n">
-        <v>0.18</v>
+        <v>0.144</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>150</v>
@@ -3683,37 +3683,37 @@
         <v>151</v>
       </c>
       <c r="Q23" t="n">
-        <v>103.17</v>
+        <v>100.58</v>
       </c>
       <c r="R23" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.025</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.062</v>
       </c>
       <c r="T23" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.07</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="V23" s="1" t="n">
-        <v>-0.094</v>
+        <v>-0.136</v>
       </c>
       <c r="W23" s="1" t="n">
-        <v>0.087</v>
+        <v>0.034</v>
       </c>
       <c r="X23" s="1" t="n">
-        <v>0.547</v>
+        <v>0.508</v>
       </c>
       <c r="Y23" s="1" t="n">
-        <v>0.831</v>
+        <v>0.708</v>
       </c>
       <c r="Z23" s="1" t="n">
-        <v>3.304</v>
+        <v>3.196</v>
       </c>
       <c r="AA23" s="1" t="n">
-        <v>0.071</v>
+        <v>0.044</v>
       </c>
       <c r="AC23" s="6" t="s">
         <v>262</v>
@@ -3722,37 +3722,37 @@
         <v>263</v>
       </c>
       <c r="AE23" t="n">
-        <v>95.95</v>
+        <v>95.62</v>
       </c>
       <c r="AF23" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
       <c r="AK23" s="1" t="n">
         <v>0.066</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>0.163</v>
+        <v>0.159</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.154</v>
+        <v>0.15</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
@@ -3763,37 +3763,37 @@
         <v>51</v>
       </c>
       <c r="C24" t="n">
-        <v>65.33</v>
+        <v>63.96</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.021</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.074</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.033</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>0.109</v>
+        <v>0.083</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>0.256</v>
+        <v>0.189</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>0.593</v>
+        <v>0.56</v>
       </c>
       <c r="K24" s="1" t="n">
-        <v>0.669</v>
+        <v>0.629</v>
       </c>
       <c r="L24" s="1" t="n">
-        <v>1.569</v>
+        <v>1.515</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.002</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>152</v>
@@ -3802,35 +3802,35 @@
         <v>153</v>
       </c>
       <c r="Q24" t="n">
-        <v>37.85</v>
+        <v>36.91</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.025</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.101</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.018</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.032</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>0.105</v>
+        <v>0.062</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>0.309</v>
+        <v>0.227</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.018</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.086</v>
       </c>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="AC24" s="6" t="s">
         <v>264</v>
@@ -3839,37 +3839,37 @@
         <v>265</v>
       </c>
       <c r="AE24" t="n">
-        <v>110.97</v>
+        <v>110.53</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.004</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="AH24" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AI24" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AJ24" s="1" t="n">
         <v>0.013</v>
       </c>
-      <c r="AI24" s="1" t="n">
+      <c r="AK24" s="1" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AL24" s="1" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AM24" s="1" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AO24" s="1" t="n">
         <v>0.007</v>
-      </c>
-      <c r="AJ24" s="1" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="AK24" s="1" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AL24" s="1" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AM24" s="1" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AN24" s="1" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="AO24" s="1" t="n">
-        <v>0.011</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
@@ -3880,37 +3880,37 @@
         <v>53</v>
       </c>
       <c r="C25" t="n">
-        <v>45.29</v>
+        <v>44.45</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.019</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.057</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.015</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>0.048</v>
+        <v>0.028</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.123</v>
+        <v>0.106</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>0.169</v>
+        <v>0.127</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>0.551</v>
+        <v>0.522</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>0.907</v>
+        <v>0.855</v>
       </c>
       <c r="L25" s="1" t="n">
-        <v>1.993</v>
+        <v>1.938</v>
       </c>
       <c r="M25" s="1" t="n">
-        <v>0.035</v>
+        <v>0.016</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>154</v>
@@ -3919,37 +3919,37 @@
         <v>155</v>
       </c>
       <c r="Q25" t="n">
-        <v>85.94</v>
+        <v>84.63</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.035</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.03</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.017</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.028</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>0.224</v>
+        <v>0.195</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>0.335</v>
+        <v>0.314</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>0.159</v>
+        <v>0.118</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>1.23</v>
+        <v>1.196</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.008</v>
       </c>
       <c r="AC25" s="6" t="s">
         <v>266</v>
@@ -3958,10 +3958,10 @@
         <v>267</v>
       </c>
       <c r="AE25" t="n">
-        <v>92.57</v>
+        <v>92.41</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="AG25" s="1" t="n">
         <v>-0.001</v>
@@ -3970,25 +3970,25 @@
         <v>-0.005</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>0.028</v>
+        <v>0.021</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>0.063</v>
+        <v>0.053</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>0.244</v>
+        <v>0.236</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>0.28</v>
+        <v>0.272</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="AO25" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
@@ -3999,37 +3999,37 @@
         <v>55</v>
       </c>
       <c r="C26" t="n">
-        <v>47.24</v>
+        <v>46.24</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.021</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.049</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.109</v>
+        <v>0.091</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>0.163</v>
+        <v>0.134</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>0.309</v>
+        <v>0.268</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>0.63</v>
+        <v>0.595</v>
       </c>
       <c r="K26" s="1" t="n">
-        <v>0.864</v>
+        <v>0.801</v>
       </c>
       <c r="L26" s="1" t="n">
-        <v>1.242</v>
+        <v>1.195</v>
       </c>
       <c r="M26" s="1" t="n">
-        <v>0.074</v>
+        <v>0.051</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>156</v>
@@ -4038,37 +4038,37 @@
         <v>157</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.58</v>
+        <v>60.43</v>
       </c>
       <c r="R26" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.027</v>
       </c>
       <c r="T26" s="1" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="V26" s="1" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="W26" s="1" t="n">
-        <v>0.157</v>
+        <v>0.143</v>
       </c>
       <c r="X26" s="1" t="n">
-        <v>0.478</v>
+        <v>0.474</v>
       </c>
       <c r="Y26" s="1" t="n">
-        <v>0.255</v>
+        <v>0.235</v>
       </c>
       <c r="Z26" s="1" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="AC26" s="6" t="s">
         <v>268</v>
@@ -4077,35 +4077,35 @@
         <v>269</v>
       </c>
       <c r="AE26" t="n">
-        <v>26.59</v>
+        <v>26.5</v>
       </c>
       <c r="AF26" s="1" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="AG26" s="1" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="AH26" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AI26" s="1" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AJ26" s="1" t="n">
         <v>0.005</v>
       </c>
-      <c r="AG26" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AH26" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AI26" s="1" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="AJ26" s="1" t="n">
-        <v>0.019</v>
-      </c>
       <c r="AK26" s="1" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>0.187</v>
+        <v>0.178</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>0.147</v>
+        <v>0.142</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
@@ -4116,37 +4116,37 @@
         <v>57</v>
       </c>
       <c r="C27" t="n">
-        <v>45.23</v>
+        <v>44.28</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.021</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.084</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.032</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.003</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>0.068</v>
+        <v>0.046</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>0.14</v>
+        <v>0.083</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>0.321</v>
+        <v>0.293</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>0.551</v>
+        <v>0.514</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.503</v>
+        <v>1.451</v>
       </c>
       <c r="M27" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.016</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>158</v>
@@ -4158,22 +4158,22 @@
         <v>26.42</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.03</v>
       </c>
       <c r="T27" s="1" t="n">
-        <v>0.018</v>
+        <v>0.03</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.015</v>
       </c>
       <c r="V27" s="1" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="W27" s="1" t="n">
-        <v>0.037</v>
+        <v>0.026</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
@@ -4188,37 +4188,37 @@
         <v>271</v>
       </c>
       <c r="AE27" t="n">
-        <v>52.87</v>
+        <v>52.83</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AI27" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>0.194</v>
+        <v>0.193</v>
       </c>
       <c r="AM27" s="1" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.319</v>
+        <v>0.318</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
@@ -4229,37 +4229,37 @@
         <v>59</v>
       </c>
       <c r="C28" t="n">
-        <v>42.1</v>
+        <v>41.18</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.022</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.076</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.039</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.006</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>0.018</v>
+        <v>-0.004</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>0.156</v>
+        <v>0.087</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>0.612</v>
+        <v>0.577</v>
       </c>
       <c r="K28" s="1" t="n">
-        <v>0.482</v>
+        <v>0.452</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.185</v>
+        <v>1.137</v>
       </c>
       <c r="M28" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.031</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>160</v>
@@ -4268,37 +4268,37 @@
         <v>161</v>
       </c>
       <c r="Q28" t="n">
-        <v>74.82</v>
+        <v>73.21</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.022</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-0.022</v>
+        <v>-0.046</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.017</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>0.123</v>
+        <v>0.104</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>0.088</v>
+        <v>0.063</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>0.093</v>
+        <v>0.068</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>0.247</v>
+        <v>0.22</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>0.526</v>
+        <v>0.471</v>
       </c>
       <c r="Z28" s="1" t="n">
-        <v>1.556</v>
+        <v>1.501</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>0.118</v>
+        <v>0.094</v>
       </c>
       <c r="AC28" s="6" t="s">
         <v>272</v>
@@ -4307,37 +4307,37 @@
         <v>273</v>
       </c>
       <c r="AE28" t="n">
-        <v>54.07</v>
+        <v>53.91</v>
       </c>
       <c r="AF28" s="1" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="AK28" s="1" t="n">
         <v>0.074</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>0.234</v>
+        <v>0.23</v>
       </c>
       <c r="AM28" s="1" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.394</v>
+        <v>0.389</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
@@ -4348,37 +4348,37 @@
         <v>61</v>
       </c>
       <c r="C29" t="n">
-        <v>62.56</v>
+        <v>61.05</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.024</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.055</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.019</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>0.08</v>
+        <v>0.052</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>0.123</v>
+        <v>0.085</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>0.209</v>
+        <v>0.177</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>0.506</v>
+        <v>0.47</v>
       </c>
       <c r="K29" s="1" t="n">
-        <v>0.606</v>
+        <v>0.557</v>
       </c>
       <c r="L29" s="1" t="n">
-        <v>1.636</v>
+        <v>1.572</v>
       </c>
       <c r="M29" s="1" t="n">
-        <v>0.043</v>
+        <v>0.018</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>162</v>
@@ -4387,37 +4387,37 @@
         <v>163</v>
       </c>
       <c r="Q29" t="n">
-        <v>45.55</v>
+        <v>44.68</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.019</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.028</v>
       </c>
       <c r="T29" s="1" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>0.173</v>
+        <v>0.154</v>
       </c>
       <c r="V29" s="1" t="n">
-        <v>0.155</v>
+        <v>0.132</v>
       </c>
       <c r="W29" s="1" t="n">
-        <v>0.301</v>
+        <v>0.252</v>
       </c>
       <c r="X29" s="1" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="Y29" s="1" t="n">
-        <v>0.325</v>
+        <v>0.268</v>
       </c>
       <c r="Z29" s="1" t="n">
-        <v>1.5</v>
+        <v>1.452</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>0.181</v>
+        <v>0.158</v>
       </c>
       <c r="AC29" s="6" t="s">
         <v>274</v>
@@ -4426,37 +4426,37 @@
         <v>275</v>
       </c>
       <c r="AE29" t="n">
-        <v>50.94</v>
+        <v>50.66</v>
       </c>
       <c r="AF29" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="AG29" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.01</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AJ29" s="1" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AL29" s="1" t="n">
-        <v>0.162</v>
+        <v>0.156</v>
       </c>
       <c r="AM29" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.049</v>
       </c>
       <c r="AN29" s="1" t="n">
-        <v>0.361</v>
+        <v>0.354</v>
       </c>
       <c r="AO29" s="1" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
@@ -4467,37 +4467,37 @@
         <v>63</v>
       </c>
       <c r="C30" t="n">
-        <v>100.16</v>
+        <v>97.89</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.023</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.083</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.015</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.096</v>
+        <v>0.058</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>0.186</v>
+        <v>0.145</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>0.388</v>
+        <v>0.309</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>0.586</v>
+        <v>0.55</v>
       </c>
       <c r="K30" s="1" t="n">
-        <v>0.202</v>
+        <v>0.165</v>
       </c>
       <c r="L30" s="1" t="n">
-        <v>1.409</v>
+        <v>1.355</v>
       </c>
       <c r="M30" s="1" t="n">
-        <v>0.065</v>
+        <v>0.041</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>164</v>
@@ -4506,37 +4506,37 @@
         <v>165</v>
       </c>
       <c r="Q30" t="n">
-        <v>49.32</v>
+        <v>48.74</v>
       </c>
       <c r="R30" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.034</v>
       </c>
       <c r="T30" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.016</v>
       </c>
       <c r="U30" s="1" t="n">
-        <v>0.1</v>
+        <v>0.092</v>
       </c>
       <c r="V30" s="1" t="n">
-        <v>0.046</v>
+        <v>0.035</v>
       </c>
       <c r="W30" s="1" t="n">
-        <v>0.094</v>
+        <v>0.084</v>
       </c>
       <c r="X30" s="1" t="n">
-        <v>0.132</v>
+        <v>0.119</v>
       </c>
       <c r="Y30" s="1" t="n">
-        <v>0.408</v>
+        <v>0.349</v>
       </c>
       <c r="Z30" s="1" t="n">
-        <v>0.767</v>
+        <v>0.746</v>
       </c>
       <c r="AA30" s="1" t="n">
-        <v>0.101</v>
+        <v>0.088</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>276</v>
@@ -4545,37 +4545,37 @@
         <v>277</v>
       </c>
       <c r="AE30" t="n">
-        <v>24.28</v>
+        <v>24.18</v>
       </c>
       <c r="AF30" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="AG30" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AH30" s="1" t="n">
         <v>-0.014</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ30" s="1" t="n">
-        <v>0.028</v>
+        <v>0.018</v>
       </c>
       <c r="AK30" s="1" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="AL30" s="1" t="n">
-        <v>0.256</v>
+        <v>0.246</v>
       </c>
       <c r="AM30" s="1" t="n">
-        <v>0.279</v>
+        <v>0.273</v>
       </c>
       <c r="AN30" s="1" t="n">
-        <v>0.689</v>
+        <v>0.675</v>
       </c>
       <c r="AO30" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
@@ -4586,37 +4586,37 @@
         <v>65</v>
       </c>
       <c r="C31" t="n">
-        <v>19.49</v>
+        <v>19.25</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.059</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.018</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>0.095</v>
+        <v>0.08</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>0.16</v>
+        <v>0.133</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>0.305</v>
+        <v>0.259</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>0.485</v>
+        <v>0.467</v>
       </c>
       <c r="K31" s="1" t="n">
-        <v>0.591</v>
+        <v>0.548</v>
       </c>
       <c r="L31" s="1" t="n">
-        <v>1.01</v>
+        <v>0.985</v>
       </c>
       <c r="M31" s="1" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>166</v>
@@ -4625,37 +4625,37 @@
         <v>167</v>
       </c>
       <c r="Q31" t="n">
-        <v>65.51</v>
+        <v>64.29</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.019</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.023</v>
       </c>
       <c r="T31" s="1" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>0.138</v>
+        <v>0.112</v>
       </c>
       <c r="W31" s="1" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="X31" s="1" t="n">
-        <v>0.249</v>
+        <v>0.226</v>
       </c>
       <c r="Y31" s="1" t="n">
-        <v>0.448</v>
+        <v>0.391</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>1.67</v>
+        <v>1.621</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.012</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>278</v>
@@ -4664,37 +4664,37 @@
         <v>279</v>
       </c>
       <c r="AE31" t="n">
-        <v>80.4</v>
+        <v>80.08</v>
       </c>
       <c r="AF31" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.004</v>
       </c>
       <c r="AG31" s="1" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AI31" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AJ31" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AK31" s="1" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AL31" s="1" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AM31" s="1" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="AN31" s="1" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO31" s="1" t="n">
         <v>-0.002</v>
-      </c>
-      <c r="AH31" s="1" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="AI31" s="1" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="AJ31" s="1" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="AK31" s="1" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AL31" s="1" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="AM31" s="1" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="AN31" s="1" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="AO31" s="1" t="n">
-        <v>0.002</v>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
@@ -4705,37 +4705,37 @@
         <v>67</v>
       </c>
       <c r="C32" t="n">
-        <v>37.46</v>
+        <v>37.25</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.006</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>-0.012</v>
+        <v>0.003</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.05</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.059</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>0.096</v>
+        <v>0.089</v>
       </c>
       <c r="K32" s="1" t="n">
-        <v>0.276</v>
+        <v>0.263</v>
       </c>
       <c r="L32" s="1" t="n">
-        <v>1.17</v>
+        <v>1.158</v>
       </c>
       <c r="M32" s="1" t="n">
-        <v>0.029</v>
+        <v>0.023</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>168</v>
@@ -4744,37 +4744,37 @@
         <v>169</v>
       </c>
       <c r="Q32" t="n">
-        <v>45.87</v>
+        <v>45.21</v>
       </c>
       <c r="R32" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.014</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="T32" s="1" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="U32" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.056</v>
       </c>
       <c r="V32" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.047</v>
       </c>
       <c r="W32" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.103</v>
       </c>
       <c r="X32" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.095</v>
       </c>
       <c r="Y32" s="1" t="n">
-        <v>0.032</v>
+        <v>-0.007</v>
       </c>
       <c r="Z32" s="1" t="n">
-        <v>1.145</v>
+        <v>1.114</v>
       </c>
       <c r="AA32" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.057</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>280</v>
@@ -4783,37 +4783,37 @@
         <v>281</v>
       </c>
       <c r="AE32" t="n">
-        <v>29.41</v>
+        <v>29.23</v>
       </c>
       <c r="AF32" s="1" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="AH32" s="1" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AI32" s="1" t="n">
         <v>0.003</v>
       </c>
-      <c r="AG32" s="1" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="AH32" s="1" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="AI32" s="1" t="n">
-        <v>0.008</v>
-      </c>
       <c r="AJ32" s="1" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>0.078</v>
+        <v>0.069</v>
       </c>
       <c r="AL32" s="1" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="AM32" s="1" t="n">
-        <v>0.202</v>
+        <v>0.191</v>
       </c>
       <c r="AN32" s="1" t="n">
-        <v>1.006</v>
+        <v>0.994</v>
       </c>
       <c r="AO32" s="1" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
@@ -4824,37 +4824,37 @@
         <v>69</v>
       </c>
       <c r="C33" t="n">
-        <v>50.27</v>
+        <v>50.37</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.042</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.049</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-0.065</v>
+        <v>-0.067</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.04</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>0.051</v>
+        <v>0.029</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>0.265</v>
+        <v>0.268</v>
       </c>
       <c r="K33" s="1" t="n">
-        <v>0.275</v>
+        <v>0.271</v>
       </c>
       <c r="L33" s="1" t="n">
-        <v>1.149</v>
+        <v>1.153</v>
       </c>
       <c r="M33" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.068</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>170</v>
@@ -4863,37 +4863,37 @@
         <v>171</v>
       </c>
       <c r="Q33" t="n">
-        <v>89.84</v>
+        <v>87.77</v>
       </c>
       <c r="R33" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.023</v>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.033</v>
       </c>
       <c r="T33" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="U33" s="1" t="n">
-        <v>0.089</v>
+        <v>0.064</v>
       </c>
       <c r="V33" s="1" t="n">
-        <v>0.275</v>
+        <v>0.245</v>
       </c>
       <c r="W33" s="1" t="n">
-        <v>0.272</v>
+        <v>0.233</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0.585</v>
+        <v>0.548</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0.712</v>
+        <v>0.642</v>
       </c>
       <c r="Z33" s="1" t="n">
-        <v>1.254</v>
+        <v>1.202</v>
       </c>
       <c r="AA33" s="1" t="n">
-        <v>0.059</v>
+        <v>0.035</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>282</v>
@@ -4902,35 +4902,35 @@
         <v>283</v>
       </c>
       <c r="AE33" t="n">
-        <v>47.98</v>
+        <v>47.89</v>
       </c>
       <c r="AF33" s="1" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AG33" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="AH33" s="1" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AI33" s="1" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AJ33" s="1" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="AK33" s="1" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="AL33" s="1" t="n">
-        <v>0.169</v>
+        <v>0.167</v>
       </c>
       <c r="AM33" s="1" t="n">
-        <v>0.024</v>
+        <v>0.021</v>
       </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
@@ -4941,37 +4941,37 @@
         <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>88.59</v>
+        <v>85.89</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.071</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>0.099</v>
+        <v>0.065</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>0.167</v>
+        <v>0.125</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>0.687</v>
+        <v>0.635</v>
       </c>
       <c r="K34" s="1" t="n">
-        <v>0.479</v>
+        <v>0.422</v>
       </c>
       <c r="L34" s="1" t="n">
-        <v>1.352</v>
+        <v>1.28</v>
       </c>
       <c r="M34" s="1" t="n">
-        <v>0.097</v>
+        <v>0.064</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>172</v>
@@ -4980,37 +4980,37 @@
         <v>173</v>
       </c>
       <c r="Q34" t="n">
-        <v>172.97</v>
+        <v>168.67</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>0.017</v>
+        <v>-0.025</v>
       </c>
       <c r="S34" s="1" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="T34" s="1" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="U34" s="1" t="n">
         <v>-0.013</v>
       </c>
-      <c r="T34" s="1" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="U34" s="1" t="n">
-        <v>0.006</v>
-      </c>
       <c r="V34" s="1" t="n">
-        <v>0.234</v>
+        <v>0.18</v>
       </c>
       <c r="W34" s="1" t="n">
-        <v>0.291</v>
+        <v>0.236</v>
       </c>
       <c r="X34" s="1" t="n">
-        <v>0.336</v>
+        <v>0.303</v>
       </c>
       <c r="Y34" s="1" t="n">
-        <v>0.191</v>
+        <v>0.139</v>
       </c>
       <c r="Z34" s="1" t="n">
-        <v>1.024</v>
+        <v>0.974</v>
       </c>
       <c r="AA34" s="1" t="n">
-        <v>0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="AC34" s="6" t="s">
         <v>284</v>
@@ -5019,37 +5019,37 @@
         <v>285</v>
       </c>
       <c r="AE34" t="n">
-        <v>104.42</v>
+        <v>103.31</v>
       </c>
       <c r="AF34" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.011</v>
       </c>
       <c r="AG34" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="AH34" s="1" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="AI34" s="1" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="AJ34" s="1" t="n">
-        <v>0.115</v>
+        <v>0.095</v>
       </c>
       <c r="AK34" s="1" t="n">
-        <v>0.247</v>
+        <v>0.22</v>
       </c>
       <c r="AL34" s="1" t="n">
-        <v>0.503</v>
+        <v>0.487</v>
       </c>
       <c r="AM34" s="1" t="n">
-        <v>0.231</v>
+        <v>0.212</v>
       </c>
       <c r="AN34" s="1" t="n">
-        <v>2.373</v>
+        <v>2.337</v>
       </c>
       <c r="AO34" s="1" t="n">
-        <v>0.061</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
@@ -5060,37 +5060,37 @@
         <v>73</v>
       </c>
       <c r="C35" t="n">
-        <v>57.13</v>
+        <v>56.18</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.017</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.051</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.065</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.092</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.073</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0.09</v>
+        <v>0.021</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0.224</v>
+        <v>0.204</v>
       </c>
       <c r="K35" s="1" t="n">
-        <v>-0.249</v>
+        <v>-0.265</v>
       </c>
       <c r="L35" s="1" t="n">
-        <v>0.657</v>
+        <v>0.63</v>
       </c>
       <c r="M35" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.065</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>174</v>
@@ -5099,37 +5099,37 @@
         <v>175</v>
       </c>
       <c r="Q35" t="n">
-        <v>58.81</v>
+        <v>57.88</v>
       </c>
       <c r="R35" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.04</v>
       </c>
       <c r="T35" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.001</v>
       </c>
       <c r="U35" s="1" t="n">
-        <v>-0.07</v>
+        <v>-0.087</v>
       </c>
       <c r="V35" s="1" t="n">
-        <v>-0.049</v>
+        <v>-0.071</v>
       </c>
       <c r="W35" s="1" t="n">
-        <v>-0.065</v>
+        <v>-0.084</v>
       </c>
       <c r="X35" s="1" t="n">
-        <v>0.115</v>
+        <v>0.097</v>
       </c>
       <c r="Y35" s="1" t="n">
-        <v>0.132</v>
+        <v>0.096</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>2.093</v>
+        <v>2.044</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.069</v>
       </c>
       <c r="AC35" t="s">
         <v>25</v>
@@ -5155,37 +5155,37 @@
         <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>23.31</v>
+        <v>23.15</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.007</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.03</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>-0.008</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>0.09</v>
+        <v>0.084</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>0.146</v>
+        <v>0.128</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>0.401</v>
+        <v>0.343</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>0.265</v>
+        <v>0.257</v>
       </c>
       <c r="K36" s="1" t="n">
-        <v>0.065</v>
+        <v>0.053</v>
       </c>
       <c r="L36" s="1" t="n">
-        <v>0.725</v>
+        <v>0.713</v>
       </c>
       <c r="M36" s="1" t="n">
-        <v>0.097</v>
+        <v>0.089</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>176</v>
@@ -5194,35 +5194,35 @@
         <v>177</v>
       </c>
       <c r="Q36" t="n">
-        <v>30.47</v>
+        <v>29.64</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.027</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.04</v>
       </c>
       <c r="T36" s="1" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>0.135</v>
+        <v>0.106</v>
       </c>
       <c r="V36" s="1" t="n">
-        <v>0.358</v>
+        <v>0.296</v>
       </c>
       <c r="W36" s="1" t="n">
-        <v>0.402</v>
+        <v>0.332</v>
       </c>
       <c r="X36" s="1" t="n">
-        <v>0.289</v>
+        <v>0.254</v>
       </c>
       <c r="Y36" s="1" t="n">
-        <v>-0.264</v>
+        <v>-0.291</v>
       </c>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="n">
-        <v>0.163</v>
+        <v>0.132</v>
       </c>
       <c r="AC36" s="4" t="s">
         <v>286</v>
@@ -5248,37 +5248,37 @@
         <v>77</v>
       </c>
       <c r="C37" t="n">
-        <v>71.62</v>
+        <v>70.4</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.017</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>-0.071</v>
+        <v>-0.075</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.051</v>
+        <v>0.037</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>0.161</v>
+        <v>0.127</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>0.263</v>
+        <v>0.223</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>0.468</v>
+        <v>0.414</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>0.941</v>
+        <v>0.908</v>
       </c>
       <c r="K37" s="1" t="n">
-        <v>0.836</v>
+        <v>0.786</v>
       </c>
       <c r="L37" s="1" t="n">
-        <v>3.412</v>
+        <v>3.337</v>
       </c>
       <c r="M37" s="1" t="n">
-        <v>0.127</v>
+        <v>0.108</v>
       </c>
       <c r="O37" s="7" t="s">
         <v>178</v>
@@ -5287,37 +5287,37 @@
         <v>179</v>
       </c>
       <c r="Q37" t="n">
-        <v>122.77</v>
+        <v>122</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.006</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.029</v>
       </c>
       <c r="T37" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.039</v>
       </c>
       <c r="U37" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.035</v>
       </c>
       <c r="V37" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.008</v>
       </c>
       <c r="W37" s="1" t="n">
-        <v>0.101</v>
+        <v>0.085</v>
       </c>
       <c r="X37" s="1" t="n">
-        <v>0.615</v>
+        <v>0.605</v>
       </c>
       <c r="Y37" s="1" t="n">
-        <v>0.842</v>
+        <v>0.798</v>
       </c>
       <c r="Z37" s="1" t="n">
-        <v>2.489</v>
+        <v>2.467</v>
       </c>
       <c r="AA37" s="1" t="n">
-        <v>-0.048</v>
+        <v>-0.054</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>287</v>
@@ -5326,37 +5326,37 @@
         <v>288</v>
       </c>
       <c r="AE37" t="n">
-        <v>96.65</v>
+        <v>95.52</v>
       </c>
       <c r="AF37" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="AG37" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.023</v>
       </c>
       <c r="AH37" s="1" t="n">
-        <v>0.04</v>
+        <v>0.055</v>
       </c>
       <c r="AI37" s="1" t="n">
-        <v>0.219</v>
+        <v>0.207</v>
       </c>
       <c r="AJ37" s="1" t="n">
-        <v>0.444</v>
+        <v>0.41</v>
       </c>
       <c r="AK37" s="1" t="n">
-        <v>0.756</v>
+        <v>0.731</v>
       </c>
       <c r="AL37" s="1" t="n">
-        <v>1.747</v>
+        <v>1.714</v>
       </c>
       <c r="AM37" s="1" t="n">
-        <v>1.989</v>
+        <v>1.952</v>
       </c>
       <c r="AN37" s="1" t="n">
-        <v>2.971</v>
+        <v>2.924</v>
       </c>
       <c r="AO37" s="1" t="n">
-        <v>0.191</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
@@ -5367,37 +5367,37 @@
         <v>79</v>
       </c>
       <c r="C38" t="n">
-        <v>134.37</v>
+        <v>125.74</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.064</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>-0.098</v>
+        <v>-0.164</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.117</v>
+        <v>0.046</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>0.495</v>
+        <v>0.363</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>0.88</v>
+        <v>0.746</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>1.518</v>
+        <v>1.294</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>1.382</v>
+        <v>1.229</v>
       </c>
       <c r="K38" s="1" t="n">
-        <v>0.704</v>
+        <v>0.569</v>
       </c>
       <c r="L38" s="1" t="n">
-        <v>2.263</v>
+        <v>2.053</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0.382</v>
+        <v>0.293</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>180</v>
@@ -5406,37 +5406,37 @@
         <v>181</v>
       </c>
       <c r="Q38" t="n">
-        <v>61.83</v>
+        <v>60.95</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.014</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.051</v>
       </c>
       <c r="T38" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.078</v>
       </c>
       <c r="U38" s="1" t="n">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="V38" s="1" t="n">
-        <v>0.016</v>
+        <v>0.009</v>
       </c>
       <c r="W38" s="1" t="n">
-        <v>0.164</v>
+        <v>0.147</v>
       </c>
       <c r="X38" s="1" t="n">
-        <v>0.406</v>
+        <v>0.386</v>
       </c>
       <c r="Y38" s="1" t="n">
-        <v>0.391</v>
+        <v>0.339</v>
       </c>
       <c r="Z38" s="1" t="n">
-        <v>1.549</v>
+        <v>1.512</v>
       </c>
       <c r="AA38" s="1" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="AC38" s="6" t="s">
         <v>289</v>
@@ -5445,37 +5445,37 @@
         <v>290</v>
       </c>
       <c r="AE38" t="n">
-        <v>75.34</v>
+        <v>74.27</v>
       </c>
       <c r="AF38" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.014</v>
       </c>
       <c r="AG38" s="1" t="n">
-        <v>-0.059</v>
+        <v>-0.077</v>
       </c>
       <c r="AH38" s="1" t="n">
-        <v>-0.048</v>
+        <v>0.114</v>
       </c>
       <c r="AI38" s="1" t="n">
-        <v>0.456</v>
+        <v>0.403</v>
       </c>
       <c r="AJ38" s="1" t="n">
-        <v>1.04</v>
+        <v>0.996</v>
       </c>
       <c r="AK38" s="1" t="n">
-        <v>1.598</v>
+        <v>1.495</v>
       </c>
       <c r="AL38" s="1" t="n">
-        <v>2.854</v>
+        <v>2.799</v>
       </c>
       <c r="AM38" s="1" t="n">
-        <v>2.198</v>
+        <v>2.179</v>
       </c>
       <c r="AN38" s="1" t="n">
-        <v>4.104</v>
+        <v>4.032</v>
       </c>
       <c r="AO38" s="1" t="n">
-        <v>0.17</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
@@ -5486,37 +5486,37 @@
         <v>81</v>
       </c>
       <c r="C39" t="n">
-        <v>27.97</v>
+        <v>27.27</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.025</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>-0.084</v>
+        <v>-0.105</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>-0.011</v>
+        <v>0.004</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>0.266</v>
+        <v>0.219</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.718</v>
+        <v>0.631</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>0.753</v>
+        <v>0.709</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.501</v>
+        <v>0.442</v>
       </c>
       <c r="L39" s="1" t="n">
-        <v>0.986</v>
+        <v>0.936</v>
       </c>
       <c r="M39" s="1" t="n">
-        <v>0.046</v>
+        <v>0.019</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>182</v>
@@ -5525,37 +5525,37 @@
         <v>183</v>
       </c>
       <c r="Q39" t="n">
-        <v>67.5</v>
+        <v>66.6</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.013</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.054</v>
       </c>
       <c r="T39" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.079</v>
       </c>
       <c r="U39" s="1" t="n">
-        <v>0.047</v>
+        <v>0.035</v>
       </c>
       <c r="V39" s="1" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="W39" s="1" t="n">
-        <v>0.173</v>
+        <v>0.164</v>
       </c>
       <c r="X39" s="1" t="n">
-        <v>0.223</v>
+        <v>0.207</v>
       </c>
       <c r="Y39" s="1" t="n">
-        <v>0.178</v>
+        <v>0.133</v>
       </c>
       <c r="Z39" s="1" t="n">
-        <v>1.253</v>
+        <v>1.223</v>
       </c>
       <c r="AA39" s="1" t="n">
-        <v>0.042</v>
+        <v>0.028</v>
       </c>
       <c r="AC39" s="6" t="s">
         <v>291</v>
@@ -5564,37 +5564,37 @@
         <v>292</v>
       </c>
       <c r="AE39" t="n">
-        <v>195.25</v>
+        <v>191.91</v>
       </c>
       <c r="AF39" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="AG39" s="1" t="n">
-        <v>-0.058</v>
+        <v>-0.073</v>
       </c>
       <c r="AH39" s="1" t="n">
-        <v>-0.031</v>
+        <v>0.056</v>
       </c>
       <c r="AI39" s="1" t="n">
-        <v>0.3</v>
+        <v>0.282</v>
       </c>
       <c r="AJ39" s="1" t="n">
-        <v>0.558</v>
+        <v>0.526</v>
       </c>
       <c r="AK39" s="1" t="n">
-        <v>1.225</v>
+        <v>1.169</v>
       </c>
       <c r="AL39" s="1" t="n">
-        <v>1.161</v>
+        <v>1.124</v>
       </c>
       <c r="AM39" s="1" t="n">
-        <v>0.849</v>
+        <v>0.81</v>
       </c>
       <c r="AN39" s="1" t="n">
-        <v>1.066</v>
+        <v>1.031</v>
       </c>
       <c r="AO39" s="1" t="n">
-        <v>0.047</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
@@ -5605,37 +5605,37 @@
         <v>83</v>
       </c>
       <c r="C40" t="n">
-        <v>74.34</v>
+        <v>71.42</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.039</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>-0.074</v>
+        <v>-0.116</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>0.169</v>
+        <v>0.11</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>0.386</v>
+        <v>0.301</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0.76</v>
+        <v>0.643</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>1.07</v>
+        <v>0.989</v>
       </c>
       <c r="K40" s="1" t="n">
-        <v>0.955</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="1" t="n">
-        <v>1.45</v>
+        <v>1.354</v>
       </c>
       <c r="M40" s="1" t="n">
-        <v>0.081</v>
+        <v>0.038</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>184</v>
@@ -5644,37 +5644,37 @@
         <v>185</v>
       </c>
       <c r="Q40" t="n">
-        <v>136.12</v>
+        <v>135.14</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="T40" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="U40" s="1" t="n">
         <v>0.03</v>
       </c>
       <c r="V40" s="1" t="n">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="W40" s="1" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="X40" s="1" t="n">
-        <v>0.527</v>
+        <v>0.516</v>
       </c>
       <c r="Y40" s="1" t="n">
-        <v>1.078</v>
+        <v>1.008</v>
       </c>
       <c r="Z40" s="1" t="n">
-        <v>2.388</v>
+        <v>2.364</v>
       </c>
       <c r="AA40" s="1" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="AC40" s="6" t="s">
         <v>293</v>
@@ -5683,37 +5683,37 @@
         <v>294</v>
       </c>
       <c r="AE40" t="n">
-        <v>35.97</v>
+        <v>35.58</v>
       </c>
       <c r="AF40" s="1" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="AG40" s="1" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="AH40" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="AG40" s="1" t="n">
-        <v>-0.022</v>
-      </c>
-      <c r="AH40" s="1" t="n">
-        <v>-0.009</v>
-      </c>
       <c r="AI40" s="1" t="n">
-        <v>0.095</v>
+        <v>0.067</v>
       </c>
       <c r="AJ40" s="1" t="n">
-        <v>0.281</v>
+        <v>0.273</v>
       </c>
       <c r="AK40" s="1" t="n">
-        <v>0.263</v>
+        <v>0.183</v>
       </c>
       <c r="AL40" s="1" t="n">
-        <v>0.447</v>
+        <v>0.432</v>
       </c>
       <c r="AM40" s="1" t="n">
-        <v>0.475</v>
+        <v>0.413</v>
       </c>
       <c r="AN40" s="1" t="n">
-        <v>1.4</v>
+        <v>1.374</v>
       </c>
       <c r="AO40" s="1" t="n">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
@@ -5724,37 +5724,37 @@
         <v>85</v>
       </c>
       <c r="C41" t="n">
-        <v>29.35</v>
+        <v>28.61</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.025</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>-0.027</v>
+        <v>-0.051</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.135</v>
+        <v>0.105</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>0.11</v>
+        <v>0.081</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.267</v>
+        <v>0.21</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.391</v>
+        <v>0.356</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.442</v>
+        <v>0.397</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>1.327</v>
+        <v>1.269</v>
       </c>
       <c r="M41" s="1" t="n">
-        <v>0.121</v>
+        <v>0.092</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>186</v>
@@ -5763,37 +5763,37 @@
         <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>173.29</v>
+        <v>170.5</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.016</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0</v>
+        <v>-0.035</v>
       </c>
       <c r="T41" s="1" t="n">
-        <v>-0.026</v>
+        <v>-0.02</v>
       </c>
       <c r="U41" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.043</v>
       </c>
       <c r="V41" s="1" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="W41" s="1" t="n">
-        <v>0.209</v>
+        <v>0.172</v>
       </c>
       <c r="X41" s="1" t="n">
-        <v>0.768</v>
+        <v>0.739</v>
       </c>
       <c r="Y41" s="1" t="n">
-        <v>1.048</v>
+        <v>0.994</v>
       </c>
       <c r="Z41" s="1" t="n">
-        <v>4.469</v>
+        <v>4.381</v>
       </c>
       <c r="AA41" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.049</v>
       </c>
       <c r="AC41" s="6" t="s">
         <v>295</v>
@@ -5841,37 +5841,37 @@
         <v>87</v>
       </c>
       <c r="C42" t="n">
-        <v>71.42</v>
+        <v>69.88</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.022</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.064</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>0.086</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>0.157</v>
+        <v>0.125</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>0.324</v>
+        <v>0.265</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>0.608</v>
+        <v>0.573</v>
       </c>
       <c r="K42" s="1" t="n">
-        <v>0.515</v>
+        <v>0.469</v>
       </c>
       <c r="L42" s="1" t="n">
-        <v>1.429</v>
+        <v>1.376</v>
       </c>
       <c r="M42" s="1" t="n">
-        <v>0.064</v>
+        <v>0.041</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>188</v>
@@ -5880,35 +5880,35 @@
         <v>189</v>
       </c>
       <c r="Q42" t="n">
-        <v>25.3</v>
+        <v>25.46</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0.044</v>
+        <v>0.031</v>
       </c>
       <c r="T42" s="1" t="n">
-        <v>0.027</v>
+        <v>0.076</v>
       </c>
       <c r="U42" s="1" t="n">
-        <v>-0.171</v>
+        <v>-0.159</v>
       </c>
       <c r="V42" s="1" t="n">
-        <v>-0.239</v>
+        <v>-0.237</v>
       </c>
       <c r="W42" s="1" t="n">
-        <v>-0.137</v>
+        <v>-0.146</v>
       </c>
       <c r="X42" s="1" t="n">
-        <v>0.2</v>
+        <v>0.207</v>
       </c>
       <c r="Y42" s="1" t="n">
-        <v>-0.391</v>
+        <v>-0.389</v>
       </c>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.135</v>
       </c>
       <c r="AC42" s="6" t="s">
         <v>297</v>
@@ -5956,37 +5956,37 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>101.38</v>
+        <v>99.16</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.022</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.061</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>0.077</v>
+        <v>0.054</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>0.273</v>
+        <v>0.216</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>0.575</v>
+        <v>0.541</v>
       </c>
       <c r="K43" s="1" t="n">
-        <v>0.597</v>
+        <v>0.552</v>
       </c>
       <c r="L43" s="1" t="n">
-        <v>1.426</v>
+        <v>1.373</v>
       </c>
       <c r="M43" s="1" t="n">
-        <v>0.056</v>
+        <v>0.033</v>
       </c>
       <c r="O43" s="7" t="s">
         <v>190</v>
@@ -5995,37 +5995,37 @@
         <v>191</v>
       </c>
       <c r="Q43" t="n">
-        <v>191.44</v>
+        <v>191.71</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>0.013</v>
+        <v>0.001</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.008</v>
       </c>
       <c r="T43" s="1" t="n">
-        <v>0.006</v>
+        <v>0.027</v>
       </c>
       <c r="U43" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.055</v>
       </c>
       <c r="V43" s="1" t="n">
-        <v>0.047</v>
+        <v>0.049</v>
       </c>
       <c r="W43" s="1" t="n">
-        <v>0.278</v>
+        <v>0.261</v>
       </c>
       <c r="X43" s="1" t="n">
-        <v>1.254</v>
+        <v>1.257</v>
       </c>
       <c r="Y43" s="1" t="n">
-        <v>1.326</v>
+        <v>1.289</v>
       </c>
       <c r="Z43" s="1" t="n">
-        <v>6.887</v>
+        <v>6.898</v>
       </c>
       <c r="AA43" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.04</v>
       </c>
       <c r="AC43" s="6" t="s">
         <v>299</v>
@@ -6034,37 +6034,37 @@
         <v>300</v>
       </c>
       <c r="AE43" t="n">
-        <v>52.77</v>
+        <v>50.06</v>
       </c>
       <c r="AF43" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.051</v>
       </c>
       <c r="AG43" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.088</v>
       </c>
       <c r="AH43" s="1" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="AI43" s="1" t="n">
-        <v>0.124</v>
+        <v>0.095</v>
       </c>
       <c r="AJ43" s="1" t="n">
-        <v>0.369</v>
+        <v>0.288</v>
       </c>
       <c r="AK43" s="1" t="n">
-        <v>1.299</v>
+        <v>1.126</v>
       </c>
       <c r="AL43" s="1" t="n">
-        <v>1.782</v>
+        <v>1.639</v>
       </c>
       <c r="AM43" s="1" t="n">
-        <v>2.635</v>
+        <v>2.414</v>
       </c>
       <c r="AN43" s="1" t="n">
-        <v>4.498</v>
+        <v>4.215</v>
       </c>
       <c r="AO43" s="1" t="n">
-        <v>0.235</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
@@ -6075,37 +6075,37 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>43.76</v>
+        <v>42.95</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.019</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.048</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>0.155</v>
+        <v>0.138</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>0.239</v>
+        <v>0.201</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.642</v>
+        <v>0.612</v>
       </c>
       <c r="K44" s="1" t="n">
-        <v>0.975</v>
+        <v>0.918</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>2.095</v>
+        <v>2.038</v>
       </c>
       <c r="M44" s="1" t="n">
-        <v>0.058</v>
+        <v>0.038</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>192</v>
@@ -6114,37 +6114,37 @@
         <v>193</v>
       </c>
       <c r="Q44" t="n">
-        <v>85.65</v>
+        <v>87.62</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="T44" s="1" t="n">
-        <v>0.022</v>
+        <v>0.1</v>
       </c>
       <c r="U44" s="1" t="n">
-        <v>-0.207</v>
+        <v>-0.2</v>
       </c>
       <c r="V44" s="1" t="n">
-        <v>-0.198</v>
+        <v>-0.19</v>
       </c>
       <c r="W44" s="1" t="n">
-        <v>-0.103</v>
+        <v>-0.098</v>
       </c>
       <c r="X44" s="1" t="n">
-        <v>0.484</v>
+        <v>0.518</v>
       </c>
       <c r="Y44" s="1" t="n">
-        <v>0.282</v>
+        <v>0.302</v>
       </c>
       <c r="Z44" s="1" t="n">
-        <v>3.533</v>
+        <v>3.637</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>-0.19</v>
+        <v>-0.171</v>
       </c>
       <c r="AC44" s="6" t="s">
         <v>301</v>
@@ -6153,37 +6153,37 @@
         <v>302</v>
       </c>
       <c r="AE44" t="n">
-        <v>91.56</v>
+        <v>96.31</v>
       </c>
       <c r="AF44" s="1" t="n">
-        <v>0.015</v>
+        <v>0.052</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0.148</v>
+        <v>0.207</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0.176</v>
+        <v>0.256</v>
       </c>
       <c r="AI44" s="1" t="n">
-        <v>0.283</v>
+        <v>0.339</v>
       </c>
       <c r="AJ44" s="1" t="n">
-        <v>0.234</v>
+        <v>0.326</v>
       </c>
       <c r="AK44" s="1" t="n">
-        <v>0.249</v>
+        <v>0.349</v>
       </c>
       <c r="AL44" s="1" t="n">
-        <v>0.311</v>
+        <v>0.379</v>
       </c>
       <c r="AM44" s="1" t="n">
-        <v>1.126</v>
+        <v>1.167</v>
       </c>
       <c r="AN44" s="1" t="n">
-        <v>0.186</v>
+        <v>0.248</v>
       </c>
       <c r="AO44" s="1" t="n">
-        <v>0.324</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
@@ -6194,37 +6194,37 @@
         <v>93</v>
       </c>
       <c r="C45" t="n">
-        <v>59.05</v>
+        <v>57.63</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>0.011</v>
+        <v>-0.024</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.081</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.015</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>0.102</v>
+        <v>0.068</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>0.202</v>
+        <v>0.159</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>0.4</v>
+        <v>0.327</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>0.608</v>
+        <v>0.569</v>
       </c>
       <c r="K45" s="1" t="n">
-        <v>0.246</v>
+        <v>0.203</v>
       </c>
       <c r="L45" s="1" t="n">
-        <v>1.246</v>
+        <v>1.192</v>
       </c>
       <c r="M45" s="1" t="n">
-        <v>0.079</v>
+        <v>0.053</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>194</v>
@@ -6233,37 +6233,37 @@
         <v>195</v>
       </c>
       <c r="Q45" t="n">
-        <v>75.9</v>
+        <v>77.46</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>0.009</v>
+        <v>0.021</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="T45" s="1" t="n">
-        <v>0.019</v>
+        <v>0.063</v>
       </c>
       <c r="U45" s="1" t="n">
-        <v>-0.099</v>
+        <v>-0.08</v>
       </c>
       <c r="V45" s="1" t="n">
-        <v>-0.089</v>
+        <v>-0.087</v>
       </c>
       <c r="W45" s="1" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="X45" s="1" t="n">
-        <v>0.614</v>
+        <v>0.647</v>
       </c>
       <c r="Y45" s="1" t="n">
-        <v>0.414</v>
+        <v>0.435</v>
       </c>
       <c r="Z45" s="1" t="n">
-        <v>2.416</v>
+        <v>2.486</v>
       </c>
       <c r="AA45" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.036</v>
       </c>
       <c r="AC45" s="6" t="s">
         <v>303</v>
@@ -6272,37 +6272,37 @@
         <v>304</v>
       </c>
       <c r="AE45" t="n">
-        <v>38.9</v>
+        <v>40.24</v>
       </c>
       <c r="AF45" s="1" t="n">
-        <v>0.008</v>
+        <v>0.034</v>
       </c>
       <c r="AG45" s="1" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="AH45" s="1" t="n">
-        <v>0.204</v>
+        <v>0.264</v>
       </c>
       <c r="AI45" s="1" t="n">
-        <v>0.332</v>
+        <v>0.367</v>
       </c>
       <c r="AJ45" s="1" t="n">
-        <v>0.294</v>
+        <v>0.362</v>
       </c>
       <c r="AK45" s="1" t="n">
-        <v>0.326</v>
+        <v>0.405</v>
       </c>
       <c r="AL45" s="1" t="n">
-        <v>0.366</v>
+        <v>0.413</v>
       </c>
       <c r="AM45" s="1" t="n">
-        <v>1.302</v>
+        <v>1.299</v>
       </c>
       <c r="AN45" s="1" t="n">
-        <v>2.22</v>
+        <v>2.331</v>
       </c>
       <c r="AO45" s="1" t="n">
-        <v>0.374</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
@@ -6313,29 +6313,29 @@
         <v>95</v>
       </c>
       <c r="C46" t="n">
-        <v>32.95</v>
+        <v>32.44</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.038</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>0.081</v>
+        <v>0.07</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>0.134</v>
+        <v>0.109</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1" t="n">
-        <v>0.083</v>
+        <v>0.066</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>196</v>
@@ -6344,37 +6344,37 @@
         <v>197</v>
       </c>
       <c r="Q46" t="n">
-        <v>341.54</v>
+        <v>337.76</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>0.02</v>
+        <v>-0.011</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.053</v>
       </c>
       <c r="T46" s="1" t="n">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
       <c r="U46" s="1" t="n">
-        <v>0.117</v>
+        <v>0.093</v>
       </c>
       <c r="V46" s="1" t="n">
-        <v>0.404</v>
+        <v>0.372</v>
       </c>
       <c r="W46" s="1" t="n">
-        <v>0.7</v>
+        <v>0.646</v>
       </c>
       <c r="X46" s="1" t="n">
-        <v>1.498</v>
+        <v>1.47</v>
       </c>
       <c r="Y46" s="1" t="n">
-        <v>1.774</v>
+        <v>1.664</v>
       </c>
       <c r="Z46" s="1" t="n">
-        <v>11.859</v>
+        <v>11.717</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>0.134</v>
+        <v>0.122</v>
       </c>
       <c r="AC46" s="6" t="s">
         <v>305</v>
@@ -6383,37 +6383,37 @@
         <v>306</v>
       </c>
       <c r="AE46" t="n">
-        <v>11.78</v>
+        <v>12.05</v>
       </c>
       <c r="AF46" s="1" t="n">
-        <v>-0.041</v>
+        <v>0.023</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>0.016</v>
+        <v>0.059</v>
       </c>
       <c r="AH46" s="1" t="n">
-        <v>-0.125</v>
+        <v>-0.109</v>
       </c>
       <c r="AI46" s="1" t="n">
-        <v>-0.248</v>
+        <v>-0.264</v>
       </c>
       <c r="AJ46" s="1" t="n">
-        <v>-0.101</v>
+        <v>-0.069</v>
       </c>
       <c r="AK46" s="1" t="n">
         <v>-0.49</v>
       </c>
       <c r="AL46" s="1" t="n">
-        <v>-0.702</v>
+        <v>-0.695</v>
       </c>
       <c r="AM46" s="1" t="n">
-        <v>-0.713</v>
+        <v>-0.701</v>
       </c>
       <c r="AN46" s="1" t="n">
-        <v>-0.876</v>
+        <v>-0.873</v>
       </c>
       <c r="AO46" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
@@ -6424,37 +6424,37 @@
         <v>97</v>
       </c>
       <c r="C47" t="n">
-        <v>48.07</v>
+        <v>47.11</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.02</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.049</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.009</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>0.125</v>
+        <v>0.096</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>0.224</v>
+        <v>0.18</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>0.494</v>
+        <v>0.465</v>
       </c>
       <c r="K47" s="1" t="n">
-        <v>0.549</v>
+        <v>0.513</v>
       </c>
       <c r="L47" s="1" t="n">
-        <v>1.475</v>
+        <v>1.425</v>
       </c>
       <c r="M47" s="1" t="n">
-        <v>0.058</v>
+        <v>0.037</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>198</v>
@@ -6463,37 +6463,37 @@
         <v>199</v>
       </c>
       <c r="Q47" t="n">
-        <v>124.91</v>
+        <v>125.17</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.002</v>
       </c>
       <c r="T47" s="1" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="U47" s="1" t="n">
-        <v>-0.052</v>
+        <v>-0.057</v>
       </c>
       <c r="V47" s="1" t="n">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="W47" s="1" t="n">
-        <v>0.288</v>
+        <v>0.269</v>
       </c>
       <c r="X47" s="1" t="n">
-        <v>1.382</v>
+        <v>1.387</v>
       </c>
       <c r="Y47" s="1" t="n">
-        <v>1.212</v>
+        <v>1.177</v>
       </c>
       <c r="Z47" s="1" t="n">
-        <v>6.421</v>
+        <v>6.436</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>-0.033</v>
+        <v>-0.031</v>
       </c>
       <c r="AC47" s="6" t="s">
         <v>307</v>
@@ -6543,37 +6543,37 @@
         <v>99</v>
       </c>
       <c r="C48" t="n">
-        <v>42.75</v>
+        <v>41.99</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.018</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-0.046</v>
+        <v>-0.062</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.007</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>0.11</v>
+        <v>0.093</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>0.209</v>
+        <v>0.184</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>0.507</v>
+        <v>0.455</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>0.804</v>
+        <v>0.772</v>
       </c>
       <c r="K48" s="1" t="n">
-        <v>0.876</v>
+        <v>0.819</v>
       </c>
       <c r="L48" s="1" t="n">
-        <v>1.672</v>
+        <v>1.625</v>
       </c>
       <c r="M48" s="1" t="n">
-        <v>0.084</v>
+        <v>0.064</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>200</v>
@@ -6582,35 +6582,35 @@
         <v>201</v>
       </c>
       <c r="Q48" t="n">
-        <v>49.38</v>
+        <v>48.78</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>0.026</v>
+        <v>-0.012</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>-0.058</v>
       </c>
       <c r="T48" s="1" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="U48" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.015</v>
       </c>
       <c r="V48" s="1" t="n">
-        <v>0.161</v>
+        <v>0.142</v>
       </c>
       <c r="W48" s="1" t="n">
-        <v>0.424</v>
+        <v>0.383</v>
       </c>
       <c r="X48" s="1" t="n">
-        <v>0.632</v>
+        <v>0.612</v>
       </c>
       <c r="Y48" s="1" t="n">
-        <v>0.191</v>
+        <v>0.169</v>
       </c>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1" t="n">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="AC48" s="6" t="s">
         <v>309</v>
@@ -6619,37 +6619,37 @@
         <v>310</v>
       </c>
       <c r="AE48" t="n">
-        <v>26.12</v>
+        <v>26.41</v>
       </c>
       <c r="AF48" s="1" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="AG48" s="1" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AH48" s="1" t="n">
-        <v>0.016</v>
+        <v>0.025</v>
       </c>
       <c r="AI48" s="1" t="n">
-        <v>0.023</v>
+        <v>0.032</v>
       </c>
       <c r="AJ48" s="1" t="n">
-        <v>-0.007</v>
+        <v>0.007</v>
       </c>
       <c r="AK48" s="1" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="AL48" s="1" t="n">
-        <v>0.45</v>
+        <v>0.466</v>
       </c>
       <c r="AM48" s="1" t="n">
-        <v>0.729</v>
+        <v>0.74</v>
       </c>
       <c r="AN48" s="1" t="n">
-        <v>0.492</v>
+        <v>0.509</v>
       </c>
       <c r="AO48" s="1" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
@@ -6660,37 +6660,37 @@
         <v>101</v>
       </c>
       <c r="C49" t="n">
-        <v>50.83</v>
+        <v>49.38</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.029</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>-0.042</v>
+        <v>-0.069</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>0.082</v>
+        <v>0.052</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>0.133</v>
+        <v>0.099</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>0.328</v>
+        <v>0.261</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="K49" s="1" t="n">
-        <v>0.67</v>
+        <v>0.616</v>
       </c>
       <c r="L49" s="1" t="n">
-        <v>1.74</v>
+        <v>1.661</v>
       </c>
       <c r="M49" s="1" t="n">
-        <v>0.06</v>
+        <v>0.029</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>202</v>
@@ -6699,31 +6699,31 @@
         <v>203</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.25</v>
+        <v>33.77</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>0.023</v>
+        <v>-0.014</v>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.051</v>
+        <v>-0.042</v>
       </c>
       <c r="T49" s="1" t="n">
-        <v>0.049</v>
+        <v>0.04</v>
       </c>
       <c r="U49" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.02</v>
       </c>
       <c r="V49" s="1" t="n">
-        <v>0.099</v>
+        <v>0.066</v>
       </c>
       <c r="W49" s="1" t="n">
-        <v>0.415</v>
+        <v>0.365</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1" t="n">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="AC49" s="6" t="s">
         <v>311</v>
@@ -6732,37 +6732,37 @@
         <v>312</v>
       </c>
       <c r="AE49" t="n">
-        <v>17.79</v>
+        <v>18.19</v>
       </c>
       <c r="AF49" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.022</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="AI49" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.019</v>
       </c>
       <c r="AJ49" s="1" t="n">
-        <v>0.009</v>
+        <v>0.038</v>
       </c>
       <c r="AK49" s="1" t="n">
-        <v>-0.039</v>
+        <v>-0.025</v>
       </c>
       <c r="AL49" s="1" t="n">
-        <v>-0.299</v>
+        <v>-0.283</v>
       </c>
       <c r="AM49" s="1" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="AN49" s="1" t="n">
-        <v>-0.144</v>
+        <v>-0.125</v>
       </c>
       <c r="AO49" s="1" t="n">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
@@ -6788,37 +6788,37 @@
         <v>205</v>
       </c>
       <c r="Q50" t="n">
-        <v>40.54</v>
+        <v>39.8</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.018</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.097</v>
+        <v>0.075</v>
       </c>
       <c r="U50" s="1" t="n">
-        <v>0.236</v>
+        <v>0.203</v>
       </c>
       <c r="V50" s="1" t="n">
-        <v>0.286</v>
+        <v>0.261</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0.497</v>
+        <v>0.455</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>0.888</v>
+        <v>0.854</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>0.492</v>
+        <v>0.433</v>
       </c>
       <c r="Z50" s="1" t="n">
-        <v>0.719</v>
+        <v>0.688</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>0.196</v>
+        <v>0.174</v>
       </c>
       <c r="AC50" s="6" t="s">
         <v>313</v>
@@ -6827,37 +6827,37 @@
         <v>314</v>
       </c>
       <c r="AE50" t="n">
-        <v>21.79</v>
+        <v>22.35</v>
       </c>
       <c r="AF50" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.026</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>0.058</v>
+        <v>0.071</v>
       </c>
       <c r="AI50" s="1" t="n">
-        <v>0.044</v>
+        <v>0.08</v>
       </c>
       <c r="AJ50" s="1" t="n">
-        <v>0.045</v>
+        <v>0.072</v>
       </c>
       <c r="AK50" s="1" t="n">
-        <v>-0.073</v>
+        <v>-0.067</v>
       </c>
       <c r="AL50" s="1" t="n">
-        <v>-0.394</v>
+        <v>-0.378</v>
       </c>
       <c r="AM50" s="1" t="n">
-        <v>-0.3</v>
+        <v>-0.289</v>
       </c>
       <c r="AN50" s="1" t="n">
-        <v>-0.505</v>
+        <v>-0.493</v>
       </c>
       <c r="AO50" s="1" t="n">
-        <v>0.091</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
@@ -6883,37 +6883,37 @@
         <v>207</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.68</v>
+        <v>53.73</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="T51" s="1" t="n">
-        <v>-0.034</v>
+        <v>0.042</v>
       </c>
       <c r="U51" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.121</v>
       </c>
       <c r="V51" s="1" t="n">
-        <v>-0.162</v>
+        <v>-0.149</v>
       </c>
       <c r="W51" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="X51" s="1" t="n">
-        <v>0.524</v>
+        <v>0.554</v>
       </c>
       <c r="Y51" s="1" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
       <c r="Z51" s="1" t="n">
-        <v>1.351</v>
+        <v>1.392</v>
       </c>
       <c r="AA51" s="1" t="n">
-        <v>-0.116</v>
+        <v>-0.098</v>
       </c>
       <c r="AC51" s="6" t="s">
         <v>315</v>
@@ -6922,37 +6922,37 @@
         <v>316</v>
       </c>
       <c r="AE51" t="n">
-        <v>23.79</v>
+        <v>24</v>
       </c>
       <c r="AF51" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.009</v>
       </c>
       <c r="AG51" s="1" t="n">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="AH51" s="1" t="n">
-        <v>0.052</v>
+        <v>0.045</v>
       </c>
       <c r="AI51" s="1" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="AJ51" s="1" t="n">
-        <v>0.079</v>
+        <v>0.095</v>
       </c>
       <c r="AK51" s="1" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AL51" s="1" t="n">
-        <v>-0.156</v>
+        <v>-0.148</v>
       </c>
       <c r="AM51" s="1" t="n">
-        <v>0.126</v>
+        <v>0.119</v>
       </c>
       <c r="AN51" s="1" t="n">
-        <v>0.361</v>
+        <v>0.373</v>
       </c>
       <c r="AO51" s="1" t="n">
-        <v>0.088</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
@@ -6963,31 +6963,31 @@
         <v>104</v>
       </c>
       <c r="C52" t="n">
-        <v>41.44</v>
+        <v>40.39</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>0.071</v>
+        <v>-0.025</v>
       </c>
       <c r="E52" s="1" t="n">
         <v>0.056</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.119</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-0.211</v>
+        <v>-0.203</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>-0.335</v>
+        <v>-0.363</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>-0.161</v>
+        <v>-0.215</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1" t="n">
-        <v>-0.165</v>
+        <v>-0.187</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>208</v>
@@ -6996,37 +6996,37 @@
         <v>209</v>
       </c>
       <c r="Q52" t="n">
-        <v>47.77</v>
+        <v>46.97</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>0.009</v>
+        <v>-0.017</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.05</v>
       </c>
       <c r="T52" s="1" t="n">
-        <v>-0.074</v>
+        <v>-0.082</v>
       </c>
       <c r="U52" s="1" t="n">
-        <v>-0.135</v>
+        <v>-0.163</v>
       </c>
       <c r="V52" s="1" t="n">
-        <v>-0.166</v>
+        <v>-0.198</v>
       </c>
       <c r="W52" s="1" t="n">
-        <v>0.049</v>
+        <v>-0.006</v>
       </c>
       <c r="X52" s="1" t="n">
-        <v>0.348</v>
+        <v>0.325</v>
       </c>
       <c r="Y52" s="1" t="n">
-        <v>-0.289</v>
+        <v>-0.305</v>
       </c>
       <c r="Z52" s="1" t="n">
-        <v>1.753</v>
+        <v>1.707</v>
       </c>
       <c r="AA52" s="1" t="n">
-        <v>-0.135</v>
+        <v>-0.149</v>
       </c>
       <c r="AC52" s="6" t="s">
         <v>317</v>
@@ -7074,31 +7074,31 @@
         <v>106</v>
       </c>
       <c r="C53" t="n">
-        <v>16.25</v>
+        <v>15.8</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>0.088</v>
+        <v>-0.028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>-0.006</v>
+        <v>0.124</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-0.316</v>
+        <v>-0.309</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>-0.497</v>
+        <v>-0.518</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>0.003</v>
+        <v>-0.066</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="n">
-        <v>-0.276</v>
+        <v>-0.296</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>210</v>
@@ -7107,35 +7107,35 @@
         <v>211</v>
       </c>
       <c r="Q53" t="n">
-        <v>92.76</v>
+        <v>90.01</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.03</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.048</v>
       </c>
       <c r="T53" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.035</v>
       </c>
       <c r="U53" s="1" t="n">
-        <v>-0.14</v>
+        <v>-0.165</v>
       </c>
       <c r="V53" s="1" t="n">
-        <v>-0.178</v>
+        <v>-0.208</v>
       </c>
       <c r="W53" s="1" t="n">
-        <v>0.037</v>
+        <v>-0.015</v>
       </c>
       <c r="X53" s="1" t="n">
-        <v>0.955</v>
+        <v>0.897</v>
       </c>
       <c r="Y53" s="1" t="n">
-        <v>0.443</v>
+        <v>0.411</v>
       </c>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1" t="n">
-        <v>-0.105</v>
+        <v>-0.131</v>
       </c>
       <c r="AC53" s="6" t="s">
         <v>319</v>
@@ -7144,37 +7144,37 @@
         <v>320</v>
       </c>
       <c r="AE53" t="n">
-        <v>9.2</v>
+        <v>9.23</v>
       </c>
       <c r="AF53" s="1" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="AG53" s="1" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AG53" s="1" t="n">
-        <v>-0.014</v>
-      </c>
       <c r="AH53" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.001</v>
       </c>
       <c r="AI53" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.036</v>
       </c>
       <c r="AJ53" s="1" t="n">
-        <v>-0.13</v>
+        <v>-0.118</v>
       </c>
       <c r="AK53" s="1" t="n">
-        <v>-0.208</v>
+        <v>-0.211</v>
       </c>
       <c r="AL53" s="1" t="n">
-        <v>-0.142</v>
+        <v>-0.139</v>
       </c>
       <c r="AM53" s="1" t="n">
-        <v>0.243</v>
+        <v>0.227</v>
       </c>
       <c r="AN53" s="1" t="n">
-        <v>-0.081</v>
+        <v>-0.078</v>
       </c>
       <c r="AO53" s="1" t="n">
-        <v>-0.057</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
@@ -7185,37 +7185,37 @@
         <v>108</v>
       </c>
       <c r="C54" t="n">
-        <v>60.21</v>
+        <v>59.49</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>0.019</v>
+        <v>-0.012</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.037</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>-0.064</v>
+        <v>-0.051</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-0.077</v>
+        <v>-0.095</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>-0.119</v>
+        <v>-0.129</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>-0.045</v>
+        <v>-0.066</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>0.354</v>
+        <v>0.337</v>
       </c>
       <c r="K54" s="1" t="n">
-        <v>0.139</v>
+        <v>0.125</v>
       </c>
       <c r="L54" s="1" t="n">
-        <v>1.246</v>
+        <v>1.22</v>
       </c>
       <c r="M54" s="1" t="n">
-        <v>-0.102</v>
+        <v>-0.113</v>
       </c>
       <c r="O54" s="7" t="s">
         <v>212</v>
@@ -7224,37 +7224,37 @@
         <v>213</v>
       </c>
       <c r="Q54" t="n">
-        <v>119.69</v>
+        <v>118.88</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="T54" s="1" t="n">
-        <v>0.094</v>
+        <v>0.085</v>
       </c>
       <c r="U54" s="1" t="n">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="V54" s="1" t="n">
-        <v>0.132</v>
+        <v>0.129</v>
       </c>
       <c r="W54" s="1" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="X54" s="1" t="n">
-        <v>0.58</v>
+        <v>0.569</v>
       </c>
       <c r="Y54" s="1" t="n">
-        <v>0.855</v>
+        <v>0.81</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1.67</v>
+        <v>1.652</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>0.105</v>
+        <v>0.097</v>
       </c>
       <c r="AC54" s="6" t="s">
         <v>321</v>
@@ -7304,37 +7304,37 @@
         <v>110</v>
       </c>
       <c r="C55" t="n">
-        <v>39.64</v>
+        <v>39.54</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.026</v>
+        <v>0.033</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>0.11</v>
+        <v>0.103</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>0.186</v>
+        <v>0.187</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="K55" s="1" t="n">
-        <v>0.353</v>
+        <v>0.335</v>
       </c>
       <c r="L55" s="1" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="M55" s="1" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>214</v>
@@ -7343,37 +7343,37 @@
         <v>215</v>
       </c>
       <c r="Q55" t="n">
-        <v>47.27</v>
+        <v>46.9</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="T55" s="1" t="n">
-        <v>0.097</v>
+        <v>0.088</v>
       </c>
       <c r="U55" s="1" t="n">
-        <v>0.09</v>
+        <v>0.091</v>
       </c>
       <c r="V55" s="1" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="W55" s="1" t="n">
-        <v>0.246</v>
+        <v>0.245</v>
       </c>
       <c r="X55" s="1" t="n">
-        <v>0.565</v>
+        <v>0.553</v>
       </c>
       <c r="Y55" s="1" t="n">
-        <v>0.875</v>
+        <v>0.83</v>
       </c>
       <c r="Z55" s="1" t="n">
-        <v>1.76</v>
+        <v>1.738</v>
       </c>
       <c r="AA55" s="1" t="n">
-        <v>0.107</v>
+        <v>0.099</v>
       </c>
       <c r="AC55" s="6" t="s">
         <v>323</v>
@@ -7421,35 +7421,35 @@
         <v>112</v>
       </c>
       <c r="C56" t="n">
-        <v>29.47</v>
+        <v>31.37</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>-0.033</v>
+        <v>0.064</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.076</v>
+        <v>0.132</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.066</v>
+        <v>0.069</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-0.052</v>
+        <v>0.021</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>-0.167</v>
+        <v>-0.116</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>-0.417</v>
+        <v>-0.353</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>-0.831</v>
+        <v>-0.82</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>-0.972</v>
+        <v>-0.968</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="n">
-        <v>0.113</v>
+        <v>0.185</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>216</v>
@@ -7458,37 +7458,37 @@
         <v>217</v>
       </c>
       <c r="Q56" t="n">
-        <v>72.09</v>
+        <v>70.54</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.022</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.041</v>
       </c>
       <c r="T56" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.031</v>
       </c>
       <c r="U56" s="1" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="V56" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.038</v>
       </c>
       <c r="W56" s="1" t="n">
-        <v>0.104</v>
+        <v>0.066</v>
       </c>
       <c r="X56" s="1" t="n">
-        <v>0.363</v>
+        <v>0.334</v>
       </c>
       <c r="Y56" s="1" t="n">
-        <v>0.577</v>
+        <v>0.517</v>
       </c>
       <c r="Z56" s="1" t="n">
-        <v>2.546</v>
+        <v>2.47</v>
       </c>
       <c r="AA56" s="1" t="n">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="AC56" s="6" t="s">
         <v>325</v>
@@ -7546,37 +7546,37 @@
         <v>219</v>
       </c>
       <c r="Q57" t="n">
-        <v>101.06</v>
+        <v>100.18</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.009</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.009</v>
       </c>
       <c r="T57" s="1" t="n">
-        <v>0.049</v>
+        <v>0.042</v>
       </c>
       <c r="U57" s="1" t="n">
-        <v>0.068</v>
+        <v>0.059</v>
       </c>
       <c r="V57" s="1" t="n">
-        <v>0.061</v>
+        <v>0.041</v>
       </c>
       <c r="W57" s="1" t="n">
-        <v>0.059</v>
+        <v>0.037</v>
       </c>
       <c r="X57" s="1" t="n">
-        <v>0.239</v>
+        <v>0.228</v>
       </c>
       <c r="Y57" s="1" t="n">
-        <v>0.35</v>
+        <v>0.321</v>
       </c>
       <c r="Z57" s="1" t="n">
-        <v>0.842</v>
+        <v>0.826</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>0.076</v>
+        <v>0.067</v>
       </c>
       <c r="AC57"/>
       <c r="AD57"/>
@@ -7610,37 +7610,37 @@
         <v>221</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.58</v>
+        <v>88.93</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="T58" s="1" t="n">
-        <v>0.061</v>
+        <v>0.051</v>
       </c>
       <c r="U58" s="1" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="V58" s="1" t="n">
-        <v>0.081</v>
+        <v>0.062</v>
       </c>
       <c r="W58" s="1" t="n">
-        <v>0.057</v>
+        <v>0.04</v>
       </c>
       <c r="X58" s="1" t="n">
-        <v>0.314</v>
+        <v>0.305</v>
       </c>
       <c r="Y58" s="1" t="n">
-        <v>0.455</v>
+        <v>0.428</v>
       </c>
       <c r="Z58" s="1" t="n">
-        <v>0.975</v>
+        <v>0.96</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>0.084</v>
+        <v>0.076</v>
       </c>
       <c r="AC58"/>
       <c r="AD58" s="9" t="s">
@@ -7678,37 +7678,37 @@
         <v>223</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.54</v>
+        <v>94.58</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>0.001</v>
+        <v>-0.01</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="T59" s="1" t="n">
-        <v>0.05</v>
+        <v>0.041</v>
       </c>
       <c r="U59" s="1" t="n">
-        <v>0.071</v>
+        <v>0.062</v>
       </c>
       <c r="V59" s="1" t="n">
-        <v>0.064</v>
+        <v>0.042</v>
       </c>
       <c r="W59" s="1" t="n">
-        <v>0.065</v>
+        <v>0.043</v>
       </c>
       <c r="X59" s="1" t="n">
-        <v>0.24</v>
+        <v>0.227</v>
       </c>
       <c r="Y59" s="1" t="n">
-        <v>0.339</v>
+        <v>0.311</v>
       </c>
       <c r="Z59" s="1" t="n">
-        <v>0.779</v>
+        <v>0.762</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0.08</v>
+        <v>0.069</v>
       </c>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -7744,37 +7744,37 @@
         <v>225</v>
       </c>
       <c r="Q60" t="n">
-        <v>22.6</v>
+        <v>22.52</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0.008</v>
+        <v>-0.009</v>
       </c>
       <c r="T60" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.01</v>
       </c>
       <c r="U60" s="1" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="V60" s="1" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="W60" s="1" t="n">
-        <v>0.077</v>
+        <v>0.062</v>
       </c>
       <c r="X60" s="1" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="Y60" s="1" t="n">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="Z60" s="1" t="n">
-        <v>0.494</v>
+        <v>0.489</v>
       </c>
       <c r="AA60" s="1" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -7810,37 +7810,37 @@
         <v>227</v>
       </c>
       <c r="Q61" t="n">
-        <v>98.15</v>
+        <v>96.75</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.014</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="T61" s="1" t="n">
-        <v>0.135</v>
+        <v>0.144</v>
       </c>
       <c r="U61" s="1" t="n">
-        <v>0.128</v>
+        <v>0.115</v>
       </c>
       <c r="V61" s="1" t="n">
-        <v>0.19</v>
+        <v>0.165</v>
       </c>
       <c r="W61" s="1" t="n">
-        <v>0.289</v>
+        <v>0.258</v>
       </c>
       <c r="X61" s="1" t="n">
-        <v>0.478</v>
+        <v>0.457</v>
       </c>
       <c r="Y61" s="1" t="n">
-        <v>0.609</v>
+        <v>0.573</v>
       </c>
       <c r="Z61" s="1" t="n">
-        <v>1.964</v>
+        <v>1.922</v>
       </c>
       <c r="AA61" s="1" t="n">
-        <v>0.155</v>
+        <v>0.138</v>
       </c>
       <c r="AC61"/>
       <c r="AD61"/>

--- a/etf_returns.xlsx
+++ b/etf_returns.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">Last Observation From Closing Prices</t>
   </si>
   <si>
-    <t xml:space="preserve">03/05/2026 at 4:00 PM ET</t>
+    <t xml:space="preserve">03/06/2026 at 4:00 PM ET</t>
   </si>
   <si>
     <t xml:space="preserve">Ticker</t>
@@ -1666,37 +1666,37 @@
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>334.51</v>
+        <v>330.86</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.012</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.031</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.039</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>0.187</v>
+        <v>0.196</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>0.907</v>
+        <v>0.881</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>1.035</v>
+        <v>1.012</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>3.387</v>
+        <v>3.339</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.035</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>114</v>
@@ -1705,37 +1705,37 @@
         <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.68</v>
+        <v>59.75</v>
       </c>
       <c r="R5" s="1" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0.026</v>
+        <v>0.012</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>0.081</v>
+        <v>0.062</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="V5" s="1" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="W5" s="1" t="n">
         <v>0.358</v>
       </c>
       <c r="X5" s="1" t="n">
-        <v>0.404</v>
+        <v>0.407</v>
       </c>
       <c r="Y5" s="1" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="Z5" s="1" t="n">
         <v>1.471</v>
       </c>
-      <c r="Z5" s="1" t="n">
-        <v>1.469</v>
-      </c>
       <c r="AA5" s="1" t="n">
-        <v>0.256</v>
+        <v>0.257</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>229</v>
@@ -1744,13 +1744,13 @@
         <v>230</v>
       </c>
       <c r="AE5" t="n">
-        <v>82.69</v>
+        <v>82.73</v>
       </c>
       <c r="AF5" s="1" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="AH5" s="1" t="n">
         <v>0.001</v>
@@ -1759,22 +1759,22 @@
         <v>0.005</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AK5" s="1" t="n">
         <v>0.039</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>0.139</v>
+        <v>0.14</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>0.086</v>
+        <v>0.087</v>
       </c>
       <c r="AN5" s="1" t="n">
         <v>0.179</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
@@ -1785,37 +1785,37 @@
         <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>684.46</v>
+        <v>675.4</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.026</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.016</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.059</v>
+        <v>0.045</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.183</v>
+        <v>0.189</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>0.758</v>
+        <v>0.733</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>0.909</v>
+        <v>0.884</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>3.013</v>
+        <v>2.96</v>
       </c>
       <c r="M6" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.014</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>116</v>
@@ -1824,37 +1824,37 @@
         <v>117</v>
       </c>
       <c r="Q6" t="n">
-        <v>113.86</v>
+        <v>114.07</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.072</v>
+        <v>0.052</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>0.135</v>
+        <v>0.107</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>0.269</v>
+        <v>0.272</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.347</v>
+        <v>0.36</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>0.334</v>
+        <v>0.352</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.502</v>
+        <v>1.507</v>
       </c>
       <c r="Z6" s="1" t="n">
-        <v>1.871</v>
+        <v>1.876</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>0.276</v>
+        <v>0.278</v>
       </c>
       <c r="AC6" s="6" t="s">
         <v>231</v>
@@ -1863,16 +1863,16 @@
         <v>232</v>
       </c>
       <c r="AE6" t="n">
-        <v>119.4</v>
+        <v>119.41</v>
       </c>
       <c r="AF6" s="1" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>0.006</v>
@@ -1884,7 +1884,7 @@
         <v>0.052</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AM6" s="1" t="n">
         <v>0.024</v>
@@ -1904,37 +1904,37 @@
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>69.86</v>
+        <v>68.22</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.023</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.046</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.049</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.055</v>
+        <v>0.03</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.066</v>
+        <v>0.041</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.175</v>
+        <v>0.165</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>0.38</v>
+        <v>0.364</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>0.497</v>
+        <v>0.462</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>1.904</v>
+        <v>1.836</v>
       </c>
       <c r="M7" s="1" t="n">
-        <v>0.058</v>
+        <v>0.034</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>118</v>
@@ -1943,37 +1943,37 @@
         <v>119</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.55</v>
+        <v>27.12</v>
       </c>
       <c r="R7" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.016</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.064</v>
       </c>
       <c r="T7" s="1" t="n">
-        <v>0.064</v>
+        <v>0.007</v>
       </c>
       <c r="U7" s="1" t="n">
-        <v>0.268</v>
+        <v>0.248</v>
       </c>
       <c r="V7" s="1" t="n">
-        <v>0.466</v>
+        <v>0.443</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>0.511</v>
+        <v>0.497</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>0.251</v>
+        <v>0.237</v>
       </c>
       <c r="Y7" s="1" t="n">
-        <v>0.888</v>
+        <v>0.858</v>
       </c>
       <c r="Z7" s="1" t="n">
-        <v>-0.097</v>
+        <v>-0.111</v>
       </c>
       <c r="AA7" s="1" t="n">
-        <v>0.32</v>
+        <v>0.299</v>
       </c>
       <c r="AC7" s="6" t="s">
         <v>233</v>
@@ -1982,37 +1982,37 @@
         <v>234</v>
       </c>
       <c r="AE7" t="n">
-        <v>96.51</v>
+        <v>96.45</v>
       </c>
       <c r="AF7" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG7" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.013</v>
       </c>
       <c r="AH7" s="1" t="n">
         <v>0.007</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AJ7" s="1" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AK7" s="1" t="n">
         <v>0.057</v>
       </c>
       <c r="AL7" s="1" t="n">
-        <v>0.122</v>
+        <v>0.124</v>
       </c>
       <c r="AM7" s="1" t="n">
-        <v>-0.038</v>
+        <v>-0.039</v>
       </c>
       <c r="AN7" s="1" t="n">
-        <v>0.102</v>
+        <v>0.101</v>
       </c>
       <c r="AO7" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
@@ -2023,37 +2023,37 @@
         <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>256.76</v>
+        <v>250.89</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.023</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>0.004</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0.027</v>
-      </c>
       <c r="H8" s="1" t="n">
-        <v>0.087</v>
+        <v>0.062</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.245</v>
+        <v>0.236</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>0.392</v>
+        <v>0.381</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.254</v>
+        <v>0.225</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>1.713</v>
+        <v>1.651</v>
       </c>
       <c r="M8" s="1" t="n">
-        <v>0.043</v>
+        <v>0.019</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>120</v>
@@ -2062,37 +2062,37 @@
         <v>121</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.79</v>
+        <v>17.43</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>-0.017</v>
+        <v>-0.02</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.047</v>
+        <v>-0.043</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.063</v>
       </c>
       <c r="U8" s="1" t="n">
-        <v>0.063</v>
+        <v>0.041</v>
       </c>
       <c r="V8" s="1" t="n">
-        <v>0.221</v>
+        <v>0.197</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>0.605</v>
+        <v>0.575</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>-0.055</v>
+        <v>-0.082</v>
       </c>
       <c r="Y8" s="1" t="n">
-        <v>-0.17</v>
+        <v>-0.187</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>1.379</v>
+        <v>1.331</v>
       </c>
       <c r="AA8" s="1" t="n">
-        <v>0.083</v>
+        <v>0.061</v>
       </c>
       <c r="AC8" s="6" t="s">
         <v>235</v>
@@ -2101,37 +2101,37 @@
         <v>236</v>
       </c>
       <c r="AE8" t="n">
-        <v>102.84</v>
+        <v>102.56</v>
       </c>
       <c r="AF8" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="AG8" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.02</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ8" s="1" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="AK8" s="1" t="n">
         <v>0.037</v>
       </c>
       <c r="AL8" s="1" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="AM8" s="1" t="n">
-        <v>-0.153</v>
+        <v>-0.155</v>
       </c>
       <c r="AN8" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.038</v>
       </c>
       <c r="AO8" s="1" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
@@ -2157,37 +2157,37 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.03</v>
+        <v>25.78</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.035</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>0.055</v>
+        <v>0.025</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>0.078</v>
+        <v>0.068</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>0.232</v>
+        <v>0.215</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>0.243</v>
+        <v>0.23</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>0.983</v>
+        <v>0.964</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>1.332</v>
+        <v>1.309</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>0.106</v>
+        <v>0.096</v>
       </c>
       <c r="AC9" s="6" t="s">
         <v>237</v>
@@ -2196,37 +2196,37 @@
         <v>238</v>
       </c>
       <c r="AE9" t="n">
-        <v>88.79</v>
+        <v>88.46</v>
       </c>
       <c r="AF9" s="1" t="n">
         <v>-0.004</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.023</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>0.021</v>
+        <v>0.017</v>
       </c>
       <c r="AK9" s="1" t="n">
         <v>0.019</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.017</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>-0.252</v>
+        <v>-0.255</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>-0.096</v>
+        <v>-0.099</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
@@ -2252,37 +2252,37 @@
         <v>125</v>
       </c>
       <c r="Q10" t="n">
-        <v>179.57</v>
+        <v>176.39</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.018</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-0.041</v>
+        <v>-0.065</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>0.039</v>
+        <v>-0.002</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>0.219</v>
+        <v>0.198</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>0.219</v>
+        <v>0.197</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>0.331</v>
+        <v>0.311</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>0.64</v>
+        <v>0.611</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>2.021</v>
+        <v>1.968</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>0.166</v>
+        <v>0.146</v>
       </c>
       <c r="AC10" s="6" t="s">
         <v>239</v>
@@ -2291,37 +2291,37 @@
         <v>240</v>
       </c>
       <c r="AE10" t="n">
-        <v>111.22</v>
+        <v>111.43</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AG10" s="1" t="n">
         <v>-0.004</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>0.123</v>
+        <v>0.132</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
@@ -2332,37 +2332,37 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>220.59</v>
+        <v>217.72</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.035</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.031</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>0.104</v>
+        <v>0.09</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>0.492</v>
+        <v>0.476</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>0.648</v>
+        <v>0.627</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>1.834</v>
+        <v>1.798</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>0.049</v>
+        <v>0.035</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>126</v>
@@ -2371,37 +2371,37 @@
         <v>127</v>
       </c>
       <c r="Q11" t="n">
-        <v>58.79</v>
+        <v>57.37</v>
       </c>
       <c r="R11" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.024</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-0.083</v>
+        <v>-0.108</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>0.024</v>
+        <v>-0.032</v>
       </c>
       <c r="U11" s="1" t="n">
-        <v>0.215</v>
+        <v>0.185</v>
       </c>
       <c r="V11" s="1" t="n">
-        <v>0.428</v>
+        <v>0.394</v>
       </c>
       <c r="W11" s="1" t="n">
-        <v>0.633</v>
+        <v>0.597</v>
       </c>
       <c r="X11" s="1" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="Y11" s="1" t="n">
-        <v>0.736</v>
+        <v>0.694</v>
       </c>
       <c r="Z11" s="1" t="n">
-        <v>3.565</v>
+        <v>3.455</v>
       </c>
       <c r="AA11" s="1" t="n">
-        <v>0.145</v>
+        <v>0.117</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>241</v>
@@ -2410,37 +2410,37 @@
         <v>242</v>
       </c>
       <c r="AE11" t="n">
-        <v>103.26</v>
+        <v>103.5</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AJ11" s="1" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AO11" s="1" t="n">
         <v>0.011</v>
-      </c>
-      <c r="AK11" s="1" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="AL11" s="1" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AM11" s="1" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AN11" s="1" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AO11" s="1" t="n">
-        <v>0.008</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
@@ -2451,37 +2451,37 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>453.02</v>
+        <v>447.06</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.015</v>
+        <v>-0.021</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.053</v>
+        <v>-0.065</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.01</v>
+        <v>-0.003</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>0.968</v>
+        <v>0.939</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>0.987</v>
+        <v>0.96</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>4.117</v>
+        <v>4.05</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>-0.043</v>
+        <v>-0.055</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>128</v>
@@ -2490,34 +2490,34 @@
         <v>129</v>
       </c>
       <c r="Q12" t="n">
-        <v>87.22</v>
+        <v>87.2</v>
       </c>
       <c r="R12" s="1" t="n">
-        <v>-0.042</v>
+        <v>0</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-0.106</v>
+        <v>-0.123</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>0.107</v>
+        <v>0.049</v>
       </c>
       <c r="U12" s="1" t="n">
         <v>0.263</v>
       </c>
       <c r="V12" s="1" t="n">
-        <v>0.54</v>
+        <v>0.539</v>
       </c>
       <c r="W12" s="1" t="n">
-        <v>1.55</v>
+        <v>1.571</v>
       </c>
       <c r="X12" s="1" t="n">
-        <v>3.109</v>
+        <v>3.193</v>
       </c>
       <c r="Y12" s="1" t="n">
-        <v>2.553</v>
+        <v>2.552</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>4.958</v>
+        <v>4.957</v>
       </c>
       <c r="AA12" s="1" t="n">
         <v>0.184</v>
@@ -2529,34 +2529,34 @@
         <v>244</v>
       </c>
       <c r="AE12" t="n">
-        <v>107.62</v>
+        <v>107.55</v>
       </c>
       <c r="AF12" s="1" t="n">
         <v>-0.001</v>
       </c>
       <c r="AG12" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.01</v>
       </c>
       <c r="AH12" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AJ12" s="1" t="n">
         <v>0.036</v>
       </c>
       <c r="AK12" s="1" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="AL12" s="1" t="n">
         <v>0.114</v>
       </c>
       <c r="AM12" s="1" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="AN12" s="1" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="AO12" s="1" t="n">
         <v>0.007</v>
@@ -2570,37 +2570,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>201.68</v>
+        <v>198.66</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.015</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.024</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>0.072</v>
+        <v>0.056</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>0.137</v>
+        <v>0.139</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>0.718</v>
+        <v>0.691</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>0.824</v>
+        <v>0.797</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>2.677</v>
+        <v>2.622</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>130</v>
@@ -2609,37 +2609,37 @@
         <v>131</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.47</v>
+        <v>39.86</v>
       </c>
       <c r="R13" s="1" t="n">
-        <v>-0.054</v>
+        <v>-0.015</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.129</v>
+        <v>-0.161</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>0.077</v>
+        <v>-0.014</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="V13" s="1" t="n">
-        <v>0.765</v>
+        <v>0.739</v>
       </c>
       <c r="W13" s="1" t="n">
-        <v>1.988</v>
+        <v>1.961</v>
       </c>
       <c r="X13" s="1" t="n">
-        <v>3.141</v>
+        <v>3.14</v>
       </c>
       <c r="Y13" s="1" t="n">
-        <v>1.878</v>
+        <v>1.835</v>
       </c>
       <c r="Z13" s="1" t="n">
-        <v>5.112</v>
+        <v>5.02</v>
       </c>
       <c r="AA13" s="1" t="n">
-        <v>0.181</v>
+        <v>0.163</v>
       </c>
       <c r="AC13" s="6" t="s">
         <v>245</v>
@@ -2648,37 +2648,37 @@
         <v>246</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.07</v>
+        <v>23.15</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="AG13" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.009</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>0.023</v>
+        <v>0.027</v>
       </c>
       <c r="AJ13" s="1" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="AK13" s="1" t="n">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="AL13" s="1" t="n">
-        <v>0.107</v>
+        <v>0.116</v>
       </c>
       <c r="AM13" s="1" t="n">
-        <v>0.1</v>
+        <v>0.104</v>
       </c>
       <c r="AN13" s="1" t="n">
-        <v>0.269</v>
+        <v>0.273</v>
       </c>
       <c r="AO13" s="1" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
@@ -2689,37 +2689,37 @@
         <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>96.81</v>
+        <v>96.65</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>0.425</v>
+        <v>0.422</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.575</v>
+        <v>0.573</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1.728</v>
+        <v>1.724</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>132</v>
@@ -2728,31 +2728,31 @@
         <v>133</v>
       </c>
       <c r="Q14" t="n">
-        <v>50.69</v>
+        <v>49.09</v>
       </c>
       <c r="R14" s="1" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>-0.052</v>
       </c>
-      <c r="S14" s="1" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="T14" s="1" t="n">
-        <v>0.013</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>0.226</v>
+        <v>0.187</v>
       </c>
       <c r="V14" s="1" t="n">
-        <v>0.555</v>
+        <v>0.506</v>
       </c>
       <c r="W14" s="1" t="n">
-        <v>0.938</v>
+        <v>0.893</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="n">
-        <v>0.144</v>
+        <v>0.108</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>247</v>
@@ -2761,25 +2761,25 @@
         <v>248</v>
       </c>
       <c r="AE14" t="n">
-        <v>75.19</v>
+        <v>75.17</v>
       </c>
       <c r="AF14" s="1" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="1" t="n">
-        <v>-0.016</v>
+        <v>-0.018</v>
       </c>
       <c r="AH14" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.015</v>
       </c>
       <c r="AI14" s="1" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="AJ14" s="1" t="n">
         <v>0.001</v>
       </c>
       <c r="AK14" s="1" t="n">
-        <v>0.086</v>
+        <v>0.087</v>
       </c>
       <c r="AL14" s="1" t="n">
         <v>0.143</v>
@@ -2802,37 +2802,37 @@
         <v>36</v>
       </c>
       <c r="C15" t="n">
-        <v>247.03</v>
+        <v>241.48</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.022</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>-0.031</v>
+        <v>-0.045</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.012</v>
+        <v>-0.047</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.02</v>
+        <v>-0.042</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.016</v>
+        <v>-0.007</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>0.173</v>
+        <v>0.193</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>0.797</v>
+        <v>0.754</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.683</v>
+        <v>0.645</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>2.928</v>
+        <v>2.839</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>-0.013</v>
+        <v>-0.035</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>134</v>
@@ -2841,31 +2841,31 @@
         <v>135</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.21</v>
+        <v>16.12</v>
       </c>
       <c r="R15" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.005</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-0.121</v>
+        <v>-0.108</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>0.042</v>
+        <v>-0.027</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>0.117</v>
+        <v>0.111</v>
       </c>
       <c r="V15" s="1" t="n">
-        <v>0.558</v>
+        <v>0.55</v>
       </c>
       <c r="W15" s="1" t="n">
-        <v>0.874</v>
+        <v>0.858</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="n">
-        <v>0.037</v>
+        <v>0.032</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>249</v>
@@ -2874,37 +2874,37 @@
         <v>250</v>
       </c>
       <c r="AE15" t="n">
-        <v>96.38</v>
+        <v>95.75</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>-0.005</v>
+        <v>-0.007</v>
       </c>
       <c r="AG15" s="1" t="n">
-        <v>-0.009</v>
+        <v>-0.016</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.006</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="AJ15" s="1" t="n">
-        <v>0.038</v>
+        <v>0.031</v>
       </c>
       <c r="AK15" s="1" t="n">
         <v>0.106</v>
       </c>
       <c r="AL15" s="1" t="n">
-        <v>0.315</v>
+        <v>0.311</v>
       </c>
       <c r="AM15" s="1" t="n">
-        <v>0.127</v>
+        <v>0.12</v>
       </c>
       <c r="AN15" s="1" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AO15" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
@@ -2915,37 +2915,37 @@
         <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>136.52</v>
+        <v>135.99</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.03</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.006</v>
+        <v>-0.008</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>0.128</v>
+        <v>0.124</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>0.484</v>
+        <v>0.475</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>0.751</v>
+        <v>0.744</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>1.574</v>
+        <v>1.564</v>
       </c>
       <c r="M16" s="1" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>136</v>
@@ -2954,37 +2954,37 @@
         <v>137</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.16</v>
+        <v>73.43</v>
       </c>
       <c r="R16" s="1" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.056</v>
+        <v>-0.063</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.057</v>
       </c>
       <c r="U16" s="1" t="n">
-        <v>0.063</v>
+        <v>0.053</v>
       </c>
       <c r="V16" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>-0.037</v>
+        <v>-0.045</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>0.048</v>
+        <v>0.054</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>-0.035</v>
+        <v>-0.045</v>
       </c>
       <c r="Z16" s="1" t="n">
-        <v>1.024</v>
+        <v>1.004</v>
       </c>
       <c r="AA16" s="1" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>251</v>
@@ -2993,37 +2993,37 @@
         <v>252</v>
       </c>
       <c r="AE16" t="n">
-        <v>41.73</v>
+        <v>41.57</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="AG16" s="1" t="n">
-        <v>-0.028</v>
+        <v>-0.032</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>-0.014</v>
+        <v>-0.023</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AJ16" s="1" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AM16" s="1" t="n">
         <v>0.048</v>
       </c>
-      <c r="AK16" s="1" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="AL16" s="1" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="AM16" s="1" t="n">
-        <v>0.052</v>
-      </c>
       <c r="AN16" s="1" t="n">
-        <v>0.232</v>
+        <v>0.228</v>
       </c>
       <c r="AO16" s="1" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
@@ -3034,35 +3034,35 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>148.11</v>
+        <v>146.22</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-0.012</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.007</v>
+        <v>-0.026</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.023</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.053</v>
+        <v>0.04</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>0.175</v>
+        <v>0.183</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>0.718</v>
+        <v>0.697</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>0.796</v>
+        <v>0.773</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.019</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>138</v>
@@ -3071,37 +3071,37 @@
         <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>102.4</v>
+        <v>99.62</v>
       </c>
       <c r="R17" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.027</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.068</v>
+        <v>-0.083</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.067</v>
       </c>
       <c r="U17" s="1" t="n">
-        <v>0.078</v>
+        <v>0.048</v>
       </c>
       <c r="V17" s="1" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="W17" s="1" t="n">
-        <v>0.453</v>
+        <v>0.45</v>
       </c>
       <c r="X17" s="1" t="n">
-        <v>1.242</v>
+        <v>1.21</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>1.247</v>
+        <v>1.186</v>
       </c>
       <c r="Z17" s="1" t="n">
-        <v>3.535</v>
+        <v>3.412</v>
       </c>
       <c r="AA17" s="1" t="n">
-        <v>0.106</v>
+        <v>0.076</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>253</v>
@@ -3110,37 +3110,37 @@
         <v>254</v>
       </c>
       <c r="AE17" t="n">
-        <v>41.88</v>
+        <v>41.83</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="AG17" s="1" t="n">
-        <v>-0.023</v>
+        <v>-0.027</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.013</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ17" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AK17" s="1" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="AL17" s="1" t="n">
         <v>0.11</v>
       </c>
       <c r="AM17" s="1" t="n">
-        <v>-0.184</v>
+        <v>-0.185</v>
       </c>
       <c r="AN17" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.073</v>
       </c>
       <c r="AO17" s="1" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
@@ -3166,37 +3166,37 @@
         <v>141</v>
       </c>
       <c r="Q18" t="n">
-        <v>156.83</v>
+        <v>154.41</v>
       </c>
       <c r="R18" s="1" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-0.025</v>
+        <v>-0.041</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>0.004</v>
+        <v>-0.036</v>
       </c>
       <c r="U18" s="1" t="n">
-        <v>0.073</v>
+        <v>0.057</v>
       </c>
       <c r="V18" s="1" t="n">
-        <v>0.085</v>
+        <v>0.068</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>0.181</v>
+        <v>0.178</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>0.573</v>
+        <v>0.551</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>0.629</v>
+        <v>0.604</v>
       </c>
       <c r="Z18" s="1" t="n">
-        <v>2.409</v>
+        <v>2.356</v>
       </c>
       <c r="AA18" s="1" t="n">
-        <v>0.058</v>
+        <v>0.042</v>
       </c>
       <c r="AC18" t="s">
         <v>25</v>
@@ -3237,31 +3237,31 @@
         <v>143</v>
       </c>
       <c r="Q19" t="n">
-        <v>34.94</v>
+        <v>34.2</v>
       </c>
       <c r="R19" s="1" t="n">
-        <v>-0.024</v>
+        <v>-0.021</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-0.044</v>
+        <v>-0.06</v>
       </c>
       <c r="T19" s="1" t="n">
-        <v>0.021</v>
+        <v>-0.036</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>0.121</v>
+        <v>0.097</v>
       </c>
       <c r="V19" s="1" t="n">
-        <v>0.229</v>
+        <v>0.203</v>
       </c>
       <c r="W19" s="1" t="n">
-        <v>0.473</v>
+        <v>0.456</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="n">
-        <v>0.12</v>
+        <v>0.096</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>255</v>
@@ -3287,37 +3287,37 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>56.91</v>
+        <v>56.35</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>-0.01</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.028</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.051</v>
+        <v>0.024</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>0.168</v>
+        <v>0.156</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>0.419</v>
+        <v>0.418</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>0.737</v>
+        <v>0.729</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>0.904</v>
+        <v>0.886</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>2.104</v>
+        <v>2.074</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>0.055</v>
+        <v>0.045</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>144</v>
@@ -3326,37 +3326,37 @@
         <v>145</v>
       </c>
       <c r="Q20" t="n">
-        <v>78.96</v>
+        <v>76.45</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>-0.032</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.04</v>
+        <v>-0.065</v>
       </c>
       <c r="T20" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.071</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>0.044</v>
+        <v>0.011</v>
       </c>
       <c r="V20" s="1" t="n">
-        <v>0.128</v>
+        <v>0.092</v>
       </c>
       <c r="W20" s="1" t="n">
-        <v>0.166</v>
+        <v>0.138</v>
       </c>
       <c r="X20" s="1" t="n">
-        <v>0.381</v>
+        <v>0.348</v>
       </c>
       <c r="Y20" s="1" t="n">
-        <v>0.391</v>
+        <v>0.346</v>
       </c>
       <c r="Z20" s="1" t="n">
-        <v>1.578</v>
+        <v>1.496</v>
       </c>
       <c r="AA20" s="1" t="n">
-        <v>0.06</v>
+        <v>0.026</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>256</v>
@@ -3365,37 +3365,37 @@
         <v>257</v>
       </c>
       <c r="AE20" t="n">
-        <v>100.24</v>
+        <v>100.12</v>
       </c>
       <c r="AF20" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="AG20" s="1" t="n">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>0.009</v>
+        <v>0.007</v>
       </c>
       <c r="AJ20" s="1" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AK20" s="1" t="n">
         <v>0.054</v>
       </c>
       <c r="AL20" s="1" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="AM20" s="1" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="AN20" s="1" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="AO20" s="1" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
@@ -3406,37 +3406,37 @@
         <v>45</v>
       </c>
       <c r="C21" t="n">
-        <v>34.15</v>
+        <v>33.81</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>-0.029</v>
+        <v>-0.01</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-0.072</v>
+        <v>-0.073</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>-0.03</v>
+        <v>-0.062</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>0.141</v>
+        <v>0.129</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>0.278</v>
+        <v>0.266</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>0.574</v>
+        <v>0.553</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>0.654</v>
+        <v>0.632</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>0.789</v>
+        <v>0.771</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>1.295</v>
+        <v>1.272</v>
       </c>
       <c r="M21" s="1" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>146</v>
@@ -3445,37 +3445,37 @@
         <v>147</v>
       </c>
       <c r="Q21" t="n">
-        <v>240.04</v>
+        <v>242.2</v>
       </c>
       <c r="R21" s="1" t="n">
-        <v>-0.028</v>
+        <v>0.009</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="T21" s="1" t="n">
-        <v>0.061</v>
+        <v>0.035</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>0.186</v>
+        <v>0.197</v>
       </c>
       <c r="V21" s="1" t="n">
-        <v>0.216</v>
+        <v>0.227</v>
       </c>
       <c r="W21" s="1" t="n">
-        <v>0.584</v>
+        <v>0.631</v>
       </c>
       <c r="X21" s="1" t="n">
-        <v>1.091</v>
+        <v>1.114</v>
       </c>
       <c r="Y21" s="1" t="n">
-        <v>1.557</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" s="1" t="n">
-        <v>3.645</v>
+        <v>3.687</v>
       </c>
       <c r="AA21" s="1" t="n">
-        <v>0.118</v>
+        <v>0.128</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>258</v>
@@ -3484,37 +3484,37 @@
         <v>259</v>
       </c>
       <c r="AE21" t="n">
-        <v>50.41</v>
+        <v>50.34</v>
       </c>
       <c r="AF21" s="1" t="n">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AG21" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="AJ21" s="1" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="AK21" s="1" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="AL21" s="1" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="AM21" s="1" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="AN21" s="1" t="n">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="AO21" s="1" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
@@ -3525,37 +3525,37 @@
         <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>75.25</v>
+        <v>73.72</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>-0.034</v>
+        <v>-0.02</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-0.067</v>
+        <v>-0.089</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>-0.021</v>
+        <v>-0.077</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>0.117</v>
+        <v>0.094</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>0.202</v>
+        <v>0.177</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>0.53</v>
+        <v>0.487</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>1.114</v>
+        <v>1.071</v>
       </c>
       <c r="L22" s="1" t="n">
-        <v>0.914</v>
+        <v>0.875</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>0.085</v>
+        <v>0.063</v>
       </c>
       <c r="O22" s="7" t="s">
         <v>148</v>
@@ -3564,37 +3564,37 @@
         <v>149</v>
       </c>
       <c r="Q22" t="n">
-        <v>102.37</v>
+        <v>101.04</v>
       </c>
       <c r="R22" s="1" t="n">
-        <v>-0.003</v>
+        <v>-0.013</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.002</v>
+        <v>-0.021</v>
       </c>
       <c r="T22" s="1" t="n">
-        <v>0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="U22" s="1" t="n">
-        <v>-0.011</v>
+        <v>-0.024</v>
       </c>
       <c r="V22" s="1" t="n">
-        <v>-0.019</v>
+        <v>-0.032</v>
       </c>
       <c r="W22" s="1" t="n">
-        <v>0.089</v>
+        <v>0.104</v>
       </c>
       <c r="X22" s="1" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
       <c r="Y22" s="1" t="n">
-        <v>0.464</v>
+        <v>0.445</v>
       </c>
       <c r="Z22" s="1" t="n">
-        <v>2.122</v>
+        <v>2.082</v>
       </c>
       <c r="AA22" s="1" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="AC22" s="6" t="s">
         <v>260</v>
@@ -3603,37 +3603,37 @@
         <v>261</v>
       </c>
       <c r="AE22" t="n">
-        <v>49.35</v>
+        <v>49.39</v>
       </c>
       <c r="AF22" s="1" t="n">
-        <v>-0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG22" s="1" t="n">
-        <v>-0.001</v>
+        <v>-0.007</v>
       </c>
       <c r="AH22" s="1" t="n">
         <v>0.005</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AJ22" s="1" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AK22" s="1" t="n">
         <v>0.06</v>
       </c>
       <c r="AL22" s="1" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="AM22" s="1" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="AN22" s="1" t="n">
-        <v>0.265</v>
+        <v>0.266</v>
       </c>
       <c r="AO22" s="1" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
  